--- a/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.613349700210279e-10</v>
+        <v>5.613349700210207e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.740547859108336e-10</v>
+        <v>5.740547859108369e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.592699107678405e-10</v>
+        <v>5.592699107678349e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.572896410616061e-10</v>
+        <v>5.572896410616019e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.576344934873412e-10</v>
+        <v>5.576344934873343e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.663589763499672e-10</v>
+        <v>5.663589763499617e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.585320443772048e-10</v>
+        <v>5.585320443771974e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.608086191728495e-10</v>
+        <v>5.608086191728502e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.623701150925596e-10</v>
+        <v>5.623701150925656e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.639961089046321e-10</v>
+        <v>5.639961089046272e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.633955050302193e-10</v>
+        <v>5.633955050302213e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.693617128577805e-10</v>
+        <v>5.693617128577818e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.604859909317126e-10</v>
+        <v>5.604859909317103e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>8.165769754938363e-10</v>
+        <v>8.165769754938365e-10</v>
       </c>
       <c r="P2" t="n">
         <v>5.611975159367813e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.570199997710217e-10</v>
+        <v>5.570199997710181e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.578020384773911e-10</v>
+        <v>5.578020384773831e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.617947285646203e-10</v>
+        <v>5.617947285646157e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.600592791692729e-10</v>
+        <v>5.600592791692699e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>8.176549333916993e-10</v>
+        <v>8.176549333916943e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.577640580406407e-10</v>
+        <v>5.57764058040638e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>8.432500406669419e-10</v>
+        <v>8.432500406669495e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.591710041042605e-10</v>
+        <v>5.591710041042644e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.595102587023429e-10</v>
+        <v>5.59510258702335e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.323324811177313e-10</v>
+        <v>8.323324811177276e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.578537261707299e-10</v>
+        <v>5.578537261707359e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.662568946155289e-10</v>
+        <v>5.662568946155281e-10</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.135982813195075e-10</v>
+        <v>5.135982813195138e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.02799577747784e-10</v>
+        <v>5.027995777477841e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.99253058314265e-10</v>
+        <v>4.992530583142647e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.842532666650679e-10</v>
+        <v>4.842532666650701e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.876152145475685e-10</v>
+        <v>4.876152145475701e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.494356637263498e-10</v>
+        <v>5.494356637263537e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.941058691898567e-10</v>
+        <v>4.94105869189867e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.103129530473888e-10</v>
+        <v>5.103129530473956e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.211232285787759e-10</v>
+        <v>5.211232285787818e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.330448286007626e-10</v>
+        <v>5.330448286007604e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.285177053721936e-10</v>
+        <v>5.285177053721915e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.80592363825107e-10</v>
+        <v>5.805923638251042e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.078564080485443e-10</v>
+        <v>5.078564080485425e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>9.306201792197307e-10</v>
+        <v>9.30620179219721e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.12644183359232e-10</v>
+        <v>5.126441833592342e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.831064387997282e-10</v>
+        <v>4.831064387997287e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.888094326821396e-10</v>
+        <v>4.888094326821417e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.169656220646834e-10</v>
+        <v>5.169656220646836e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.049178675572428e-10</v>
+        <v>5.049178675572454e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.658914563692677e-10</v>
+        <v>9.658914563692716e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.881168688202236e-10</v>
+        <v>4.881168688202328e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.754073353409914e-10</v>
+        <v>9.754073353409978e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.985125106458844e-10</v>
+        <v>4.985125106458829e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.008388101053342e-10</v>
+        <v>5.008388101053336e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.518999171575998e-10</v>
+        <v>9.518999171576013e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.890106159209484e-10</v>
+        <v>4.890106159209452e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.499714332655375e-10</v>
+        <v>5.49971433265541e-10</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.699025232441771e-10</v>
+        <v>5.699025232441802e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>5.041405711618768e-10</v>
+        <v>5.041405711618764e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.465767290052439e-10</v>
+        <v>5.465767290052446e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>5.242086717042499e-10</v>
+        <v>5.242086717042492e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.281039384928753e-10</v>
+        <v>5.281039384928749e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>6.266509858866353e-10</v>
+        <v>6.266509858866375e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.382421886876992e-10</v>
+        <v>5.382421886877004e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.639571482807038e-10</v>
+        <v>5.63957148280704e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.815353769526507e-10</v>
+        <v>5.815353769526525e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.999613111188677e-10</v>
+        <v>5.999613111188696e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.931772140660282e-10</v>
+        <v>5.93177214066033e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.770393742927498e-10</v>
+        <v>6.770393742927489e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>5.60312913880715e-10</v>
+        <v>5.603129138807164e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>5.610855848496056e-10</v>
+        <v>5.610855848496021e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.683499161306934e-10</v>
+        <v>5.683499161307004e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.211629492859928e-10</v>
+        <v>5.211629492859923e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>5.299964362299787e-10</v>
+        <v>5.299964362299809e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.750957074934309e-10</v>
+        <v>5.750957074934322e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.554930082268366e-10</v>
+        <v>5.554930082268372e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>6.268085535596521e-10</v>
+        <v>6.268085535596489e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>5.293874616009697e-10</v>
+        <v>5.293874616009701e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.620935803962593e-10</v>
+        <v>5.620935803962575e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.454595327408872e-10</v>
+        <v>5.454595327408874e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.472985214294187e-10</v>
+        <v>5.472985214294114e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.511035367806087e-10</v>
+        <v>5.511035367806104e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.305802725038885e-10</v>
+        <v>5.305802725038917e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.262440678145117e-10</v>
+        <v>6.262440678145128e-10</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.641250920723578e-09</v>
+        <v>2.641250920723609e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.496194853585181e-09</v>
+        <v>1.496194853585184e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.405222558126957e-09</v>
+        <v>2.40522255812696e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.439769197337033e-09</v>
+        <v>1.439769197337011e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>2.05355352555458e-09</v>
+        <v>2.053553525554585e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.772630656148311e-09</v>
+        <v>3.772630656148395e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.308110512036565e-09</v>
+        <v>2.308110512036573e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.801619461444509e-09</v>
+        <v>2.80161946144451e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.958116631022871e-09</v>
+        <v>2.958116631022841e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>3.516325620212432e-09</v>
+        <v>3.516325620212423e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.236717802681892e-09</v>
+        <v>3.236717802681846e-09</v>
       </c>
       <c r="M5" t="n">
         <v>5.249119737029969e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.827930855888252e-09</v>
+        <v>3.827930855888186e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>2.452257906244133e-09</v>
+        <v>2.452257906244126e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.625983869387371e-09</v>
+        <v>2.625983869387314e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.840610426477359e-09</v>
+        <v>1.840610426477336e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>2.090737879940866e-09</v>
+        <v>2.090737879940875e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.796957096856794e-09</v>
+        <v>2.796957096856844e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>2.603230381408567e-09</v>
+        <v>2.603230381408487e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>3.896419543628681e-09</v>
+        <v>3.896419543628639e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.831402864690695e-09</v>
+        <v>1.831402864690696e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.632306757683508e-09</v>
+        <v>2.632306757683515e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.362132859807863e-09</v>
+        <v>2.362132859807822e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.382851976302461e-09</v>
+        <v>2.382851976302405e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.323047480373704e-09</v>
+        <v>2.323047480373702e-09</v>
       </c>
       <c r="AA5" t="n">
         <v>2.002814078555703e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.274945763657392e-09</v>
+        <v>4.274945763657348e-09</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.634582215695181e-10</v>
+        <v>1.051029512923992e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.852675608416876e-10</v>
+        <v>9.852675608416878e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.401324273305822e-10</v>
+        <v>6.401324273305838e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>1.005335661384062e-09</v>
+        <v>6.177643700295878e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.216596368182144e-10</v>
+        <v>1.009230928172687e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.202066842119739e-10</v>
+        <v>1.107777975566449e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.019369178367512e-09</v>
+        <v>1.019369178367513e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.045084137960518e-09</v>
+        <v>6.575128466060424e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>6.750910752779855e-10</v>
+        <v>1.062662366632465e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>6.93517009444206e-10</v>
+        <v>6.935170094442086e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>1.074304203745841e-09</v>
+        <v>6.867329123913716e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>7.705950726180918e-10</v>
+        <v>7.705950726180884e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>6.540769678348259e-10</v>
+        <v>6.540769678348261e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>1.040635531789041e-09</v>
+        <v>1.040635531789049e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.047899689516206e-09</v>
+        <v>1.047899689516202e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.14718647611332e-10</v>
+        <v>6.147186476113313e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>1.01112342590979e-09</v>
+        <v>6.235521345553191e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>1.056222697173243e-09</v>
+        <v>1.056222697173244e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>6.490487065521775e-10</v>
+        <v>6.490487065521755e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>7.223572999465124e-10</v>
+        <v>7.223572999465105e-10</v>
       </c>
       <c r="V6" t="n">
         <v>1.010514451280781e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>6.670016703805342e-10</v>
+        <v>1.041643425384156e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.026586522420697e-09</v>
+        <v>1.026586522420701e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.524511034572725e-10</v>
+        <v>6.524511034572702e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.446592351059473e-10</v>
+        <v>6.446592351059496e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.011707262183701e-09</v>
+        <v>6.241359708292297e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.204534038871059e-10</v>
+        <v>7.204534038871049e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.506774193080486e-09</v>
+        <v>1.506774193080484e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.441012240998172e-09</v>
+        <v>1.441012240998181e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.483448398841541e-09</v>
+        <v>1.483448398841548e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.461080341540545e-09</v>
+        <v>1.461080341540554e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.464975608329173e-09</v>
+        <v>1.464975608329179e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.563522655722937e-09</v>
+        <v>1.563522655722942e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.475113858523994e-09</v>
+        <v>1.475113858524004e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.500828818116999e-09</v>
+        <v>1.500828818117007e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.518407046788961e-09</v>
+        <v>1.518407046788956e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.536832980955167e-09</v>
+        <v>1.536832980955173e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.530048883902333e-09</v>
+        <v>1.530048883902336e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.613911044129047e-09</v>
+        <v>1.613911044129054e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.497184583717011e-09</v>
+        <v>1.497184583717021e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.497922212292812e-09</v>
+        <v>1.497922212292818e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.505186543573916e-09</v>
+        <v>1.505186543573918e-09</v>
       </c>
       <c r="Q7" t="n">
         <v>1.458034619122297e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.466868106066283e-09</v>
+        <v>1.466868106066285e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.511967377329732e-09</v>
+        <v>1.511967377329733e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.492364678063138e-09</v>
+        <v>1.49236467806314e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.565633185546719e-09</v>
+        <v>1.56563318554672e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.466259131437278e-09</v>
+        <v>1.466259131437273e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.498965250232555e-09</v>
+        <v>1.49896525023256e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.482331202577186e-09</v>
+        <v>1.482331202577191e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.486163239327242e-09</v>
+        <v>1.48616323932724e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.487975206616912e-09</v>
+        <v>1.487975206616914e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.467451942340194e-09</v>
+        <v>1.467451942340195e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.563115737650808e-09</v>
+        <v>1.563115737650816e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.484503189640826e-09</v>
+        <v>1.484503189640827e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>2.083927294757936e-09</v>
+        <v>2.083927294757946e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.126363452601314e-09</v>
+        <v>2.126363452601315e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>2.103995395300309e-09</v>
+        <v>1.749803441583705e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.54633281841902e-09</v>
+        <v>1.546332818419017e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.206437709482691e-09</v>
+        <v>2.344368371733991e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>2.11802891228376e-09</v>
+        <v>2.11802891228377e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.143743871876778e-09</v>
+        <v>2.143743871876774e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.161322100548715e-09</v>
+        <v>2.161322100548721e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.179748034714945e-09</v>
+        <v>2.179748034714939e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.172963937662091e-09</v>
+        <v>2.172963937662101e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.256826097888813e-09</v>
+        <v>2.25682609788882e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.624469159968895e-09</v>
+        <v>1.624469159968903e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.766941563351832e-09</v>
+        <v>1.766941563351831e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.739471866267214e-09</v>
+        <v>1.739471866267209e-09</v>
       </c>
       <c r="Q8" t="n">
         <v>1.305039373287087e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>2.109783159826042e-09</v>
+        <v>2.109783159826051e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>2.154882431089481e-09</v>
+        <v>2.154882431089501e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>2.135279731822899e-09</v>
+        <v>2.135279731822908e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.799263790418034e-09</v>
+        <v>1.883915980292011e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>2.109174185197034e-09</v>
+        <v>1.927364494955221e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>2.142011032208467e-09</v>
+        <v>2.142011032208471e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.390301580687875e-09</v>
+        <v>1.390301580687877e-09</v>
       </c>
       <c r="Y8" t="n">
         <v>2.790450962691139e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.13089026037666e-09</v>
+        <v>1.453348030649946e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.110366996099957e-09</v>
+        <v>2.110366996099962e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.90087325019754e-09</v>
+        <v>2.900873250197534e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.282563832459313e-09</v>
+        <v>1.282563832459316e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.450478890638767e-09</v>
+        <v>1.450478890638777e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.49291504848214e-09</v>
+        <v>1.492915048482145e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.470546991181133e-09</v>
+        <v>1.416615469569266e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.474442257969777e-09</v>
+        <v>9.357526687133786e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.572989305363532e-09</v>
+        <v>1.57298953833858e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.484580508164596e-09</v>
+        <v>1.4845805081646e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.510295467757607e-09</v>
+        <v>1.510295467757604e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.527873696429544e-09</v>
+        <v>1.527873696429552e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.546299630595771e-09</v>
+        <v>1.54629963059577e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.539515533542936e-09</v>
+        <v>1.539515533542933e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.623377693769641e-09</v>
+        <v>1.623377693769648e-09</v>
       </c>
       <c r="N9" t="n">
         <v>1.506651233357616e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.584864469736064e-09</v>
+        <v>1.584864469736071e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.608970744669288e-09</v>
+        <v>1.60897074466929e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46750150173794e-09</v>
+        <v>1.467501501737935e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.476334755706875e-09</v>
+        <v>1.476334755706881e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.521434026970335e-09</v>
+        <v>1.521434026970331e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.501831327703738e-09</v>
+        <v>1.501831327703737e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.575139921098066e-09</v>
+        <v>1.575139921098072e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.475725781077863e-09</v>
+        <v>1.745384070114394e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.50843189987316e-09</v>
+        <v>1.508431899873158e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.491797852217779e-09</v>
+        <v>1.491797852217786e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.495629888967833e-09</v>
+        <v>1.495629888967835e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.497441856257505e-09</v>
+        <v>1.356555490952001e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.476918591980788e-09</v>
+        <v>1.47691859198079e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57258238729141e-09</v>
+        <v>1.572582387291413e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.078716162412109e-10</v>
+        <v>5.078716162412074e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.211687240009703e-10</v>
+        <v>5.211687240009698e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.087928408272605e-10</v>
+        <v>5.087928408272575e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.073098964003221e-10</v>
+        <v>5.07309896400319e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.083297152456419e-10</v>
+        <v>5.083297152456388e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.087553999117722e-10</v>
+        <v>5.087553999117678e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.08150827918647e-10</v>
+        <v>5.081508279186444e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.087914348102673e-10</v>
+        <v>5.087914348102639e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.086909171612417e-10</v>
+        <v>5.086909171612396e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.087724819173396e-10</v>
+        <v>5.087724819173368e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.085684911292795e-10</v>
+        <v>5.085684911292764e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.06941785658434e-10</v>
+        <v>5.069417856584336e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.076208881650835e-10</v>
+        <v>5.076208881650803e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.952769273603733e-10</v>
+        <v>6.95276927360372e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.073146451140569e-10</v>
+        <v>5.073146451140537e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.080300164234827e-10</v>
+        <v>5.080300164234797e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.093906152785829e-10</v>
+        <v>5.093906152785796e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.083445270468062e-10</v>
+        <v>5.083445270468083e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.076052325828627e-10</v>
+        <v>5.076052325828589e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.911154036877573e-10</v>
+        <v>6.911154036877575e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.085154299076617e-10</v>
+        <v>5.085154299076589e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.212506210322454e-10</v>
+        <v>7.212506210322423e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.115278100490509e-10</v>
+        <v>5.115278100490516e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.119517262246092e-10</v>
+        <v>5.119517262246072e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.517941500394851e-10</v>
+        <v>7.517941500394836e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.08840588517627e-10</v>
+        <v>5.088405885176232e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.094903930024883e-10</v>
+        <v>5.094903930024877e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1534,82 +1534,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.368712525671238e-10</v>
+        <v>4.368712525671232e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.565801080228422e-10</v>
+        <v>4.56580108022842e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.436054979478163e-10</v>
+        <v>4.436054979478165e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.322606287256147e-10</v>
+        <v>4.322606287256136e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.403380762024081e-10</v>
+        <v>4.403380762024074e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.431477936622968e-10</v>
+        <v>4.43147793662295e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.391359248176238e-10</v>
+        <v>4.391359248176233e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.436413825438812e-10</v>
+        <v>4.436413825438804e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.427594944402827e-10</v>
+        <v>4.427594944402794e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.433983729935895e-10</v>
+        <v>4.433983729935891e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.418790371623929e-10</v>
+        <v>4.418790371623942e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.397500419187343e-10</v>
+        <v>4.39750041918734e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.352180140580252e-10</v>
+        <v>4.352180140580245e-10</v>
       </c>
       <c r="O3" t="n">
         <v>7.417865535694298e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.329036191227412e-10</v>
+        <v>4.329036191227424e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.381011453232902e-10</v>
+        <v>4.381011453232921e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.47975021222177e-10</v>
+        <v>4.479750212221775e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.402355905794087e-10</v>
+        <v>4.402355905794111e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.351515505661125e-10</v>
+        <v>4.351515505661112e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.442689838927927e-10</v>
+        <v>7.442689838927915e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.413377665834919e-10</v>
+        <v>4.413377665834952e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.279724619213452e-10</v>
+        <v>8.27972461921345e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.630594545770821e-10</v>
+        <v>4.630594545770781e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.661369410074902e-10</v>
+        <v>4.661369410074901e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.429523474451742e-10</v>
+        <v>8.42952347445177e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.439021826229578e-10</v>
+        <v>4.439021826229592e-10</v>
       </c>
       <c r="AB3" t="n">
         <v>4.495204721693716e-10</v>
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.379633416541583e-10</v>
+        <v>4.379633416541581e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.333978907291334e-10</v>
+        <v>4.33397890729133e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.483689971378381e-10</v>
+        <v>4.483689971378391e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.316184576474336e-10</v>
+        <v>4.316184576474348e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.431377806451646e-10</v>
+        <v>4.431377806451653e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.479460847737114e-10</v>
+        <v>4.479460847737125e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.41117165994525e-10</v>
+        <v>4.411171659945257e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.483531155291028e-10</v>
+        <v>4.483531155291036e-10</v>
       </c>
       <c r="J4" t="n">
         <v>4.471745834399882e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.48139033884726e-10</v>
+        <v>4.481390338847271e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.458348640931858e-10</v>
+        <v>4.45834864093186e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.445981504144776e-10</v>
+        <v>4.445981504144783e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.346551324682035e-09</v>
+        <v>1.346551324682032e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.287681978512156e-10</v>
+        <v>4.287681978512168e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.316720965535806e-10</v>
+        <v>4.316720965535808e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.397525445806089e-10</v>
+        <v>4.397525445806096e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.551211345553594e-10</v>
+        <v>4.551211345553599e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.433050867530798e-10</v>
+        <v>4.433050867530802e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.349544156905684e-10</v>
+        <v>4.349544156905682e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.470861800930292e-10</v>
+        <v>4.470861800930293e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.451680838149961e-10</v>
+        <v>4.451680838149974e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.178210062598677e-10</v>
+        <v>5.178210062598688e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.792617326459716e-10</v>
+        <v>4.79261732645974e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.840264739147829e-10</v>
+        <v>4.840264739147825e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.451794418887832e-10</v>
+        <v>4.451794418887834e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.489083292655487e-10</v>
+        <v>4.489083292655498e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.576797009839463e-10</v>
+        <v>4.57679700983947e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1713,46 +1713,46 @@
         <v>1.326048785975791e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.324304828629231e-09</v>
+        <v>1.324304828629233e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.592705137091307e-09</v>
+        <v>1.592705137091308e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>9.020643847536912e-10</v>
+        <v>9.020643847536926e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.519837987239865e-09</v>
+        <v>1.519837987239866e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.486510374461345e-09</v>
+        <v>1.486510374461353e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.522747406406749e-09</v>
+        <v>1.522747406406748e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.616220815799132e-09</v>
+        <v>1.61622081579913e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.510854308434978e-09</v>
+        <v>1.510854308434974e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.556599964580872e-09</v>
+        <v>1.556599964580876e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.482968980234841e-09</v>
+        <v>1.48296898023484e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.549008100466444e-09</v>
+        <v>1.549008100466445e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.346551324682035e-09</v>
+        <v>1.346551324682032e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.181420520165624e-09</v>
+        <v>1.181420520165625e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.218662998182975e-09</v>
+        <v>1.218662998182974e-09</v>
       </c>
       <c r="Q5" t="n">
         <v>1.40919639028096e-09</v>
@@ -1764,22 +1764,22 @@
         <v>1.414903633795965e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.366884312564389e-09</v>
+        <v>1.366884312564391e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.493882614422467e-09</v>
+        <v>1.493882614422471e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.388053260576827e-09</v>
+        <v>1.38805326057683e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.786184959165745e-09</v>
+        <v>2.786184959165737e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.105070074343398e-09</v>
+        <v>2.105070074343425e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.21669457407532e-09</v>
+        <v>2.216694574075318e-09</v>
       </c>
       <c r="Z5" t="n">
         <v>1.421202701823466e-09</v>
@@ -1788,7 +1788,7 @@
         <v>1.579394049878356e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.839638106942552e-09</v>
+        <v>1.839638106942559e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.469484775096253e-10</v>
+        <v>5.318542626956654e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.423830265846009e-10</v>
+        <v>5.272888117706397e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.573541329933039e-10</v>
+        <v>8.573541329933058e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.406035935029008e-10</v>
+        <v>5.255093786889395e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.521229165006304e-10</v>
+        <v>5.370287016866709e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.418370058152176e-10</v>
+        <v>8.569312206291785e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.350080870360309e-10</v>
+        <v>8.501023018499938e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.422440365706082e-10</v>
+        <v>8.573382513845724e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.410655044814926e-10</v>
+        <v>8.561597192954564e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.571241697401925e-10</v>
+        <v>5.420299549262331e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.397257851346913e-10</v>
+        <v>8.548199999486536e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>5.384890714559827e-10</v>
+        <v>8.535832862699467e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.346551324682035e-09</v>
+        <v>1.346551324682032e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>8.364274390576841e-10</v>
+        <v>8.364274390576855e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.153004438082315e-10</v>
+        <v>8.393411623084799e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.48737680436076e-10</v>
+        <v>8.487376804360755e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.490120555968655e-10</v>
+        <v>8.641062704108271e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.371960077945849e-10</v>
+        <v>8.52290222608546e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.439395515460348e-10</v>
+        <v>5.288453367320744e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>5.410006880797343e-10</v>
+        <v>8.560949028936965e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.390590048565015e-10</v>
+        <v>8.541532196704632e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.213390221065925e-10</v>
+        <v>6.213390221065931e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.731526536874769e-10</v>
+        <v>5.731526536874795e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.859302762461633e-10</v>
+        <v>5.859302762461655e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.54164577744251e-10</v>
+        <v>5.390703629302899e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.427992503070535e-10</v>
+        <v>5.427992503070552e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.517211195922412e-10</v>
+        <v>5.517211195922435e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1892,10 +1892,10 @@
         <v>1.180592805562127e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.195563911970832e-09</v>
+        <v>1.19556391197083e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.178813372480428e-09</v>
+        <v>1.178813372480426e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.190332695478159e-09</v>
@@ -1904,10 +1904,10 @@
         <v>1.195140999606706e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.188312080827521e-09</v>
+        <v>1.18831208082752e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.195548030362097e-09</v>
+        <v>1.195548030362095e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.19436949827298e-09</v>
@@ -1916,31 +1916,31 @@
         <v>1.19533394871772e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.193029778926179e-09</v>
+        <v>1.193029778926178e-09</v>
       </c>
       <c r="M7" t="n">
         <v>1.191793065247472e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.346551324682035e-09</v>
+        <v>1.346551324682032e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.175933332020777e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.178837230723139e-09</v>
+        <v>1.178837230723142e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.186947459413601e-09</v>
+        <v>1.1869474594136e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.202316049388352e-09</v>
+        <v>1.202316049388351e-09</v>
       </c>
       <c r="S7" t="n">
         <v>1.190500001586072e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.182149330523562e-09</v>
+        <v>1.18214933052356e-09</v>
       </c>
       <c r="U7" t="n">
         <v>1.194493112538273e-09</v>
@@ -1949,22 +1949,22 @@
         <v>1.19236299864799e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.265015921092861e-09</v>
+        <v>1.26501592109286e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.226456647478963e-09</v>
+        <v>1.226456647478966e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.231244975692976e-09</v>
+        <v>1.231244975692977e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.192374356721777e-09</v>
+        <v>1.192374356721775e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.196103244098543e-09</v>
+        <v>1.196103244098542e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.204874615816942e-09</v>
+        <v>1.204874615816943e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1974,25 +1974,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.123673548010963e-09</v>
+        <v>1.123673548010965e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.613391924312584e-09</v>
+        <v>1.613391924312587e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.628363030721287e-09</v>
+        <v>1.62836303072129e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.611612491230884e-09</v>
+        <v>1.348420933679882e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.205851630475079e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.627940118357162e-09</v>
+        <v>1.730433089897319e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.621111199577974e-09</v>
+        <v>1.621111199577977e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.628347149112554e-09</v>
@@ -2001,58 +2001,58 @@
         <v>1.627168617023439e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.628133067468177e-09</v>
+        <v>1.628133067468179e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.625828897676636e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.624592183997927e-09</v>
+        <v>1.62459218399794e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.346551324682035e-09</v>
+        <v>1.346551324682032e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.330903250772971e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.307997124912301e-09</v>
+        <v>1.307997124912304e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.028324697391758e-09</v>
+        <v>1.028324697391759e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.635115168138811e-09</v>
+        <v>1.635115168138813e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.62329912033653e-09</v>
+        <v>1.623299120336531e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.614948449274016e-09</v>
+        <v>1.61494844927402e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.323106060085596e-09</v>
+        <v>1.386019570150276e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.625162117398443e-09</v>
+        <v>1.490253416203023e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.697912180847271e-09</v>
+        <v>1.697912180847273e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1131359804215e-09</v>
+        <v>1.113135980421503e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.155788548558795e-09</v>
+        <v>2.155788548558798e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.625173475472233e-09</v>
+        <v>1.121708072383656e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.628902362849e-09</v>
+        <v>1.628902362849001e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.153994523510585e-09</v>
+        <v>2.153994523510589e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.012952901589954e-10</v>
+        <v>9.012952901589948e-10</v>
       </c>
       <c r="C9" t="n">
         <v>1.050368589636992e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.065339696045696e-09</v>
+        <v>1.065339696045697e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.048589156555293e-09</v>
+        <v>1.013130119288714e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.060108479553024e-09</v>
+        <v>7.059289569762487e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.064916783681569e-09</v>
+        <v>1.064916991227765e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.058087864902382e-09</v>
+        <v>1.058087864902383e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.065323814436961e-09</v>
+        <v>1.06532381443696e-09</v>
       </c>
       <c r="J9" t="n">
         <v>1.064145282347847e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.065109732792584e-09</v>
+        <v>1.065109732792585e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.062805563001044e-09</v>
+        <v>1.062805563001042e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.061568849322337e-09</v>
+        <v>1.061568849322335e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.346551324682035e-09</v>
+        <v>1.346551324682032e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.096654853796672e-09</v>
+        <v>1.096654853796674e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.110632054446236e-09</v>
+        <v>1.110632054446234e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.056723451034662e-09</v>
+        <v>1.056723451034664e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.072091833463218e-09</v>
+        <v>1.072091833463216e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.060275785660939e-09</v>
+        <v>1.060275785660937e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.051925114598422e-09</v>
+        <v>1.051925114598425e-09</v>
       </c>
       <c r="U9" t="n">
         <v>1.064080465946085e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.062138782722854e-09</v>
+        <v>1.239434695160338e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.134791705167727e-09</v>
+        <v>1.134791705167726e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.09623243155383e-09</v>
+        <v>1.096232431553831e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.101020759767837e-09</v>
+        <v>1.101020759767841e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.062150140796639e-09</v>
+        <v>9.695197188086763e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.065879028173407e-09</v>
+        <v>1.065879028173406e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.074650399891806e-09</v>
+        <v>1.074650399891803e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.518908559012834e-10</v>
+        <v>5.518908559012838e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.645636364132062e-10</v>
+        <v>5.645636364132056e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.505623164113766e-10</v>
+        <v>5.505623164113771e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.485055264863479e-10</v>
+        <v>5.485055264863463e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.477167690728087e-10</v>
+        <v>5.477167690728097e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.576832580892241e-10</v>
+        <v>5.576832580892256e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.476209946179038e-10</v>
+        <v>5.47620994617904e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.492836535100389e-10</v>
+        <v>5.492836535100393e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.538122565965996e-10</v>
+        <v>5.538122565966009e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.541911368128692e-10</v>
+        <v>5.541911368128637e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.546463795106443e-10</v>
+        <v>5.546463795106444e-10</v>
       </c>
       <c r="M2" t="n">
         <v>5.596981471202452e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.491853287427501e-10</v>
+        <v>5.491853287427502e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.93630448880635e-10</v>
+        <v>7.936304488806329e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.539608544972427e-10</v>
+        <v>5.539608544972435e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.479515406088341e-10</v>
+        <v>5.479515406088422e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.473087609852223e-10</v>
+        <v>5.473087609852225e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.534908669264125e-10</v>
+        <v>5.534908669264119e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.498694590398463e-10</v>
+        <v>5.498694590398468e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.931086396258691e-10</v>
+        <v>7.931086396258697e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.482690653760798e-10</v>
+        <v>5.482690653760801e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>8.19905429075586e-10</v>
+        <v>8.199054290755864e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.514051542713974e-10</v>
+        <v>5.514051542713979e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.508026032090277e-10</v>
+        <v>5.508026032090337e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.167017948132087e-10</v>
+        <v>8.167017948132149e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.496897653516002e-10</v>
+        <v>5.496897653516104e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.575650435156047e-10</v>
+        <v>5.575650435156044e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.001190143392012e-10</v>
+        <v>5.001190143392035e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.944019581438775e-10</v>
+        <v>4.944019581438769e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.910130566466951e-10</v>
+        <v>4.910130566466981e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.75471955144701e-10</v>
+        <v>4.754719551447019e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.706824395887355e-10</v>
+        <v>4.70682439588738e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.413929079946569e-10</v>
+        <v>5.413929079946599e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.700486149948655e-10</v>
+        <v>4.700486149948669e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.818895123245671e-10</v>
+        <v>4.818895123245696e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.139534620202981e-10</v>
+        <v>5.139534620203014e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.167571103319315e-10</v>
+        <v>5.167571103319351e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.199858923360477e-10</v>
+        <v>5.199858923360519e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.654273589961451e-10</v>
+        <v>5.654273589961448e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.810874111918619e-10</v>
+        <v>4.810874111918645e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.935854095870553e-10</v>
+        <v>8.935854095870575e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.148713294028718e-10</v>
+        <v>5.148713294028749e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.722836640369661e-10</v>
+        <v>4.722836640369672e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.677654912871263e-10</v>
+        <v>4.677654912871276e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.115812623444516e-10</v>
+        <v>5.115812623444557e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.860578536044693e-10</v>
+        <v>4.860578536044724e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.223199455413093e-10</v>
+        <v>9.223199455413128e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.742731130878844e-10</v>
+        <v>4.742731130878877e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.488588506909975e-10</v>
+        <v>9.488588506909977e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.969991473567981e-10</v>
+        <v>4.969991473568049e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.92585948688249e-10</v>
+        <v>4.925859486882523e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.289375968806347e-10</v>
+        <v>9.289375968806376e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.846480463302593e-10</v>
+        <v>4.846480463302598e-10</v>
       </c>
       <c r="AB3" t="n">
         <v>5.417961291248978e-10</v>
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.428619885212646e-10</v>
+        <v>5.428619885212648e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.877535204392926e-10</v>
+        <v>4.877535204392915e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.278555238244018e-10</v>
+        <v>5.278555238244003e-10</v>
       </c>
       <c r="E4" t="n">
         <v>5.046231354510976e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.95713757618835e-10</v>
+        <v>4.95713757618834e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>6.082898358707081e-10</v>
+        <v>6.082898358707076e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.946319410922522e-10</v>
+        <v>4.946319410922519e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.134124381397995e-10</v>
+        <v>5.134124381397982e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.644974483586424e-10</v>
+        <v>5.644974483586423e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.688447195991182e-10</v>
+        <v>5.688447195991167e-10</v>
       </c>
       <c r="L4" t="n">
         <v>5.739868952924751e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.474404232289874e-10</v>
+        <v>6.474404232289852e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>5.123018146616419e-10</v>
+        <v>5.123018146616402e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>5.314016636760055e-10</v>
+        <v>5.314016636760052e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.662435749090275e-10</v>
+        <v>5.662435749090265e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.983656101185724e-10</v>
+        <v>4.983656101185718e-10</v>
       </c>
       <c r="R4" t="n">
         <v>4.911051185765465e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.609348490915204e-10</v>
+        <v>5.609348490915199e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.200293810828314e-10</v>
+        <v>5.200293810828295e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.891953921733193e-10</v>
+        <v>5.891953921733206e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>5.017177933365074e-10</v>
+        <v>5.017177933365065e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.554096297829932e-10</v>
+        <v>5.554096297829923e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.373757651779059e-10</v>
+        <v>5.373757651779052e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.286250528546611e-10</v>
+        <v>5.286250528546614e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.255854532970573e-10</v>
+        <v>5.255854532970566e-10</v>
       </c>
       <c r="AA4" t="n">
         <v>5.179996582110234e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.076125370287319e-10</v>
+        <v>6.076125370287299e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.302923853215747e-09</v>
+        <v>2.302923853215742e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.422313081108935e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.228237834167905e-09</v>
+        <v>2.228237834167903e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.30973162433241e-09</v>
+        <v>1.309731624332411e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.608378129743428e-09</v>
+        <v>1.608378129743429e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.502893322716165e-09</v>
+        <v>3.502893322716195e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.615576507225462e-09</v>
+        <v>1.615576507225461e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.956448826005236e-09</v>
+        <v>1.956448826005235e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.78068612466953e-09</v>
+        <v>2.780686124669546e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.917043788100519e-09</v>
+        <v>2.917043788100517e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.002977312663707e-09</v>
+        <v>3.002977312663731e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.659297081705662e-09</v>
+        <v>4.659297081705664e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.199039921804151e-09</v>
+        <v>3.199039921804146e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>2.084779206959665e-09</v>
+        <v>2.084779206959664e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.733136733819866e-09</v>
+        <v>2.733136733819869e-09</v>
       </c>
       <c r="Q5" t="n">
         <v>1.617168233600741e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.518471987771328e-09</v>
+        <v>1.51847198777133e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.668496897764369e-09</v>
+        <v>2.668496897764374e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07456384929293e-09</v>
+        <v>2.074563849292926e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>3.277878120202487e-09</v>
+        <v>3.277878120202481e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.530838547422718e-09</v>
+        <v>1.530838547422693e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.672620417082064e-09</v>
+        <v>2.672620417082058e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.39195866647854e-09</v>
+        <v>2.391958666478544e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.200557067211331e-09</v>
+        <v>2.200557067211336e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.026931603416609e-09</v>
+        <v>2.026931603416606e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.965374256146239e-09</v>
+        <v>1.965374256146243e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.984743149776592e-09</v>
+        <v>3.984743149776586e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.91577277266156e-10</v>
+        <v>6.323907261872738e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>9.364688091841824e-10</v>
+        <v>9.364688091841832e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.173842614904118e-10</v>
+        <v>9.765708125692906e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.941518731171069e-10</v>
+        <v>5.94151873117107e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>9.444290463637266e-10</v>
+        <v>5.852424952848446e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.057005124615599e-09</v>
+        <v>6.978185735367173e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.841606787582628e-10</v>
+        <v>9.433472298371409e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>6.029411758058101e-10</v>
+        <v>6.029411758058099e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.013212737103531e-09</v>
+        <v>1.013212737103532e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>6.583734572651289e-10</v>
+        <v>1.017560008344007e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>6.635156329584852e-10</v>
+        <v>6.635156329584863e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>7.369691608949963e-10</v>
+        <v>7.369691608949957e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>6.019561053301474e-10</v>
+        <v>6.0195610533015e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>9.785974431828128e-10</v>
+        <v>9.785974431828145e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>1.013442559320608e-09</v>
+        <v>1.013442559320611e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.878943477845834e-10</v>
+        <v>9.47080898863461e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.806338562425565e-10</v>
+        <v>9.398204073214338e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>6.5046358675753e-10</v>
+        <v>1.00965013783641e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>9.687446698277221e-10</v>
+        <v>6.095581187488405e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>1.039855301804867e-09</v>
+        <v>6.806687507259851e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>9.504330820813974e-10</v>
+        <v>9.504330820813968e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>1.002601059614683e-09</v>
+        <v>1.002601059614682e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>6.26904502843917e-10</v>
+        <v>9.860910539227946e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.288920351389863e-10</v>
+        <v>6.288920351389888e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.151141909630679e-10</v>
+        <v>9.743007420419475e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.667149469559141e-10</v>
+        <v>6.075283958770339e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.977584576519621e-10</v>
+        <v>6.977584576519612e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2746,16 +2746,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.405438446475501e-09</v>
+        <v>1.405438446475498e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.350329978393526e-09</v>
+        <v>1.350329978393525e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.390431981778635e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.367199593405332e-09</v>
+        <v>1.367199593405331e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.358290215573069e-09</v>
@@ -2767,64 +2767,64 @@
         <v>1.357208399046488e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.375988896094036e-09</v>
+        <v>1.375988896094037e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.427073906312878e-09</v>
+        <v>1.427073906312875e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.431421177553354e-09</v>
+        <v>1.431421177553353e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43656335324671e-09</v>
+        <v>1.436563353246711e-09</v>
       </c>
       <c r="M7" t="n">
         <v>1.510016881183221e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.374878272615876e-09</v>
+        <v>1.374878272615877e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.393945474461118e-09</v>
+        <v>1.393945474461116e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.42878738569414e-09</v>
+        <v>1.428787385694137e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.360942068072807e-09</v>
+        <v>1.360942068072806e-09</v>
       </c>
       <c r="R7" t="n">
         <v>1.353681576530782e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.423511307045755e-09</v>
+        <v>1.423511307045754e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.382605839037066e-09</v>
+        <v>1.382605839037065e-09</v>
       </c>
       <c r="U7" t="n">
         <v>1.453682903380807e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.364294251290742e-09</v>
+        <v>1.364294251290741e-09</v>
       </c>
       <c r="W7" t="n">
         <v>1.417986087737228e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.39995222313214e-09</v>
+        <v>1.399952223132139e-09</v>
       </c>
       <c r="Y7" t="n">
         <v>1.393146131695554e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.388161911251294e-09</v>
+        <v>1.388161911251293e-09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.380576116165258e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.470188994982966e-09</v>
+        <v>1.470188994982965e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2837,82 +2837,82 @@
         <v>1.374110329118881e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.922984233538878e-09</v>
+        <v>1.922984233538879e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.963086236923987e-09</v>
+        <v>1.963086236923986e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.939853848550682e-09</v>
+        <v>1.618251051541622e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.421055492971512e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.043520548970292e-09</v>
+        <v>2.168760228494116e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.929862654191837e-09</v>
+        <v>1.929862654191836e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.948643151239385e-09</v>
+        <v>1.948643151239382e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.999728161458228e-09</v>
+        <v>1.999728161458226e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.004075432698702e-09</v>
+        <v>2.004075432698701e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.009217608392058e-09</v>
+        <v>2.009217608392057e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.082671136328572e-09</v>
+        <v>2.082671136328558e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.479345145044852e-09</v>
+        <v>1.479345145044849e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.627106952078121e-09</v>
+        <v>1.627106952078118e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.630410708487039e-09</v>
+        <v>1.630410708487037e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.210917629272075e-09</v>
+        <v>1.210917629272074e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.926335831676132e-09</v>
+        <v>1.92633583167613e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.996165562191106e-09</v>
+        <v>1.996165562191107e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.955260094182417e-09</v>
+        <v>1.955260094182416e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.654710752475915e-09</v>
+        <v>1.731574278118292e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.936948506436092e-09</v>
+        <v>1.771870230340382e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.990759042811532e-09</v>
+        <v>1.99075904281153e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.305283968955468e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.566325092002798e-09</v>
+        <v>2.566325092002801e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.960816166396642e-09</v>
+        <v>1.345614511233392e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.953230371310608e-09</v>
+        <v>1.953230371310604e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.673753342471195e-09</v>
+        <v>2.673753342471194e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.160616554279217e-09</v>
+        <v>1.160616554279215e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.309350558978156e-09</v>
+        <v>1.309350558978155e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.349452562363265e-09</v>
+        <v>1.349452562363264e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.32622017398996e-09</v>
+        <v>1.279174328963253e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.317310796157698e-09</v>
+        <v>8.473979804257722e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.429886874409571e-09</v>
+        <v>1.429887090519724e-09</v>
       </c>
       <c r="H9" t="n">
         <v>1.316228979631115e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.335009476678662e-09</v>
+        <v>1.335009476678661e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.386094486897506e-09</v>
+        <v>1.386094486897504e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.39044175813798e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.395583933831338e-09</v>
+        <v>1.395583933831339e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.46903746176785e-09</v>
+        <v>1.469037461767849e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.333898853200504e-09</v>
+        <v>1.333898853200503e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.420552118514384e-09</v>
+        <v>1.420552118514379e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.470085691770823e-09</v>
+        <v>1.470085691770822e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.319962864767594e-09</v>
+        <v>1.319962864767587e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31270215711541e-09</v>
+        <v>1.312702157115408e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.382531887630383e-09</v>
+        <v>1.382531887630382e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.341626419621694e-09</v>
+        <v>1.341626419621692e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.412737051598839e-09</v>
+        <v>1.412737051598838e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.323314831875374e-09</v>
+        <v>1.558544705879069e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.377006668321856e-09</v>
+        <v>1.377006668321855e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.358972803716769e-09</v>
+        <v>1.358972803716766e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.352166712280184e-09</v>
+        <v>1.35216671228018e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.347182491835921e-09</v>
+        <v>1.224283692943922e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.339596696749888e-09</v>
+        <v>1.339596696749885e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.429209575567599e-09</v>
+        <v>1.429209575567595e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.431247049506007e-10</v>
+        <v>5.431247049506e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.555674146999584e-10</v>
+        <v>5.555674146999589e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.440661931426305e-10</v>
+        <v>5.440661931426314e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.409679780779849e-10</v>
+        <v>5.409679780779834e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.403830437197263e-10</v>
+        <v>5.403830437197254e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.491946572400478e-10</v>
+        <v>5.491946572400466e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.391308810553537e-10</v>
+        <v>5.391308810553538e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.437307328544871e-10</v>
+        <v>5.437307328544876e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.456775656638399e-10</v>
+        <v>5.456775656638374e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.446260573291296e-10</v>
+        <v>5.44626057329131e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.460403898207965e-10</v>
+        <v>5.460403898207958e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.50368402898989e-10</v>
+        <v>5.503684028989901e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.401558741177534e-10</v>
+        <v>5.401558741177522e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.698680218545908e-10</v>
+        <v>7.69868021854588e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.459873325416875e-10</v>
+        <v>5.459873325416886e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.408289341457169e-10</v>
+        <v>5.408289341457159e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.388654849135707e-10</v>
+        <v>5.388654849135717e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.453797596735253e-10</v>
+        <v>5.453797596735261e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.416968492292824e-10</v>
+        <v>5.416968492292817e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.665685350789612e-10</v>
+        <v>7.665685350789615e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.409134839750782e-10</v>
+        <v>5.409134839750774e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.944537640960659e-10</v>
+        <v>7.944537640960666e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.453288718092512e-10</v>
+        <v>5.453288718092514e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.461477272684304e-10</v>
+        <v>5.461477272684325e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.026335689555868e-10</v>
+        <v>8.026335689555841e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.42923617919125e-10</v>
+        <v>5.429236179191244e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.491223609843559e-10</v>
+        <v>5.491223609843567e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3254,64 +3254,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.873486817139826e-10</v>
+        <v>4.873486817139816e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.859049327862786e-10</v>
+        <v>4.859049327862803e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.943982617797918e-10</v>
+        <v>4.943982617797931e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.714193003648671e-10</v>
+        <v>4.714193003648658e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.68076265314953e-10</v>
+        <v>4.680762653149528e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.305032699201098e-10</v>
+        <v>5.305032699201134e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.591683132121866e-10</v>
+        <v>4.59168313212188e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.920497423286937e-10</v>
+        <v>4.920497423286954e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.056291878251372e-10</v>
+        <v>5.05629187825141e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.981472885679644e-10</v>
+        <v>4.981472885679627e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.082914099742084e-10</v>
+        <v>5.082914099742087e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.48598223444415e-10</v>
+        <v>5.485982234444161e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.663736538788192e-10</v>
+        <v>4.663736538788205e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.557977524431716e-10</v>
+        <v>8.557977524431797e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.076745807415322e-10</v>
+        <v>5.07674580741533e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.711725420080575e-10</v>
+        <v>4.711725420080593e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.57225107186767e-10</v>
+        <v>4.572251071867626e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.034134584278016e-10</v>
+        <v>5.03413458427804e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.774639384950868e-10</v>
+        <v>4.774639384950894e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.698157901246637e-10</v>
+        <v>8.698157901246696e-10</v>
       </c>
       <c r="V3" t="n">
         <v>4.714852389269045e-10</v>
@@ -3320,19 +3320,19 @@
         <v>9.13759721582858e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.033818889950979e-10</v>
+        <v>5.033818889951055e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.091019635231977e-10</v>
+        <v>5.09101963523203e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.129019149664082e-10</v>
+        <v>9.129019149664096e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.861020823658107e-10</v>
+        <v>4.861020823658056e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.313428815444713e-10</v>
+        <v>5.313428815444732e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.176343274774274e-10</v>
+        <v>5.176343274774292e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.722085997753205e-10</v>
+        <v>4.722085997753206e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.282688697123639e-10</v>
+        <v>5.282688697123624e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.93273105307847e-10</v>
+        <v>4.932731053078497e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.866660026482197e-10</v>
+        <v>4.866660026482212e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.861972309027351e-10</v>
+        <v>5.861972309027359e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.725222493308604e-10</v>
+        <v>4.725222493308618e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.244796914384314e-10</v>
+        <v>5.24479691438436e-10</v>
       </c>
       <c r="J4" t="n">
         <v>5.464027384297867e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.345927932491246e-10</v>
+        <v>5.345927932491353e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.505683293675872e-10</v>
+        <v>5.505683293675889e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.159315330633423e-10</v>
+        <v>6.159315330633438e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.841000174907537e-10</v>
+        <v>4.841000174907546e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>5.056871198689294e-10</v>
+        <v>5.056871198689452e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.499690229925108e-10</v>
+        <v>5.499690229925297e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.917025401295115e-10</v>
+        <v>4.917025401295154e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.69524477821165e-10</v>
+        <v>4.695244778211665e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.431062079492876e-10</v>
+        <v>5.431062079492922e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.015060402590521e-10</v>
+        <v>5.015060402590575e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.42946955109974e-10</v>
+        <v>5.429469551099927e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.924255112858379e-10</v>
+        <v>4.924255112858368e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.41026847082078e-10</v>
+        <v>5.410268470820794e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.425314061127171e-10</v>
+        <v>5.425314061127315e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.501011881524666e-10</v>
+        <v>5.50101188152467e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.119631535692611e-10</v>
+        <v>5.119631535692615e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.153629569522996e-10</v>
+        <v>5.153629569522999e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.861681906055995e-10</v>
+        <v>5.861681906056011e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.011213754784447e-09</v>
+        <v>2.011213754784455e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.329327426286875e-09</v>
+        <v>1.329327426286881e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.370385682349775e-09</v>
+        <v>2.370385682349907e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.302206828047455e-09</v>
+        <v>1.302206828047509e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.616341556748009e-09</v>
+        <v>1.616341556748017e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.137337035298916e-09</v>
+        <v>3.137337035298915e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.381108352355938e-09</v>
+        <v>1.381108352355942e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.327038941268715e-09</v>
+        <v>2.327038941268839e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.552564606644187e-09</v>
+        <v>2.552564606644176e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.354361822333169e-09</v>
+        <v>2.354361822333145e-09</v>
       </c>
       <c r="L5" t="n">
         <v>2.662805996493594e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.060179441704423e-09</v>
+        <v>4.060179441704455e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.457004185144742e-09</v>
+        <v>2.457004185144899e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.784695810852542e-09</v>
+        <v>1.784695810852468e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.528787550251783e-09</v>
+        <v>2.528787550251825e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.660819764079204e-09</v>
+        <v>1.660819764079247e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.302663438614999e-09</v>
+        <v>1.302663438615005e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.446354794612724e-09</v>
+        <v>2.44635479461303e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.884501057412863e-09</v>
+        <v>1.884501057412895e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.517530689827775e-09</v>
+        <v>2.517530689827914e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.526810630098516e-09</v>
+        <v>1.526810630098398e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.520476000658149e-09</v>
+        <v>2.520476000658154e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.608042035264483e-09</v>
+        <v>2.608042035264592e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.707300814277108e-09</v>
+        <v>2.707300814277378e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.880290562222472e-09</v>
+        <v>1.880290562222477e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.068761835026642e-09</v>
+        <v>2.068761835026748e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.617573217091561e-09</v>
+        <v>3.617573217091562e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.348530868667121e-10</v>
+        <v>6.029324597212483e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.575067320191386e-10</v>
+        <v>5.575067320191409e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.454876291016492e-10</v>
+        <v>9.454876291016643e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.785712375516649e-10</v>
+        <v>5.785712375516674e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.719641348920383e-10</v>
+        <v>9.038847620375087e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.00341599029202e-09</v>
+        <v>6.714953631465547e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.578203815746794e-10</v>
+        <v>5.578203815746816e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>9.416984508277167e-10</v>
+        <v>6.097778236822639e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.636214978190706e-10</v>
+        <v>9.636214978190733e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>6.19890925492941e-10</v>
+        <v>9.51811552638417e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.677870887568732e-10</v>
+        <v>6.358664616114074e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.033150292452628e-09</v>
+        <v>1.03315029245263e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.694815133037973e-10</v>
+        <v>5.694815133037982e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>9.216028781767237e-10</v>
+        <v>5.910686156819835e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.658892547071114e-10</v>
+        <v>9.658892547071197e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.089212995187966e-10</v>
+        <v>9.089212995188026e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.867432372104504e-10</v>
+        <v>8.86743237210452e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>6.284043401930972e-10</v>
+        <v>6.284043401931056e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.868041725028714e-10</v>
+        <v>5.868041725028771e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.618452815631058e-10</v>
+        <v>6.299246544176485e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>9.096442706751221e-10</v>
+        <v>9.096442706751248e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.569394292842474e-10</v>
+        <v>6.360804349836786e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>6.278295383565378e-10</v>
+        <v>6.278295383565578e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.451930608057646e-10</v>
+        <v>6.451930608057731e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.291819129585468e-10</v>
+        <v>5.972612858130812e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.006610891961179e-10</v>
+        <v>9.325817163415883e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.719864928549882e-10</v>
+        <v>6.719864928549907e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.308874221007653e-09</v>
+        <v>1.308874221007654e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.263448493305546e-09</v>
+        <v>1.263448493305547e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.31950876324259e-09</v>
+        <v>1.319508763242594e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.284512998838073e-09</v>
+        <v>1.284512998838077e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.277905896178444e-09</v>
+        <v>1.277905896178445e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.37743712443296e-09</v>
+        <v>1.377437124432962e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.263762142861086e-09</v>
+        <v>1.263762142861087e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.315719584968659e-09</v>
+        <v>1.315719584968668e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.337642631960009e-09</v>
+        <v>1.337642631960011e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.325832686779346e-09</v>
+        <v>1.325832686779353e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.341808222897812e-09</v>
+        <v>1.341808222897814e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.407171426593569e-09</v>
+        <v>1.407171426593567e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.275339911020979e-09</v>
+        <v>1.275339911020982e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.296896746981658e-09</v>
+        <v>1.296896746981667e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.341178650105221e-09</v>
+        <v>1.341178650105248e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.282942433659736e-09</v>
+        <v>1.282942433659742e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.260764371351389e-09</v>
+        <v>1.260764371351393e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.334346101479508e-09</v>
+        <v>1.334346101479524e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.292745933789277e-09</v>
+        <v>1.292745933789276e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.335909238964509e-09</v>
+        <v>1.335909238964523e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.283665404816066e-09</v>
+        <v>1.283665404816064e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.332266740612303e-09</v>
+        <v>1.332266740612306e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.333771299642946e-09</v>
+        <v>1.333771299642952e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.343020648746538e-09</v>
+        <v>1.343020648746537e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.303203047099486e-09</v>
+        <v>1.303203047099487e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.306602850482525e-09</v>
+        <v>1.306602850482526e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.377408084135826e-09</v>
+        <v>1.377408084135828e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.26701984654222e-09</v>
+        <v>1.267019846542222e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.766172109800911e-09</v>
+        <v>1.766172109800912e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.822232379737955e-09</v>
+        <v>1.82223237973796e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.787236615333439e-09</v>
+        <v>1.497264899177353e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.320890408096534e-09</v>
+        <v>1.320890408096535e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.880160740928324e-09</v>
+        <v>1.993082534955355e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.766485759356451e-09</v>
+        <v>1.766485759356454e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.818443201464029e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.840366248455374e-09</v>
+        <v>1.840366248455377e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.828556303274715e-09</v>
+        <v>1.828556303274721e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.844531839393176e-09</v>
+        <v>1.844531839393179e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.909895043088932e-09</v>
+        <v>1.909895043088928e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.355924478628488e-09</v>
+        <v>1.355924478628491e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.493519057053558e-09</v>
+        <v>1.49351905705357e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.509364724660077e-09</v>
+        <v>1.509364724660098e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.134066054564411e-09</v>
+        <v>1.134066054564413e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.763487987846755e-09</v>
+        <v>1.763487987846758e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.837069717974868e-09</v>
+        <v>1.837069717974885e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.795469550284641e-09</v>
+        <v>1.795469550284648e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.503538278340496e-09</v>
+        <v>1.572845425964789e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.786389021311427e-09</v>
+        <v>1.637610120432345e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.835097382364107e-09</v>
+        <v>1.835097382364114e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.234806575559306e-09</v>
+        <v>1.234806575559314e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.387302665468766e-09</v>
+        <v>2.38730266546878e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.805926663594851e-09</v>
+        <v>1.251232856858966e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.80932646697789e-09</v>
+        <v>1.809326466977901e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.448988949131955e-09</v>
+        <v>2.448988949131957e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.056444348034568e-09</v>
+        <v>1.056444348034571e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.189812202756209e-09</v>
+        <v>1.189812202756214e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.245872472693252e-09</v>
+        <v>1.245872472693262e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.210876708288734e-09</v>
+        <v>1.16961203429781e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.204269605629107e-09</v>
+        <v>7.921013367946182e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.303800833883623e-09</v>
+        <v>1.303801036101378e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.190125852311751e-09</v>
+        <v>1.190125852311756e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.242083294419321e-09</v>
+        <v>1.242083294419335e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.264006341410677e-09</v>
+        <v>1.264006341410681e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.252196396230016e-09</v>
+        <v>1.252196396230025e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.268171932348477e-09</v>
+        <v>1.268171932348479e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.333535136044232e-09</v>
+        <v>1.333535136044236e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.201703620471643e-09</v>
+        <v>1.201703620471644e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.282542951187365e-09</v>
+        <v>1.282542951187368e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.339711153398388e-09</v>
+        <v>1.339711153398391e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.209306345328151e-09</v>
+        <v>1.209306345328156e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.187128080802054e-09</v>
+        <v>1.187128080802056e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.260709810930173e-09</v>
+        <v>1.260709810930194e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.219109643239941e-09</v>
+        <v>1.219109643239951e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.262230125154707e-09</v>
+        <v>1.262230125154723e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.210029114266727e-09</v>
+        <v>1.416353114113886e-09</v>
       </c>
       <c r="W9" t="n">
         <v>1.258630450062966e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.260135009093607e-09</v>
+        <v>1.260135009093616e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.269384358197204e-09</v>
+        <v>1.269384358197213e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.229566756550149e-09</v>
+        <v>1.121770205592758e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.232966559933188e-09</v>
+        <v>1.232966559933195e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.303771793586488e-09</v>
+        <v>1.303771793586494e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.382897200603019e-10</v>
+        <v>5.382897200603002e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.50479745533868e-10</v>
+        <v>5.504797455338666e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.38687058887736e-10</v>
+        <v>5.386870588877357e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.360693218914432e-10</v>
+        <v>5.360693218914438e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.366649474555795e-10</v>
+        <v>5.366649474555799e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.437238992551162e-10</v>
+        <v>5.437238992551152e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.351043288850879e-10</v>
+        <v>5.35104328885087e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.393080534627155e-10</v>
+        <v>5.393080534627149e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.408589516386295e-10</v>
+        <v>5.408589516386287e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.409892731401766e-10</v>
+        <v>5.409892731401751e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.408094317865943e-10</v>
+        <v>5.408094317865944e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.443147983238758e-10</v>
+        <v>5.443147983238751e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.350861823397238e-10</v>
+        <v>5.350861823397227e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.566213745581047e-10</v>
+        <v>7.566213745581007e-10</v>
       </c>
       <c r="P2" t="n">
         <v>5.41057528265251e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.364596412352525e-10</v>
+        <v>5.364596412352522e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.360038318159532e-10</v>
+        <v>5.360038318159533e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.408364780240705e-10</v>
+        <v>5.408364780240702e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.378716923838574e-10</v>
+        <v>5.378716923838576e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.548467004279641e-10</v>
+        <v>7.548467004279654e-10</v>
       </c>
       <c r="V2" t="n">
         <v>5.379672064563502e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.817052271179622e-10</v>
+        <v>7.817052271179655e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.419874057274074e-10</v>
+        <v>5.419874057274067e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.460972466836094e-10</v>
+        <v>5.460972466836081e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.955355467001658e-10</v>
+        <v>7.95535546700166e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.392251102608865e-10</v>
+        <v>5.392251102608868e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.444484100329033e-10</v>
+        <v>5.444484100329025e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.795865304015893e-10</v>
+        <v>4.795865304015907e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.79620409854853e-10</v>
+        <v>4.796204098548527e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.826954491932646e-10</v>
+        <v>4.826954491932638e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.63210514917443e-10</v>
+        <v>4.632105149174416e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.683107786452671e-10</v>
+        <v>4.683107786452675e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.181612242104764e-10</v>
+        <v>5.181612242104751e-10</v>
       </c>
       <c r="H3" t="n">
         <v>4.572114344172996e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.872191496390475e-10</v>
+        <v>4.872191496390459e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.979708417162963e-10</v>
+        <v>4.979708417162961e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.989501764144438e-10</v>
+        <v>4.989501764144436e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.976470222268444e-10</v>
+        <v>4.97647022226844e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.319951402998973e-10</v>
+        <v>5.319951402998969e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.56957903638107e-10</v>
+        <v>4.569579036381048e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.316295649745211e-10</v>
+        <v>8.316295649745199e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.992055315635257e-10</v>
+        <v>4.992055315635244e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.667361952159368e-10</v>
+        <v>4.667361952159363e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.636180953804133e-10</v>
+        <v>4.636180953804121e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.977365786453031e-10</v>
+        <v>4.97736578645301e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.769471774037203e-10</v>
+        <v>4.769471774037201e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.547390119008979e-10</v>
+        <v>8.547390119009007e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.77164064052064e-10</v>
+        <v>4.771640640520635e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.964975342973129e-10</v>
+        <v>8.964975342973132e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.062202236165709e-10</v>
+        <v>5.062202236165707e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.355978801413578e-10</v>
+        <v>5.355978801413559e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.043722065353594e-10</v>
+        <v>9.043722065353583e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.864905885548865e-10</v>
+        <v>4.864905885548851e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.246820091574098e-10</v>
+        <v>5.246820091574092e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4202,82 +4202,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.063406634917036e-10</v>
+        <v>5.063406634917029e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.647526272155442e-10</v>
+        <v>4.647526272155436e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.108287883324762e-10</v>
+        <v>5.108287883324751e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.812602447408412e-10</v>
+        <v>4.812602447408407e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.879881094890554e-10</v>
+        <v>4.879881094890542e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.677222173430822e-10</v>
+        <v>5.677222173430813e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.703602048153303e-10</v>
+        <v>4.703602048153302e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.178432077284899e-10</v>
+        <v>5.178432077284896e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.353056077502044e-10</v>
+        <v>5.353056077502034e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.368333573846612e-10</v>
+        <v>5.368333573846594e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.348019665648564e-10</v>
+        <v>5.348019665648555e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.909950244223746e-10</v>
+        <v>5.909950244223744e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.701552312376266e-10</v>
+        <v>4.701552312376233e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.890437163106728e-10</v>
+        <v>4.890437163106718e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.376043304212958e-10</v>
+        <v>5.376043304212918e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.85669081284926e-10</v>
+        <v>4.856690812849235e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.805205042112496e-10</v>
+        <v>4.805205042112492e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.351074662590295e-10</v>
+        <v>5.351074662590256e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.016188485840474e-10</v>
+        <v>5.016188485840456e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.404265994051425e-10</v>
+        <v>5.404265994051417e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>5.025443575845738e-10</v>
+        <v>5.02544357584573e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.3700051899538e-10</v>
+        <v>5.370005189953789e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.481077241211144e-10</v>
+        <v>5.481077241211122e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.931557573470169e-10</v>
+        <v>5.931557573470141e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.068743506848262e-10</v>
+        <v>5.068743506848264e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.169063261080704e-10</v>
+        <v>5.169063261080683e-10</v>
       </c>
       <c r="AB4" t="n">
         <v>5.767123748377257e-10</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.86369776676167e-09</v>
+        <v>1.863697766761669e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.265127950814446e-09</v>
+        <v>1.265127950814444e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.084600556225557e-09</v>
+        <v>2.084600556225548e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.146008191834473e-09</v>
+        <v>1.14600819183447e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.705106161107408e-09</v>
+        <v>1.705106161107398e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.840860149318151e-09</v>
+        <v>2.840860149318146e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.413470095792294e-09</v>
+        <v>1.413470095792292e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.256147690353181e-09</v>
+        <v>2.256147690353175e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.401576000561148e-09</v>
+        <v>2.401576000561139e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.453176096015847e-09</v>
+        <v>2.453176096015848e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.407081334197319e-09</v>
+        <v>2.407081334197313e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.562601631583625e-09</v>
+        <v>3.562601631583623e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.417158441215584e-09</v>
+        <v>2.417158441215632e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.582670266122104e-09</v>
+        <v>1.582670266122083e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.346695277309022e-09</v>
+        <v>2.346695277309032e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.607446964149374e-09</v>
+        <v>1.607446964149371e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58636420343089e-09</v>
+        <v>1.586364203430897e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.358861858060047e-09</v>
+        <v>2.358861858060013e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.958522046056501e-09</v>
+        <v>1.958522046056502e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.488804320377773e-09</v>
+        <v>2.488804320377774e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.73657848220515e-09</v>
+        <v>1.736578482205145e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.518534743445724e-09</v>
+        <v>2.518534743445709e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.728411189085758e-09</v>
+        <v>2.72841118908571e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.57305838313298e-09</v>
+        <v>3.57305838313302e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.818788482159325e-09</v>
+        <v>1.818788482159327e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.16879240123437e-09</v>
+        <v>2.16879240123434e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.472352808401969e-09</v>
+        <v>3.472352808401964e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.929259486890644e-10</v>
+        <v>9.229946203171893e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.51337912412905e-10</v>
+        <v>5.513379124129064e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.974140735298376e-10</v>
+        <v>5.974140735298357e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.678455299382018e-10</v>
+        <v>8.979142015663272e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.745733946864165e-10</v>
+        <v>5.745733946864169e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>6.543075025404429e-10</v>
+        <v>9.843761741685676e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.870141616408178e-10</v>
+        <v>5.569454900126922e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>6.044284929258516e-10</v>
+        <v>6.044284929258501e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>6.218908929475662e-10</v>
+        <v>9.519595645756902e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>9.534873142101429e-10</v>
+        <v>9.534873142101413e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.213872517622181e-10</v>
+        <v>9.514559233903411e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.775803096197364e-10</v>
+        <v>6.775803096197352e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.569178022068431e-10</v>
+        <v>5.569178022068415e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.758062872798891e-10</v>
+        <v>9.045146819780413e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.530804271984489e-10</v>
+        <v>6.136146154437906e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.023230381104125e-10</v>
+        <v>9.023230381104127e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.971744610367379e-10</v>
+        <v>8.971744610367354e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>9.517614230845161e-10</v>
+        <v>9.517614230845157e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.882041337814079e-10</v>
+        <v>9.182728054095315e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.584550672252718e-10</v>
+        <v>6.283863955971518e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>9.191983144100599e-10</v>
+        <v>5.891296427819326e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.524695992896814e-10</v>
+        <v>9.524695992896785e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>6.346930093184713e-10</v>
+        <v>6.346930093184716e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.893682625054262e-10</v>
+        <v>6.893682625054248e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.235283075103135e-10</v>
+        <v>9.235283075103139e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.33560282933557e-10</v>
+        <v>9.335602829335547e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.638319678656422e-10</v>
+        <v>6.638319678656404e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.291338328399283e-09</v>
+        <v>1.291338328399279e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.249750292123124e-09</v>
+        <v>1.249750292123122e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.295826453240054e-09</v>
+        <v>1.295826453240053e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.26625790964842e-09</v>
+        <v>1.266257909648419e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.272985774396633e-09</v>
+        <v>1.272985774396632e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.352719882250661e-09</v>
+        <v>1.352719882250657e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.25535786972291e-09</v>
+        <v>1.255357869722908e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.302840872636069e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.320303272657784e-09</v>
+        <v>1.320303272657785e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.32183102229224e-09</v>
+        <v>1.321831022292237e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.319799631472438e-09</v>
+        <v>1.319799631472437e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.375992689329955e-09</v>
+        <v>1.375992689329953e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.255152896145206e-09</v>
+        <v>1.255152896145204e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.274011154524657e-09</v>
+        <v>1.274011154524656e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.322571768635284e-09</v>
+        <v>1.322571768635282e-09</v>
       </c>
       <c r="Q7" t="n">
         <v>1.270666746192507e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.265518169118829e-09</v>
+        <v>1.265518169118828e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.320105131166609e-09</v>
+        <v>1.320105131166608e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.286616513491625e-09</v>
+        <v>1.286616513491623e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.326986262937349e-09</v>
+        <v>1.326986262937351e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.287542022492152e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.321998183902958e-09</v>
+        <v>1.321998183902957e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.333105389028693e-09</v>
+        <v>1.333105389028689e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.379527933249242e-09</v>
+        <v>1.37952793324924e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.291872015592407e-09</v>
+        <v>1.291872015592406e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.301903991015649e-09</v>
+        <v>1.301903991015648e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.361710039745304e-09</v>
+        <v>1.361710039745303e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.242753272845469e-09</v>
+        <v>1.242753272845468e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.73636085956303e-09</v>
+        <v>1.736360859563027e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.782437020679961e-09</v>
+        <v>1.782437020679956e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.752868477088327e-09</v>
+        <v>1.467892595112557e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.307777941950911e-09</v>
+        <v>1.30777794195091e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.839330449690569e-09</v>
+        <v>1.950306748599044e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.741968437162818e-09</v>
+        <v>1.741968437162815e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.789451440075976e-09</v>
+        <v>1.789451440075972e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.80691384009769e-09</v>
+        <v>1.806913840097688e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.808441589732147e-09</v>
+        <v>1.808441589732143e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.806410198912343e-09</v>
+        <v>1.806410198912342e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.862603256769861e-09</v>
+        <v>1.862603256769865e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32689731950721e-09</v>
+        <v>1.326897319507209e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.459794623234793e-09</v>
+        <v>1.459794623234789e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.48040892104968e-09</v>
+        <v>1.480408921049676e-09</v>
       </c>
       <c r="Q8" t="n">
         <v>1.116903535456961e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.752128736558736e-09</v>
+        <v>1.752128736558735e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.806715698606517e-09</v>
+        <v>1.806715698606511e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.773227080931532e-09</v>
+        <v>1.773227080931533e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.484236251625216e-09</v>
+        <v>1.552356225641211e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.774152589932059e-09</v>
+        <v>1.628061653252793e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.808713932693254e-09</v>
+        <v>1.808713932693251e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.22839392063641e-09</v>
+        <v>1.228393920636408e-09</v>
       </c>
       <c r="Y8" t="n">
         <v>2.398559963214109e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.778482583032313e-09</v>
+        <v>1.233345426565583e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.788514558455557e-09</v>
+        <v>1.788514558455553e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.407377187801702e-09</v>
+        <v>2.407377187801701e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4648,49 +4648,49 @@
         <v>1.148500549917817e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.19457671103475e-09</v>
+        <v>1.194576711034749e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.165008167443116e-09</v>
+        <v>1.125525950242798e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.17173603219133e-09</v>
+        <v>7.773715854813336e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.251470140045355e-09</v>
+        <v>1.251470342193263e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.154108127517606e-09</v>
+        <v>1.154108127517601e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.201591130430764e-09</v>
+        <v>1.201591130430761e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.219053530452479e-09</v>
+        <v>1.219053530452477e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.220581280086934e-09</v>
+        <v>1.220581280086932e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.218549889267131e-09</v>
+        <v>1.218549889267127e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.274742947124649e-09</v>
+        <v>1.274742947124645e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1539031539399e-09</v>
+        <v>1.153903153939899e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.229484446529718e-09</v>
+        <v>1.229484446529715e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.290374729626731e-09</v>
+        <v>1.290374729626728e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.169417206135111e-09</v>
+        <v>1.169417206135112e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.164268426913524e-09</v>
+        <v>1.164268426913522e-09</v>
       </c>
       <c r="S9" t="n">
         <v>1.218855388961303e-09</v>
@@ -4699,28 +4699,28 @@
         <v>1.18536677128632e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.225549033102061e-09</v>
+        <v>1.22554903310206e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.186292280286847e-09</v>
+        <v>1.38370401304602e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.220748441697655e-09</v>
+        <v>1.220748441697653e-09</v>
       </c>
       <c r="X9" t="n">
         <v>1.231855646823384e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.278278191043935e-09</v>
+        <v>1.278278191043934e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.1906222733871e-09</v>
+        <v>1.087482056750897e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.200654248810344e-09</v>
+        <v>1.200654248810343e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.26046029754e-09</v>
+        <v>1.260460297539996e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.178872279366123e-10</v>
+        <v>5.178872279366171e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.30943386366724e-10</v>
+        <v>5.309433863667233e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.202445907028044e-10</v>
+        <v>5.202445907028058e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.172396632738703e-10</v>
+        <v>5.172396632738727e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.174465932174815e-10</v>
+        <v>5.174465932174822e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.197155995112444e-10</v>
+        <v>5.19715599511247e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.185745551622589e-10</v>
+        <v>5.185745551622618e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.179960016408219e-10</v>
+        <v>5.179960016408251e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.191283340255679e-10</v>
+        <v>5.191283340255709e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.209435847174226e-10</v>
+        <v>5.209435847174247e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.200584416133762e-10</v>
+        <v>5.200584416133771e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.205661855254953e-10</v>
+        <v>5.205661855254948e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.19467912900432e-10</v>
+        <v>5.194679129004334e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.196118932091743e-10</v>
+        <v>7.196118932091763e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.186369206572459e-10</v>
+        <v>5.186369206572467e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.182977380175053e-10</v>
+        <v>5.182977380175081e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.176605741737876e-10</v>
+        <v>5.176605741737927e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.188128695270251e-10</v>
+        <v>5.188128695270317e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.176059353042665e-10</v>
+        <v>5.176059353042679e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.159435990763544e-10</v>
+        <v>7.1594359907636e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.17447912685326e-10</v>
+        <v>5.174479126853277e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.423898427328714e-10</v>
+        <v>7.423898427328761e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.184868926619049e-10</v>
+        <v>5.184868926619111e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.176586112536249e-10</v>
+        <v>5.176586112536269e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.676667998517943e-10</v>
+        <v>7.676667998517956e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.181157841883598e-10</v>
+        <v>5.181157841883614e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.201110369062046e-10</v>
+        <v>5.201110369062052e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.472398659183616e-10</v>
+        <v>4.472398659183667e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.603477116503099e-10</v>
+        <v>4.603477116503091e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.642921613129082e-10</v>
+        <v>4.642921613129129e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.420235562590866e-10</v>
+        <v>4.420235562590902e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.443081400442774e-10</v>
+        <v>4.443081400442815e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.601911878060417e-10</v>
+        <v>4.60191187806046e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.524601686423182e-10</v>
+        <v>4.52460168642321e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.482349801202345e-10</v>
+        <v>4.48234980120236e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.560864404786174e-10</v>
+        <v>4.560864404786206e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.691312977999147e-10</v>
+        <v>4.691312977999229e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.626879614359473e-10</v>
+        <v>4.626879614359523e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.756243922513846e-10</v>
+        <v>4.75624392251385e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.586375045541499e-10</v>
+        <v>4.586375045541543e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.766673360859445e-10</v>
+        <v>7.76667336085947e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.525678275860826e-10</v>
+        <v>4.525678275860885e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.502884395430553e-10</v>
+        <v>4.5028843954306e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.458623633071488e-10</v>
+        <v>4.458623633071521e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.537479481984168e-10</v>
+        <v>4.537479481984205e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.454174232551447e-10</v>
+        <v>4.454174232551489e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.850584160840396e-10</v>
+        <v>7.850584160840426e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.440174845452264e-10</v>
+        <v>4.440174845452347e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.349404788486067e-10</v>
+        <v>8.349404788486135e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.516963923194876e-10</v>
+        <v>4.516963923194912e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.457295508769133e-10</v>
+        <v>4.457295508769189e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.628017512396362e-10</v>
+        <v>8.628017512396382e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.48988052311843e-10</v>
+        <v>4.489880523118485e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.641767528784827e-10</v>
+        <v>4.641767528784821e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.616875493317166e-10</v>
+        <v>4.61687549331717e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.443084004072544e-10</v>
+        <v>4.44308400407255e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.88315046216295e-10</v>
+        <v>4.883150462162951e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.543730085715706e-10</v>
+        <v>4.543730085715711e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.567103774771271e-10</v>
+        <v>4.567103774771276e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.823398473596648e-10</v>
+        <v>4.823398473596653e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.694512265315403e-10</v>
+        <v>4.694512265315397e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.629161983591516e-10</v>
+        <v>4.629161983591514e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.756569415850788e-10</v>
+        <v>4.756569415850791e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.962105051645459e-10</v>
+        <v>4.962105051645452e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.862124066183797e-10</v>
+        <v>4.862124066183802e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.087623728851027e-10</v>
+        <v>5.087623728851043e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.795421131490593e-10</v>
+        <v>4.795421131490595e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.54311810066377e-10</v>
+        <v>4.543118100663775e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.70155673486943e-10</v>
+        <v>4.701556734869432e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.663244495393736e-10</v>
+        <v>4.663244495393729e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.591273908147589e-10</v>
+        <v>4.591273908147583e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.721430969116406e-10</v>
+        <v>4.721430969116413e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.585102196483525e-10</v>
+        <v>4.585102196483519e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.820065456924903e-10</v>
+        <v>4.820065456924923e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.56614535654375e-10</v>
+        <v>4.566145356543745e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.966929705682699e-10</v>
+        <v>4.966929705682705e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.684610382633094e-10</v>
+        <v>4.684610382633095e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.580217956321991e-10</v>
+        <v>4.580217956321995e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.68466810293212e-10</v>
+        <v>4.684668102932109e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.642691973362642e-10</v>
+        <v>4.642691973362653e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.881612722726101e-10</v>
+        <v>4.881612722726107e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.474523855520076e-09</v>
+        <v>1.47452385552008e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.238950341315663e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.104618664608948e-09</v>
+        <v>2.104618664608952e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.005528428447452e-09</v>
+        <v>1.005528428447456e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.498935393238694e-09</v>
+        <v>1.498935393238697e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.810592038811205e-09</v>
+        <v>1.810592038811217e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.796403265388862e-09</v>
+        <v>1.796403265388861e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.619436059202933e-09</v>
+        <v>1.619436059202936e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.733278638480567e-09</v>
+        <v>1.733278638480573e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.170694504034871e-09</v>
+        <v>2.170694504034867e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.911561821033541e-09</v>
+        <v>1.911561821033548e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>2.436283397595838e-09</v>
+        <v>2.436283397595837e-09</v>
       </c>
       <c r="N5" t="n">
         <v>1.891676400918282e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.349792464313917e-09</v>
+        <v>1.349792464313918e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.622051137426313e-09</v>
+        <v>1.622051137426328e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.628236948866553e-09</v>
+        <v>1.628236948866556e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.559669129795392e-09</v>
+        <v>1.559669129795391e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.617564439202464e-09</v>
+        <v>1.617564439202459e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.517422623266374e-09</v>
+        <v>1.517422623266372e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.895224256557997e-09</v>
+        <v>1.895224256557985e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33222039786091e-09</v>
+        <v>1.332220397860861e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.200534511825126e-09</v>
+        <v>2.200534511825143e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.700862524096497e-09</v>
+        <v>1.700862524096499e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.493177362180134e-09</v>
+        <v>1.493177362180135e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.581677658141226e-09</v>
+        <v>1.581677658141227e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.588389999324483e-09</v>
+        <v>1.588389999324481e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.158268373130041e-09</v>
+        <v>2.158268373130036e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5238,70 +5238,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.57856441831272e-10</v>
+        <v>5.578564418312714e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.836450625366948e-10</v>
+        <v>8.836450625366954e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.276517083457377e-10</v>
+        <v>5.844839387158493e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.937096707010133e-10</v>
+        <v>5.50541901071125e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.960470396065667e-10</v>
+        <v>8.960470396065706e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.785087398592199e-10</v>
+        <v>9.216765094891083e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.656201190310943e-10</v>
+        <v>5.656201190310942e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>9.022528604885926e-10</v>
+        <v>5.590850908587055e-10</v>
       </c>
       <c r="J6" t="n">
         <v>5.718258340846331e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>9.355471672939882e-10</v>
+        <v>5.923793976640998e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.255490687478215e-10</v>
+        <v>5.823812991179347e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.049312653846584e-10</v>
+        <v>9.480990350145476e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.7578179237673e-10</v>
+        <v>5.757817923767296e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.927204181080409e-10</v>
+        <v>8.927204181080442e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.085676882177311e-10</v>
+        <v>5.55168895894427e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.056611116688144e-10</v>
+        <v>9.056611116688161e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.984640529441995e-10</v>
+        <v>5.552962833143121e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>9.114797590410824e-10</v>
+        <v>5.683119894111955e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.546791121479065e-10</v>
+        <v>8.978468817777941e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.224266309182225e-10</v>
+        <v>5.792588612883366e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.527834281539309e-10</v>
+        <v>8.959511977838192e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.030027031616733e-10</v>
+        <v>6.030027031616741e-10</v>
       </c>
       <c r="X6" t="n">
         <v>5.646299307628637e-10</v>
@@ -5310,13 +5310,13 @@
         <v>5.63823328269941e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.646357027927642e-10</v>
+        <v>9.078034724226534e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.604380898358198e-10</v>
+        <v>9.036058594657081e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.845402457985984e-10</v>
+        <v>5.845402457985994e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5326,28 +5326,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.280287128853421e-09</v>
+        <v>1.280287128853422e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.262907979928957e-09</v>
+        <v>1.262907979928958e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.306914625737998e-09</v>
+        <v>1.306914625738001e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.272972588093273e-09</v>
+        <v>1.272972588093274e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.275309956998829e-09</v>
+        <v>1.27530995699883e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.300939426881369e-09</v>
+        <v>1.30093942688137e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.288050806053242e-09</v>
+        <v>1.288050806053243e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.281515777880853e-09</v>
+        <v>1.281515777880854e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.294256521106782e-09</v>
@@ -5356,55 +5356,55 @@
         <v>1.314810084686249e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.304811986140084e-09</v>
+        <v>1.304811986140086e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.327361952406806e-09</v>
+        <v>1.327361952406808e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.298141692670761e-09</v>
+        <v>1.298141692670763e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.272879227540888e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.288723090961454e-09</v>
+        <v>1.288723090961458e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.284924029061076e-09</v>
+        <v>1.284924029061078e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.277726970336462e-09</v>
+        <v>1.277726970336464e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.290742676433344e-09</v>
+        <v>1.290742676433346e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.277109799170053e-09</v>
+        <v>1.277109799170055e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.301794726514337e-09</v>
+        <v>1.301794726514339e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.275214115176076e-09</v>
+        <v>1.275214115176078e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.315292550089973e-09</v>
+        <v>1.315292550089975e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.287060617785012e-09</v>
+        <v>1.287060617785013e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.277704798250191e-09</v>
+        <v>1.277704798250194e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.287066389814913e-09</v>
+        <v>1.287066389814915e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.282868776857969e-09</v>
+        <v>1.28286877685797e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.306760851794314e-09</v>
+        <v>1.306760851794313e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5414,25 +5414,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.216279708425515e-09</v>
+        <v>1.216279708425517e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.745006556138703e-09</v>
+        <v>1.745006556138704e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.789013201947746e-09</v>
+        <v>1.789013201947745e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.755071164303019e-09</v>
+        <v>1.46428583019728e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.296379468380772e-09</v>
+        <v>1.296379468380773e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.783038003091115e-09</v>
+        <v>1.896276639049378e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.77014938226299e-09</v>
+        <v>1.770149382262989e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.763614354090601e-09</v>
@@ -5441,16 +5441,16 @@
         <v>1.776355097316529e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.796908660895995e-09</v>
+        <v>1.796908660895993e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.78691056234983e-09</v>
+        <v>1.786910562349832e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.809460528616552e-09</v>
+        <v>1.809460528616555e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.356916759963486e-09</v>
+        <v>1.356916759963485e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.448019432828445e-09</v>
@@ -5459,40 +5459,40 @@
         <v>1.435347272841049e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.113594316012603e-09</v>
+        <v>1.113594316012604e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.759825546546206e-09</v>
+        <v>1.759825546546208e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.772841252643092e-09</v>
+        <v>1.772841252643091e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.759208375379802e-09</v>
+        <v>1.759208375379801e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.447842870073373e-09</v>
+        <v>1.51734751172598e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.757312691385828e-09</v>
+        <v>1.608171083315239e-09</v>
       </c>
       <c r="W8" t="n">
         <v>1.797498451853545e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.165782604505041e-09</v>
+        <v>1.16578260450504e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.302966216632342e-09</v>
+        <v>2.302966216632341e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.769164966024663e-09</v>
+        <v>1.21291477012195e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.764967353067714e-09</v>
+        <v>1.764967353067713e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.359312806204532e-09</v>
+        <v>2.359312806204531e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5502,28 +5502,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.021012400481373e-09</v>
+        <v>1.021012400481375e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.187325445412262e-09</v>
+        <v>1.187325445412263e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.231332091221302e-09</v>
+        <v>1.231332091221305e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.197390053576578e-09</v>
+        <v>1.154994812579092e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.199727422482135e-09</v>
+        <v>7.762664960762294e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.225356892364672e-09</v>
+        <v>1.225357110873014e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.212468271536547e-09</v>
+        <v>1.212468271536549e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.205933243364158e-09</v>
+        <v>1.20593324336416e-09</v>
       </c>
       <c r="J9" t="n">
         <v>1.218673986590087e-09</v>
@@ -5532,55 +5532,55 @@
         <v>1.239227550169553e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.229229451623387e-09</v>
+        <v>1.22922945162339e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.251779417890111e-09</v>
+        <v>1.251779417890112e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.222559158154066e-09</v>
+        <v>1.222559158154067e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.258204498512443e-09</v>
+        <v>1.258204498512445e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.287287722409439e-09</v>
+        <v>1.28728772240944e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.20934171305272e-09</v>
+        <v>1.209341713052721e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.202144435819767e-09</v>
+        <v>1.202144435819768e-09</v>
       </c>
       <c r="S9" t="n">
         <v>1.215160141916649e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.20152726465336e-09</v>
+        <v>1.201527264653361e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22610701379379e-09</v>
+        <v>1.226107013793791e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.199631580659382e-09</v>
+        <v>1.411608509097953e-09</v>
       </c>
       <c r="W9" t="n">
         <v>1.239710015573278e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.211478083268317e-09</v>
+        <v>1.211478083268318e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.202122263733498e-09</v>
+        <v>1.202122263733499e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.211483855298218e-09</v>
+        <v>1.100733883717909e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.207286242341273e-09</v>
+        <v>1.207286242341275e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.231178317277617e-09</v>
+        <v>1.23117831727762e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.10413131858705e-10</v>
+        <v>5.104131318586915e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.228972075799205e-10</v>
+        <v>5.22897207579919e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.11274461377081e-10</v>
+        <v>5.112744613770673e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.088259355332508e-10</v>
+        <v>5.088259355332366e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.103500926835464e-10</v>
+        <v>5.103500926835323e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.096494582098038e-10</v>
+        <v>5.096494582097896e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.101152231257354e-10</v>
+        <v>5.101152231257229e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.105274078370726e-10</v>
+        <v>5.105274078370706e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.100509851295829e-10</v>
+        <v>5.10050985129576e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.102773650807855e-10</v>
+        <v>5.102773650807742e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.106085426487542e-10</v>
+        <v>5.106085426487455e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.086904014365095e-10</v>
+        <v>5.086904014365089e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.09768284258285e-10</v>
+        <v>5.097682842582714e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.975997496518759e-10</v>
+        <v>6.97599749651865e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.088486577627292e-10</v>
+        <v>5.088486577627156e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.095353608530237e-10</v>
+        <v>5.095353608530105e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.105807643917684e-10</v>
+        <v>5.105807643917548e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.102765012915788e-10</v>
+        <v>5.102765012915641e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.094264741745115e-10</v>
+        <v>5.094264741744969e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.905121136310017e-10</v>
+        <v>6.905121136309934e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.098210475531082e-10</v>
+        <v>5.09821047553094e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.176796405571599e-10</v>
+        <v>7.176796405571487e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.126614064484722e-10</v>
+        <v>5.126614064484582e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.11146042293282e-10</v>
+        <v>5.111460422932685e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.533783928666707e-10</v>
+        <v>7.533783928666552e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.102211999352106e-10</v>
+        <v>5.10221199935196e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.103384239512879e-10</v>
+        <v>5.103384239512866e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.448741813765527e-10</v>
+        <v>4.448741813765418e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.583585028073103e-10</v>
+        <v>4.583585028073082e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.511814112672983e-10</v>
+        <v>4.511814112672914e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.329653593152592e-10</v>
+        <v>4.329653593152556e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.446297870967109e-10</v>
+        <v>4.446297870967063e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.394403382874179e-10</v>
+        <v>4.39440338287413e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.43047283222535e-10</v>
+        <v>4.430472832225304e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.459077274712519e-10</v>
+        <v>4.459077274712406e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.423268061074116e-10</v>
+        <v>4.423268061074074e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.440339645504443e-10</v>
+        <v>4.440339645504405e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.462368834200428e-10</v>
+        <v>4.462368834200301e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.420331884379825e-10</v>
+        <v>4.420331884379815e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.403866166422279e-10</v>
+        <v>4.40386616642223e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.473828018327009e-10</v>
+        <v>7.4738280183269e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.337419510458522e-10</v>
+        <v>4.337419510458512e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.386887188015763e-10</v>
+        <v>4.386887188015699e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.463259968187983e-10</v>
+        <v>4.463259968187932e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.43848609018474e-10</v>
+        <v>4.438486090184649e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.380178522947385e-10</v>
+        <v>4.380178522947324e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.377029816400379e-10</v>
+        <v>7.377029816400279e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.405442060100629e-10</v>
+        <v>4.405442060100579e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.019842444452999e-10</v>
+        <v>8.019842444452862e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.610208120797842e-10</v>
+        <v>4.610208120797809e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.502398436139173e-10</v>
+        <v>4.502398436139134e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.450560262106898e-10</v>
+        <v>8.450560262106842e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.436300427195791e-10</v>
+        <v>4.436300427195671e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.454441607191591e-10</v>
+        <v>4.454441607191575e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.539789622366113e-10</v>
+        <v>4.539789622366111e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.39316759754263e-10</v>
+        <v>4.393167597542618e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.637080753778257e-10</v>
+        <v>4.637080753778253e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.360508495942277e-10</v>
+        <v>4.360508495942265e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.532669057537498e-10</v>
+        <v>4.532669057537492e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.45352917065041e-10</v>
+        <v>4.453529170650401e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.506139460529372e-10</v>
+        <v>4.506139460529358e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.552697619818492e-10</v>
+        <v>4.55269761981848e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.498447360030026e-10</v>
+        <v>4.498447360030019e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.524454140242441e-10</v>
+        <v>4.524454140242427e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.561862170036328e-10</v>
+        <v>4.561862170036317e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.51620888459075e-10</v>
+        <v>4.51620888459074e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.466951119453259e-10</v>
+        <v>4.466951119453252e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.405782533117302e-10</v>
+        <v>4.405782533117297e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.36307507628936e-10</v>
+        <v>4.363075076289353e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.440641349328503e-10</v>
+        <v>4.440641349328498e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.558724488123473e-10</v>
+        <v>4.558724488123467e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.524356571277606e-10</v>
+        <v>4.524356571277594e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.428342098086913e-10</v>
+        <v>4.428342098086906e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.429390527528873e-10</v>
+        <v>4.429390527528862e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.47220541192453e-10</v>
+        <v>4.472205411924553e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.847667632775859e-10</v>
+        <v>4.847667632775847e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.793742579854485e-10</v>
+        <v>4.79374257985451e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.614797326100416e-10</v>
+        <v>4.614797326100408e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.522379780634143e-10</v>
+        <v>4.522379780634133e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.518110028676968e-10</v>
+        <v>4.518110028676959e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.547076712386927e-10</v>
+        <v>4.547076712386925e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.49390406923376e-09</v>
+        <v>1.493904069233759e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.324154408090209e-09</v>
+        <v>1.324154408090208e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.748832307328177e-09</v>
+        <v>1.748832307328173e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>8.757673023601042e-10</v>
+        <v>8.757673023601046e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.587815429179239e-09</v>
+        <v>1.587815429179238e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.349906456551081e-09</v>
+        <v>1.349906456551079e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.589488355557899e-09</v>
+        <v>1.589488355557897e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.62968248130145e-09</v>
+        <v>1.629682481301448e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.440832683882834e-09</v>
+        <v>1.440832683882829e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.533506019405443e-09</v>
+        <v>1.533506019405442e-09</v>
       </c>
       <c r="L5" t="n">
         <v>1.516383398100743e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.536630039215278e-09</v>
+        <v>1.536630039215276e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.346924843247235e-09</v>
+        <v>1.346924843247233e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.273347095477022e-09</v>
+        <v>1.273347095477019e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.198715390141899e-09</v>
+        <v>1.198715390141898e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.359604406378121e-09</v>
+        <v>1.359604406378118e-09</v>
       </c>
       <c r="R5" t="n">
         <v>1.659755184664705e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.440472448498836e-09</v>
+        <v>1.440472448498834e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.39291933559302e-09</v>
+        <v>1.392919335593017e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.343946574195375e-09</v>
+        <v>1.343946574195373e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.321527770459093e-09</v>
+        <v>1.321527770459152e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.051221771852326e-09</v>
+        <v>2.051221771852322e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.995186308195199e-09</v>
+        <v>1.995186308195244e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.710203524182833e-09</v>
+        <v>1.710203524182836e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.446955121191464e-09</v>
+        <v>1.446955121191463e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.520695297410073e-09</v>
+        <v>1.520695297410069e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.635708674142315e-09</v>
+        <v>1.635708674142313e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.447377985693176e-10</v>
+        <v>5.447377985693161e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.471301257899471e-10</v>
+        <v>5.300755960869683e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.544669117105327e-10</v>
+        <v>5.544669117105314e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.438642156299126e-10</v>
+        <v>8.438642156299111e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.610802717894353e-10</v>
+        <v>8.610802717894325e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.531662831007246e-10</v>
+        <v>5.361117533977466e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.584273120886227e-10</v>
+        <v>5.413727823856429e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.460285983145558e-10</v>
+        <v>5.460285983145535e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.576581020386897e-10</v>
+        <v>5.40603572335708e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.432042503569498e-10</v>
+        <v>5.432042503569493e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.639995830393177e-10</v>
+        <v>8.639995830393162e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>5.423797247917812e-10</v>
+        <v>8.594342544947575e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.375345928822239e-10</v>
+        <v>5.375345928822253e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.314177342486288e-10</v>
+        <v>5.314177342486282e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.433773928331472e-10</v>
+        <v>5.167659625839705e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.51877500968538e-10</v>
+        <v>5.348229712655564e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.636858148480321e-10</v>
+        <v>8.636858148480306e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>8.602490231634455e-10</v>
+        <v>5.431944934604658e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.506475758443763e-10</v>
+        <v>8.506475758443742e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>5.34475679226175e-10</v>
+        <v>5.344756792261739e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.37979377525163e-10</v>
+        <v>8.550339072281373e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.849400618501887e-10</v>
+        <v>5.849400618501874e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.701330943181563e-10</v>
+        <v>5.701330943181576e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.609857949644719e-10</v>
+        <v>5.609857949644709e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.600513440990996e-10</v>
+        <v>8.600513440991007e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.425698392004036e-10</v>
+        <v>8.596243689033792e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.455788695119651e-10</v>
+        <v>5.455788695119638e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.205713994649594e-09</v>
+        <v>1.20571399464959e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.191051792167246e-09</v>
+        <v>1.191051792167242e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.215443107790809e-09</v>
+        <v>1.215443107790805e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.18778588200721e-09</v>
+        <v>1.187785882007206e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.205001938166732e-09</v>
+        <v>1.205001938166729e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.197087949478024e-09</v>
+        <v>1.197087949478019e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.202348978465919e-09</v>
+        <v>1.202348978465916e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.207004794394831e-09</v>
+        <v>1.207004794394828e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.201579768415984e-09</v>
+        <v>1.20157976841598e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.204180446437225e-09</v>
+        <v>1.204180446437222e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.207921249416615e-09</v>
+        <v>1.207921249416612e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.203355920872057e-09</v>
+        <v>1.203355920872053e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.198430144358309e-09</v>
+        <v>1.198430144358305e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.192283502355937e-09</v>
+        <v>1.192283502355933e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.18801275667314e-09</v>
+        <v>1.188012756673136e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.195799167345833e-09</v>
+        <v>1.19579916734583e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.207607481225328e-09</v>
+        <v>1.207607481225325e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.204170689540743e-09</v>
+        <v>1.204170689540739e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.194569242221674e-09</v>
+        <v>1.194569242221671e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.195621456959662e-09</v>
+        <v>1.195621456959657e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.198955573605438e-09</v>
+        <v>1.198955573605434e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.236501795690569e-09</v>
+        <v>1.236501795690565e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.231109290398432e-09</v>
+        <v>1.231109290398431e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.213992555163602e-09</v>
+        <v>1.213992555163599e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.203973010476396e-09</v>
+        <v>1.203973010476392e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.203546035280677e-09</v>
+        <v>1.203546035280674e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.206442703651676e-09</v>
+        <v>1.206442703651673e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.13229293162456e-09</v>
+        <v>1.132292931624559e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.609087567654793e-09</v>
+        <v>1.60908756765479e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.633478883278355e-09</v>
+        <v>1.633478883278353e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.605821657494757e-09</v>
+        <v>1.344135388043494e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.208144106812593e-09</v>
+        <v>1.208144106812592e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.615123724965569e-09</v>
+        <v>1.717030501979607e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.620384753953467e-09</v>
+        <v>1.620384753953464e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.625040569882379e-09</v>
+        <v>1.625040569882377e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.619615543903532e-09</v>
+        <v>1.619615543903529e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.622216221924773e-09</v>
+        <v>1.62221622192477e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.625957024904164e-09</v>
+        <v>1.625957024904161e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.621391696359605e-09</v>
+        <v>1.621391696359625e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.235504651077921e-09</v>
+        <v>1.235504651077918e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.334079256968105e-09</v>
+        <v>1.334079256968103e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.304146103626306e-09</v>
+        <v>1.304146103626303e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.025795618580889e-09</v>
+        <v>1.025795618580888e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.625643256712876e-09</v>
+        <v>1.625643256712874e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.62220646502829e-09</v>
+        <v>1.622206465028288e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.612605017709221e-09</v>
+        <v>1.612605017709218e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.311215777632735e-09</v>
+        <v>1.373768630354775e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.616991349092984e-09</v>
+        <v>1.482839197179738e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.654634156595563e-09</v>
+        <v>1.654634156595562e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.106148737463572e-09</v>
+        <v>1.106148737463574e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.120936988598657e-09</v>
+        <v>2.120936988598656e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.622008785963944e-09</v>
+        <v>1.121422884356348e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.621581810768226e-09</v>
+        <v>1.621581810768223e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.137846241979571e-09</v>
+        <v>2.137846241979568e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6362,79 +6362,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.384334338597685e-10</v>
+        <v>9.384334338597641e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.084066533050061e-09</v>
+        <v>1.084066533050059e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.108457848673624e-09</v>
+        <v>1.108457848673623e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.080800622890025e-09</v>
+        <v>1.043805280526539e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.098016679049548e-09</v>
+        <v>7.284919894166968e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.090102690360843e-09</v>
+        <v>1.090102897626933e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.095363719348734e-09</v>
+        <v>1.095363719348735e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.100019535277645e-09</v>
+        <v>1.100019535277643e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0945945092988e-09</v>
+        <v>1.094594509298799e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.097195187320044e-09</v>
+        <v>1.097195187320038e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.100935990299432e-09</v>
+        <v>1.10093599029943e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.096370661754873e-09</v>
+        <v>1.096370661754867e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.091444885241125e-09</v>
+        <v>1.091444885241121e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.138449955646943e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.14573227303455e-09</v>
+        <v>1.145732273034551e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.088814115494747e-09</v>
+        <v>1.088814115494741e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.100622222108146e-09</v>
+        <v>1.100622222108141e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.097185430423559e-09</v>
+        <v>1.097185430423556e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.087583983104487e-09</v>
+        <v>1.087583983104486e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.088466616189267e-09</v>
+        <v>1.088466616189265e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.091970314488255e-09</v>
+        <v>1.27694774693601e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.129516536573383e-09</v>
+        <v>1.129516536573382e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.124124031281247e-09</v>
+        <v>1.124124031281246e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.10700729604642e-09</v>
+        <v>1.107007296046416e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.096987751359212e-09</v>
+        <v>1.000344020768073e-09</v>
       </c>
       <c r="AA9" t="n">
         <v>1.096560776163494e-09</v>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.117645109527437e-10</v>
+        <v>5.117645109527445e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.237465063654125e-10</v>
+        <v>5.23746506365412e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.119057551873132e-10</v>
+        <v>5.119057551873149e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.101832229367657e-10</v>
+        <v>5.101832229367683e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.105655715892271e-10</v>
+        <v>5.105655715892272e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.112939595923247e-10</v>
+        <v>5.112939595923283e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.105029861491791e-10</v>
+        <v>5.105029861491793e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.111553856064387e-10</v>
+        <v>5.111553856064418e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.111038456017612e-10</v>
+        <v>5.111038456017601e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.106300259009181e-10</v>
+        <v>5.10630025900921e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.108562379456699e-10</v>
+        <v>5.108562379456708e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.08922330396668e-10</v>
+        <v>5.089223303966683e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.102973697343211e-10</v>
+        <v>5.102973697343234e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.962644189892725e-10</v>
+        <v>6.962644189892692e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.096334468895153e-10</v>
+        <v>5.096334468895177e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.100105755658043e-10</v>
+        <v>5.100105755658053e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.116732089885755e-10</v>
+        <v>5.116732089885758e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.106636776516964e-10</v>
+        <v>5.106636776516997e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.101128212762671e-10</v>
+        <v>5.101128212762669e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.89105427232243e-10</v>
+        <v>6.891054272322401e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1074696253886e-10</v>
+        <v>5.107469625388607e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.217433734472869e-10</v>
+        <v>7.21743373447283e-10</v>
       </c>
       <c r="X2" t="n">
         <v>5.139135809888716e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.122955570688326e-10</v>
+        <v>5.12295557068835e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.527617633444022e-10</v>
+        <v>7.52761763344404e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.109383864937906e-10</v>
+        <v>5.109383864937904e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.116175001643468e-10</v>
+        <v>5.116175001643448e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.510936365658465e-10</v>
+        <v>4.510936365658446e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.60972257859849e-10</v>
+        <v>4.609722578598476e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.523152124151675e-10</v>
+        <v>4.523152124151629e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.392428197907673e-10</v>
+        <v>4.392428197907656e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.427972801039629e-10</v>
+        <v>4.427972801039611e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.477400105807055e-10</v>
+        <v>4.477400105807045e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.424124829435042e-10</v>
+        <v>4.42412482943502e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.470068499199587e-10</v>
+        <v>4.470068499199574e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.464598483735061e-10</v>
+        <v>4.464598483735018e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.431837791890923e-10</v>
+        <v>4.431837791890915e-10</v>
       </c>
       <c r="L3" t="n">
         <v>4.446670372182634e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.403685284496589e-10</v>
+        <v>4.403685284496583e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.407883266433422e-10</v>
+        <v>4.407883266433402e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.450470391022768e-10</v>
+        <v>7.450470391022736e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.359396073685479e-10</v>
+        <v>4.35939607368548e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.387258093032082e-10</v>
+        <v>4.387258093032078e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.507522379543961e-10</v>
+        <v>4.507522379543937e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.432705297540365e-10</v>
+        <v>4.43270529754037e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.395329125274897e-10</v>
+        <v>4.395329125274906e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.3676890665644e-10</v>
+        <v>7.367689066564357e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.437507973986099e-10</v>
+        <v>4.437507973986125e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.401221639706596e-10</v>
+        <v>8.401221639706579e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.665257131355575e-10</v>
+        <v>4.66525713135556e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.550678944658162e-10</v>
+        <v>4.550678944658143e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.428102588314957e-10</v>
+        <v>8.428102588315003e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.453591356824037e-10</v>
+        <v>4.453591356824012e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.512033388574896e-10</v>
+        <v>4.512033388574888e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.649523000930654e-10</v>
+        <v>4.649523000930658e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.445072055530235e-10</v>
+        <v>4.445072055530232e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.665477186980951e-10</v>
+        <v>4.665477186980942e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.470909245241791e-10</v>
+        <v>4.470909245241793e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.514097284427897e-10</v>
+        <v>4.514097284427919e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.596372060128258e-10</v>
+        <v>4.596372060128273e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.507027971067301e-10</v>
+        <v>4.507027971067308e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.580719490950539e-10</v>
+        <v>4.580719490950545e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.574436317049213e-10</v>
+        <v>4.574436317049209e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.521377695438031e-10</v>
+        <v>4.52137769543803e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.546929386519551e-10</v>
+        <v>4.546929386519549e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.499929044970473e-10</v>
+        <v>4.499929044970486e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.483802651126921e-10</v>
+        <v>4.483802651126926e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.430051321517977e-10</v>
+        <v>4.430051321517987e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.408809511610064e-10</v>
+        <v>4.408809511610053e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.451407930474471e-10</v>
+        <v>4.451407930474482e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.639210024068014e-10</v>
+        <v>4.639210024068022e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.525178815494208e-10</v>
+        <v>4.525178815494207e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.462957053824595e-10</v>
+        <v>4.462957053824601e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.486157702268377e-10</v>
+        <v>4.486157702268376e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.533712602944387e-10</v>
+        <v>4.53371260294439e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.522822165636373e-10</v>
+        <v>5.52282216563638e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.892270347721651e-10</v>
+        <v>4.892270347721677e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.702786781859359e-10</v>
+        <v>4.702786781859362e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.524165257678814e-10</v>
+        <v>4.524165257678824e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.556208442931454e-10</v>
+        <v>4.556208442931474e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.647919277964376e-10</v>
+        <v>4.647919277964377e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6873,82 +6873,82 @@
         <v>1.63565298781399e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.380110806520869e-09</v>
+        <v>1.380110806520867e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.774516078835036e-09</v>
+        <v>1.774516078835029e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.026903900955414e-09</v>
+        <v>1.02690390095541e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.531145173613552e-09</v>
+        <v>1.531145173613549e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.544094111065608e-09</v>
+        <v>1.544094111065604e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.550708760077052e-09</v>
+        <v>1.55070876007705e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.648997113646283e-09</v>
+        <v>1.648997113646281e-09</v>
       </c>
       <c r="J5" t="n">
         <v>1.545810283453027e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.505924727545836e-09</v>
+        <v>1.505924727545833e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.483111204744404e-09</v>
+        <v>1.4831112047444e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.497938977251834e-09</v>
+        <v>1.49793897725183e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.401242509169649e-09</v>
+        <v>1.401242509169648e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.279912573996304e-09</v>
+        <v>1.2799125739963e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.23866321900513e-09</v>
+        <v>1.238663219005127e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.36303777971376e-09</v>
+        <v>1.363037779713762e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.778180622101262e-09</v>
+        <v>1.77818062210126e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.433139709865249e-09</v>
+        <v>1.433139709865246e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.423559608188219e-09</v>
+        <v>1.42355960818822e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.402150046365439e-09</v>
+        <v>1.402150046365436e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.390540357425478e-09</v>
+        <v>1.390540357425476e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>3.181564864563027e-09</v>
+        <v>3.181564864563005e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.113734171360082e-09</v>
+        <v>2.113734171360084e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.837178588736237e-09</v>
+        <v>1.837178588736243e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.411523778943244e-09</v>
+        <v>1.411523778943243e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.554351011873668e-09</v>
+        <v>1.554351011873664e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.811006313743677e-09</v>
+        <v>1.811006313743675e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.75283901718157e-10</v>
+        <v>8.752839017181569e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.548388071781141e-10</v>
+        <v>8.548388071781143e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.768793203231861e-10</v>
+        <v>8.768793203231846e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.574225261492698e-10</v>
+        <v>8.5742252614927e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.43136960457301e-10</v>
+        <v>8.617413300678807e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.513644380273367e-10</v>
+        <v>8.699688076379166e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.424300291212409e-10</v>
+        <v>5.424300291212404e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.684035507201456e-10</v>
+        <v>5.497991811095658e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.677752333300126e-10</v>
+        <v>5.491708637194313e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.438650015583139e-10</v>
+        <v>8.624693711688922e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.650245402770459e-10</v>
+        <v>8.650245402770431e-10</v>
       </c>
       <c r="M6" t="n">
         <v>8.603245061221372e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.401543355351203e-10</v>
+        <v>5.401543355351209e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.347792025742255e-10</v>
+        <v>8.51639896840745e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.495175175139209e-10</v>
+        <v>8.495175175139203e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.55472394672537e-10</v>
+        <v>8.554723946725371e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.742526040318919e-10</v>
+        <v>5.556482344213114e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.442451135639325e-10</v>
+        <v>5.442451135639312e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.566273070075498e-10</v>
+        <v>8.566273070075488e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>8.596194039335741e-10</v>
+        <v>8.596194039335702e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4509849230895e-10</v>
+        <v>5.450984923089495e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.60913582223723e-10</v>
+        <v>9.609135822237241e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>8.995586363972569e-10</v>
+        <v>5.809542667866762e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.706606774409447e-10</v>
+        <v>5.706606774409438e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.627481273929712e-10</v>
+        <v>5.44143757782391e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.65952445918236e-10</v>
+        <v>5.473480763076559e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.566215446415555e-10</v>
+        <v>5.566215446415561e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.216341000003399e-09</v>
+        <v>1.216341000003395e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.195895905463357e-09</v>
+        <v>1.195895905463354e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.21793641860843e-09</v>
+        <v>1.217936418608428e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.198479624434509e-09</v>
+        <v>1.198479624434505e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.202798428353123e-09</v>
+        <v>1.20279842835312e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.211025905923156e-09</v>
+        <v>1.211025905923155e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.202091497017062e-09</v>
+        <v>1.202091497017061e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.209460649005385e-09</v>
+        <v>1.209460649005383e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.208832331615255e-09</v>
+        <v>1.208832331615251e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.203526469454137e-09</v>
+        <v>1.203526469454134e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.206081638562288e-09</v>
+        <v>1.206081638562287e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.201381604407379e-09</v>
+        <v>1.201381604407378e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.199768965023024e-09</v>
+        <v>1.199768965023019e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.194364083502119e-09</v>
+        <v>1.194364083502118e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.192239902511327e-09</v>
+        <v>1.192239902511326e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.196529492957777e-09</v>
+        <v>1.196529492957775e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.215309702317133e-09</v>
+        <v>1.21530970231713e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.203906581459754e-09</v>
+        <v>1.203906581459752e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.197684405292791e-09</v>
+        <v>1.197684405292785e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.200862931551015e-09</v>
+        <v>1.200862931551013e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.20475996020477e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.30367091647397e-09</v>
+        <v>1.303670916473968e-09</v>
       </c>
       <c r="X7" t="n">
         <v>1.240615734682496e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.222339410177912e-09</v>
+        <v>1.222339410177907e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.203805225678213e-09</v>
+        <v>1.203805225678214e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.207009544203478e-09</v>
+        <v>1.207009544203475e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.216180627706769e-09</v>
+        <v>1.216180627706765e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.140294175014906e-09</v>
+        <v>1.140294175014905e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.609616541835734e-09</v>
+        <v>1.60961654183572e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.631657054980805e-09</v>
+        <v>1.631657054980795e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.612200260806889e-09</v>
+        <v>1.351413534856363e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.203051649818974e-09</v>
+        <v>1.203051649818967e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.624746542295536e-09</v>
+        <v>1.726303015951495e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.615812133389442e-09</v>
+        <v>1.615812133389429e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.623181285377765e-09</v>
+        <v>1.623181285377756e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.622552967987634e-09</v>
+        <v>1.622552967987622e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.617247105826513e-09</v>
+        <v>1.617247105826502e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.619802274934665e-09</v>
+        <v>1.619802274934659e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.615102240779757e-09</v>
+        <v>1.615102240779795e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.233837882545528e-09</v>
+        <v>1.233837882545521e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.332794338417878e-09</v>
+        <v>1.332794338417877e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305095963995902e-09</v>
+        <v>1.305095963995893e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.024232183399167e-09</v>
+        <v>1.024232183399163e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.629030338689511e-09</v>
+        <v>1.629030338689495e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.617627217832131e-09</v>
+        <v>1.617627217832124e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61140504166517e-09</v>
+        <v>1.611405041665161e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.313177054735008e-09</v>
+        <v>1.375515710150772e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.618480596577149e-09</v>
+        <v>1.484804548134673e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.717487806248146e-09</v>
+        <v>1.717487806248132e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1132065861783e-09</v>
+        <v>1.113206586178292e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.123311285036334e-09</v>
+        <v>2.123311285036327e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.617525862050592e-09</v>
+        <v>1.118660718643094e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.620730180575856e-09</v>
+        <v>1.620730180575847e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.141504331216648e-09</v>
+        <v>2.141504331216627e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7222,82 +7222,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.338812363709449e-10</v>
+        <v>9.338812363709438e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.069524416907531e-09</v>
+        <v>1.069524416907527e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.091564930052603e-09</v>
+        <v>1.091564930052601e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.072108135878685e-09</v>
+        <v>1.036083759151223e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.076426939797295e-09</v>
+        <v>7.166005928797449e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.084654417367332e-09</v>
+        <v>1.084654626008626e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.075720008461236e-09</v>
+        <v>1.075720008461234e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.08308916044956e-09</v>
+        <v>1.083089160449562e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.082460843059428e-09</v>
+        <v>1.082460843059421e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.077154980898308e-09</v>
+        <v>1.077154980898309e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.079710150006461e-09</v>
+        <v>1.079710150006462e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.075010115851553e-09</v>
+        <v>1.07501011585155e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0733974764672e-09</v>
+        <v>1.073397476467198e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.119750071271374e-09</v>
+        <v>1.119750071271371e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.128875738195199e-09</v>
+        <v>1.128875738195196e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.070158213043252e-09</v>
+        <v>1.070158213043248e-09</v>
       </c>
       <c r="R9" t="n">
         <v>1.088938213761309e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.077535092903928e-09</v>
+        <v>1.077535092903924e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.071312916736968e-09</v>
+        <v>1.071312916736963e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.07430501366299e-09</v>
+        <v>1.074305013662987e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.078388471648945e-09</v>
+        <v>1.258511089364208e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.177299427918143e-09</v>
+        <v>1.177299427918138e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.114244246126672e-09</v>
+        <v>1.114244246126675e-09</v>
       </c>
       <c r="Y9" t="n">
         <v>1.095967921622087e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.077433737122386e-09</v>
+        <v>9.833264700113238e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.080638055647651e-09</v>
+        <v>1.080638055647648e-09</v>
       </c>
       <c r="AB9" t="n">
         <v>1.089809139150944e-09</v>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.334586295010446e-10</v>
+        <v>5.334586295010427e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.459323154854646e-10</v>
+        <v>5.459323154854645e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.334739753329197e-10</v>
+        <v>5.334739753329194e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.316357898476482e-10</v>
+        <v>5.31635789847649e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.31686313229649e-10</v>
+        <v>5.316863132296485e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.407569668172725e-10</v>
+        <v>5.407569668172731e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.313918132889273e-10</v>
+        <v>5.313918132889278e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.334066806038021e-10</v>
+        <v>5.334066806038015e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.367027628866857e-10</v>
+        <v>5.36702762886684e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.361315653994264e-10</v>
+        <v>5.361315653994262e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.376115765891958e-10</v>
+        <v>5.376115765891931e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.431395086285715e-10</v>
+        <v>5.431395086285717e-10</v>
       </c>
       <c r="N2" t="n">
         <v>5.345478245758089e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.490957971625161e-10</v>
+        <v>7.490957971625148e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.357706333117885e-10</v>
+        <v>5.357706333117883e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.319785440824078e-10</v>
+        <v>5.319785440824072e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.316195407420498e-10</v>
+        <v>5.316195407420491e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.345304716775919e-10</v>
+        <v>5.345304716775908e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.329108159666513e-10</v>
+        <v>5.329108159666511e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.467668959620222e-10</v>
+        <v>7.467668959620243e-10</v>
       </c>
       <c r="V2" t="n">
         <v>5.315424383657975e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.705062151077211e-10</v>
+        <v>7.705062151077198e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.357584932166962e-10</v>
+        <v>5.357584932166963e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.339653141508655e-10</v>
+        <v>5.339653141508657e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.880835201327262e-10</v>
+        <v>7.880835201327248e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.327923579611735e-10</v>
+        <v>5.327923579611732e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.396417271999471e-10</v>
+        <v>5.39641727199947e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7554,82 +7554,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.716024513100331e-10</v>
+        <v>4.716024513100305e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.757687261591968e-10</v>
+        <v>4.757687261591963e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.720116541262285e-10</v>
+        <v>4.720116541262261e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.580533353129604e-10</v>
+        <v>4.580533353129611e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.592429032125466e-10</v>
+        <v>4.592429032125456e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.23420528202564e-10</v>
+        <v>5.234205282025641e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.571974412047842e-10</v>
+        <v>4.571974412047856e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.715483318820409e-10</v>
+        <v>4.715483318820394e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.947253566985525e-10</v>
+        <v>4.947253566985516e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.907813017920412e-10</v>
+        <v>4.907813017920402e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.012896051886846e-10</v>
+        <v>5.012896051886841e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.496245684949395e-10</v>
+        <v>5.496245684949404e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.796082726115648e-10</v>
+        <v>4.796082726115635e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.233150175604032e-10</v>
+        <v>8.233150175603978e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.880652131742359e-10</v>
+        <v>4.880652131742335e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.612405120471827e-10</v>
+        <v>4.612405120471824e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.587860242728227e-10</v>
+        <v>4.587860242728215e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.791861281667765e-10</v>
+        <v>4.791861281667741e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.679842708610894e-10</v>
+        <v>4.679842708610885e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.464102132574698e-10</v>
+        <v>8.464102132574688e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.578859806994392e-10</v>
+        <v>4.578859806994386e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.690231888129535e-10</v>
+        <v>8.690231888129554e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.883108330461534e-10</v>
+        <v>4.883108330461533e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.753907910723767e-10</v>
+        <v>4.753907910723751e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.920500116207585e-10</v>
+        <v>8.920500116207567e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.670249622093361e-10</v>
+        <v>4.670249622093347e-10</v>
       </c>
       <c r="AB3" t="n">
         <v>5.168719701520228e-10</v>
@@ -7642,64 +7642,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.008708776263595e-10</v>
+        <v>5.0087087762636e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.669053200687497e-10</v>
+        <v>4.669053200687493e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.010442158568386e-10</v>
+        <v>5.01044215856838e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.802810651936027e-10</v>
+        <v>4.802810651936029e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.808517500351936e-10</v>
+        <v>4.80851750035193e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.833089550142111e-10</v>
+        <v>5.833089550142117e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.775252377280831e-10</v>
+        <v>4.775252377280833e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.002840909343503e-10</v>
+        <v>5.002840909343499e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.374397100683004e-10</v>
+        <v>5.374397100682976e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.310629182098654e-10</v>
+        <v>5.310629182098648e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.477803254370664e-10</v>
+        <v>5.477803254370653e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.263674585805612e-10</v>
+        <v>6.263674585805607e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>5.131738370503294e-10</v>
+        <v>5.131738370503292e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.921263009169851e-10</v>
+        <v>4.921263009169832e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.269860242430297e-10</v>
+        <v>5.269860242430283e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.841526319499463e-10</v>
+        <v>4.841526319499465e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.800975240709058e-10</v>
+        <v>4.800975240709056e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.129778280822335e-10</v>
+        <v>5.129778280822372e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.946830717487314e-10</v>
+        <v>4.946830717487304e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.446889452569056e-10</v>
+        <v>5.446889452569062e-10</v>
       </c>
       <c r="V4" t="n">
         <v>4.789419752444453e-10</v>
@@ -7708,19 +7708,19 @@
         <v>5.131319263692051e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.26848896284242e-10</v>
+        <v>5.268488962842461e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.047507916380425e-10</v>
+        <v>5.04750791638043e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.011362963442979e-10</v>
+        <v>5.01136296344297e-10</v>
       </c>
       <c r="AA4" t="n">
         <v>4.933450340834821e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.715575455379995e-10</v>
+        <v>5.71557545537999e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.863143511834706e-09</v>
+        <v>1.863143511834705e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.348732336008479e-09</v>
+        <v>1.348732336008477e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.033088041270992e-09</v>
+        <v>2.033088041270969e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.17383448072327e-09</v>
+        <v>1.173834480723293e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.645664030887744e-09</v>
+        <v>1.64566403088774e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.27142429398995e-09</v>
+        <v>3.271424293989935e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.614132945968579e-09</v>
+        <v>1.614132945968576e-09</v>
       </c>
       <c r="I5" t="n">
         <v>2.028150011879073e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.538890766886961e-09</v>
+        <v>2.538890766886957e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.490724648368431e-09</v>
+        <v>2.490724648368425e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.776444176440306e-09</v>
+        <v>2.776444176440291e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.323019777362161e-09</v>
+        <v>4.323019777362137e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.72603197373314e-09</v>
+        <v>2.726031973733132e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.70409226877709e-09</v>
+        <v>1.704092268777076e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.335723133108896e-09</v>
+        <v>2.335723133108857e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.659103508670984e-09</v>
+        <v>1.659103508670982e-09</v>
       </c>
       <c r="R5" t="n">
         <v>1.642348070589036e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.055291018883857e-09</v>
+        <v>2.055291018883849e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.908314647513957e-09</v>
+        <v>1.90831464751395e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.759390404134219e-09</v>
+        <v>2.759390404134225e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.431076558323903e-09</v>
+        <v>1.431076558323901e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.192264242385452e-09</v>
+        <v>2.192264242385454e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.517919889305811e-09</v>
+        <v>2.517919889305847e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.067075142445168e-09</v>
+        <v>2.067075142445152e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.87575153740936e-09</v>
+        <v>1.875751537409357e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.819687236032531e-09</v>
+        <v>1.819687236032533e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.578385217416369e-09</v>
+        <v>3.578385217416366e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.464053235874324e-10</v>
+        <v>9.464053235874297e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.609777211275996e-10</v>
+        <v>5.609777211275978e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.465786618179117e-10</v>
+        <v>9.465786618179098e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>9.258155111546751e-10</v>
+        <v>9.258155111546716e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>9.263861959962644e-10</v>
+        <v>9.26386195996262e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>6.773813560730639e-10</v>
+        <v>6.773813560730613e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.230596836891547e-10</v>
+        <v>9.230596836891527e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.943564919932015e-10</v>
+        <v>5.943564919931991e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.829741560293721e-10</v>
+        <v>6.315121111271486e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>6.251353192687155e-10</v>
+        <v>6.251353192687138e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.418527264959157e-10</v>
+        <v>9.933147713981339e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.071901904541632e-09</v>
+        <v>1.07190190454163e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.073535533216623e-10</v>
+        <v>6.073535533216628e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.863060171883156e-10</v>
+        <v>5.863060171883191e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.716344998502496e-10</v>
+        <v>9.716344998502461e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.782250330087977e-10</v>
+        <v>9.296870779110156e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>9.256319700319783e-10</v>
+        <v>9.256319700319762e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>9.585122740433068e-10</v>
+        <v>9.585122740433066e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>9.402175177098037e-10</v>
+        <v>5.887554728075807e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.920667134124928e-10</v>
+        <v>9.920667134124907e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.73014376303295e-10</v>
+        <v>9.244764212055168e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.174472749073901e-10</v>
+        <v>6.174472749073909e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>9.723833422453147e-10</v>
+        <v>6.209212973430926e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.092498278870215e-10</v>
+        <v>6.09249827887023e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.952086974031479e-10</v>
+        <v>5.952086974031477e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.388794800445548e-10</v>
+        <v>9.388794800445508e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.661808093290176e-10</v>
+        <v>6.661808093290175e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7918,73 +7918,73 @@
         <v>1.314517852635589e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.315088537477179e-09</v>
+        <v>1.315088537477178e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.417545742456199e-09</v>
+        <v>1.417545742456198e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.311762025170071e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.334520878376335e-09</v>
+        <v>1.334520878376334e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.371676497510287e-09</v>
+        <v>1.371676497510289e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.365299705651852e-09</v>
+        <v>1.36529970565185e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.382017112879056e-09</v>
+        <v>1.382017112879053e-09</v>
       </c>
       <c r="M7" t="n">
         <v>1.460604246022548e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.347410624492316e-09</v>
+        <v>1.347410624492315e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.326330803147518e-09</v>
+        <v>1.32633080314752e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361190526473566e-09</v>
+        <v>1.361190526473558e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.318389419391935e-09</v>
+        <v>1.318389419391934e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.314334311512893e-09</v>
+        <v>1.314334311512892e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.347214615524222e-09</v>
+        <v>1.347214615524223e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.328919859190716e-09</v>
+        <v>1.328919859190719e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.380765793559039e-09</v>
+        <v>1.38076579355904e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.313178762686431e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.347368713811192e-09</v>
+        <v>1.347368713811193e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.361085683726227e-09</v>
+        <v>1.361085683726231e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.340830901274543e-09</v>
+        <v>1.340830901274541e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.335373083786286e-09</v>
+        <v>1.335373083786285e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.32758182152547e-09</v>
+        <v>1.327581821525471e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.405794332979987e-09</v>
+        <v>1.405794332979986e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7994,25 +7994,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.283162698179866e-09</v>
+        <v>1.283162698179865e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.816261091595189e-09</v>
+        <v>1.816261091595192e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.850399987383281e-09</v>
+        <v>1.850399987383279e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.829636836720044e-09</v>
+        <v>1.527692010151294e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.351485506743464e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.932664726540653e-09</v>
+        <v>2.050249130858845e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.826881009254526e-09</v>
+        <v>1.826881009254525e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.849639862460792e-09</v>
@@ -8021,58 +8021,58 @@
         <v>1.88679548159474e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.880418689736307e-09</v>
+        <v>1.880418689736309e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.897136096963507e-09</v>
+        <v>1.897136096963508e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.975723230107003e-09</v>
+        <v>1.975723230107e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.422960178861061e-09</v>
+        <v>1.42296017886106e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.522710138772995e-09</v>
+        <v>1.522710138772993e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.527959476937099e-09</v>
+        <v>1.527959476937097e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.155003443513438e-09</v>
+        <v>1.155003443513437e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.829453295597349e-09</v>
+        <v>1.829453295597347e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.862333599608679e-09</v>
+        <v>1.862333599608676e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.844038843275173e-09</v>
+        <v>1.844038843275172e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.546967529852765e-09</v>
+        <v>1.619134185865732e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.828297746770887e-09</v>
+        <v>1.673335427619201e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.862599142290227e-09</v>
+        <v>1.862599142290226e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.249672245776527e-09</v>
+        <v>1.249672245776526e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.419807143246142e-09</v>
+        <v>2.419807143246137e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.850492067870739e-09</v>
+        <v>1.272894612870951e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.842700805609923e-09</v>
+        <v>1.842700805609926e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.513259031045791e-09</v>
+        <v>2.513259031045786e-09</v>
       </c>
     </row>
     <row r="9">
@@ -8085,49 +8085,49 @@
         <v>1.091936668826262e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.251902974381682e-09</v>
+        <v>1.251902974381683e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.286041870169773e-09</v>
+        <v>1.286041870169769e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.265278719506535e-09</v>
+        <v>1.220520197712108e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.265849404348127e-09</v>
+        <v>8.187832573395913e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.368306609327148e-09</v>
+        <v>1.368306818866318e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.262522892041017e-09</v>
+        <v>1.26252289204102e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.285281745247284e-09</v>
+        <v>1.285281745247282e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.322437364381233e-09</v>
+        <v>1.322437364381234e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.316060572522799e-09</v>
+        <v>1.3160605725228e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.332777979749999e-09</v>
+        <v>1.33277797975e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.411365112893495e-09</v>
+        <v>1.41136511289349e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.298171491363264e-09</v>
+        <v>1.298171491363265e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.341392999713735e-09</v>
+        <v>1.341392999713732e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.390230091972694e-09</v>
+        <v>1.390230091972689e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.26915049580205e-09</v>
+        <v>1.269150495802051e-09</v>
       </c>
       <c r="R9" t="n">
         <v>1.265095178383839e-09</v>
@@ -8136,31 +8136,31 @@
         <v>1.297975482395168e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.279680726061664e-09</v>
+        <v>1.279680726061665e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.331529921764353e-09</v>
+        <v>1.331529921764352e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.263939629557379e-09</v>
+        <v>1.487732875049678e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.298129580682139e-09</v>
+        <v>1.298129580682138e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.311846550597175e-09</v>
+        <v>1.311846550597178e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.291591768145491e-09</v>
+        <v>1.291591768145498e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.286133950657231e-09</v>
+        <v>1.1692103654999e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.278342688396418e-09</v>
+        <v>1.278342688396417e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.356555199850935e-09</v>
+        <v>1.356555199850936e-09</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.212615794336067e-10</v>
+        <v>5.212615794336085e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.357932067048121e-10</v>
+        <v>5.357932067048118e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.223335161525052e-10</v>
+        <v>5.223335161525072e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.208479907678764e-10</v>
+        <v>5.208479907678783e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.215394331902215e-10</v>
+        <v>5.215394331902234e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.282333208587655e-10</v>
+        <v>5.282333208587673e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2090744118362e-10</v>
+        <v>5.209074411836202e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.220594365288337e-10</v>
+        <v>5.220594365288351e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.239080166163905e-10</v>
+        <v>5.239080166163922e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.227466408088799e-10</v>
+        <v>5.227466408088816e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.238587819927193e-10</v>
+        <v>5.238587819927209e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.217277489153613e-10</v>
+        <v>5.217277489153612e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.208926794662456e-10</v>
+        <v>5.208926794662476e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.223217844712434e-10</v>
+        <v>7.223217844712425e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.231435262050626e-10</v>
+        <v>5.231435262050622e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.222318411082255e-10</v>
+        <v>5.222318411082266e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.219449313973622e-10</v>
+        <v>5.219449313973648e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.220319598179174e-10</v>
+        <v>5.220319598179194e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.209835085945431e-10</v>
+        <v>5.209835085945435e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.169275456950499e-10</v>
+        <v>7.169275456950514e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.213256635824659e-10</v>
+        <v>5.213256635824683e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.445092630355652e-10</v>
+        <v>7.445092630355654e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.246720786046989e-10</v>
+        <v>5.246720786047016e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.265890728923794e-10</v>
+        <v>5.265890728923811e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.69948345294149e-10</v>
+        <v>7.699483452941495e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.215992393364594e-10</v>
+        <v>5.215992393364619e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.273713071259451e-10</v>
+        <v>5.273713071259429e-10</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.485432574368588e-10</v>
+        <v>4.485432574368551e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.70874863324745e-10</v>
+        <v>4.708748633247439e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.563697499074797e-10</v>
+        <v>4.563697499074792e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.449828570626747e-10</v>
+        <v>4.449828570626754e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.507190356730959e-10</v>
+        <v>4.507190356730977e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.979377242340375e-10</v>
+        <v>4.979377242340376e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.462724132683802e-10</v>
+        <v>4.462724132683806e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.544535364313723e-10</v>
+        <v>4.544535364313743e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.673550440860847e-10</v>
+        <v>4.673550440860852e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.592196502441569e-10</v>
+        <v>4.592196502441592e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.670354067355526e-10</v>
+        <v>4.670354067355558e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.613660514565801e-10</v>
+        <v>4.613660514565796e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.460383185736127e-10</v>
+        <v>4.460383185736123e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.767086175055609e-10</v>
+        <v>7.767086175055599e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.618972528482212e-10</v>
+        <v>4.618972528482205e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.555198024861211e-10</v>
+        <v>4.555198024861247e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.536648816931256e-10</v>
+        <v>4.536648816931281e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.53998740290503e-10</v>
+        <v>4.539987402905039e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.467353597081714e-10</v>
+        <v>4.467353597081686e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.76043420823589e-10</v>
+        <v>7.760434208235913e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.488839976333643e-10</v>
+        <v>4.48883997633364e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.342556008380334e-10</v>
+        <v>8.342556008380379e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.730257723130869e-10</v>
+        <v>4.730257723130881e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.866580532198903e-10</v>
+        <v>4.866580532198919e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.611910516202525e-10</v>
+        <v>8.611910516202526e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.510568144412254e-10</v>
+        <v>4.510568144412267e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.930807432028026e-10</v>
+        <v>4.930807432027996e-10</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.57861768021284e-10</v>
+        <v>4.578617680212838e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.544996146086503e-10</v>
+        <v>4.544996146086482e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.699697863764951e-10</v>
+        <v>4.699697863764938e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.53190093781676e-10</v>
+        <v>4.531900937816743e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.610002540212983e-10</v>
+        <v>4.610002540212962e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.366107945779609e-10</v>
+        <v>5.366107945779568e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.538616135760427e-10</v>
+        <v>4.538616135760414e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.668739309442573e-10</v>
+        <v>4.668739309442575e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.876878694158937e-10</v>
+        <v>4.876878694158931e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.746362194169742e-10</v>
+        <v>4.746362194169721e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.871983656986574e-10</v>
+        <v>4.871983656986548e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.803218199908436e-10</v>
+        <v>4.803218199908418e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.536948731875701e-10</v>
+        <v>4.536948731875702e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.501521132466037e-10</v>
+        <v>4.501521132466011e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.791192225431622e-10</v>
+        <v>4.791192225431632e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.688213199785113e-10</v>
+        <v>4.688213199785099e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.655805428093404e-10</v>
+        <v>4.655805428093387e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.665635688545575e-10</v>
+        <v>4.665635688545576e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.547208299751577e-10</v>
+        <v>4.547208299751569e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.64803041432833e-10</v>
+        <v>4.648030414328328e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.583586412906577e-10</v>
+        <v>4.583586412906576e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.930664969368011e-10</v>
+        <v>4.930664969368014e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.963849250659009e-10</v>
+        <v>4.963849250658992e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.166887144418833e-10</v>
+        <v>5.16688714441883e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.623592622526154e-10</v>
+        <v>4.623592622526135e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.616757919552425e-10</v>
+        <v>4.616757919552428e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.277771181707412e-10</v>
+        <v>5.277771181707414e-10</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.362458828253521e-09</v>
+        <v>1.362458828253519e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.380393776378875e-09</v>
+        <v>1.380393776378871e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.667830476886112e-09</v>
+        <v>1.66783047688611e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>9.644423436437415e-10</v>
+        <v>9.644423436437408e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.517841492566948e-09</v>
+        <v>1.517841492566949e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.567046464095735e-09</v>
+        <v>2.567046464095705e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.424716096785836e-09</v>
+        <v>1.424716096785833e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.633755678132257e-09</v>
+        <v>1.633755678132255e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.851726170286075e-09</v>
+        <v>1.851726170286066e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.699271792001389e-09</v>
+        <v>1.69927179200139e-09</v>
       </c>
       <c r="L5" t="n">
         <v>1.858411745495758e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.839315773178087e-09</v>
+        <v>1.839315773178084e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.509450201225082e-09</v>
+        <v>1.509450201225083e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23821351035432e-09</v>
+        <v>1.238213510354319e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.698242361815282e-09</v>
+        <v>1.698242361815284e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.583109071926192e-09</v>
+        <v>1.583109071926191e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.625687775035353e-09</v>
+        <v>1.625687775035351e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.49420506434107e-09</v>
+        <v>1.494205064341071e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.398480453128762e-09</v>
+        <v>1.398480453128758e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.521907912434652e-09</v>
+        <v>1.521907912434651e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.314593144976652e-09</v>
+        <v>1.314593144976654e-09</v>
       </c>
       <c r="W5" t="n">
         <v>2.037831749909338e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.117191402918293e-09</v>
+        <v>2.117191402918291e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.474564519276233e-09</v>
+        <v>2.474564519276231e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.421411560266837e-09</v>
+        <v>1.421411560266835e-09</v>
       </c>
       <c r="AA5" t="n">
         <v>1.483636053952253e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.827743998830864e-09</v>
+        <v>2.827743998830862e-09</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.699761746872821e-10</v>
+        <v>5.462317034971636e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.666140212746463e-10</v>
+        <v>8.666140212746423e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.58339721852377e-10</v>
+        <v>5.583397218523736e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.41560029257557e-10</v>
+        <v>8.653045004476691e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.493701894971766e-10</v>
+        <v>8.731146606872933e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.487252012439581e-10</v>
+        <v>6.24980730053837e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.422315490519228e-10</v>
+        <v>8.659760202420373e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.552438664201391e-10</v>
+        <v>8.789883376102528e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.998022760818911e-10</v>
+        <v>5.760578048917724e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.630061548928506e-10</v>
+        <v>8.867506260829679e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.993127723646546e-10</v>
+        <v>5.755683011745353e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>5.686917554667246e-10</v>
+        <v>8.924362266568365e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.421313867134238e-10</v>
+        <v>5.421313867134206e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.613822345391953e-10</v>
+        <v>5.385886267724518e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.570609097830561e-10</v>
+        <v>5.570609097830509e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.571912554543938e-10</v>
+        <v>8.809357266445056e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.77694949475339e-10</v>
+        <v>8.776949494753345e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.549335043304406e-10</v>
+        <v>5.549335043304379e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.430907654510401e-10</v>
+        <v>5.430907654510368e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>8.782669910631386e-10</v>
+        <v>5.545225198730195e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>8.704730479566542e-10</v>
+        <v>8.704730479566521e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.909020430686476e-10</v>
+        <v>5.909020430686483e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>9.084993317318995e-10</v>
+        <v>5.847548605417799e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.143278156530076e-10</v>
+        <v>6.143278156530064e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.507291977284974e-10</v>
+        <v>5.507291977284948e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.737901986212408e-10</v>
+        <v>8.737901986212377e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.165681044360644e-10</v>
+        <v>6.165681044360669e-10</v>
       </c>
     </row>
     <row r="7">
@@ -8766,58 +8766,58 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.22359422575951e-09</v>
+        <v>1.223594225759509e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.220232072346875e-09</v>
+        <v>1.220232072346873e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.23570224411472e-09</v>
+        <v>1.235702244114719e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.218922551519901e-09</v>
+        <v>1.2189225515199e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.226732711759523e-09</v>
+        <v>1.226732711759522e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.302343252316186e-09</v>
+        <v>1.302343252316181e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.219594071314266e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.232606388682481e-09</v>
+        <v>1.232606388682482e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.25342032715412e-09</v>
+        <v>1.253420327154119e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.240368677155196e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.252930823436881e-09</v>
+        <v>1.25293082343688e-09</v>
       </c>
       <c r="M7" t="n">
         <v>1.246054277729067e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.219427330925796e-09</v>
+        <v>1.219427330925795e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.215854612148043e-09</v>
+        <v>1.215854612148041e-09</v>
       </c>
       <c r="P7" t="n">
         <v>1.244821721444602e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.234553777716736e-09</v>
+        <v>1.234553777716734e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.231313000547566e-09</v>
+        <v>1.231313000547565e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.232296026592782e-09</v>
+        <v>1.232296026592783e-09</v>
       </c>
       <c r="T7" t="n">
         <v>1.220453287713382e-09</v>
@@ -8826,25 +8826,25 @@
         <v>1.231971942598961e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.224091099028881e-09</v>
+        <v>1.224091099028882e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.258798954675028e-09</v>
+        <v>1.258798954675026e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.262117382804128e-09</v>
+        <v>1.262117382804125e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.283770715144416e-09</v>
+        <v>1.283770715144415e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.228091719990839e-09</v>
+        <v>1.228091719990838e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.227408249693466e-09</v>
+        <v>1.227408249693468e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.293509575908967e-09</v>
+        <v>1.293509575908966e-09</v>
       </c>
     </row>
     <row r="8">
@@ -8857,82 +8857,82 @@
         <v>1.162110065663492e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.66948391235713e-09</v>
+        <v>1.669483912357129e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.684954084124977e-09</v>
+        <v>1.684954084124976e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.668174391530158e-09</v>
+        <v>1.396222537228995e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.244815251390907e-09</v>
+        <v>1.244815251390906e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75159509232644e-09</v>
+        <v>1.85749952908932e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.668845911324523e-09</v>
+        <v>1.668845911324524e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.68185822869274e-09</v>
+        <v>1.681858228692738e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.702672167164375e-09</v>
+        <v>1.702672167164373e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.689620517165454e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.702182663447137e-09</v>
+        <v>1.702182663447135e-09</v>
       </c>
       <c r="M8" t="n">
         <v>1.695306117739325e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.272773326600713e-09</v>
+        <v>1.272773326600712e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.378028930313463e-09</v>
+        <v>1.378028930313464e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.380326931737438e-09</v>
+        <v>1.380326931737434e-09</v>
       </c>
       <c r="Q8" t="n">
         <v>1.072698336601014e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.680564840557825e-09</v>
+        <v>1.680564840557822e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.681547866603042e-09</v>
+        <v>1.681547866603038e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.669705127723639e-09</v>
+        <v>1.669705127723638e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.366941578120543e-09</v>
+        <v>1.431944020342524e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.673342939039138e-09</v>
+        <v>1.533850977722278e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.708151169015053e-09</v>
+        <v>1.708151169015052e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.14707191098967e-09</v>
+        <v>1.147071910989669e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.240990662072973e-09</v>
+        <v>2.240990662072976e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.677343560001099e-09</v>
+        <v>1.157120376474845e-09</v>
       </c>
       <c r="AA8" t="n">
         <v>1.676660089703724e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.276267875145823e-09</v>
+        <v>2.27626787514582e-09</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.671446336635699e-10</v>
+        <v>9.671446336635688e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.13216324839381e-09</v>
+        <v>1.132163248393807e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.147633420161656e-09</v>
+        <v>1.147633420161653e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.130853727566836e-09</v>
+        <v>1.091992296727993e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.138663887806456e-09</v>
+        <v>7.504999840894231e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.214274428363118e-09</v>
+        <v>1.214274641097141e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.131525247361204e-09</v>
+        <v>1.1315252473612e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.144537564729416e-09</v>
+        <v>1.144537564729414e-09</v>
       </c>
       <c r="J9" t="n">
         <v>1.165351503201052e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.152299853202131e-09</v>
+        <v>1.15229985320213e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.164861999483817e-09</v>
+        <v>1.164861999483814e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.157985453776004e-09</v>
+        <v>1.157985453776001e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.131358506972731e-09</v>
+        <v>1.131358506972728e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.183617196352387e-09</v>
+        <v>1.183617196352388e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.224720117218511e-09</v>
+        <v>1.224720117218512e-09</v>
       </c>
       <c r="Q9" t="n">
         <v>1.146485166497695e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.143244176594503e-09</v>
+        <v>1.143244176594498e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.144227202639719e-09</v>
+        <v>1.144227202639717e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.132384463760318e-09</v>
+        <v>1.132384463760316e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.143816218182302e-09</v>
+        <v>1.143816218182299e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.136022275075817e-09</v>
+        <v>1.330330158069539e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.170730130721962e-09</v>
+        <v>1.17073013072196e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.174048558851059e-09</v>
+        <v>1.174048558851057e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.195701891191349e-09</v>
+        <v>1.19570189119135e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.140022896037776e-09</v>
+        <v>1.038504350324071e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.139339425740402e-09</v>
+        <v>1.139339425740401e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.205440751955904e-09</v>
+        <v>1.205440751955901e-09</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.613349700210207e-10</v>
+        <v>5.463350399950662e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.740547859108369e-10</v>
+        <v>5.566409182810974e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.592699107678349e-10</v>
+        <v>5.437747928212817e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.572896410616019e-10</v>
+        <v>5.413850846182864e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.576344934873343e-10</v>
+        <v>5.419965723545119e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.663589763499617e-10</v>
+        <v>5.469774847293357e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.585320443771974e-10</v>
+        <v>5.417742460407256e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.608086191728502e-10</v>
+        <v>5.442570036359376e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.623701150925656e-10</v>
+        <v>5.454049694833294e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.639961089046272e-10</v>
+        <v>5.47875269366498e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.633955050302213e-10</v>
+        <v>5.495618211097335e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.693617128577818e-10</v>
+        <v>5.508167853264101e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.604859909317103e-10</v>
+        <v>5.446978530106121e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>8.165769754938365e-10</v>
+        <v>7.794812284623043e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.611975159367813e-10</v>
+        <v>5.440006820984992e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.570199997710181e-10</v>
+        <v>5.414039406885866e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.578020384773831e-10</v>
+        <v>5.414918486672363e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.617947285646157e-10</v>
+        <v>5.446232639314269e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.600592791692699e-10</v>
+        <v>5.430159990910536e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>8.176549333916943e-10</v>
+        <v>7.833122721035108e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.57764058040638e-10</v>
+        <v>5.425933292949138e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>8.432500406669495e-10</v>
+        <v>8.05901524709959e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.591710041042644e-10</v>
+        <v>5.433583777265464e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.59510258702335e-10</v>
+        <v>5.441964549356359e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.323324811177276e-10</v>
+        <v>8.084158133055745e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.578537261707359e-10</v>
+        <v>5.41878994853187e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.662568946155281e-10</v>
+        <v>5.578555737762103e-10</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.135982813195138e-10</v>
+        <v>5.039254990513439e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.027995777477841e-10</v>
+        <v>4.85996076865679e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.992530583142647e-10</v>
+        <v>4.860577024389669e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.842532666650701e-10</v>
+        <v>4.681387067931344e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.876152145475701e-10</v>
+        <v>4.73395094261016e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.494356637263537e-10</v>
+        <v>5.085753031214825e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.94105869189867e-10</v>
+        <v>4.718474892095622e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.103129530473956e-10</v>
+        <v>4.895488937338291e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.211232285787818e-10</v>
+        <v>4.974574519610227e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.330448286007604e-10</v>
+        <v>5.153725553452698e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.285177053721915e-10</v>
+        <v>5.271796557493943e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.805923638251042e-10</v>
+        <v>5.456463229842169e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.078564080485425e-10</v>
+        <v>4.925678703795427e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>9.30620179219721e-10</v>
+        <v>8.71924039275439e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.126441833592342e-10</v>
+        <v>4.873443566215607e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.831064387997287e-10</v>
+        <v>4.690468960942268e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.888094326821417e-10</v>
+        <v>4.697698395169668e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.169656220646836e-10</v>
+        <v>4.918366515723401e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.049178675572454e-10</v>
+        <v>4.806370041668763e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.658914563692716e-10</v>
+        <v>9.240486037601669e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.881168688202328e-10</v>
+        <v>4.772296199229701e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.754073353409978e-10</v>
+        <v>9.24711702221403e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.985125106458829e-10</v>
+        <v>4.830461821189937e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.008388101053336e-10</v>
+        <v>4.889387831829121e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.518999171576013e-10</v>
+        <v>9.233379269836608e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.890106159209452e-10</v>
+        <v>4.723913764442237e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.49971433265541e-10</v>
+        <v>5.869615553295345e-10</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.699025232441802e-10</v>
+        <v>5.278539630987049e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>5.041405711618764e-10</v>
+        <v>4.556029312365732e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.465767290052446e-10</v>
+        <v>4.989347934989025e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>5.242086717042492e-10</v>
+        <v>4.719419400259566e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.281039384928749e-10</v>
+        <v>4.788489753049216e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>6.266509858866375e-10</v>
+        <v>5.351106719114338e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>5.382421886877004e-10</v>
+        <v>4.763376973155262e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.63957148280704e-10</v>
+        <v>5.043815864783575e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.815353769526525e-10</v>
+        <v>5.173000419988158e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.999613111188696e-10</v>
+        <v>5.452515623895238e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.93177214066033e-10</v>
+        <v>5.643019401814586e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.770393742927489e-10</v>
+        <v>5.951278492036231e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>5.603129138807164e-10</v>
+        <v>2.513277329215015e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.610855848496021e-10</v>
+        <v>4.930299884108517e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.683499161307004e-10</v>
+        <v>5.014863167992645e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.211629492859923e-10</v>
+        <v>4.721549280142036e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>5.299964362299809e-10</v>
+        <v>4.731478890727428e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.750957074934322e-10</v>
+        <v>5.085186650039876e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.554930082268372e-10</v>
+        <v>4.903638692536289e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>6.268085535596489e-10</v>
+        <v>5.849051698081356e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>5.293874616009701e-10</v>
+        <v>4.854865348122859e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.620935803962575e-10</v>
+        <v>5.115111492096298e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.454595327408874e-10</v>
+        <v>4.942311934434479e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.472985214294114e-10</v>
+        <v>5.023658279055335e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.511035367806104e-10</v>
+        <v>5.004292380824816e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.305802725038917e-10</v>
+        <v>4.775208833391105e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.262440678145128e-10</v>
+        <v>6.574072979529895e-10</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.641250920723609e-09</v>
+        <v>2.69129623603007e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.496194853585184e-09</v>
+        <v>1.421779736162714e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.40522255812696e-09</v>
+        <v>2.349528101263999e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.439769197337011e-09</v>
+        <v>1.292711840886585e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>2.053553525554585e-09</v>
+        <v>1.962065067111062e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.772630656148395e-09</v>
+        <v>2.875851870210899e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.308110512036573e-09</v>
+        <v>1.934761487268682e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.80161946144451e-09</v>
+        <v>2.488711582602199e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.958116631022841e-09</v>
+        <v>2.58067567571185e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>3.516325620212423e-09</v>
+        <v>3.311696676376759e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.236717802681846e-09</v>
+        <v>3.558687250907498e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.249119737029969e-09</v>
+        <v>4.454857823689363e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.827930855888186e-09</v>
+        <v>2.513277329215015e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>2.452257906244126e-09</v>
+        <v>2.02720925174244e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.625983869387314e-09</v>
+        <v>2.207432314895757e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.840610426477336e-09</v>
+        <v>1.756797377524902e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>2.090737879940875e-09</v>
+        <v>1.833577527877228e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.796957096856844e-09</v>
+        <v>2.378110820512817e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>2.603230381408487e-09</v>
+        <v>2.173867464006194e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>3.896419543628639e-09</v>
+        <v>3.941546644881726e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.831402864690696e-09</v>
+        <v>1.845367915879351e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.632306757683515e-09</v>
+        <v>2.517990060444773e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.362132859807822e-09</v>
+        <v>2.23130413640702e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.382851976302405e-09</v>
+        <v>2.369161511032239e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.323047480373702e-09</v>
+        <v>2.210767804694137e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.002814078555703e-09</v>
+        <v>1.837513173851547e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.274945763657348e-09</v>
+        <v>5.9698153636282e-09</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.051029512923992e-09</v>
+        <v>6.286053064078741e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>9.852675608416878e-10</v>
+        <v>9.348824884006454e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>6.401324273305838e-10</v>
+        <v>9.782143506629735e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>6.177643700295878e-10</v>
+        <v>9.512214971900305e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.009230928172687e-09</v>
+        <v>5.796003186140914e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.107777975566449e-09</v>
+        <v>1.014390229075508e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.019369178367513e-09</v>
+        <v>9.556172544796012e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>6.575128466060424e-10</v>
+        <v>6.051329297875246e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.062662366632465e-09</v>
+        <v>6.180513853079852e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>6.935170094442086e-10</v>
+        <v>1.024531119553598e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>6.867329123913716e-10</v>
+        <v>1.043581497345531e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>7.705950726180884e-10</v>
+        <v>1.074407406367704e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.540769678348261e-10</v>
+        <v>2.513277329215015e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.040635531789049e-09</v>
+        <v>5.940246048475644e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>1.047899689516202e-09</v>
+        <v>9.780336611064409e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.147186476113313e-10</v>
+        <v>9.514344851782772e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>6.235521345553191e-10</v>
+        <v>9.524274462368165e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>1.056222697173244e-09</v>
+        <v>6.092700083131551e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>6.490487065521755e-10</v>
+        <v>5.911152125627971e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>7.223572999465105e-10</v>
+        <v>6.869883462664456e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>1.010514451280781e-09</v>
+        <v>9.647660919763598e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>1.041643425384156e-09</v>
+        <v>9.880585587546732e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>1.026586522420701e-09</v>
+        <v>9.735107506075219e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.524511034572702e-10</v>
+        <v>6.140147808017167e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.446592351059496e-10</v>
+        <v>6.011805813916512e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.241359708292297e-10</v>
+        <v>9.568004405031842e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.204534038871049e-10</v>
+        <v>7.593388326474463e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.506774193080484e-09</v>
+        <v>1.437131800305525e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.441012240998181e-09</v>
+        <v>1.36488076844339e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.483448398841548e-09</v>
+        <v>1.408212630705725e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.461080341540554e-09</v>
+        <v>1.381219777232775e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.464975608329179e-09</v>
+        <v>1.38812681251174e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.563522655722942e-09</v>
+        <v>1.444388509118252e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.475113858524004e-09</v>
+        <v>1.385615534522345e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.500828818117007e-09</v>
+        <v>1.413659423685175e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.518407046788956e-09</v>
+        <v>1.426577879205633e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.536832980955173e-09</v>
+        <v>1.454529399596343e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.530048883902336e-09</v>
+        <v>1.473579777388279e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.613911044129054e-09</v>
+        <v>1.504405686410443e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.497184583717021e-09</v>
+        <v>2.513277329215015e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.497922212292818e-09</v>
+        <v>1.402273097932817e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.505186543573918e-09</v>
+        <v>1.410729426321227e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.458034619122297e-09</v>
+        <v>1.381432765221022e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.466868106066285e-09</v>
+        <v>1.382425726279564e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.511967377329733e-09</v>
+        <v>1.417796502210806e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.49236467806314e-09</v>
+        <v>1.399641706460448e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.56563318554672e-09</v>
+        <v>1.495464165135048e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.466259131437273e-09</v>
+        <v>1.394764372019103e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.49896525023256e-09</v>
+        <v>1.420788986416448e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.482331202577191e-09</v>
+        <v>1.40350903065027e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48616323932724e-09</v>
+        <v>1.412975498261499e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.487975206616914e-09</v>
+        <v>1.409707075289303e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.467451942340195e-09</v>
+        <v>1.386798720545928e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.563115737650816e-09</v>
+        <v>1.566685135159808e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.484503189640827e-09</v>
+        <v>1.415411597736131e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>2.083927294757946e-09</v>
+        <v>1.984176771714035e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.126363452601315e-09</v>
+        <v>2.02750863397636e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.749803441583705e-09</v>
+        <v>1.659193559670535e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.546332818419017e-09</v>
+        <v>1.466269443108632e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.344368371733991e-09</v>
+        <v>2.196603398508552e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>2.11802891228377e-09</v>
+        <v>2.004911537792989e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.143743871876774e-09</v>
+        <v>2.032955426955823e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.161322100548721e-09</v>
+        <v>2.045873882476282e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.179748034714939e-09</v>
+        <v>2.073825402866986e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.172963937662101e-09</v>
+        <v>2.092875780658924e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.25682609788882e-09</v>
+        <v>2.123701689681094e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.624469159968903e-09</v>
+        <v>2.513277329215015e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.766941563351831e-09</v>
+        <v>1.661260035038454e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.739471866267209e-09</v>
+        <v>1.636244412480984e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.305039373287087e-09</v>
+        <v>1.233738247699306e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>2.109783159826051e-09</v>
+        <v>2.00172172955021e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>2.154882431089501e-09</v>
+        <v>2.037092505481452e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>2.135279731822908e-09</v>
+        <v>2.018937709731091e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.883915980292011e-09</v>
+        <v>1.801927030166309e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.927364494955221e-09</v>
+        <v>1.838847349538308e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>2.142011032208471e-09</v>
+        <v>2.040210967830786e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.390301580687877e-09</v>
+        <v>1.314564922168587e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.790450962691139e-09</v>
+        <v>2.669598182239766e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.453348030649946e-09</v>
+        <v>1.376079667590832e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.110366996099962e-09</v>
+        <v>2.006094723816577e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.900873250197534e-09</v>
+        <v>2.855576166418481e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.282563832459316e-09</v>
+        <v>1.209899623825658e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.450478890638777e-09</v>
+        <v>1.359817565357394e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.492915048482145e-09</v>
+        <v>1.40314942761972e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.416615469569266e-09</v>
+        <v>1.324881058804325e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>9.357526687133786e-10</v>
+        <v>8.709031888745905e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57298953833858e-09</v>
+        <v>1.439325536798189e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4845805081646e-09</v>
+        <v>1.38055233143635e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.510295467757604e-09</v>
+        <v>1.408596220599181e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.527873696429552e-09</v>
+        <v>1.421514676119642e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.54629963059577e-09</v>
+        <v>1.449466196510347e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.539515533542933e-09</v>
+        <v>1.468516574302284e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.623377693769648e-09</v>
+        <v>1.499342483324443e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.506651233357616e-09</v>
+        <v>2.513277329215015e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.584864469736071e-09</v>
+        <v>1.470871436650505e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.60897074466929e-09</v>
+        <v>1.495340283698702e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.467501501737935e-09</v>
+        <v>1.376369792900963e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.476334755706881e-09</v>
+        <v>1.377362523193568e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.521434026970331e-09</v>
+        <v>1.412733299124816e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.501831327703737e-09</v>
+        <v>1.394578503374453e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.575139921098072e-09</v>
+        <v>1.490451637078102e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.745384070114394e-09</v>
+        <v>1.646079437391094e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.508431899873158e-09</v>
+        <v>1.415725783330456e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.491797852217786e-09</v>
+        <v>1.398445827564275e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.495629888967835e-09</v>
+        <v>1.407912295175505e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.356555490952001e-09</v>
+        <v>1.270695828917359e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.47691859198079e-09</v>
+        <v>1.381735517459935e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.572582387291413e-09</v>
+        <v>1.561621932073816e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.078716162412074e-10</v>
+        <v>5.091314136844836e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.211687240009698e-10</v>
+        <v>5.225784815283206e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.087928408272575e-10</v>
+        <v>5.100515504461368e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.07309896400319e-10</v>
+        <v>5.085593698658594e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.083297152456388e-10</v>
+        <v>5.095928088777841e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.087553999117678e-10</v>
+        <v>5.099286458878716e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.081508279186444e-10</v>
+        <v>5.094138956386602e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.087914348102639e-10</v>
+        <v>5.101445541055579e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.086909171612396e-10</v>
+        <v>5.09934703410606e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.087724819173368e-10</v>
+        <v>5.101534284832617e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.085684911292764e-10</v>
+        <v>5.098490894829952e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.069417856584336e-10</v>
+        <v>5.081717217625309e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.076208881650803e-10</v>
+        <v>5.088833085173329e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.95276927360372e-10</v>
+        <v>6.973392357873451e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.073146451140537e-10</v>
+        <v>5.085702209408072e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.080300164234797e-10</v>
+        <v>5.092887926116366e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.093906152785796e-10</v>
+        <v>5.107014094023465e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.083445270468083e-10</v>
+        <v>5.095910268834568e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.076052325828589e-10</v>
+        <v>5.089854427135086e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.911154036877575e-10</v>
+        <v>6.935223347738282e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.085154299076589e-10</v>
+        <v>5.097782667292361e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.212506210322423e-10</v>
+        <v>7.236919018682414e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.115278100490516e-10</v>
+        <v>5.127698571970541e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.119517262246072e-10</v>
+        <v>5.132226518931026e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.517941500394836e-10</v>
+        <v>7.533538920223219e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.088405885176232e-10</v>
+        <v>5.1012149784431e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.094903930024877e-10</v>
+        <v>5.108386095086277e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.368712525671232e-10</v>
+        <v>4.381430842107281e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.56580108022842e-10</v>
+        <v>4.580921150632367e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.436054979478165e-10</v>
+        <v>4.448702123318799e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.322606287256136e-10</v>
+        <v>4.334607980500482e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.403380762024074e-10</v>
+        <v>4.416340130050556e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.43147793662295e-10</v>
+        <v>4.438063779753066e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.391359248176233e-10</v>
+        <v>4.404318748263574e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.436413825438804e-10</v>
+        <v>4.455809442524184e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.427594944402794e-10</v>
+        <v>4.439185341604759e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.433983729935891e-10</v>
+        <v>4.455316317522803e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.418790371623942e-10</v>
+        <v>4.432990876924551e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.39750041918734e-10</v>
+        <v>4.408166320414989e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.352180140580245e-10</v>
+        <v>4.365086991983586e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.417865535694298e-10</v>
+        <v>7.443935797005104e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.329036191227424e-10</v>
+        <v>4.341455260230435e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.381011453232921e-10</v>
+        <v>4.393660439905271e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.479750212221775e-10</v>
+        <v>4.496125916825716e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.402355905794111e-10</v>
+        <v>4.414132163495868e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.351515505661112e-10</v>
+        <v>4.372852020934303e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.442689838927915e-10</v>
+        <v>7.479991410324358e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.413377665834952e-10</v>
+        <v>4.426315121848939e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.27972461921345e-10</v>
+        <v>8.312787538394468e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.630594545770781e-10</v>
+        <v>4.642052333172201e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.661369410074901e-10</v>
+        <v>4.67488313414939e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.42952347445177e-10</v>
+        <v>8.447352235636884e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.439021826229592e-10</v>
+        <v>4.453248096256128e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.495204721693716e-10</v>
+        <v>4.514212695330936e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.379633416541581e-10</v>
+        <v>4.227097106614178e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.33397890729133e-10</v>
+        <v>4.181280627933661e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.483689971378391e-10</v>
+        <v>4.331030786681071e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.316184576474348e-10</v>
+        <v>4.162482125768976e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.431377806451653e-10</v>
+        <v>4.279213816220001e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.479460847737125e-10</v>
+        <v>4.317148151436151e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.411171659945257e-10</v>
+        <v>4.259004742819681e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.483531155291036e-10</v>
+        <v>4.341535977850651e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.471745834399882e-10</v>
+        <v>4.317403693042728e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.481390338847271e-10</v>
+        <v>4.342538379635831e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.45834864093186e-10</v>
+        <v>4.308161889527786e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.445981504144783e-10</v>
+        <v>4.29020310484379e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.346551324682032e-09</v>
+        <v>1.333792638285733e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.287681978512168e-10</v>
+        <v>4.135357866215628e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.316720965535808e-10</v>
+        <v>4.163707804601695e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.397525445806096e-10</v>
+        <v>4.244873780414783e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.551211345553599e-10</v>
+        <v>4.404435345283799e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.433050867530802e-10</v>
+        <v>4.279012531763187e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.349544156905682e-10</v>
+        <v>4.210609013942677e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.470861800930293e-10</v>
+        <v>4.326658362420881e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.451680838149974e-10</v>
+        <v>4.299510920719e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.178210062598688e-10</v>
+        <v>5.027406542560451e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.79261732645974e-10</v>
+        <v>4.638076039026314e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.840264739147825e-10</v>
+        <v>4.68560839150519e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.451794418887834e-10</v>
+        <v>4.29958545271572e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.489083292655498e-10</v>
+        <v>4.338931667078746e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.57679700983947e-10</v>
+        <v>4.434150824724813e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.326048785975791e-09</v>
+        <v>1.312696829544578e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.324304828629233e-09</v>
+        <v>1.311021795760219e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.592705137091308e-09</v>
+        <v>1.579470939089917e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>9.020643847536926e-10</v>
+        <v>8.8769694981767e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.519837987239866e-09</v>
+        <v>1.507445159057147e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.486510374461353e-09</v>
+        <v>1.458186220073036e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.522747406406748e-09</v>
+        <v>1.510452083722514e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.61622081579913e-09</v>
+        <v>1.622387020502036e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.510854308434974e-09</v>
+        <v>1.49507129410519e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.556599964580876e-09</v>
+        <v>1.565782246780789e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48296898023484e-09</v>
+        <v>1.473649139594923e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.549008100466445e-09</v>
+        <v>1.530320505814614e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.346551324682032e-09</v>
+        <v>1.333792638285733e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.181420520165625e-09</v>
+        <v>1.168545675609558e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.218662998182974e-09</v>
+        <v>1.204573962888344e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.40919639028096e-09</v>
+        <v>1.395824778683682e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.765596808263443e-09</v>
+        <v>1.763351704646206e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.414903633795965e-09</v>
+        <v>1.399257754568171e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.366884312564391e-09</v>
+        <v>1.378846789043674e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.493882614422471e-09</v>
+        <v>1.499177676399711e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38805326057683e-09</v>
+        <v>1.37542573897606e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.786184959165737e-09</v>
+        <v>2.775919261305543e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.105070074343425e-09</v>
+        <v>2.08849941878168e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.216694574075318e-09</v>
+        <v>2.205626986232897e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.421202701823466e-09</v>
+        <v>1.408446054897895e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.579394049878356e-09</v>
+        <v>1.570321363563355e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.839638106942559e-09</v>
+        <v>1.845434896241143e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.318542626956654e-10</v>
+        <v>5.169330384226747e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.272888117706397e-10</v>
+        <v>8.279948646097649e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.573541329933058e-10</v>
+        <v>5.273264064293659e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.255093786889395e-10</v>
+        <v>8.26115014393296e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.370287016866709e-10</v>
+        <v>8.377881834384002e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.569312206291785e-10</v>
+        <v>5.259381429048739e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.501023018499938e-10</v>
+        <v>5.201238020432257e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.573382513845724e-10</v>
+        <v>5.283769255463227e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.561597192954564e-10</v>
+        <v>8.416071711206725e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.420299549262331e-10</v>
+        <v>5.28477165724841e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.548199999486536e-10</v>
+        <v>8.406829907691789e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>8.535832862699467e-10</v>
+        <v>5.232436382456378e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.346551324682032e-09</v>
+        <v>1.333792638285733e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>8.364274390576855e-10</v>
+        <v>8.223396620189937e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.393411623084799e-10</v>
+        <v>5.002660523056427e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.487376804360755e-10</v>
+        <v>5.187107058027372e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.641062704108271e-10</v>
+        <v>5.346668622896392e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>8.52290222608546e-10</v>
+        <v>8.37768054992719e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.288453367320744e-10</v>
+        <v>5.152842291555273e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>8.560949028936965e-10</v>
+        <v>8.428939271982974e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>8.541532196704632e-10</v>
+        <v>5.241744198331598e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.213390221065931e-10</v>
+        <v>6.066158058872262e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.731526536874795e-10</v>
+        <v>8.736744057190303e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.859302762461655e-10</v>
+        <v>5.711518424178121e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.390703629302899e-10</v>
+        <v>5.241818730328308e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.427992503070552e-10</v>
+        <v>8.437599685242747e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.517211195922435e-10</v>
+        <v>5.377733187785074e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.185158256487153e-09</v>
+        <v>1.170174219501497e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.180592805562127e-09</v>
+        <v>1.165592571633446e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.19556391197083e-09</v>
+        <v>1.180567587508188e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.178813372480426e-09</v>
+        <v>1.16371272141698e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.190332695478159e-09</v>
+        <v>1.175385890462081e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.195140999606706e-09</v>
+        <v>1.179179323983693e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.18831208082752e-09</v>
+        <v>1.173364983122045e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.195548030362095e-09</v>
+        <v>1.181618106625143e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.19436949827298e-09</v>
+        <v>1.179204878144352e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.19533394871772e-09</v>
+        <v>1.181718346803666e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.193029778926178e-09</v>
+        <v>1.178280697792858e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.191793065247472e-09</v>
+        <v>1.17648481932446e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.346551324682032e-09</v>
+        <v>1.333792638285733e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.175933332020777e-09</v>
+        <v>1.160970564021574e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.178837230723142e-09</v>
+        <v>1.163805557860182e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.1869474594136e-09</v>
+        <v>1.171951886881559e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.202316049388351e-09</v>
+        <v>1.18790804336846e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.190500001586072e-09</v>
+        <v>1.175365762016399e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.18214933052356e-09</v>
+        <v>1.168525410234347e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.194493112538273e-09</v>
+        <v>1.180581336831955e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19236299864799e-09</v>
+        <v>1.177415600911982e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.26501592109286e-09</v>
+        <v>1.250205163096127e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.226456647478966e-09</v>
+        <v>1.211272112742711e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.231244975692977e-09</v>
+        <v>1.216386637130404e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.192374356721775e-09</v>
+        <v>1.177423054111652e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.196103244098542e-09</v>
+        <v>1.181357675547955e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.204874615816943e-09</v>
+        <v>1.190879591312561e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.123673548010965e-09</v>
+        <v>1.109164248626489e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.613391924312587e-09</v>
+        <v>1.599703530640594e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.62836303072129e-09</v>
+        <v>1.614678546515336e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.348420933679882e-09</v>
+        <v>1.334186390403853e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.205851630475079e-09</v>
+        <v>1.191509973869554e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.730433089897319e-09</v>
+        <v>1.715956833219123e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.621111199577977e-09</v>
+        <v>1.607475942129197e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.628347149112554e-09</v>
+        <v>1.615729065632287e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.627168617023439e-09</v>
+        <v>1.613315837151496e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.628133067468179e-09</v>
+        <v>1.615829305810814e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.625828897676636e-09</v>
+        <v>1.612391656800012e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.62459218399794e-09</v>
+        <v>1.610595778331579e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.346551324682032e-09</v>
+        <v>1.333792638285733e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.330903250772971e-09</v>
+        <v>1.316781701069695e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.307997124912304e-09</v>
+        <v>1.293762959347283e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.028324697391759e-09</v>
+        <v>1.013639352685646e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.635115168138813e-09</v>
+        <v>1.622019002375603e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.623299120336531e-09</v>
+        <v>1.609476721023543e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61494844927402e-09</v>
+        <v>1.60263636924149e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.386019570150276e-09</v>
+        <v>1.373033234151551e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.490253416203023e-09</v>
+        <v>1.476304633566983e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.697912180847273e-09</v>
+        <v>1.684413427613152e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.113135980421503e-09</v>
+        <v>1.098338395627527e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.155788548558798e-09</v>
+        <v>2.142943407644375e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.121708072383656e-09</v>
+        <v>1.107215957763989e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.628902362849001e-09</v>
+        <v>1.615468634555097e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.153994523510589e-09</v>
+        <v>2.142185762975544e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.012952901589948e-10</v>
+        <v>8.928976274997083e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.050368589636992e-09</v>
+        <v>1.044009285480794e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.065339696045697e-09</v>
+        <v>1.058984301355529e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.013130119288714e-09</v>
+        <v>1.006196215461901e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.059289569762487e-10</v>
+        <v>6.948867698722101e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.064916991227765e-09</v>
+        <v>1.057596246002218e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.058087864902383e-09</v>
+        <v>1.051781696969393e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.06532381443696e-09</v>
+        <v>1.060034820472487e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.064145282347847e-09</v>
+        <v>1.057621591991702e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.065109732792585e-09</v>
+        <v>1.060135060651007e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.062805563001042e-09</v>
+        <v>1.056697411640204e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.061568849322335e-09</v>
+        <v>1.054901533171803e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.346551324682032e-09</v>
+        <v>1.333792638285733e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.096654853796674e-09</v>
+        <v>1.091013844163316e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.110632054446234e-09</v>
+        <v>1.105070219056443e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.056723451034664e-09</v>
+        <v>1.050368808900082e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.072091833463216e-09</v>
+        <v>1.066324757215804e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.060275785660937e-09</v>
+        <v>1.053782475863743e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.051925114598425e-09</v>
+        <v>1.046942124081692e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.064080465946085e-09</v>
+        <v>1.058908348069322e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.239434695160338e-09</v>
+        <v>1.235499141471615e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.134791705167726e-09</v>
+        <v>1.128621876943472e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.096232431553831e-09</v>
+        <v>1.089688826590056e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.101020759767841e-09</v>
+        <v>1.094803350977751e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.695197188086763e-10</v>
+        <v>9.619706319833966e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.065879028173406e-09</v>
+        <v>1.059774389395301e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.074650399891803e-09</v>
+        <v>1.069296305159906e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.518908559012838e-10</v>
+        <v>5.369498967361081e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.645636364132056e-10</v>
+        <v>5.475404596684078e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.505623164113771e-10</v>
+        <v>5.352574855747016e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.485055264863463e-10</v>
+        <v>5.32901257238037e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.477167690728097e-10</v>
+        <v>5.322908501725607e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.576832580892256e-10</v>
+        <v>5.385371418553571e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.47620994617904e-10</v>
+        <v>5.321341066993048e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.492836535100393e-10</v>
+        <v>5.337775485270309e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.538122565966009e-10</v>
+        <v>5.368432290971372e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.541911368128637e-10</v>
+        <v>5.381882853276554e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.546463795106444e-10</v>
+        <v>5.409383968497138e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.596981471202452e-10</v>
+        <v>5.413921284836647e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.491853287427502e-10</v>
+        <v>5.334068969138743e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.936304488806329e-10</v>
+        <v>7.566427590917513e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.539608544972435e-10</v>
+        <v>5.364226786100682e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.479515406088422e-10</v>
+        <v>5.325637047816076e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.473087609852225e-10</v>
+        <v>5.323791225831114e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.534908669264119e-10</v>
+        <v>5.364585967668531e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.498694590398468e-10</v>
+        <v>5.328165221844254e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.931086396258697e-10</v>
+        <v>7.59331055894997e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.482690653760801e-10</v>
+        <v>5.331906659147608e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>8.199054290755864e-10</v>
+        <v>7.829774981658756e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.514051542713979e-10</v>
+        <v>5.357745662691407e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.508026032090337e-10</v>
+        <v>5.356425647987616e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.167017948132149e-10</v>
+        <v>7.929765354200614e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.496897653516104e-10</v>
+        <v>5.329176224736212e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.575650435156044e-10</v>
+        <v>5.490490588085911e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.001190143392035e-10</v>
+        <v>4.893500357089301e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.944019581438769e-10</v>
+        <v>4.784627349307483e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.910130566466981e-10</v>
+        <v>4.776525696214732e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.754719551447019e-10</v>
+        <v>4.599754115032902e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.70682439588738e-10</v>
+        <v>4.5645408459109e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.413929079946599e-10</v>
+        <v>5.007047970342079e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.700486149948669e-10</v>
+        <v>4.553792972537976e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.818895123245696e-10</v>
+        <v>4.670864965355184e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.139534620203014e-10</v>
+        <v>4.887441237575542e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.167571103319351e-10</v>
+        <v>4.984228505079783e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.199858923360519e-10</v>
+        <v>5.180232012286045e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.654273589961448e-10</v>
+        <v>5.306924548949995e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.810874111918645e-10</v>
+        <v>4.643440558968436e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.935854095870575e-10</v>
+        <v>8.349384993506578e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.148713294028749e-10</v>
+        <v>4.856286943824886e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.722836640369672e-10</v>
+        <v>4.583311171203277e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.677654912871276e-10</v>
+        <v>4.570933573695537e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.115812623444557e-10</v>
+        <v>4.859322604469126e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.860578536044724e-10</v>
+        <v>4.601843283281719e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.223199455413128e-10</v>
+        <v>8.820767887132148e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.742731130878877e-10</v>
+        <v>4.625221322114942e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.488588506909977e-10</v>
+        <v>8.984722261421285e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.969991473568049e-10</v>
+        <v>4.813098479123926e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.925859486882523e-10</v>
+        <v>4.802607797543661e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.289375968806376e-10</v>
+        <v>9.005606397608311e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.846480463302598e-10</v>
+        <v>4.608159522933141e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.417961291248978e-10</v>
+        <v>5.764618116125067e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.428619885212648e-10</v>
+        <v>4.997046019078404e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.877535204392915e-10</v>
+        <v>4.410277686009478e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.278555238244003e-10</v>
+        <v>4.805880392921566e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>5.046231354510976e-10</v>
+        <v>4.539733563109406e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.95713757618834e-10</v>
+        <v>4.470785277052627e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>6.082898358707076e-10</v>
+        <v>5.176332656985839e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.946319410922519e-10</v>
+        <v>4.453080380692683e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.134124381397982e-10</v>
+        <v>4.638714695340341e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.644974483586423e-10</v>
+        <v>4.984420524719977e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.688447195991167e-10</v>
+        <v>5.136927707362653e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.739868952924751e-10</v>
+        <v>5.447565454916974e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.474404232289852e-10</v>
+        <v>5.664916766869213e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>5.123018146616402e-10</v>
+        <v>1.709162838388546e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.314016636760052e-10</v>
+        <v>4.644263542304369e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.662435749090265e-10</v>
+        <v>4.937494306418962e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.983656101185718e-10</v>
+        <v>4.501605460337663e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.911051185765465e-10</v>
+        <v>4.480756051897577e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.609348490915199e-10</v>
+        <v>4.94155142745947e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.200293810828295e-10</v>
+        <v>4.530162349003424e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.891953921733206e-10</v>
+        <v>5.499214422739959e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>5.017177933365065e-10</v>
+        <v>4.570763047884662e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.554096297829923e-10</v>
+        <v>5.053926835260188e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.373757651779052e-10</v>
+        <v>4.864287036047153e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.286250528546614e-10</v>
+        <v>4.835482647942534e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.255854532970566e-10</v>
+        <v>4.759986191149284e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.179996582110234e-10</v>
+        <v>4.541582091752452e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.076125370287299e-10</v>
+        <v>6.35756571874659e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.302923853215742e-09</v>
+        <v>2.309804799539831e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.422313081108935e-09</v>
+        <v>1.365298508109441e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.228237834167903e-09</v>
+        <v>2.160443069630955e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.309731624332411e-09</v>
+        <v>1.178568858160216e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.608378129743429e-09</v>
+        <v>1.512688636471565e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.502893322716195e-09</v>
+        <v>2.663543961950732e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.615576507225461e-09</v>
+        <v>1.503626717944205e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.956448826005235e-09</v>
+        <v>1.84231634234115e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.780686124669546e-09</v>
+        <v>2.37338083816723e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.917043788100517e-09</v>
+        <v>2.704639212691327e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.002977312663731e-09</v>
+        <v>3.276789173226854e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.659297081705664e-09</v>
+        <v>3.913769430243907e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.199039921804146e-09</v>
+        <v>1.709162838388546e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>2.084779206959664e-09</v>
+        <v>1.687440289448535e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.733136733819869e-09</v>
+        <v>2.220252340756994e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.617168233600741e-09</v>
+        <v>1.531840938318311e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51847198777133e-09</v>
+        <v>1.536695803627269e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.668496897764374e-09</v>
+        <v>2.254183007465324e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>2.074563849292926e-09</v>
+        <v>1.612998951882021e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>3.277878120202481e-09</v>
+        <v>3.349074760539093e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.530838547422693e-09</v>
+        <v>1.507831371303322e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.672620417082058e-09</v>
+        <v>2.554062985841157e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.391958666478544e-09</v>
+        <v>2.252440009253706e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.200557067211336e-09</v>
+        <v>2.164758011631567e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.026931603416606e-09</v>
+        <v>1.920582997082591e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.965374256146243e-09</v>
+        <v>1.58457438540471e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.984743149776586e-09</v>
+        <v>5.490054187496271e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.323907261872738e-10</v>
+        <v>5.956412252894589e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>9.364688091841832e-10</v>
+        <v>8.882301318722722e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.765708125692906e-10</v>
+        <v>5.765246626737768e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.94151873117107e-10</v>
+        <v>9.011757195822643e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.852424952848446e-10</v>
+        <v>5.430151510868834e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>6.978185735367173e-10</v>
+        <v>9.648356289699084e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.433472298371409e-10</v>
+        <v>8.925104013405928e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>6.029411758058099e-10</v>
+        <v>9.110738328053609e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>1.013212737103532e-09</v>
+        <v>9.456444157433206e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.017560008344007e-09</v>
+        <v>6.096293941178849e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.635156329584863e-10</v>
+        <v>9.91958908763022e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>7.369691608949957e-10</v>
+        <v>1.013694039958247e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.0195610533015e-10</v>
+        <v>1.709162838388546e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>9.785974431828145e-10</v>
+        <v>5.605249100152386e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>1.013442559320611e-09</v>
+        <v>9.384386538499475e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.47080898863461e-10</v>
+        <v>5.460971694153858e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>9.398204073214338e-10</v>
+        <v>8.952779684610844e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>1.00965013783641e-09</v>
+        <v>5.900917661275679e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>6.095581187488405e-10</v>
+        <v>5.489528582819637e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.806687507259851e-10</v>
+        <v>6.472474871344611e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>9.504330820813968e-10</v>
+        <v>5.530129281700862e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>1.002601059614682e-09</v>
+        <v>6.117330574885778e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>9.860910539227946e-10</v>
+        <v>9.336310668760424e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.288920351389888e-10</v>
+        <v>5.896333217922434e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.743007420419475e-10</v>
+        <v>5.71935242496549e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.075283958770339e-10</v>
+        <v>9.013605724465713e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.977584576519612e-10</v>
+        <v>7.327702943158122e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.405438446475498e-09</v>
+        <v>1.337919411957618e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.350329978393525e-09</v>
+        <v>1.279242578650726e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.390431981778635e-09</v>
+        <v>1.318802849341938e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.367199593405331e-09</v>
+        <v>1.292188166360719e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.358290215573069e-09</v>
+        <v>1.28529333775504e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.470866293824942e-09</v>
+        <v>1.355848075748363e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.357208399046488e-09</v>
+        <v>1.283522848119048e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.375988896094037e-09</v>
+        <v>1.302086279583814e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.427073906312875e-09</v>
+        <v>1.336656862521777e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.431421177553353e-09</v>
+        <v>1.351907580786045e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.436563353246711e-09</v>
+        <v>1.382971355541473e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.510016881183221e-09</v>
+        <v>1.404706486736699e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.374878272615877e-09</v>
+        <v>1.709162838388546e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.393945474461116e-09</v>
+        <v>1.302608831564928e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.428787385694137e-09</v>
+        <v>1.331931907976385e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.360942068072806e-09</v>
+        <v>1.288375356083546e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.353681576530782e-09</v>
+        <v>1.286290415239536e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.423511307045754e-09</v>
+        <v>1.332369952795727e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.382605839037065e-09</v>
+        <v>1.291231044950123e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.453682903380807e-09</v>
+        <v>1.389461013526718e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.364294251290741e-09</v>
+        <v>1.295291114838244e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.417986087737228e-09</v>
+        <v>1.343607493575797e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.399952223132139e-09</v>
+        <v>1.324643513654494e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.393146131695554e-09</v>
+        <v>1.323152496322878e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.388161911251293e-09</v>
+        <v>1.314213429164707e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.380576116165258e-09</v>
+        <v>1.292373019225024e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.470188994982965e-09</v>
+        <v>1.473971381924437e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.374110329118881e-09</v>
+        <v>1.30729795209697e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.922984233538879e-09</v>
+        <v>1.831360652261892e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.963086236923986e-09</v>
+        <v>1.870920922953101e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.618251051541622e-09</v>
+        <v>1.53401462812304e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.421055492971512e-09</v>
+        <v>1.345455886598257e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.168760228494116e-09</v>
+        <v>2.028800987825819e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.929862654191836e-09</v>
+        <v>1.835640921730211e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.948643151239382e-09</v>
+        <v>1.854204353194975e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.999728161458226e-09</v>
+        <v>1.888774936132931e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.004075432698701e-09</v>
+        <v>1.904025654397207e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.009217608392057e-09</v>
+        <v>1.935089429152638e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.082671136328558e-09</v>
+        <v>1.956824560347839e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.479345145044849e-09</v>
+        <v>1.709162838388546e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.627106952078118e-09</v>
+        <v>1.527175360283274e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.630410708487037e-09</v>
+        <v>1.526069519452759e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.210917629272074e-09</v>
+        <v>1.143232277493983e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.92633583167613e-09</v>
+        <v>1.838408488850704e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.996165562191107e-09</v>
+        <v>1.884488026406885e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.955260094182416e-09</v>
+        <v>1.843349118561284e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.731574278118292e-09</v>
+        <v>1.6571913058461e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.771870230340382e-09</v>
+        <v>1.688110054552134e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.99075904281153e-09</v>
+        <v>1.895840092283664e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.305283968955468e-09</v>
+        <v>1.2329096712782e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.566325092002801e-09</v>
+        <v>2.454632365570599e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.345614511233392e-09</v>
+        <v>1.272767283284427e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.953230371310604e-09</v>
+        <v>1.844491092836184e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.673753342471194e-09</v>
+        <v>2.634809626208707e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.160616554279215e-09</v>
+        <v>1.090266345425976e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.309350558978155e-09</v>
+        <v>1.225207559148575e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.349452562363264e-09</v>
+        <v>1.264767829839781e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.279174328963253e-09</v>
+        <v>1.193467056931219e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>8.473979804257722e-10</v>
+        <v>7.849155955074694e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.429887090519724e-09</v>
+        <v>1.30181327149912e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.316228979631115e-09</v>
+        <v>1.229487828616893e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.335009476678661e-09</v>
+        <v>1.24805126008166e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.386094486897504e-09</v>
+        <v>1.282621843019625e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.39044175813798e-09</v>
+        <v>1.297872561283891e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.395583933831339e-09</v>
+        <v>1.328936336039323e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.469037461767849e-09</v>
+        <v>1.350671467234546e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.333898853200503e-09</v>
+        <v>1.709162838388546e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.420552118514379e-09</v>
+        <v>1.312771198629964e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.470085691770822e-09</v>
+        <v>1.356049026553432e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.319962864767587e-09</v>
+        <v>1.234340551834303e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.312702157115408e-09</v>
+        <v>1.232255395737385e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.382531887630382e-09</v>
+        <v>1.278334933293573e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.341626419621692e-09</v>
+        <v>1.237196025447965e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.412737051598838e-09</v>
+        <v>1.335490654300465e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.558544705879069e-09</v>
+        <v>1.464687206884831e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.377006668321855e-09</v>
+        <v>1.289572474073646e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.358972803716766e-09</v>
+        <v>1.270608494152342e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35216671228018e-09</v>
+        <v>1.269117476820725e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.224283692943922e-09</v>
+        <v>1.143444029966845e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.339596696749885e-09</v>
+        <v>1.238337999722869e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.429209575567595e-09</v>
+        <v>1.419936362422285e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.431247049506e-10</v>
+        <v>5.317365516493956e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.555674146999589e-10</v>
+        <v>5.427913972493869e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.440661931426314e-10</v>
+        <v>5.32302079191079e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.409679780779834e-10</v>
+        <v>5.290860008535743e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.403830437197254e-10</v>
+        <v>5.285800692847646e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.491946572400466e-10</v>
+        <v>5.338804060193316e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.391308810553538e-10</v>
+        <v>5.275343138096681e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.437307328544876e-10</v>
+        <v>5.302984589839375e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.456775656638374e-10</v>
+        <v>5.323855239649691e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.44626057329131e-10</v>
+        <v>5.298781051793126e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.460403898207958e-10</v>
+        <v>5.357101084984788e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.503684028989901e-10</v>
+        <v>5.36027412271625e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.401558741177522e-10</v>
+        <v>5.277784966021475e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.69868021854588e-10</v>
+        <v>7.431658565311672e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.459873325416886e-10</v>
+        <v>5.32050213787174e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.408289341457159e-10</v>
+        <v>5.291226042117174e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.388654849135717e-10</v>
+        <v>5.275797705613774e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.453797596735261e-10</v>
+        <v>5.321121708146667e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.416968492292817e-10</v>
+        <v>5.280973477534954e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.665685350789615e-10</v>
+        <v>7.440673818746111e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.409134839750774e-10</v>
+        <v>5.296073925395367e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.944537640960666e-10</v>
+        <v>7.691073186771887e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.453288718092514e-10</v>
+        <v>5.333041454857642e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.461477272684325e-10</v>
+        <v>5.347308663063973e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.026335689555841e-10</v>
+        <v>7.85479342877576e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.429236179191244e-10</v>
+        <v>5.286767184346348e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.491223609843567e-10</v>
+        <v>5.436369455765956e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.873486817139816e-10</v>
+        <v>4.787425483830111e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.859049327862803e-10</v>
+        <v>4.736706502438215e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.943982617797931e-10</v>
+        <v>4.831075037190014e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.714193003648658e-10</v>
+        <v>4.592889984646148e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.680762653149528e-10</v>
+        <v>4.56507349405939e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.305032699201134e-10</v>
+        <v>4.939837925833472e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.59168313212188e-10</v>
+        <v>4.490744055235486e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.920497423286954e-10</v>
+        <v>4.688102871764972e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.05629187825141e-10</v>
+        <v>4.834681633225577e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.981472885679627e-10</v>
+        <v>4.656515040996283e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.082914099742087e-10</v>
+        <v>5.072346847418037e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.485982234444161e-10</v>
+        <v>5.189559467018109e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.663736538788205e-10</v>
+        <v>4.507021217962923e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.557977524431797e-10</v>
+        <v>8.120189960102913e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.07674580741533e-10</v>
+        <v>4.809464835026286e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.711725420080593e-10</v>
+        <v>4.602979957436005e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.572251071867626e-10</v>
+        <v>4.493606253518013e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.03413458427804e-10</v>
+        <v>4.814382145853532e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.774639384950894e-10</v>
+        <v>4.53032814402062e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.698157901246696e-10</v>
+        <v>8.482269874900453e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.714852389269045e-10</v>
+        <v>4.634581041081025e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.13759721582858e-10</v>
+        <v>8.799391041207137e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.033818889951055e-10</v>
+        <v>4.902294037822471e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.09101963523203e-10</v>
+        <v>5.002936619265402e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.129019149664096e-10</v>
+        <v>8.922249954269665e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.861020823658056e-10</v>
+        <v>4.570898432151242e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.313428815444732e-10</v>
+        <v>5.644790266603297e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.176343274774292e-10</v>
+        <v>4.78218560089118e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.722085997753206e-10</v>
+        <v>4.300493079655635e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.282688697123624e-10</v>
+        <v>4.846064538279089e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.932731053078497e-10</v>
+        <v>4.482793695367124e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.866660026482212e-10</v>
+        <v>4.425646397269813e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.861972309027359e-10</v>
+        <v>5.024343814192844e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.725222493308618e-10</v>
+        <v>4.307523505644894e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.24479691438436e-10</v>
+        <v>4.619746418774637e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.464027384297867e-10</v>
+        <v>4.854941069366897e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.345927932491353e-10</v>
+        <v>4.572265522819109e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.505683293675889e-10</v>
+        <v>5.231017126259778e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.159315330633438e-10</v>
+        <v>5.433570283603922e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.841000174907546e-10</v>
+        <v>1.316294400634626e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.056871198689452e-10</v>
+        <v>4.457431933876855e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.499690229925297e-10</v>
+        <v>4.817615182270215e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.917025401295154e-10</v>
+        <v>4.486928213053088e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.695244778211665e-10</v>
+        <v>4.312658054861721e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.431062079492922e-10</v>
+        <v>4.824613513542121e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.015060402590575e-10</v>
+        <v>4.371120779684108e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.429469551099927e-10</v>
+        <v>5.153161476503534e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.924255112858368e-10</v>
+        <v>4.540216464722602e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.410268470820794e-10</v>
+        <v>4.971297663172299e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.425314061127315e-10</v>
+        <v>4.959252535996964e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.50101188152467e-10</v>
+        <v>5.11080094868704e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.119631535692615e-10</v>
+        <v>4.672568349610516e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.153629569522999e-10</v>
+        <v>4.436563363355669e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.861681906056011e-10</v>
+        <v>6.122563672541996e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.011213754784455e-09</v>
+        <v>1.999027085160536e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.329327426286881e-09</v>
+        <v>1.269843475671804e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.370385682349907e-09</v>
+        <v>2.282377557838559e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.302206828047509e-09</v>
+        <v>1.191508332877e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.616341556748017e-09</v>
+        <v>1.520150871912371e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.137337035298915e-09</v>
+        <v>2.396462884532324e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.381108352355942e-09</v>
+        <v>1.32712244555518e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.327038941268839e-09</v>
+        <v>1.883506583139094e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.552564606644176e-09</v>
+        <v>2.177267418047516e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.354361822333145e-09</v>
+        <v>1.717288072741904e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.662805996493594e-09</v>
+        <v>2.861608960613641e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.060179441704455e-09</v>
+        <v>3.426545919439217e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.457004185144899e-09</v>
+        <v>1.316294400634626e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.784695810852468e-09</v>
+        <v>1.449223177982682e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.528787550251825e-09</v>
+        <v>2.043714386043225e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.660819764079247e-09</v>
+        <v>1.586327188954179e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.302663438615005e-09</v>
+        <v>1.316403790437112e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44635479461303e-09</v>
+        <v>2.0817652972206e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.884501057412895e-09</v>
+        <v>1.408515152594919e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.517530689827914e-09</v>
+        <v>2.694030809477031e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.526810630098398e-09</v>
+        <v>1.527640843394191e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.520476000658154e-09</v>
+        <v>2.430517458618938e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.608042035264592e-09</v>
+        <v>2.467075826973538e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.707300814277378e-09</v>
+        <v>2.690788397997651e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.880290562222477e-09</v>
+        <v>1.783273716322136e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.068761835026748e-09</v>
+        <v>1.48385589719695e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.617573217091562e-09</v>
+        <v>4.893454221233073e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.029324597212483e-10</v>
+        <v>8.947519034731369e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.575067320191409e-10</v>
+        <v>5.206937797959315e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.454876291016643e-10</v>
+        <v>9.011397972119263e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.785712375516674e-10</v>
+        <v>8.648127129207329e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>9.038847620375087e-10</v>
+        <v>5.332091115573499e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>6.714953631465547e-10</v>
+        <v>5.930788532496532e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.578203815746816e-10</v>
+        <v>5.21396822394858e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>6.097778236822639e-10</v>
+        <v>5.526191137078322e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.636214978190733e-10</v>
+        <v>9.020274503207106e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>9.51811552638417e-10</v>
+        <v>8.737598956659326e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.358664616114074e-10</v>
+        <v>9.396350560099971e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03315029245263e-09</v>
+        <v>6.340015001907614e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.694815133037982e-10</v>
+        <v>1.316294400634626e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.910686156819835e-10</v>
+        <v>8.6008539619322e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.658892547071197e-10</v>
+        <v>8.9611536611055e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.089212995188026e-10</v>
+        <v>8.6522616468933e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.86743237210452e-10</v>
+        <v>5.219102773165401e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>6.284043401931056e-10</v>
+        <v>8.98994694738232e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.868041725028771e-10</v>
+        <v>5.277565497987794e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.299246544176485e-10</v>
+        <v>6.069212462047706e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>9.096442706751248e-10</v>
+        <v>8.70554989856279e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.360804349836786e-10</v>
+        <v>9.114671590422456e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>6.278295383565578e-10</v>
+        <v>5.865697254300654e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.451930608057731e-10</v>
+        <v>6.108148840106939e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.972612858130812e-10</v>
+        <v>8.837901783450724e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.325817163415883e-10</v>
+        <v>8.601896797195838e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.719864928549907e-10</v>
+        <v>7.037982417985961e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.308874221007654e-09</v>
+        <v>1.251692617319674e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.263448493305547e-09</v>
+        <v>1.203523365196122e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.319508763242594e-09</v>
+        <v>1.258080511058466e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.284512998838077e-09</v>
+        <v>1.22175342676727e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.277905896178445e-09</v>
+        <v>1.216038696957538e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.377437124432962e-09</v>
+        <v>1.275908438649844e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.263762142861087e-09</v>
+        <v>1.204226407795046e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.315719584968668e-09</v>
+        <v>1.235448699108021e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.337642631960011e-09</v>
+        <v>1.258968164167247e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.325832686779353e-09</v>
+        <v>1.230700609512468e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.341808222897814e-09</v>
+        <v>1.296575769856536e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.407171426593567e-09</v>
+        <v>1.316831085590949e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.275339911020982e-09</v>
+        <v>1.316294400634626e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.296896746981667e-09</v>
+        <v>1.219187176743519e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.341178650105248e-09</v>
+        <v>1.255205501582858e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.282942433659742e-09</v>
+        <v>1.222166878535867e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.260764371351393e-09</v>
+        <v>1.204739862716729e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.334346101479524e-09</v>
+        <v>1.25593540858477e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.292745933789276e-09</v>
+        <v>1.210586135198967e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.335909238964523e-09</v>
+        <v>1.289756550083394e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.283665404816064e-09</v>
+        <v>1.227495703702819e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.332266740612306e-09</v>
+        <v>1.270603823547787e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.333771299642952e-09</v>
+        <v>1.269399310830255e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.343020648746537e-09</v>
+        <v>1.28551477882331e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.303203047099487e-09</v>
+        <v>1.240730892191608e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.306602850482526e-09</v>
+        <v>1.217130393566126e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.377408084135828e-09</v>
+        <v>1.385730424484757e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.267019846542222e-09</v>
+        <v>1.213807019283716e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.766172109800912e-09</v>
+        <v>1.696804045293285e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.82223237973796e-09</v>
+        <v>1.751361191155631e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.497264899177353e-09</v>
+        <v>1.43220373216988e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.320890408096535e-09</v>
+        <v>1.260902597191735e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.993082534955355e-09</v>
+        <v>1.879329906749454e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.766485759356454e-09</v>
+        <v>1.697507087892211e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.818443201464029e-09</v>
+        <v>1.728729379205185e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.840366248455377e-09</v>
+        <v>1.75224884426441e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.828556303274721e-09</v>
+        <v>1.723981289609634e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.844531839393179e-09</v>
+        <v>1.789856449953699e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.909895043088928e-09</v>
+        <v>1.810111765688086e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.355924478628491e-09</v>
+        <v>1.316294400634626e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.49351905705357e-09</v>
+        <v>1.4139056797134e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.509364724660098e-09</v>
+        <v>1.422188088607002e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.134066054564413e-09</v>
+        <v>1.079894983550216e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.763487987846758e-09</v>
+        <v>1.698020542813894e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.837069717974885e-09</v>
+        <v>1.749216088681933e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.795469550284648e-09</v>
+        <v>1.703866815296135e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.572845425964789e-09</v>
+        <v>1.523804078978927e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.637610120432345e-09</v>
+        <v>1.575631225426535e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.835097382364114e-09</v>
+        <v>1.763988893107966e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.234806575559314e-09</v>
+        <v>1.175809860721491e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.38730266546878e-09</v>
+        <v>2.306969451141911e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.251232856858966e-09</v>
+        <v>1.192978607832666e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.809326466977901e-09</v>
+        <v>1.710411073663291e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.448988949131957e-09</v>
+        <v>2.433858697557773e-09</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.056444348034571e-09</v>
+        <v>9.98546368872052e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.189812202756214e-09</v>
+        <v>1.122037502003191e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.245872472693262e-09</v>
+        <v>1.176594647865542e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.16961203429781e-09</v>
+        <v>1.100649201553173e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.921013367946182e-10</v>
+        <v>7.388285326662234e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.303801036101378e-09</v>
+        <v>1.194422776581233e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.190125852311756e-09</v>
+        <v>1.122740544602124e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.242083294419335e-09</v>
+        <v>1.153962835915094e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.264006341410681e-09</v>
+        <v>1.17748230097432e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.252196396230025e-09</v>
+        <v>1.149214746319543e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.268171932348479e-09</v>
+        <v>1.215089906663608e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.333535136044236e-09</v>
+        <v>1.235345222398025e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.201703620471644e-09</v>
+        <v>1.316294400634626e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.282542951187368e-09</v>
+        <v>1.194619682105362e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.339711153398391e-09</v>
+        <v>1.243010191257719e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.209306345328156e-09</v>
+        <v>1.140681216467253e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.187128080802056e-09</v>
+        <v>1.123253999523802e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.260709810930194e-09</v>
+        <v>1.174449545391844e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.219109643239951e-09</v>
+        <v>1.129100272006042e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.262230125154723e-09</v>
+        <v>1.208264968412034e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.416353114113886e-09</v>
+        <v>1.34410228798706e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.258630450062966e-09</v>
+        <v>1.189117960354861e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.260135009093616e-09</v>
+        <v>1.187913447637326e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.269384358197213e-09</v>
+        <v>1.204028915630386e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.121770205592758e-09</v>
+        <v>1.055749161191398e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.232966559933195e-09</v>
+        <v>1.135644530373195e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.303771793586494e-09</v>
+        <v>1.304244561291832e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.382897200603002e-10</v>
+        <v>5.2857703993488e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.504797455338666e-10</v>
+        <v>5.396787614265281e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.386870588877357e-10</v>
+        <v>5.287307160766484e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.360693218914438e-10</v>
+        <v>5.260062463059889e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.366649474555799e-10</v>
+        <v>5.265299175588467e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.437238992551152e-10</v>
+        <v>5.307064922646786e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.35104328885087e-10</v>
+        <v>5.252254961170971e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.393080534627149e-10</v>
+        <v>5.273339522302119e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.408589516386287e-10</v>
+        <v>5.295609146395659e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.409892731401751e-10</v>
+        <v>5.272549121617078e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.408094317865944e-10</v>
+        <v>5.319436523653594e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.443147983238751e-10</v>
+        <v>5.321780068662938e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.350861823397227e-10</v>
+        <v>5.246188175131118e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.566213745581007e-10</v>
+        <v>7.350107186854332e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.41057528265251e-10</v>
+        <v>5.290715083187994e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.364596412352522e-10</v>
+        <v>5.264385106475814e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.360038318159533e-10</v>
+        <v>5.260133113906978e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.408364780240702e-10</v>
+        <v>5.294454737921844e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.378716923838576e-10</v>
+        <v>5.261324300729318e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.548467004279654e-10</v>
+        <v>7.366363486699353e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.379672064563502e-10</v>
+        <v>5.285837916632269e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.817052271179655e-10</v>
+        <v>7.605552945380481e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.419874057274067e-10</v>
+        <v>5.316918030583243e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.460972466836081e-10</v>
+        <v>5.365428473806929e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.95535546700166e-10</v>
+        <v>7.809264061952091e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.392251102608868e-10</v>
+        <v>5.264048671231796e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.444484100329025e-10</v>
+        <v>5.400167504004617e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.795865304015907e-10</v>
+        <v>4.721057474657227e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.796204098548527e-10</v>
+        <v>4.693410877215122e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.826954491932638e-10</v>
+        <v>4.734784321005167e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.632105149174416e-10</v>
+        <v>4.532357963249064e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.683107786452675e-10</v>
+        <v>4.578148377179953e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.181612242104751e-10</v>
+        <v>4.872254803093553e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.572114344172996e-10</v>
+        <v>4.48545756907144e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.872191496390459e-10</v>
+        <v>4.635651028462158e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.979708417162961e-10</v>
+        <v>4.792165501984892e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.989501764144436e-10</v>
+        <v>4.628737168370746e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.97647022226844e-10</v>
+        <v>4.961963299930887e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.319951402998969e-10</v>
+        <v>5.072788906357305e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.569579036381048e-10</v>
+        <v>4.440877733394862e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.316295649745199e-10</v>
+        <v>7.989438615284742e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.992055315635244e-10</v>
+        <v>4.755909068003773e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.667361952159363e-10</v>
+        <v>4.570590957454277e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.636180953804121e-10</v>
+        <v>4.541525069475903e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.97736578645301e-10</v>
+        <v>4.783267034375883e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.769471774037201e-10</v>
+        <v>4.549633045810529e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.547390119009007e-10</v>
+        <v>8.404408578826558e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.771640640520635e-10</v>
+        <v>4.720192564934819e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.964975342973132e-10</v>
+        <v>8.681877871954358e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.062202236165707e-10</v>
+        <v>4.945826965863377e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.355978801413559e-10</v>
+        <v>5.292527247712391e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.043722065353583e-10</v>
+        <v>8.86549494659822e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.864905885548851e-10</v>
+        <v>4.568212916834032e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.246820091574092e-10</v>
+        <v>5.545201522481596e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.063406634917029e-10</v>
+        <v>4.699611008464813e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.647526272155436e-10</v>
+        <v>4.263156167664166e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.108287883324751e-10</v>
+        <v>4.716969435622675e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.812602447408407e-10</v>
+        <v>4.409228041846569e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.879881094890542e-10</v>
+        <v>4.468379118863676e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.677222173430813e-10</v>
+        <v>4.940142445080242e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.703602048153302e-10</v>
+        <v>4.321038716382912e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.178432077284896e-10</v>
+        <v>4.55919853373655e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.353056077502034e-10</v>
+        <v>4.810311332328809e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.368333573846594e-10</v>
+        <v>4.550270594396754e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.348019665648555e-10</v>
+        <v>5.07988536966977e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.909950244223744e-10</v>
+        <v>5.273814373610646e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.701552312376233e-10</v>
+        <v>1.176722493707848e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.890437163106718e-10</v>
+        <v>4.411173251146555e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.376043304212918e-10</v>
+        <v>4.75546348709542e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.856690812849235e-10</v>
+        <v>4.458054287743677e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.805205042112492e-10</v>
+        <v>4.410026075665414e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.351074662590256e-10</v>
+        <v>4.797704607640409e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>5.016188485840456e-10</v>
+        <v>4.42348107879676e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.404265994051417e-10</v>
+        <v>5.199305370061201e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>5.02544357584573e-10</v>
+        <v>4.699689957237989e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.370005189953789e-10</v>
+        <v>4.965994097397378e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.481077241211122e-10</v>
+        <v>5.05143783187611e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.931557573470141e-10</v>
+        <v>5.59527836236444e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.068743506848264e-10</v>
+        <v>4.657972096660348e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.169063261080683e-10</v>
+        <v>4.454254096894584e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.767123748377257e-10</v>
+        <v>5.989481455193677e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.863697766761669e-09</v>
+        <v>1.847234146397726e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.265127950814444e-09</v>
+        <v>1.214000179508522e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.084600556225548e-09</v>
+        <v>2.020908576929547e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.14600819183447e-09</v>
+        <v>1.063094990107764e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.705106161107398e-09</v>
+        <v>1.603837615198971e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.840860149318146e-09</v>
+        <v>2.23208985791055e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.413470095792292e-09</v>
+        <v>1.364302475526152e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.256147690353175e-09</v>
+        <v>1.77059712536252e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.401576000561139e-09</v>
+        <v>2.089787255482625e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.453176096015848e-09</v>
+        <v>1.688850530197446e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.407081334197313e-09</v>
+        <v>2.552409358493213e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.562601631583623e-09</v>
+        <v>3.056911917772113e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.417158441215632e-09</v>
+        <v>1.176722493707848e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.582670266122083e-09</v>
+        <v>1.384434894725478e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.346695277309032e-09</v>
+        <v>1.923275574106132e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.607446964149371e-09</v>
+        <v>1.532009485262258e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.586364203430897e-09</v>
+        <v>1.513437622252147e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.358861858060013e-09</v>
+        <v>2.032596332327923e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.958522046056502e-09</v>
+        <v>1.516838552501655e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.488804320377774e-09</v>
+        <v>2.716980701963347e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.736578482205145e-09</v>
+        <v>1.77872096542264e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.518534743445709e-09</v>
+        <v>2.432828550086143e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.72841118908571e-09</v>
+        <v>2.597359219821312e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.57305838313302e-09</v>
+        <v>3.591309437059962e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.818788482159327e-09</v>
+        <v>1.730774271997542e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.16879240123434e-09</v>
+        <v>1.526486070489993e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.472352808401964e-09</v>
+        <v>4.591589344060355e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.229946203171893e-10</v>
+        <v>5.618972303415881e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.513379124129064e-10</v>
+        <v>5.18251746261523e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.974140735298357e-10</v>
+        <v>8.884027348364258e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.979142015663272e-10</v>
+        <v>8.576285954588169e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.745733946864169e-10</v>
+        <v>5.387740413814735e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.843761741685676e-10</v>
+        <v>5.859503740031315e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.569454900126922e-10</v>
+        <v>8.488096629124469e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>6.044284929258501e-10</v>
+        <v>5.478559828687603e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.519595645756902e-10</v>
+        <v>8.977369245070397e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>9.534873142101413e-10</v>
+        <v>8.717328507138347e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.514559233903411e-10</v>
+        <v>5.999246664620843e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.775803096197352e-10</v>
+        <v>6.1931756685617e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.569178022068415e-10</v>
+        <v>1.176722493707848e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>9.045146819780413e-10</v>
+        <v>5.332623219026582e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>6.136146154437906e-10</v>
+        <v>8.901440840601359e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.023230381104127e-10</v>
+        <v>8.625112200485244e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.971744610367354e-10</v>
+        <v>8.577083988407e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>9.517614230845157e-10</v>
+        <v>5.717065902591469e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>9.182728054095315e-10</v>
+        <v>8.590538991538369e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.283863955971518e-10</v>
+        <v>9.370470524432341e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.891296427819326e-10</v>
+        <v>5.619051252189062e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.524695992896785e-10</v>
+        <v>5.98224425331704e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>6.346930093184716e-10</v>
+        <v>5.970799126827167e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.893682625054248e-10</v>
+        <v>6.601607419820142e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.235283075103139e-10</v>
+        <v>5.577333391611412e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.335602829335547e-10</v>
+        <v>8.621312009636162e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.638319678656404e-10</v>
+        <v>6.917434100914024e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.291338328399279e-09</v>
+        <v>1.238746609112041e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.249750292123122e-09</v>
+        <v>1.195101125031975e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.295826453240053e-09</v>
+        <v>1.240482451827827e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.266257909648419e-09</v>
+        <v>1.209708312450215e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.272985774396632e-09</v>
+        <v>1.215623420151927e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.352719882250657e-09</v>
+        <v>1.262799752773584e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.255357869722908e-09</v>
+        <v>1.20088937990385e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.302840872636069e-09</v>
+        <v>1.224705361639213e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.320303272657785e-09</v>
+        <v>1.24981664149844e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.321831022292237e-09</v>
+        <v>1.223812567705235e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.319799631472437e-09</v>
+        <v>1.276774045232537e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.375992689329953e-09</v>
+        <v>1.296166945626623e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.255152896145204e-09</v>
+        <v>1.176722493707848e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.274011154524656e-09</v>
+        <v>1.209872783107173e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.322571768635282e-09</v>
+        <v>1.244301806702059e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.270666746192507e-09</v>
+        <v>1.214590937039927e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.265518169118828e-09</v>
+        <v>1.209788115832102e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.320105131166608e-09</v>
+        <v>1.248555969029601e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.286616513491623e-09</v>
+        <v>1.211133616145234e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.326986262937351e-09</v>
+        <v>1.289229904511284e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.287542022492152e-09</v>
+        <v>1.238754503989357e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.321998183902957e-09</v>
+        <v>1.265384918005297e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.333105389028689e-09</v>
+        <v>1.273929291453168e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37952793324924e-09</v>
+        <v>1.328724068664961e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.291872015592406e-09</v>
+        <v>1.234582717931592e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.301903991015648e-09</v>
+        <v>1.214210917955018e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.361710039745303e-09</v>
+        <v>1.367733653784927e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.242753272845468e-09</v>
+        <v>1.194911011085566e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.736360859563027e-09</v>
+        <v>1.674926733202486e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.782437020679956e-09</v>
+        <v>1.720308059998338e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.467892595112557e-09</v>
+        <v>1.410699775347114e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.30777794195091e-09</v>
+        <v>1.253368117901201e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.950306748599044e-09</v>
+        <v>1.851209923389297e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.741968437162815e-09</v>
+        <v>1.68071498807436e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.789451440075972e-09</v>
+        <v>1.704530969809722e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.806913840097688e-09</v>
+        <v>1.72964224966895e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.808441589732143e-09</v>
+        <v>1.703638175875745e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.806410198912342e-09</v>
+        <v>1.756599653403046e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.862603256769865e-09</v>
+        <v>1.775992553797113e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.326897319507209e-09</v>
+        <v>1.176722493707848e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.459794623234789e-09</v>
+        <v>1.395355126152573e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.480408921049676e-09</v>
+        <v>1.402440126233876e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.116903535456961e-09</v>
+        <v>1.067843959995118e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.752128736558735e-09</v>
+        <v>1.68961372400261e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.806715698606511e-09</v>
+        <v>1.728381577200111e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.773227080931533e-09</v>
+        <v>1.690959224315746e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.552356225641211e-09</v>
+        <v>1.513463547504285e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.628061653252793e-09</v>
+        <v>1.575569452229528e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.808713932693251e-09</v>
+        <v>1.745313440673594e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.228393920636408e-09</v>
+        <v>1.175176904527302e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.398559963214109e-09</v>
+        <v>2.329390666354036e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.233345426565583e-09</v>
+        <v>1.181019844146805e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.788514558455553e-09</v>
+        <v>1.694036526125529e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.407377187801701e-09</v>
+        <v>2.394567179726707e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.019018090192385e-09</v>
+        <v>9.681026392518848e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.148500549917817e-09</v>
+        <v>1.089657350821833e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.194576711034749e-09</v>
+        <v>1.135038677617684e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.125525950242798e-09</v>
+        <v>1.066137161138806e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.773715854813336e-10</v>
+        <v>7.293478458670956e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.251470342193263e-09</v>
+        <v>1.157356179050435e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.154108127517601e-09</v>
+        <v>1.095445605693706e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.201591130430761e-09</v>
+        <v>1.119261587429071e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.219053530452477e-09</v>
+        <v>1.144372867288297e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.220581280086932e-09</v>
+        <v>1.118368793495093e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.218549889267127e-09</v>
+        <v>1.171330271022393e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.274742947124645e-09</v>
+        <v>1.190723171416482e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.153903153939899e-09</v>
+        <v>1.176722493707848e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.229484446529715e-09</v>
+        <v>1.159206454625496e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.290374729626728e-09</v>
+        <v>1.205542053822299e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.169417206135112e-09</v>
+        <v>1.109147363316782e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.164268426913522e-09</v>
+        <v>1.104344341621956e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.218855388961303e-09</v>
+        <v>1.143112194819457e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.18536677128632e-09</v>
+        <v>1.105689841935092e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22554903310206e-09</v>
+        <v>1.183682995224491e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38370401304602e-09</v>
+        <v>1.323948265195137e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.220748441697653e-09</v>
+        <v>1.159941143795154e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.231855646823384e-09</v>
+        <v>1.168485517243027e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.278278191043934e-09</v>
+        <v>1.223280294454816e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.087482056750897e-09</v>
+        <v>1.029537995530246e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.200654248810343e-09</v>
+        <v>1.108767143744874e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.260460297539996e-09</v>
+        <v>1.262289879574784e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.178872279366171e-10</v>
+        <v>5.082245678808425e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.309433863667233e-10</v>
+        <v>5.202596186647489e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.202445907028058e-10</v>
+        <v>5.105529350728374e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.172396632738727e-10</v>
+        <v>5.07564064682123e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.174465932174822e-10</v>
+        <v>5.077682449145429e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.19715599511247e-10</v>
+        <v>5.09101517375588e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.185745551622618e-10</v>
+        <v>5.088018511655712e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.179960016408251e-10</v>
+        <v>5.083358894048176e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.191283340255709e-10</v>
+        <v>5.090860968424337e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.209435847174247e-10</v>
+        <v>5.112864691623178e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.200584416133771e-10</v>
+        <v>5.10723178810469e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.205661855254948e-10</v>
+        <v>5.099854702422246e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.194679129004334e-10</v>
+        <v>5.097837449526011e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.196118932091763e-10</v>
+        <v>6.972834177389271e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.186369206572467e-10</v>
+        <v>5.086084571367426e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.182977380175081e-10</v>
+        <v>5.086027722340039e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.176605741737927e-10</v>
+        <v>5.081663591065022e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.188128695270317e-10</v>
+        <v>5.089894606504568e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.176059353042679e-10</v>
+        <v>5.078772677411654e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.1594359907636e-10</v>
+        <v>6.937504185330649e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.174479126853277e-10</v>
+        <v>5.078083832871585e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.423898427328761e-10</v>
+        <v>7.178134961137834e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.184868926619111e-10</v>
+        <v>5.087934505417027e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.176586112536269e-10</v>
+        <v>5.080112046583278e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.676667998517956e-10</v>
+        <v>7.523274771051633e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.181157841883614e-10</v>
+        <v>5.078737304416587e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.201110369062052e-10</v>
+        <v>5.118502620959505e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.472398659183667e-10</v>
+        <v>4.38766060399385e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.603477116503091e-10</v>
+        <v>4.503187832460018e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.642921613129129e-10</v>
+        <v>4.556088043709136e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.420235562590902e-10</v>
+        <v>4.334562223385503e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.443081400442815e-10</v>
+        <v>4.357196639000367e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60191187806046e-10</v>
+        <v>4.449804281564093e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.52460168642321e-10</v>
+        <v>4.431937791448984e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.48234980120236e-10</v>
+        <v>4.39776966316363e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.560864404786206e-10</v>
+        <v>4.449213446730189e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.691312977999229e-10</v>
+        <v>4.606949118990076e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.626879614359523e-10</v>
+        <v>4.565341285133832e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.75624392251385e-10</v>
+        <v>4.606459996203105e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.586375045541543e-10</v>
+        <v>4.500089621616024e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.76667336085947e-10</v>
+        <v>7.466719551148116e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.525678275860885e-10</v>
+        <v>4.414932722692932e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.5028843954306e-10</v>
+        <v>4.415829781363157e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.458623633071521e-10</v>
+        <v>4.385934152473929e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.537479481984205e-10</v>
+        <v>4.441380705207158e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.454174232551489e-10</v>
+        <v>4.364703212915359e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.850584160840426e-10</v>
+        <v>7.592705868553377e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.440174845452347e-10</v>
+        <v>4.357072431320557e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.349404788486135e-10</v>
+        <v>8.005502955385599e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.516963923194912e-10</v>
+        <v>4.43000687169238e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.457295508769189e-10</v>
+        <v>4.373631962120485e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.628017512396382e-10</v>
+        <v>8.448347402851076e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.489880523118485e-10</v>
+        <v>4.363774440136105e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.641767528784821e-10</v>
+        <v>4.655940349279107e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.61687549331717e-10</v>
+        <v>4.287463185313426e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.44308400407255e-10</v>
+        <v>4.116408283507083e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.883150462162951e-10</v>
+        <v>4.55046297066756e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.543730085715711e-10</v>
+        <v>4.212856310553274e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.567103774771276e-10</v>
+        <v>4.235919407080585e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.823398473596653e-10</v>
+        <v>4.386518664911944e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.694512265315397e-10</v>
+        <v>4.352669987957853e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.629161983591514e-10</v>
+        <v>4.300037463550771e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.756569415850791e-10</v>
+        <v>4.384273477203973e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.962105051645452e-10</v>
+        <v>4.633319020497891e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.862124066183802e-10</v>
+        <v>4.569692783992908e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.087623728851043e-10</v>
+        <v>4.655149329677643e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.795421131490595e-10</v>
+        <v>1.835028794134849e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.543118100663775e-10</v>
+        <v>4.200952118299599e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.701556734869432e-10</v>
+        <v>4.330825242745187e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.663244495393729e-10</v>
+        <v>4.330183106828999e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.591273908147583e-10</v>
+        <v>4.280888236478093e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.721430969116413e-10</v>
+        <v>4.373861342322003e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.585102196483519e-10</v>
+        <v>4.248234036877395e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.820065456924923e-10</v>
+        <v>4.565022817846471e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.566145356543745e-10</v>
+        <v>4.23929480816483e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.966929705682705e-10</v>
+        <v>4.610812858067664e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.684610382633095e-10</v>
+        <v>4.351721098847093e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.580217956321995e-10</v>
+        <v>4.25723740097161e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.684668102932109e-10</v>
+        <v>4.352704767884867e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.642691973362653e-10</v>
+        <v>4.247834482625717e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.881612722726107e-10</v>
+        <v>4.707924062354256e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.47452385552008e-09</v>
+        <v>1.438085052499762e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.238950341315663e-09</v>
+        <v>1.206587134593051e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.104618664608952e-09</v>
+        <v>2.060536416899748e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.005528428447456e-09</v>
+        <v>9.656670203366542e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.498935393238697e-09</v>
+        <v>1.457642815503923e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.810592038811217e-09</v>
+        <v>1.600649173039673e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.796403265388861e-09</v>
+        <v>1.732460542847616e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.619436059202936e-09</v>
+        <v>1.582210974625228e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.733278638480573e-09</v>
+        <v>1.625654518735431e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.170694504034867e-09</v>
+        <v>2.134243153372094e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.911561821033548e-09</v>
+        <v>1.935770926448053e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>2.436283397595837e-09</v>
+        <v>2.212226956765585e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.891676400918282e-09</v>
+        <v>1.835028794134849e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.349792464313918e-09</v>
+        <v>1.292095454803784e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.622051137426328e-09</v>
+        <v>1.513052257233892e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.628236948866556e-09</v>
+        <v>1.584293239540233e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.559669129795391e-09</v>
+        <v>1.560683505212572e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.617564439202459e-09</v>
+        <v>1.55302296152551e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.517422623266372e-09</v>
+        <v>1.465664181383474e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.895224256557985e-09</v>
+        <v>1.982898592319242e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.332220397860861e-09</v>
+        <v>1.299870936743166e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.200534511825143e-09</v>
+        <v>2.112752042520303e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.700862524096499e-09</v>
+        <v>1.656622336934374e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.493177362180135e-09</v>
+        <v>1.459209975862863e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.581677658141227e-09</v>
+        <v>1.541011927112612e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.588389999324481e-09</v>
+        <v>1.427295355396741e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.158268373130036e-09</v>
+        <v>2.432078646352091e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.578564418312714e-10</v>
+        <v>5.303887826265955e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.836450625366954e-10</v>
+        <v>5.132832924459611e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.844839387158493e-10</v>
+        <v>8.948820617202289e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.50541901071125e-10</v>
+        <v>8.611213957087996e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.960470396065706e-10</v>
+        <v>5.252344048033116e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.216765094891083e-10</v>
+        <v>5.402943305864459e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.656201190310942e-10</v>
+        <v>8.751027634492554e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.590850908587055e-10</v>
+        <v>8.698395110085487e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.718258340846331e-10</v>
+        <v>5.400698118156494e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.923793976640998e-10</v>
+        <v>9.031676667032631e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.823812991179347e-10</v>
+        <v>5.586117424945436e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>9.480990350145476e-10</v>
+        <v>9.053506976212327e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.757817923767296e-10</v>
+        <v>1.835028794134849e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>8.927204181080442e-10</v>
+        <v>8.582145732464039e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.55168895894427e-10</v>
+        <v>8.712095485221208e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.056611116688161e-10</v>
+        <v>8.728540753363696e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.552962833143121e-10</v>
+        <v>8.679245883012816e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.683119894111955e-10</v>
+        <v>5.39028598327452e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.978468817777941e-10</v>
+        <v>5.264658677829921e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>5.792588612883366e-10</v>
+        <v>5.587572885638524e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>8.959511977838192e-10</v>
+        <v>8.637652454699521e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.030027031616741e-10</v>
+        <v>8.991943368546196e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.646299307628637e-10</v>
+        <v>5.368145739799625e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.63823328269941e-10</v>
+        <v>5.364593623070212e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.078034724226534e-10</v>
+        <v>5.369129408837399e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.036058594657081e-10</v>
+        <v>8.646192129160416e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.845402457985994e-10</v>
+        <v>5.727209798874635e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.280287128853422e-09</v>
+        <v>1.228645425417472e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.262907979928958e-09</v>
+        <v>1.211539935236839e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.306914625738001e-09</v>
+        <v>1.254945403952886e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.272972588093274e-09</v>
+        <v>1.221184737941457e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.27530995699883e-09</v>
+        <v>1.223491047594188e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.30093942688137e-09</v>
+        <v>1.238550973377323e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.288050806053243e-09</v>
+        <v>1.235166105681916e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.281515777880854e-09</v>
+        <v>1.229902853241206e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.294256521106782e-09</v>
+        <v>1.238326454606527e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.314810084686249e-09</v>
+        <v>1.263231008935919e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.304811986140086e-09</v>
+        <v>1.25686838528542e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.327361952406808e-09</v>
+        <v>1.265414039853894e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.298141692670763e-09</v>
+        <v>1.835028794134849e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.272879227540888e-09</v>
+        <v>1.219962381823743e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.288723090961458e-09</v>
+        <v>1.232949694268301e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.284924029061078e-09</v>
+        <v>1.232917417569028e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.277726970336464e-09</v>
+        <v>1.227987930533939e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.290742676433346e-09</v>
+        <v>1.237285241118329e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.277109799170055e-09</v>
+        <v>1.224722510573869e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.301794726514339e-09</v>
+        <v>1.257082100872315e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.275214115176078e-09</v>
+        <v>1.223828587702617e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.315292550089975e-09</v>
+        <v>1.260980392692896e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.287060617785013e-09</v>
+        <v>1.235071216770838e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.277704798250194e-09</v>
+        <v>1.226235389667242e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.287066389814915e-09</v>
+        <v>1.235169583674615e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.28286877685797e-09</v>
+        <v>1.224682555148702e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.306760851794313e-09</v>
+        <v>1.270691513121554e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.216279708425517e-09</v>
+        <v>1.168140286495284e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.745006556138704e-09</v>
+        <v>1.682844015476172e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.789013201947745e-09</v>
+        <v>1.726249484192218e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.46428583019728e-09</v>
+        <v>1.409316096354327e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.296379468380773e-09</v>
+        <v>1.245835569640141e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.896276639049378e-09</v>
+        <v>1.820129159629699e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.770149382262989e-09</v>
+        <v>1.706470185921248e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.763614354090601e-09</v>
+        <v>1.701206933480542e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.776355097316529e-09</v>
+        <v>1.709630534845859e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.796908660895993e-09</v>
+        <v>1.734535089175255e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.786910562349832e-09</v>
+        <v>1.728172465524753e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.809460528616555e-09</v>
+        <v>1.736718120093193e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.356916759963485e-09</v>
+        <v>1.835028794134849e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.448019432828445e-09</v>
+        <v>1.392344722130601e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.435347272841049e-09</v>
+        <v>1.377562546170076e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.113594316012604e-09</v>
+        <v>1.067899629110831e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.759825546546208e-09</v>
+        <v>1.699292010773273e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.772841252643091e-09</v>
+        <v>1.708589321357663e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.759208375379801e-09</v>
+        <v>1.696026590813204e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.51734751172598e-09</v>
+        <v>1.468826609751068e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.608171083315239e-09</v>
+        <v>1.549866758154314e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.797498451853545e-09</v>
+        <v>1.732388988751082e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.16578260450504e-09</v>
+        <v>1.11879480001205e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.302966216632341e-09</v>
+        <v>2.226437988602592e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.21291477012195e-09</v>
+        <v>1.164785815469847e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.764967353067713e-09</v>
+        <v>1.695986635388034e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.359312806204531e-09</v>
+        <v>2.297514792002181e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.021012400481375e-09</v>
+        <v>9.732146788502752e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.187325445412263e-09</v>
+        <v>1.13367315798157e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.231332091221305e-09</v>
+        <v>1.177078626697618e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.154994812579092e-09</v>
+        <v>1.102337089102023e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.762664960762294e-10</v>
+        <v>7.362905737423837e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.225357110873014e-09</v>
+        <v>1.160684414871255e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.212468271536549e-09</v>
+        <v>1.157299328426647e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.20593324336416e-09</v>
+        <v>1.152036075985939e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.218673986590087e-09</v>
+        <v>1.16045967735126e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.239227550169553e-09</v>
+        <v>1.185364231680651e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22922945162339e-09</v>
+        <v>1.179001608030152e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.251779417890112e-09</v>
+        <v>1.187547262598627e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.222559158154067e-09</v>
+        <v>1.835028794134849e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.258204498512445e-09</v>
+        <v>1.200972299633094e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28728772240944e-09</v>
+        <v>1.226757289799865e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.209341713052721e-09</v>
+        <v>1.155050859062959e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.202144435819768e-09</v>
+        <v>1.150121153278673e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.215160141916649e-09</v>
+        <v>1.159418463863062e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.201527264653361e-09</v>
+        <v>1.146855733318603e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.226107013793791e-09</v>
+        <v>1.179147154099464e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.411608509097953e-09</v>
+        <v>1.350866902107753e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.239710015573278e-09</v>
+        <v>1.183113615437629e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.211478083268318e-09</v>
+        <v>1.157204439515572e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.202122263733499e-09</v>
+        <v>1.148368612411976e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.100733883717909e-09</v>
+        <v>1.050247609391377e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.207286242341275e-09</v>
+        <v>1.146815777893434e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.23117831727762e-09</v>
+        <v>1.192824735866288e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.104131318586915e-10</v>
+        <v>5.019390661626653e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.22897207579919e-10</v>
+        <v>5.135422879289229e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.112744613770673e-10</v>
+        <v>5.02733263573844e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.088259355332366e-10</v>
+        <v>5.003961771244654e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.103500926835323e-10</v>
+        <v>5.019173652090922e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.096494582097896e-10</v>
+        <v>5.011788845593362e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.101152231257229e-10</v>
+        <v>5.016453889346728e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.105274078370706e-10</v>
+        <v>5.021632290407651e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.10050985129576e-10</v>
+        <v>5.015877410043734e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.102773650807742e-10</v>
+        <v>5.018365872285037e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.106085426487455e-10</v>
+        <v>5.021392808593969e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.086904014365089e-10</v>
+        <v>5.002518095507316e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.097682842582714e-10</v>
+        <v>5.012905854217089e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.97599749651865e-10</v>
+        <v>6.778634635705039e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.088486577627156e-10</v>
+        <v>5.004262747022972e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.095353608530105e-10</v>
+        <v>5.010453734615309e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.105807643917548e-10</v>
+        <v>5.021385956452789e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.102765012915641e-10</v>
+        <v>5.017995459288228e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.094264741744969e-10</v>
+        <v>5.010568015359023e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.905121136309934e-10</v>
+        <v>6.701909674101591e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.09821047553094e-10</v>
+        <v>5.013620943461928e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.176796405571487e-10</v>
+        <v>6.957775636077873e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.126614064484582e-10</v>
+        <v>5.041900543053837e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.111460422932685e-10</v>
+        <v>5.026984144298089e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.533783928666552e-10</v>
+        <v>7.397921763552683e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.10221199935196e-10</v>
+        <v>5.017186655000765e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.103384239512866e-10</v>
+        <v>5.019006849652416e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.448741813765418e-10</v>
+        <v>4.371271121306945e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.583585028073082e-10</v>
+        <v>4.4942542661527e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.511814112672914e-10</v>
+        <v>4.429537341507296e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.329653593152556e-10</v>
+        <v>4.255304828660898e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.446297870967063e-10</v>
+        <v>4.371748720066015e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.39440338287413e-10</v>
+        <v>4.317194280850631e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.430472832225304e-10</v>
+        <v>4.353256445423672e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.459077274712406e-10</v>
+        <v>4.389425242284398e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.423268061074074e-10</v>
+        <v>4.346566881385608e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.440339645504405e-10</v>
+        <v>4.36522355902757e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.462368834200301e-10</v>
+        <v>4.385256880918808e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.420331884379815e-10</v>
+        <v>4.345173155684981e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.40386616642223e-10</v>
+        <v>4.326120876154897e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.4738280183269e-10</v>
+        <v>7.211867035465177e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.337419510458512e-10</v>
+        <v>4.26362332414237e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.386887188015699e-10</v>
+        <v>4.308287989954856e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.463259968187932e-10</v>
+        <v>4.38803142766206e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.438486090184649e-10</v>
+        <v>4.360829023282525e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.380178522947324e-10</v>
+        <v>4.310123835475931e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.377029816400279e-10</v>
+        <v>7.106544779474654e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.405442060100579e-10</v>
+        <v>4.329061777667314e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.019842444452862e-10</v>
+        <v>7.711344995758327e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.610208120797809e-10</v>
+        <v>4.532913101165586e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.502398436139134e-10</v>
+        <v>4.426791841396908e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.450560262106842e-10</v>
+        <v>8.28975051292592e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.436300427195671e-10</v>
+        <v>4.356775735885651e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.454441607191575e-10</v>
+        <v>4.379549466350429e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.539789622366111e-10</v>
+        <v>4.240048481900377e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.393167597542618e-10</v>
+        <v>4.098972007518633e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.637080753778253e-10</v>
+        <v>4.3297567329816e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.360508495942265e-10</v>
+        <v>4.065772067395494e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.532669057537492e-10</v>
+        <v>4.23759725936498e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.453529170650401e-10</v>
+        <v>4.154182472796173e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.506139460529358e-10</v>
+        <v>4.206876288016599e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.55269761981848e-10</v>
+        <v>4.265368710181908e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.498447360030019e-10</v>
+        <v>4.199885519702203e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.524454140242427e-10</v>
+        <v>4.228473014860378e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.561862170036317e-10</v>
+        <v>4.262663652929295e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.51620888459074e-10</v>
+        <v>4.220112960504977e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.466951119453252e-10</v>
+        <v>1.384556298573703e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.405782533117297e-10</v>
+        <v>4.108961285439616e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.363075076289353e-10</v>
+        <v>4.069171727267222e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.440641349328498e-10</v>
+        <v>4.139101780117659e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.558724488123467e-10</v>
+        <v>4.262586254842487e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.524356571277594e-10</v>
+        <v>4.224289029663032e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.428342098086906e-10</v>
+        <v>4.140392633689706e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.429390527528862e-10</v>
+        <v>4.139086231128668e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.472205411924553e-10</v>
+        <v>4.173887882718268e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.847667632775847e-10</v>
+        <v>4.528572460058631e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.79374257985451e-10</v>
+        <v>4.49430794767745e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.614797326100408e-10</v>
+        <v>4.322202736037577e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.522379780634133e-10</v>
+        <v>4.224790316183022e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.518110028676959e-10</v>
+        <v>4.215153213167811e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.547076712386925e-10</v>
+        <v>4.251472277017476e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.493904069233759e-09</v>
+        <v>1.455438300020762e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.324154408090208e-09</v>
+        <v>1.294120675951215e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.748832307328173e-09</v>
+        <v>1.696186604215834e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>8.757673023601046e-10</v>
+        <v>8.440644764422597e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.587815429179238e-09</v>
+        <v>1.556116301001384e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.349906456551079e-09</v>
+        <v>1.312778922528341e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.589488355557897e-09</v>
+        <v>1.549396073580122e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.629682481301448e-09</v>
+        <v>1.611924870539604e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.440832683882829e-09</v>
+        <v>1.404377970115716e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.533506019405442e-09</v>
+        <v>1.500593685487828e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.516383398100743e-09</v>
+        <v>1.479700390316298e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.536630039215276e-09</v>
+        <v>1.503404311694081e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.346924843247233e-09</v>
+        <v>1.384556298573703e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.273347095477019e-09</v>
+        <v>1.23978865289183e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.198715390141898e-09</v>
+        <v>1.169843538335472e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.359604406378118e-09</v>
+        <v>1.318363782884314e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.659755184664705e-09</v>
+        <v>1.625881688023994e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.440472448498834e-09</v>
+        <v>1.402458709305868e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.392919335593017e-09</v>
+        <v>1.373517092964938e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.343946574195373e-09</v>
+        <v>1.313787347704532e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.321527770459152e-09</v>
+        <v>1.286665571796007e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.051221771852322e-09</v>
+        <v>1.97995980138703e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.995186308195244e-09</v>
+        <v>1.956330114499688e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.710203524182836e-09</v>
+        <v>1.675838773729443e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.446955121191463e-09</v>
+        <v>1.412359798211867e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.520695297410069e-09</v>
+        <v>1.475393133269039e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.635708674142313e-09</v>
+        <v>1.602887024797316e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.447377985693161e-10</v>
+        <v>8.329738764706722e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.300755960869683e-10</v>
+        <v>5.058146622226118e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.544669117105314e-10</v>
+        <v>5.288931347689082e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.438642156299111e-10</v>
+        <v>5.02494668210298e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.610802717894325e-10</v>
+        <v>8.327287542171311e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.361117533977466e-10</v>
+        <v>8.243872755602509e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.413727823856429e-10</v>
+        <v>8.296566570822933e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.460285983145535e-10</v>
+        <v>8.355058992988251e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.40603572335708e-10</v>
+        <v>8.289575802508545e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.432042503569493e-10</v>
+        <v>8.318163297666711e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.639995830393162e-10</v>
+        <v>5.221838267636788e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>8.594342544947575e-10</v>
+        <v>8.309803243311325e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.375345928822253e-10</v>
+        <v>1.384556298573703e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.314177342486282e-10</v>
+        <v>8.183332802738364e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.167659625839705e-10</v>
+        <v>4.92604402048081e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.348229712655564e-10</v>
+        <v>8.228792062924004e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.636858148480306e-10</v>
+        <v>5.221760869549969e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.431944934604658e-10</v>
+        <v>8.313979312469374e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.506475758443742e-10</v>
+        <v>5.099567248397194e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>5.344756792261739e-10</v>
+        <v>5.101878471647392e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>8.550339072281373e-10</v>
+        <v>5.133062497425755e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.849400618501874e-10</v>
+        <v>5.580875100181961e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.701330943181576e-10</v>
+        <v>8.583998230483794e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.609857949644709e-10</v>
+        <v>5.36385170591052e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.600513440991007e-10</v>
+        <v>5.18396493089051e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.596243689033792e-10</v>
+        <v>8.304843495974149e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.455788695119638e-10</v>
+        <v>5.211491675410147e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.20571399464959e-09</v>
+        <v>1.15906316417746e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.191051792167242e-09</v>
+        <v>1.144955516739285e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.215443107790805e-09</v>
+        <v>1.168033989285582e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.187785882007206e-09</v>
+        <v>1.141635522726972e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.205001938166729e-09</v>
+        <v>1.158818041923921e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.197087949478019e-09</v>
+        <v>1.150476563267039e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.202348978465916e-09</v>
+        <v>1.155745944789083e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.207004794394828e-09</v>
+        <v>1.161595187005613e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.20157976841598e-09</v>
+        <v>1.155046867957641e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.204180446437222e-09</v>
+        <v>1.15790561747346e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.207921249416612e-09</v>
+        <v>1.161324681280353e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.203355920872053e-09</v>
+        <v>1.157069612037921e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.198430144358305e-09</v>
+        <v>1.384556298573703e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.192283502355933e-09</v>
+        <v>1.145924870847546e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.188012756673136e-09</v>
+        <v>1.141945915030309e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.19579916734583e-09</v>
+        <v>1.148968493999189e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.207607481225325e-09</v>
+        <v>1.16131694147167e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.204170689540739e-09</v>
+        <v>1.157487218953724e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.194569242221671e-09</v>
+        <v>1.149097579356393e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.195621456959657e-09</v>
+        <v>1.149416391873169e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.198955573605434e-09</v>
+        <v>1.15244710425925e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.236501795690565e-09</v>
+        <v>1.187915561993286e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.231109290398431e-09</v>
+        <v>1.184489110755166e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.213992555163599e-09</v>
+        <v>1.167640352172304e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.203973010476392e-09</v>
+        <v>1.157537347605725e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.203546035280674e-09</v>
+        <v>1.156573637304203e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.206442703651673e-09</v>
+        <v>1.160205543689171e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.132292931624559e-09</v>
+        <v>1.089497592615782e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.60908756765479e-09</v>
+        <v>1.554649115685468e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.633478883278353e-09</v>
+        <v>1.577727588231765e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.344135388043494e-09</v>
+        <v>1.296137750627747e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.208144106812592e-09</v>
+        <v>1.163915447914102e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.717030501979607e-09</v>
+        <v>1.659547673305256e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.620384753953464e-09</v>
+        <v>1.565439543735266e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.625040569882377e-09</v>
+        <v>1.571288785951796e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.619615543903529e-09</v>
+        <v>1.564740466903825e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.62221622192477e-09</v>
+        <v>1.567599216419642e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.625957024904161e-09</v>
+        <v>1.571018280226536e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.621391696359625e-09</v>
+        <v>1.5667632109841e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.235504651077918e-09</v>
+        <v>1.384556298573703e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.334079256968103e-09</v>
+        <v>1.286235092338288e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.304146103626303e-09</v>
+        <v>1.257230654640611e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.025795618580888e-09</v>
+        <v>9.852175568615236e-10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.625643256712874e-09</v>
+        <v>1.571010540417854e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.622206465028288e-09</v>
+        <v>1.567180817899909e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.612605017709218e-09</v>
+        <v>1.558791178302576e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.373768630354775e-09</v>
+        <v>1.325193172762153e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.482839197179738e-09</v>
+        <v>1.431252179843297e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.654634156595562e-09</v>
+        <v>1.597703349155769e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.106148737463574e-09</v>
+        <v>1.064663228931729e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.120936988598656e-09</v>
+        <v>2.054005899190391e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.121422884356348e-09</v>
+        <v>1.079069290895488e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.621581810768223e-09</v>
+        <v>1.566267236250385e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.137846241979568e-09</v>
+        <v>2.070525421282867e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.384334338597641e-10</v>
+        <v>8.97731954075397e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.084066533050059e-09</v>
+        <v>1.039189598083104e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.108457848673623e-09</v>
+        <v>1.062268070629399e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.043805280526539e-09</v>
+        <v>9.999659281855604e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>7.284919894166968e-10</v>
+        <v>6.944313991488635e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.090102897626933e-09</v>
+        <v>1.044710851111583e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.095363719348735e-09</v>
+        <v>1.049980026132898e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.100019535277643e-09</v>
+        <v>1.055829268349431e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.094594509298799e-09</v>
+        <v>1.049280949301461e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.097195187320038e-09</v>
+        <v>1.052139698817278e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.10093599029943e-09</v>
+        <v>1.05555876262417e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.096370661754867e-09</v>
+        <v>1.051303693381738e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.091444885241121e-09</v>
+        <v>1.384556298573703e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.138449955646943e-09</v>
+        <v>1.091742934699874e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.145732273034551e-09</v>
+        <v>1.098976133366906e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.088814115494741e-09</v>
+        <v>1.043202781843733e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.100622222108141e-09</v>
+        <v>1.055551022815488e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.097185430423556e-09</v>
+        <v>1.051721300297543e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.087583983104486e-09</v>
+        <v>1.04333166070021e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.088466616189265e-09</v>
+        <v>1.04356278302523e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27694774693601e-09</v>
+        <v>1.226200287953045e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.129516536573382e-09</v>
+        <v>1.082149643337102e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.124124031281246e-09</v>
+        <v>1.078723192098984e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.107007296046416e-09</v>
+        <v>1.061874433516123e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.000344020768073e-09</v>
+        <v>9.579794736123018e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.096560776163494e-09</v>
+        <v>1.050807718648021e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.099457444534491e-09</v>
+        <v>1.054439625032988e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.117645109527445e-10</v>
+        <v>5.028879457577148e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.23746506365412e-10</v>
+        <v>5.139136802640658e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.119057551873149e-10</v>
+        <v>5.030203952033543e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.101832229367683e-10</v>
+        <v>5.013298685780076e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.105655715892272e-10</v>
+        <v>5.017128660629707e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.112939595923283e-10</v>
+        <v>5.023872339637914e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.105029861491793e-10</v>
+        <v>5.016113829805166e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.111553856064418e-10</v>
+        <v>5.022820265769751e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.111038456017601e-10</v>
+        <v>5.022103184730329e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.10630025900921e-10</v>
+        <v>5.017599183815809e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.108562379456708e-10</v>
+        <v>5.019722223071671e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.089223303966683e-10</v>
+        <v>5.000730891284597e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.102973697343234e-10</v>
+        <v>5.013921894683169e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.962644189892692e-10</v>
+        <v>6.758101016733721e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.096334468895177e-10</v>
+        <v>5.007970554816545e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.100105755658053e-10</v>
+        <v>5.011230336581564e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.116732089885758e-10</v>
+        <v>5.028016789339373e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.106636776516997e-10</v>
+        <v>5.017835737484256e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.101128212762669e-10</v>
+        <v>5.012868869636105e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.891054272322401e-10</v>
+        <v>6.691220579275565e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.107469625388607e-10</v>
+        <v>5.018538805558936e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.21743373447283e-10</v>
+        <v>7.001244654242324e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.139135809888716e-10</v>
+        <v>5.050144769772769e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.12295557068835e-10</v>
+        <v>5.034172945212042e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.52761763344404e-10</v>
+        <v>7.386097896120483e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.109383864937904e-10</v>
+        <v>5.020029907138563e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.116175001643448e-10</v>
+        <v>5.027667631107156e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.510936365658446e-10</v>
+        <v>4.430189080491231e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.609722578598476e-10</v>
+        <v>4.51518443572085e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.523152124151629e-10</v>
+        <v>4.441750730996488e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.392428197907656e-10</v>
+        <v>4.31331334295778e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.427972801039611e-10</v>
+        <v>4.3488958104296e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.477400105807045e-10</v>
+        <v>4.394519631824568e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.42412482943502e-10</v>
+        <v>4.342254808660397e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.470068499199574e-10</v>
+        <v>4.389514972191235e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.464598483735018e-10</v>
+        <v>4.382638621144654e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.431837791890915e-10</v>
+        <v>4.351531451419697e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.446670372182634e-10</v>
+        <v>4.365401878958831e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.403685284496583e-10</v>
+        <v>4.324295751573078e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.407883266433402e-10</v>
+        <v>4.325072778893091e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.450470391022736e-10</v>
+        <v>7.179149790066066e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.35939607368548e-10</v>
+        <v>4.2815044127654e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.387258093032078e-10</v>
+        <v>4.305716309569293e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.507522379543937e-10</v>
+        <v>4.427093808392091e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.43270529754037e-10</v>
+        <v>4.351710776013832e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.395329125274906e-10</v>
+        <v>4.318167463289753e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.367689066564357e-10</v>
+        <v>7.104998196527773e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.437507973986125e-10</v>
+        <v>4.355618323355422e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.401221639706579e-10</v>
+        <v>8.08923043588671e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.66525713135556e-10</v>
+        <v>4.58289020259852e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.550678944658143e-10</v>
+        <v>4.469784609016921e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.428102588315003e-10</v>
+        <v>8.260846814679009e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.453591356824012e-10</v>
+        <v>4.368621036250412e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.512033388574888e-10</v>
+        <v>4.433201498216547e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.649523000930658e-10</v>
+        <v>4.339182305329199e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.445072055530232e-10</v>
+        <v>4.138814223765054e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.665477186980942e-10</v>
+        <v>4.35414307951239e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.470909245241793e-10</v>
+        <v>4.163190320372373e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.514097284427919e-10</v>
+        <v>4.20645164817439e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.596372060128273e-10</v>
+        <v>4.282624604817625e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.507027971067308e-10</v>
+        <v>4.194988667165867e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.580719490950545e-10</v>
+        <v>4.270740946499081e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.574436317049209e-10</v>
+        <v>4.262140528547635e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.52137769543803e-10</v>
+        <v>4.21176642401272e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.546929386519549e-10</v>
+        <v>4.235747129053971e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.499929044970486e-10</v>
+        <v>4.191636589593262e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.483802651126926e-10</v>
+        <v>1.383109448861235e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.430051321517987e-10</v>
+        <v>4.120820462449256e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.408809511610053e-10</v>
+        <v>4.103006630078024e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.451407930474482e-10</v>
+        <v>4.139827364687441e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.639210024068022e-10</v>
+        <v>4.329438070737095e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.525178815494207e-10</v>
+        <v>4.214438406518196e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.462957053824601e-10</v>
+        <v>4.158335349301269e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.486157702268376e-10</v>
+        <v>4.181708811769067e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.53371260294439e-10</v>
+        <v>4.221247947256514e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.52282216563638e-10</v>
+        <v>5.169349069961905e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.892270347721677e-10</v>
+        <v>4.579383789106074e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.702786781859362e-10</v>
+        <v>4.395252373035525e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.524165257678824e-10</v>
+        <v>4.21498908970929e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.556208442931474e-10</v>
+        <v>4.239222562131201e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.647919277964377e-10</v>
+        <v>4.340697703974212e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.63565298781399e-09</v>
+        <v>1.597118800558287e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.380110806520867e-09</v>
+        <v>1.347450657616321e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.774516078835029e-09</v>
+        <v>1.73285575414754e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.02690390095541e-09</v>
+        <v>9.917558188691559e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.531145173613549e-09</v>
+        <v>1.495689169188638e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.544094111065604e-09</v>
+        <v>1.500538637871712e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.55070876007705e-09</v>
+        <v>1.506606753412571e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.648997113646281e-09</v>
+        <v>1.609286167310093e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.545810283453027e-09</v>
+        <v>1.50378011897696e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.505924727545833e-09</v>
+        <v>1.467647160260038e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4831112047444e-09</v>
+        <v>1.443634464409098e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.49793897725183e-09</v>
+        <v>1.461558947752398e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.401242509169648e-09</v>
+        <v>1.383109448861235e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2799125739963e-09</v>
+        <v>1.243321356409309e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.238663219005127e-09</v>
+        <v>1.207553817448001e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.363037779713762e-09</v>
+        <v>1.321736233473096e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.77818062210126e-09</v>
+        <v>1.738545949287254e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.433139709865246e-09</v>
+        <v>1.394174415157858e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.42355960818822e-09</v>
+        <v>1.393693095551528e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.402150046365436e-09</v>
+        <v>1.368151422443294e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.390540357425476e-09</v>
+        <v>1.350569351788495e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>3.181564864563005e-09</v>
+        <v>3.06891018681328e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.113734171360084e-09</v>
+        <v>2.070125239862777e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.837178588736243e-09</v>
+        <v>1.79696260832744e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.411523778943243e-09</v>
+        <v>1.375368444906254e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.554351011873664e-09</v>
+        <v>1.502806130113561e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.811006313743675e-09</v>
+        <v>1.776041946441215e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.752839017181569e-10</v>
+        <v>8.452659886286909e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.548388071781143e-10</v>
+        <v>8.25229180472276e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.768793203231846e-10</v>
+        <v>8.467620660470082e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.5742252614927e-10</v>
+        <v>5.131083757191407e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.617413300678807e-10</v>
+        <v>8.319929229132102e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.699688076379166e-10</v>
+        <v>8.396102185775321e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.424300291212404e-10</v>
+        <v>8.308466248123576e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.497991811095658e-10</v>
+        <v>8.384218527456776e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.491708637194313e-10</v>
+        <v>5.23003396536666e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.624693711688922e-10</v>
+        <v>5.179659860831756e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.650245402770431e-10</v>
+        <v>8.349224710011684e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>8.603245061221372e-10</v>
+        <v>8.305114170550966e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.401543355351209e-10</v>
+        <v>1.383109448861235e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>8.51639896840745e-10</v>
+        <v>5.089092114804107e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.495175175139203e-10</v>
+        <v>8.190413581490152e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.554723946725371e-10</v>
+        <v>8.253304945645154e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.556482344213114e-10</v>
+        <v>8.442915651694797e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.442451135639312e-10</v>
+        <v>8.327915987475915e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.566273070075488e-10</v>
+        <v>5.126228786120305e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>8.596194039335702e-10</v>
+        <v>8.298908702981302e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.450984923089495e-10</v>
+        <v>5.189141384075552e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.609135822237241e-10</v>
+        <v>9.256642972945688e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.809542667866762e-10</v>
+        <v>5.547277225925111e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.706606774409438e-10</v>
+        <v>5.44569701641248e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.44143757782391e-10</v>
+        <v>5.182882526528321e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.473480763076559e-10</v>
+        <v>8.352700143088905e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.566215446415561e-10</v>
+        <v>5.309309160266124e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.216341000003395e-09</v>
+        <v>1.167301232963398e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.195895905463354e-09</v>
+        <v>1.147264424806986e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.217936418608428e-09</v>
+        <v>1.168797310381717e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.198479624434505e-09</v>
+        <v>1.149702034467717e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.20279842835312e-09</v>
+        <v>1.154028167247916e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.211025905923155e-09</v>
+        <v>1.161645462912242e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.202091497017061e-09</v>
+        <v>1.152881869147065e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.209460649005383e-09</v>
+        <v>1.160457097080387e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.208832331615251e-09</v>
+        <v>1.159597055285242e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.203526469454134e-09</v>
+        <v>1.154559644831752e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.206081638562287e-09</v>
+        <v>1.156957715335877e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.201381604407378e-09</v>
+        <v>1.152546661389805e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.199768965023019e-09</v>
+        <v>1.383109448861235e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.194364083502118e-09</v>
+        <v>1.145435525502924e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.192239902511326e-09</v>
+        <v>1.143654142265802e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.196529492957775e-09</v>
+        <v>1.147365738899223e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21530970231713e-09</v>
+        <v>1.166326809504188e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.203906581459752e-09</v>
+        <v>1.154826843082298e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.197684405292785e-09</v>
+        <v>1.149216537360606e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.200862931551013e-09</v>
+        <v>1.152025566551727e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.20475996020477e-09</v>
+        <v>1.155507797156131e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.303670916473968e-09</v>
+        <v>1.250317909426669e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.240615734682496e-09</v>
+        <v>1.191321381341088e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.222339410177907e-09</v>
+        <v>1.173280470759485e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.203805225678214e-09</v>
+        <v>1.154881911401408e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.207009544203475e-09</v>
+        <v>1.157305258643599e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.216180627706765e-09</v>
+        <v>1.167452772827899e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.140294175014905e-09</v>
+        <v>1.094168531604426e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.60961654183572e-09</v>
+        <v>1.550187023709203e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.631657054980795e-09</v>
+        <v>1.571719909283936e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.351413534856363e-09</v>
+        <v>1.299139228723323e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.203051649818967e-09</v>
+        <v>1.155059317900423e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.726303015951495e-09</v>
+        <v>1.663281229539298e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.615812133389429e-09</v>
+        <v>1.555804468049284e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.623181285377756e-09</v>
+        <v>1.563379695982606e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.622552967987622e-09</v>
+        <v>1.562519654187462e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.617247105826502e-09</v>
+        <v>1.55748224373397e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.619802274934659e-09</v>
+        <v>1.559880314238095e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.615102240779795e-09</v>
+        <v>1.555469260292045e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.233837882545521e-09</v>
+        <v>1.383109448861235e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.332794338417877e-09</v>
+        <v>1.280775734770642e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305095963995893e-09</v>
+        <v>1.254136166184853e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.024232183399163e-09</v>
+        <v>9.806773055934511e-10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.629030338689495e-09</v>
+        <v>1.569249408406408e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.617627217832124e-09</v>
+        <v>1.557749441984519e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.611405041665161e-09</v>
+        <v>1.552139136262825e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.375515710150772e-09</v>
+        <v>1.322592427878117e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.484804548134673e-09</v>
+        <v>1.428427549198417e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.717487806248132e-09</v>
+        <v>1.65333406688945e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.113206586178292e-09</v>
+        <v>1.068264362273124e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.123311285036327e-09</v>
+        <v>2.049705008703568e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.118660718643094e-09</v>
+        <v>1.072906238428894e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.620730180575847e-09</v>
+        <v>1.560227857545818e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.141504331216627e-09</v>
+        <v>2.067654939998463e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.338812363709438e-10</v>
+        <v>8.920880574706688e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.069524416907527e-09</v>
+        <v>1.023369424529829e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.091564930052601e-09</v>
+        <v>1.044902310104567e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.036083759151223e-09</v>
+        <v>9.908835755300318e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>7.166005928797449e-10</v>
+        <v>6.813032047029968e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.084654626008626e-09</v>
+        <v>1.037750669294964e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.075720008461234e-09</v>
+        <v>1.028986868869912e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.083089160449562e-09</v>
+        <v>1.036562096803235e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.082460843059421e-09</v>
+        <v>1.035702055008089e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.077154980898309e-09</v>
+        <v>1.030664644554596e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.079710150006462e-09</v>
+        <v>1.033062715058721e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07501011585155e-09</v>
+        <v>1.028651661112651e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.073397476467198e-09</v>
+        <v>1.383109448861235e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.119750071271371e-09</v>
+        <v>1.071716968677217e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.128875738195196e-09</v>
+        <v>1.080841635279497e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.070158213043248e-09</v>
+        <v>1.023470945281947e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.088938213761309e-09</v>
+        <v>1.042431809227033e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.077535092903924e-09</v>
+        <v>1.030931842805146e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.071312916736963e-09</v>
+        <v>1.025321537083453e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.074305013662987e-09</v>
+        <v>1.028031114355686e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.258511089364208e-09</v>
+        <v>1.206230825004987e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.177299427918138e-09</v>
+        <v>1.126422909149514e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.114244246126675e-09</v>
+        <v>1.067426381063932e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.095967921622087e-09</v>
+        <v>1.04938547048233e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.833264700113238e-10</v>
+        <v>9.397555892687708e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.080638055647648e-09</v>
+        <v>1.033410258366444e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.089809139150944e-09</v>
+        <v>1.043557772550746e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.334586295010427e-10</v>
+        <v>5.211429091878042e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.459323154854645e-10</v>
+        <v>5.320136828626488e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.334739753329194e-10</v>
+        <v>5.208791530115093e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.31635789847649e-10</v>
+        <v>5.189383283473377e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.316863132296485e-10</v>
+        <v>5.191115304556846e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.407569668172731e-10</v>
+        <v>5.246206259422871e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.313918132889278e-10</v>
+        <v>5.187427683175164e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.334066806038015e-10</v>
+        <v>5.208208885469471e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.36702762886684e-10</v>
+        <v>5.227601902120965e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.361315653994262e-10</v>
+        <v>5.235552800901195e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.376115765891931e-10</v>
+        <v>5.264843851243377e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.431395086285717e-10</v>
+        <v>5.277530587205759e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.345478245758089e-10</v>
+        <v>5.217386553043704e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.490957971625148e-10</v>
+        <v>7.211198686476675e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.357706333117883e-10</v>
+        <v>5.218054815194457e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.319785440824072e-10</v>
+        <v>5.194196174515024e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.316195407420491e-10</v>
+        <v>5.192362686607538e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.345304716775908e-10</v>
+        <v>5.211524088856292e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.329108159666511e-10</v>
+        <v>5.197848440355634e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.467668959620243e-10</v>
+        <v>7.205735511573736e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.315424383657975e-10</v>
+        <v>5.191911881517469e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.705062151077198e-10</v>
+        <v>7.415265978089067e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.357584932166963e-10</v>
+        <v>5.229933887126964e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.339653141508657e-10</v>
+        <v>5.215887986659921e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.880835201327248e-10</v>
+        <v>7.693519331667838e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.327923579611732e-10</v>
+        <v>5.190060293642773e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.39641727199947e-10</v>
+        <v>5.329835731448866e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.716024513100305e-10</v>
+        <v>4.620098733410936e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.757687261591963e-10</v>
+        <v>4.625801707152445e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.720116541262261e-10</v>
+        <v>4.604272018047126e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.580533353129611e-10</v>
+        <v>4.457410075392912e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.592429032125456e-10</v>
+        <v>4.478017297653254e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.234205282025641e-10</v>
+        <v>4.867040293571238e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.571974412047856e-10</v>
+        <v>4.452206858652837e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.715483318820394e-10</v>
+        <v>4.600281216286131e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.947253566985516e-10</v>
+        <v>4.73576252251521e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.907813017920402e-10</v>
+        <v>4.793337705341704e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.012896051886841e-10</v>
+        <v>5.001625458662414e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.496245684949404e-10</v>
+        <v>5.182621350518366e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.796082726115635e-10</v>
+        <v>4.664944841330009e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.233150175603978e-10</v>
+        <v>7.83199811051776e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.880652131742335e-10</v>
+        <v>4.667412437782032e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.612405120471824e-10</v>
+        <v>4.499155086489872e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.587860242728215e-10</v>
+        <v>4.487161874391359e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.791861281667741e-10</v>
+        <v>4.620567256227708e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.679842708610885e-10</v>
+        <v>4.525980923176206e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.464102132574688e-10</v>
+        <v>8.175506846948152e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.578859806994386e-10</v>
+        <v>4.480393839359026e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.690231888129554e-10</v>
+        <v>8.298815211502567e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.883108330461533e-10</v>
+        <v>4.755099850881151e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.753907910723751e-10</v>
+        <v>4.653675362524934e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.920500116207567e-10</v>
+        <v>8.701598872492122e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.670249622093347e-10</v>
+        <v>4.469395843687013e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.168719701520228e-10</v>
+        <v>5.472824862891624e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0087087762636e-10</v>
+        <v>4.606072415469129e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.669053200687493e-10</v>
+        <v>4.246908608711783e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>5.01044215856838e-10</v>
+        <v>4.57627994201822e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.802810651936029e-10</v>
+        <v>4.357054867965467e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.80851750035193e-10</v>
+        <v>4.376618842872362e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.833089550142117e-10</v>
+        <v>4.998896521175376e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.775252377280833e-10</v>
+        <v>4.334965462976617e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.002840909343499e-10</v>
+        <v>4.569698702716135e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.374397100682976e-10</v>
+        <v>4.788101341413564e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.310629182098648e-10</v>
+        <v>4.878560806340066e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.477803254370653e-10</v>
+        <v>5.209416694503923e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>6.263674585805607e-10</v>
+        <v>5.516368322846793e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>5.131738370503292e-10</v>
+        <v>2.102631491862216e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.921263009169832e-10</v>
+        <v>4.421692987392203e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.269860242430283e-10</v>
+        <v>4.680913008311304e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.841526319499465e-10</v>
+        <v>4.411418686320158e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.800975240709056e-10</v>
+        <v>4.390708596958944e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.129778280822372e-10</v>
+        <v>4.607145450039242e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.946830717487304e-10</v>
+        <v>4.452672709115144e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.446889452569062e-10</v>
+        <v>5.125088908352192e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.789419752444453e-10</v>
+        <v>4.383462531196453e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.131319263692051e-10</v>
+        <v>4.686560340235182e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.268488962842461e-10</v>
+        <v>4.815092590432091e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.04750791638043e-10</v>
+        <v>4.643760614780729e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.01136296344297e-10</v>
+        <v>4.573378368206167e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.933450340834821e-10</v>
+        <v>4.364702009268911e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.71557545537999e-10</v>
+        <v>5.941018386533677e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.863143511834705e-09</v>
+        <v>1.845956456891273e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.348732336008477e-09</v>
+        <v>1.296113068757332e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.033088041270969e-09</v>
+        <v>1.956342583108897e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.173834480723293e-09</v>
+        <v>1.077762735662101e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.64566403088774e-09</v>
+        <v>1.573340655106414e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>3.271424293989935e-09</v>
+        <v>2.518361369247773e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.614132945968576e-09</v>
+        <v>1.522851985250025e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.028150011879073e-09</v>
+        <v>1.953217843762318e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.538890766886957e-09</v>
+        <v>2.204515940202846e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.490724648368425e-09</v>
+        <v>2.420508453200257e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.776444176440291e-09</v>
+        <v>3.003601290837697e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.323019777362137e-09</v>
+        <v>3.669417676325327e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.726031973733132e-09</v>
+        <v>2.102631491862216e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.704092268777076e-09</v>
+        <v>1.523433459416669e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.335723133108857e-09</v>
+        <v>1.988887348389293e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.659103508670982e-09</v>
+        <v>1.591837246744682e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.642348070589036e-09</v>
+        <v>1.613437467801049e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.055291018883849e-09</v>
+        <v>1.836335321494346e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.90831464751395e-09</v>
+        <v>1.712076013603085e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.759390404134225e-09</v>
+        <v>2.880734941796555e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.431076558323901e-09</v>
+        <v>1.406125724859248e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.192264242385454e-09</v>
+        <v>2.097476755774135e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.517919889305847e-09</v>
+        <v>2.404204242965934e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.067075142445152e-09</v>
+        <v>2.03869539540374e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.875751537409357e-09</v>
+        <v>1.797251224145742e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.819687236032533e-09</v>
+        <v>1.4900883578664e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.578385217416366e-09</v>
+        <v>4.871518920263423e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.464053235874297e-10</v>
+        <v>5.604231002648443e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.609777211275978e-10</v>
+        <v>5.245067195891086e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.465786618179098e-10</v>
+        <v>5.574438529197549e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>9.258155111546716e-10</v>
+        <v>8.80037684763709e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>9.26386195996262e-10</v>
+        <v>5.374777430051672e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>6.773813560730613e-10</v>
+        <v>9.442218500846994e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>9.230596836891527e-10</v>
+        <v>5.333124050155903e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.943564919931991e-10</v>
+        <v>5.567857289895449e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>6.315121111271486e-10</v>
+        <v>5.786259928592866e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>6.251353192687138e-10</v>
+        <v>9.321882786011659e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.933147713981339e-10</v>
+        <v>9.652738674175537e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07190190454163e-09</v>
+        <v>6.514526910026106e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>6.073535533216628e-10</v>
+        <v>2.102631491862216e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.863060171883191e-10</v>
+        <v>8.847794617450705e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.716344998502461e-10</v>
+        <v>9.107097399394832e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.296870779110156e-10</v>
+        <v>5.409577273499464e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>9.256319700319762e-10</v>
+        <v>8.834030576630556e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>9.585122740433066e-10</v>
+        <v>5.605304037218553e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.887554728075807e-10</v>
+        <v>5.450831296294448e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.920667134124907e-10</v>
+        <v>9.581087956466429e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>9.244764212055168e-10</v>
+        <v>5.381621118375767e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.174472749073909e-10</v>
+        <v>5.78576664217296e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>6.209212973430926e-10</v>
+        <v>9.258414570103691e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.09249827887023e-10</v>
+        <v>5.74023975541476e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.952086974031477e-10</v>
+        <v>9.016700347877778e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.388794800445508e-10</v>
+        <v>8.808023988940512e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.661808093290175e-10</v>
+        <v>6.948563241079735e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.335107665068346e-09</v>
+        <v>1.27420576483712e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.301142107510735e-09</v>
+        <v>1.238289384161386e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.335281003298825e-09</v>
+        <v>1.27122651749203e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.314517852635589e-09</v>
+        <v>1.249304010086753e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.315088537477178e-09</v>
+        <v>1.251260407577444e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.417545742456198e-09</v>
+        <v>1.313488175407746e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.311762025170071e-09</v>
+        <v>1.247095069587868e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.334520878376334e-09</v>
+        <v>1.270568393561821e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.371676497510289e-09</v>
+        <v>1.292408657431564e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.36529970565185e-09</v>
+        <v>1.301454603924215e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.382017112879053e-09</v>
+        <v>1.334540192740598e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.460604246022548e-09</v>
+        <v>1.365235355574887e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.347410624492315e-09</v>
+        <v>2.102631491862216e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32633080314752e-09</v>
+        <v>1.255735778929448e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361190526473558e-09</v>
+        <v>1.281657781021362e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.318389419391934e-09</v>
+        <v>1.254740391922225e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.314334311512892e-09</v>
+        <v>1.252669382986104e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.347214615524223e-09</v>
+        <v>1.274313068294132e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.328919859190719e-09</v>
+        <v>1.258865794201722e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38076579355904e-09</v>
+        <v>1.327350684328372e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.313178762686431e-09</v>
+        <v>1.251944776409855e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.347368713811193e-09</v>
+        <v>1.282254557313724e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.361085683726231e-09</v>
+        <v>1.295107782333419e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.340830901274541e-09</v>
+        <v>1.279242291612543e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.335373083786285e-09</v>
+        <v>1.270936360110824e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.327581821525471e-09</v>
+        <v>1.250068724217099e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.405794332979986e-09</v>
+        <v>1.407700361943577e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.283162698179865e-09</v>
+        <v>1.224988770149327e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.816261091595192e-09</v>
+        <v>1.739462336465647e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.850399987383279e-09</v>
+        <v>1.772399469796289e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.527692010151294e-09</v>
+        <v>1.457410551090992e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.351485506743464e-09</v>
+        <v>1.287787734096774e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.050249130858845e-09</v>
+        <v>1.92878806868328e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.826881009254525e-09</v>
+        <v>1.748268021892125e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.849639862460792e-09</v>
+        <v>1.77174134586608e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.88679548159474e-09</v>
+        <v>1.793581609735821e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.880418689736309e-09</v>
+        <v>1.802627556228473e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.897136096963508e-09</v>
+        <v>1.835713145044858e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.975723230107e-09</v>
+        <v>1.86640830787913e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.42296017886106e-09</v>
+        <v>2.102631491862216e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.522710138772993e-09</v>
+        <v>1.447542041834794e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.527959476937097e-09</v>
+        <v>1.444724325432203e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.155003443513437e-09</v>
+        <v>1.097359210593939e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.829453295597347e-09</v>
+        <v>1.753842335290364e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.862333599608676e-09</v>
+        <v>1.775486020598393e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.844038843275172e-09</v>
+        <v>1.760038746505982e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.619134185865732e-09</v>
+        <v>1.559915980982414e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.673335427619201e-09</v>
+        <v>1.602694359181426e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.862599142290226e-09</v>
+        <v>1.783535677087071e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.249672245776526e-09</v>
+        <v>1.188170933333668e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.419807143246137e-09</v>
+        <v>2.32766552486522e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.272894612870951e-09</v>
+        <v>1.211495589581182e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.842700805609926e-09</v>
+        <v>1.751241676521357e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.513259031045786e-09</v>
+        <v>2.483801636807898e-09</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.091936668826262e-09</v>
+        <v>1.029159932892054e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.251902974381683e-09</v>
+        <v>1.178645065990341e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.286041870169769e-09</v>
+        <v>1.211582199320984e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.220520197712108e-09</v>
+        <v>1.146869939876161e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>8.187832573395913e-10</v>
+        <v>7.64214725909706e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.368306818866318e-09</v>
+        <v>1.253844066674595e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.26252289204102e-09</v>
+        <v>1.187450751416821e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.285281745247282e-09</v>
+        <v>1.210924075390775e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.322437364381234e-09</v>
+        <v>1.232764339260515e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3160605725228e-09</v>
+        <v>1.241810285753167e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33277797975e-09</v>
+        <v>1.274895874569554e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.41136511289349e-09</v>
+        <v>1.305591037403841e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.298171491363265e-09</v>
+        <v>2.102631491862216e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.341392999713732e-09</v>
+        <v>1.257565601605949e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.390230091972689e-09</v>
+        <v>1.296850160239899e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.269150495802051e-09</v>
+        <v>1.195096283189071e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.265095178383839e-09</v>
+        <v>1.193025064815058e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.297975482395168e-09</v>
+        <v>1.214668750123084e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.279680726061665e-09</v>
+        <v>1.199221476030677e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.331529921764352e-09</v>
+        <v>1.267730802798643e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.487732875049678e-09</v>
+        <v>1.406249870433562e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.298129580682138e-09</v>
+        <v>1.222610239142681e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.311846550597178e-09</v>
+        <v>1.23546346416237e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.291591768145498e-09</v>
+        <v>1.219597973441498e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.1692103654999e-09</v>
+        <v>1.099511498845397e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.278342688396417e-09</v>
+        <v>1.190424406046051e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.356555199850936e-09</v>
+        <v>1.348056043772533e-09</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.212615794336085e-10</v>
+        <v>5.127503827787366e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.357932067048118e-10</v>
+        <v>5.265761733446636e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.223335161525072e-10</v>
+        <v>5.137960316170158e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.208479907678783e-10</v>
+        <v>5.123532329703418e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.215394331902234e-10</v>
+        <v>5.130610209903345e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.282333208587673e-10</v>
+        <v>5.169265927470364e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.209074411836202e-10</v>
+        <v>5.123958950695998e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.220594365288351e-10</v>
+        <v>5.135937283982902e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.239080166163922e-10</v>
+        <v>5.145909192109333e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.227466408088816e-10</v>
+        <v>5.144200259980354e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.238587819927209e-10</v>
+        <v>5.157466127059592e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.217277489153612e-10</v>
+        <v>5.130191548950537e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.208926794662476e-10</v>
+        <v>5.123969090754414e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.223217844712425e-10</v>
+        <v>7.053292669866863e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.231435262050622e-10</v>
+        <v>5.139970249864388e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.222318411082266e-10</v>
+        <v>5.136790865175958e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.219449313973648e-10</v>
+        <v>5.135183150322425e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.220319598179194e-10</v>
+        <v>5.135062304422192e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.209835085945435e-10</v>
+        <v>5.126462290014405e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.169275456950514e-10</v>
+        <v>7.004850784175676e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.213256635824683e-10</v>
+        <v>5.128334444737785e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.445092630355654e-10</v>
+        <v>7.26877084579236e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.246720786047016e-10</v>
+        <v>5.161098560615512e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.265890728923811e-10</v>
+        <v>5.181798130310448e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.699483452941495e-10</v>
+        <v>7.579224360786756e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.215992393364619e-10</v>
+        <v>5.129758225706339e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.273713071259429e-10</v>
+        <v>5.219306153759235e-10</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.485432574368551e-10</v>
+        <v>4.409756702661674e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.708748633247439e-10</v>
+        <v>4.623455084008989e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.563697499074792e-10</v>
+        <v>4.486118492774137e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.449828570626754e-10</v>
+        <v>4.375307054255642e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.507190356730977e-10</v>
+        <v>4.43382963384238e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.979377242340376e-10</v>
+        <v>4.705660280700841e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.462724132683806e-10</v>
+        <v>4.38698001029407e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.544535364313743e-10</v>
+        <v>4.472084199842949e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.673550440860852e-10</v>
+        <v>4.540790658375605e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.592196502441592e-10</v>
+        <v>4.529619200335645e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.670354067355558e-10</v>
+        <v>4.62300016694184e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.613660514565796e-10</v>
+        <v>4.523499838647698e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.460383185736123e-10</v>
+        <v>4.385787514553233e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.767086175055599e-10</v>
+        <v>7.546045898200059e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.618972528482205e-10</v>
+        <v>4.498167123176375e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.555198024861247e-10</v>
+        <v>4.476560266674695e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.536648816931281e-10</v>
+        <v>4.466998333885826e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.539987402905039e-10</v>
+        <v>4.463286528931102e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.467353597081686e-10</v>
+        <v>4.404087947581199e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.760434208235913e-10</v>
+        <v>7.560056908951535e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.48883997633364e-10</v>
+        <v>4.414554089229671e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.342556008380379e-10</v>
+        <v>8.109805555943211e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.730257723130881e-10</v>
+        <v>4.650919133036387e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.866580532198919e-10</v>
+        <v>4.798160228115407e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.611910516202526e-10</v>
+        <v>8.477763664582019e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.510568144412267e-10</v>
+        <v>4.426863307756955e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.930807432027996e-10</v>
+        <v>5.071861242456295e-10</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.578617680212838e-10</v>
+        <v>4.245292281758823e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.544996146086482e-10</v>
+        <v>4.215970627477849e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.699697863764938e-10</v>
+        <v>4.363403128264829e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.531900937816743e-10</v>
+        <v>4.200432383921294e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.610002540212962e-10</v>
+        <v>4.2803802967652e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.366107945779568e-10</v>
+        <v>4.717014409193329e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.538616135760414e-10</v>
+        <v>4.205251264287844e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.668739309442575e-10</v>
+        <v>4.340552049068986e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.876878694158931e-10</v>
+        <v>4.452603219420333e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.746362194169721e-10</v>
+        <v>4.43388616411693e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.871983656986548e-10</v>
+        <v>4.583730235377284e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.803218199908418e-10</v>
+        <v>4.446839478850853e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.536948731875702e-10</v>
+        <v>1.317427773214493e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.501521132466011e-10</v>
+        <v>4.157048217527939e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.791192225431632e-10</v>
+        <v>4.386106253956327e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.688213199785099e-10</v>
+        <v>4.350193641311242e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.655805428093387e-10</v>
+        <v>4.332033762455234e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.665635688545576e-10</v>
+        <v>4.330668752420272e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.547208299751569e-10</v>
+        <v>4.233527633482237e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.648030414328328e-10</v>
+        <v>4.33249522945062e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.583586412906576e-10</v>
+        <v>4.25295481186511e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.930664969368014e-10</v>
+        <v>4.583963773664244e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.963849250658992e-10</v>
+        <v>4.624760243393419e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.16688714441883e-10</v>
+        <v>4.849973465678e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.623592622526135e-10</v>
+        <v>4.289308953623912e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.616757919552428e-10</v>
+        <v>4.270756743327922e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.277771181707414e-10</v>
+        <v>5.285323073989097e-10</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.362458828253519e-09</v>
+        <v>1.322830622550626e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.380393776378871e-09</v>
+        <v>1.347193596308197e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.66783047688611e-09</v>
+        <v>1.621553610751429e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>9.644423436437408e-10</v>
+        <v>9.271191346765219e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.517841492566949e-09</v>
+        <v>1.483483219526255e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.567046464095705e-09</v>
+        <v>2.045491873100593e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.424716096785833e-09</v>
+        <v>1.382773665713848e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.633755678132255e-09</v>
+        <v>1.602083759316055e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.851726170286066e-09</v>
+        <v>1.673575701573037e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.69927179200139e-09</v>
+        <v>1.692625783992241e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.858411745495758e-09</v>
+        <v>1.890374440917035e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.839315773178084e-09</v>
+        <v>1.759665477576221e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.509450201225083e-09</v>
+        <v>1.317427773214493e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.238213510354319e-09</v>
+        <v>1.181451415810188e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.698242361815284e-09</v>
+        <v>1.542704452104307e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.583109071926191e-09</v>
+        <v>1.535392191338974e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.625687775035351e-09</v>
+        <v>1.602379164863251e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.494205064341071e-09</v>
+        <v>1.452306035255245e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.398480453128758e-09</v>
+        <v>1.39347670069056e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.521907912434651e-09</v>
+        <v>1.502813990854655e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.314593144976654e-09</v>
+        <v>1.280653439249472e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.037831749909338e-09</v>
+        <v>1.97354803866596e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.117191402918291e-09</v>
+        <v>2.066282311953683e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.474564519276231e-09</v>
+        <v>2.45427959671217e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.421411560266835e-09</v>
+        <v>1.380670511790999e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.483636053952253e-09</v>
+        <v>1.420564647925587e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.827743998830862e-09</v>
+        <v>3.433464839360914e-09</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.462317034971636e-10</v>
+        <v>8.36561792077949e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.666140212746423e-10</v>
+        <v>8.336296266498517e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.583397218523736e-10</v>
+        <v>8.483728767285485e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.653045004476691e-10</v>
+        <v>5.131731806382826e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.731146606872933e-10</v>
+        <v>5.211679719226726e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>6.24980730053837e-10</v>
+        <v>5.648313831654863e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.659760202420373e-10</v>
+        <v>5.136550686749373e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.789883376102528e-10</v>
+        <v>8.460877688089661e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.760578048917724e-10</v>
+        <v>8.57292885844101e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.867506260829679e-10</v>
+        <v>5.365185586578461e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.755683011745353e-10</v>
+        <v>8.70405587439795e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>8.924362266568365e-10</v>
+        <v>5.378138901312386e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.421313867134206e-10</v>
+        <v>1.317427773214493e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.385886267724518e-10</v>
+        <v>8.261290633093135e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.570609097830509e-10</v>
+        <v>5.213986798694273e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.809357266445056e-10</v>
+        <v>5.281493063772768e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.776949494753345e-10</v>
+        <v>8.452359401475906e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.549335043304379e-10</v>
+        <v>5.261968174881794e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.430907654510368e-10</v>
+        <v>5.164827055943771e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>5.545225198730195e-10</v>
+        <v>8.461418808163513e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>8.704730479566521e-10</v>
+        <v>5.184254234326648e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.909020430686483e-10</v>
+        <v>5.60903774099624e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.847548605417799e-10</v>
+        <v>8.745085882414093e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.143278156530064e-10</v>
+        <v>5.868838012211394e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.507291977284948e-10</v>
+        <v>8.409634592644585e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.737901986212377e-10</v>
+        <v>5.202056165789452e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.165681044360669e-10</v>
+        <v>6.222500104723018e-10</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.223594225759509e-09</v>
+        <v>1.175515265839223e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.220232072346873e-09</v>
+        <v>1.172583100411125e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.235702244114719e-09</v>
+        <v>1.187326350489825e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2189225515199e-09</v>
+        <v>1.171029276055471e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.226732711759522e-09</v>
+        <v>1.17902406733986e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.302343252316181e-09</v>
+        <v>1.222687478582675e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.219594071314266e-09</v>
+        <v>1.171511164092127e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.232606388682482e-09</v>
+        <v>1.18504124257024e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.253420327154119e-09</v>
+        <v>1.196246359605374e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.240368677155196e-09</v>
+        <v>1.194374654075034e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25293082343688e-09</v>
+        <v>1.20935906120107e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.246054277729067e-09</v>
+        <v>1.195669985548427e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.219427330925795e-09</v>
+        <v>1.317427773214493e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.215854612148041e-09</v>
+        <v>1.166661072805811e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.244821721444602e-09</v>
+        <v>1.18956687644865e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.234553777716734e-09</v>
+        <v>1.186005401794464e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.231313000547565e-09</v>
+        <v>1.184189413908865e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.232296026592783e-09</v>
+        <v>1.184052912905368e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.220453287713382e-09</v>
+        <v>1.174338801011565e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.231971942598961e-09</v>
+        <v>1.185126365266435e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.224091099028882e-09</v>
+        <v>1.176281518849853e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.258798954675026e-09</v>
+        <v>1.209382415029766e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.262117382804125e-09</v>
+        <v>1.213462062002685e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.283770715144415e-09</v>
+        <v>1.236843178200364e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.228091719990838e-09</v>
+        <v>1.179916933025734e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.227408249693468e-09</v>
+        <v>1.178061711996133e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.293509575908966e-09</v>
+        <v>1.27951834506225e-09</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.162110065663492e-09</v>
+        <v>1.119917962123513e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.669483912357129e-09</v>
+        <v>1.618317536794478e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.684954084124976e-09</v>
+        <v>1.633060786873175e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.396222537228995e-09</v>
+        <v>1.349819349184964e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.244815251390906e-09</v>
+        <v>1.20152838955143e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85749952908932e-09</v>
+        <v>1.772376317152675e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.668845911324524e-09</v>
+        <v>1.617245600475479e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.681858228692738e-09</v>
+        <v>1.630775678953591e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.702672167164373e-09</v>
+        <v>1.641980795988725e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.689620517165454e-09</v>
+        <v>1.640109090458384e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.702182663447135e-09</v>
+        <v>1.655093497584421e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.695306117739325e-09</v>
+        <v>1.641404421931747e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.272773326600712e-09</v>
+        <v>1.317427773214493e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.378028930313464e-09</v>
+        <v>1.330604369022817e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.380326931737434e-09</v>
+        <v>1.327332127152412e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.072698336601014e-09</v>
+        <v>1.031884968794682e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.680564840557822e-09</v>
+        <v>1.629923850292217e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.681547866603038e-09</v>
+        <v>1.62978734928872e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.669705127723638e-09</v>
+        <v>1.620073237394916e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.431944020342524e-09</v>
+        <v>1.386183576270342e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.533850977722278e-09</v>
+        <v>1.485046399559645e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.708151169015052e-09</v>
+        <v>1.655215377527783e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.147071910989669e-09</v>
+        <v>1.105289679182685e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.240990662072976e-09</v>
+        <v>2.181120955209192e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.157120376474845e-09</v>
+        <v>1.115007134848697e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.676660089703724e-09</v>
+        <v>1.623796148379484e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.27626787514582e-09</v>
+        <v>2.248935704715019e-09</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.671446336635688e-10</v>
+        <v>9.203443318034351e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.132163248393807e-09</v>
+        <v>1.080425280555058e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.147633420161653e-09</v>
+        <v>1.095168530633756e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.091992296727993e-09</v>
+        <v>1.04124885469385e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.504999840894231e-10</v>
+        <v>7.110762567355264e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.214274641097141e-09</v>
+        <v>1.130529867161193e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1315252473612e-09</v>
+        <v>1.079353344236057e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.144537564729414e-09</v>
+        <v>1.092883422714172e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.165351503201052e-09</v>
+        <v>1.104088539749305e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.15229985320213e-09</v>
+        <v>1.102216834218966e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.164861999483814e-09</v>
+        <v>1.117201241345001e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.157985453776001e-09</v>
+        <v>1.103512165692359e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.131358506972728e-09</v>
+        <v>1.317427773214493e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.183617196352388e-09</v>
+        <v>1.128555649661378e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.224720117218512e-09</v>
+        <v>1.163210398798374e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.146485166497695e-09</v>
+        <v>1.093847790372982e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.143244176594498e-09</v>
+        <v>1.092031594052796e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.144227202639717e-09</v>
+        <v>1.0918950930493e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.132384463760316e-09</v>
+        <v>1.082180981155496e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.143816218182299e-09</v>
+        <v>1.092937534721558e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.330330158069539e-09</v>
+        <v>1.272237419795731e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17073013072196e-09</v>
+        <v>1.117224595173697e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.174048558851057e-09</v>
+        <v>1.121304242146615e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19570189119135e-09</v>
+        <v>1.144685358344295e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.038504350324071e-09</v>
+        <v>9.894767837780706e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.139339425740401e-09</v>
+        <v>1.085903892140065e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.205440751955901e-09</v>
+        <v>1.187360525206182e-09</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -798,7 +798,7 @@
         <v>5.951278492036231e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.513277329215015e-09</v>
+        <v>5.093611829660402e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.930299884108517e-10</v>
@@ -974,7 +974,7 @@
         <v>1.074407406367704e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.513277329215015e-09</v>
+        <v>6.103558620165358e-10</v>
       </c>
       <c r="O6" t="n">
         <v>5.940246048475644e-10</v>
@@ -1062,7 +1062,7 @@
         <v>1.504405686410443e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.513277329215015e-09</v>
+        <v>1.418639020172861e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.402273097932817e-09</v>
@@ -1150,7 +1150,7 @@
         <v>2.123701689681094e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.513277329215015e-09</v>
+        <v>1.541040224266172e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.661260035038454e-09</v>
@@ -1238,7 +1238,7 @@
         <v>1.499342483324443e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.513277329215015e-09</v>
+        <v>1.413575817086863e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.470871436650505e-09</v>
@@ -1658,7 +1658,7 @@
         <v>4.29020310484379e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>4.199072486644411e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.135357866215628e-10</v>
@@ -1834,7 +1834,7 @@
         <v>5.232436382456378e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>5.14246091772904e-10</v>
       </c>
       <c r="O6" t="n">
         <v>8.223396620189937e-10</v>
@@ -1922,7 +1922,7 @@
         <v>1.17648481932446e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>1.167371757504515e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.160970564021574e-09</v>
@@ -2010,7 +2010,7 @@
         <v>1.610595778331579e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>1.217681163941588e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.316781701069695e-09</v>
@@ -2098,7 +2098,7 @@
         <v>1.054901533171803e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>1.04578847135187e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.091013844163316e-09</v>
@@ -2518,7 +2518,7 @@
         <v>5.664916766869213e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>4.596847890552572e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.644263542304369e-10</v>
@@ -2694,7 +2694,7 @@
         <v>1.013694039958247e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>5.558106342595712e-10</v>
       </c>
       <c r="O6" t="n">
         <v>5.605249100152386e-10</v>
@@ -2782,7 +2782,7 @@
         <v>1.404706486736699e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>1.297899599105037e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.302608831564928e-09</v>
@@ -2870,7 +2870,7 @@
         <v>1.956824560347839e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>1.398297044096357e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.527175360283274e-09</v>
@@ -2958,7 +2958,7 @@
         <v>1.350671467234546e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>1.243864579602885e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.312771198629964e-09</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.317365516493956e-10</v>
+        <v>5.317365516493969e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.427913972493869e-10</v>
+        <v>5.42791397249387e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.32302079191079e-10</v>
+        <v>5.323020791910758e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.290860008535743e-10</v>
+        <v>5.290860008535753e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.285800692847646e-10</v>
+        <v>5.285800692847647e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.338804060193316e-10</v>
+        <v>5.338804060193333e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.275343138096681e-10</v>
+        <v>5.275343138096685e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.302984589839375e-10</v>
+        <v>5.302984589839388e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.323855239649691e-10</v>
+        <v>5.323855239649696e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.298781051793126e-10</v>
+        <v>5.298781051793136e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.357101084984788e-10</v>
+        <v>5.357101084984797e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.36027412271625e-10</v>
+        <v>5.360274122716252e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.277784966021475e-10</v>
+        <v>5.27778496602148e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.431658565311672e-10</v>
+        <v>7.431658565311645e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.32050213787174e-10</v>
+        <v>5.320502137871734e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.291226042117174e-10</v>
+        <v>5.291226042117177e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.275797705613774e-10</v>
+        <v>5.275797705613781e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.321121708146667e-10</v>
+        <v>5.321121708146687e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.280973477534954e-10</v>
+        <v>5.280973477534951e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.440673818746111e-10</v>
+        <v>7.44067381874613e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.296073925395367e-10</v>
+        <v>5.296073925395379e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.691073186771887e-10</v>
+        <v>7.691073186771853e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.333041454857642e-10</v>
+        <v>5.333041454857651e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.347308663063973e-10</v>
+        <v>5.347308663063985e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.85479342877576e-10</v>
+        <v>7.854793428775745e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.286767184346348e-10</v>
+        <v>5.286767184346353e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.436369455765956e-10</v>
+        <v>5.436369455765964e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.787425483830111e-10</v>
+        <v>4.787425483830094e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.736706502438215e-10</v>
+        <v>4.736706502438217e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.831075037190014e-10</v>
+        <v>4.831075037189989e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.592889984646148e-10</v>
+        <v>4.592889984646131e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.56507349405939e-10</v>
+        <v>4.565073494059374e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.939837925833472e-10</v>
+        <v>4.939837925833455e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.490744055235486e-10</v>
+        <v>4.490744055235476e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.688102871764972e-10</v>
+        <v>4.688102871764961e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.834681633225577e-10</v>
+        <v>4.834681633225552e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.656515040996283e-10</v>
+        <v>4.656515040996269e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.072346847418037e-10</v>
+        <v>5.072346847418034e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.189559467018109e-10</v>
+        <v>5.189559467018114e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.507021217962923e-10</v>
+        <v>4.507021217962893e-10</v>
       </c>
       <c r="O3" t="n">
         <v>8.120189960102913e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.809464835026286e-10</v>
+        <v>4.809464835026262e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.602979957436005e-10</v>
+        <v>4.602979957435993e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.493606253518013e-10</v>
+        <v>4.493606253517999e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.814382145853532e-10</v>
+        <v>4.814382145853519e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.53032814402062e-10</v>
+        <v>4.530328144020603e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.482269874900453e-10</v>
+        <v>8.482269874900482e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.634581041081025e-10</v>
+        <v>4.634581041080991e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.799391041207137e-10</v>
+        <v>8.799391041207103e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.902294037822471e-10</v>
+        <v>4.90229403782246e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.002936619265402e-10</v>
+        <v>5.002936619265423e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.922249954269665e-10</v>
+        <v>8.922249954269669e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.570898432151242e-10</v>
+        <v>4.570898432151221e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.644790266603297e-10</v>
+        <v>5.644790266603305e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.78218560089118e-10</v>
+        <v>4.782185600891182e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.300493079655635e-10</v>
+        <v>4.300493079655637e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.846064538279089e-10</v>
+        <v>4.846064538279112e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.482793695367124e-10</v>
+        <v>4.482793695367129e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.425646397269813e-10</v>
+        <v>4.425646397269817e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.024343814192844e-10</v>
+        <v>5.024343814192858e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.307523505644894e-10</v>
+        <v>4.307523505644901e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.619746418774637e-10</v>
+        <v>4.619746418774631e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.854941069366897e-10</v>
+        <v>4.854941069366899e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.572265522819109e-10</v>
+        <v>4.572265522819116e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.231017126259778e-10</v>
+        <v>5.231017126259787e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.433570283603922e-10</v>
+        <v>5.43357028360392e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.316294400634626e-09</v>
+        <v>4.335105075351658e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.457431933876855e-10</v>
+        <v>4.457431933876856e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.817615182270215e-10</v>
+        <v>4.817615182270228e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.486928213053088e-10</v>
+        <v>4.486928213053096e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.312658054861721e-10</v>
+        <v>4.312658054861715e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.824613513542121e-10</v>
+        <v>4.82461351354213e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.371120779684108e-10</v>
+        <v>4.371120779684114e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.153161476503534e-10</v>
+        <v>5.153161476503573e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.540216464722602e-10</v>
+        <v>4.540216464722598e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.971297663172299e-10</v>
+        <v>4.9712976631723e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.959252535996964e-10</v>
+        <v>4.959252535996978e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.11080094868704e-10</v>
+        <v>5.110800948687052e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.672568349610516e-10</v>
+        <v>4.672568349610522e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.436563363355669e-10</v>
+        <v>4.436563363355664e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.122563672541996e-10</v>
+        <v>6.122563672541986e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.999027085160536e-09</v>
+        <v>1.999027085160532e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.269843475671804e-09</v>
+        <v>1.269843475671805e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.282377557838559e-09</v>
+        <v>2.282377557838554e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.191508332877e-09</v>
+        <v>1.191508332876996e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.520150871912371e-09</v>
+        <v>1.520150871912374e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.396462884532324e-09</v>
+        <v>2.396462884532306e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.32712244555518e-09</v>
+        <v>1.327122445555183e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.883506583139094e-09</v>
+        <v>1.88350658313909e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.177267418047516e-09</v>
+        <v>2.177267418047513e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.717288072741904e-09</v>
+        <v>1.717288072741898e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.861608960613641e-09</v>
+        <v>2.861608960613632e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.426545919439217e-09</v>
+        <v>3.426545919439199e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.316294400634626e-09</v>
+        <v>1.316294400634628e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.449223177982682e-09</v>
+        <v>1.449223177982691e-09</v>
       </c>
       <c r="P5" t="n">
         <v>2.043714386043225e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.586327188954179e-09</v>
+        <v>1.586327188954172e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.316403790437112e-09</v>
+        <v>1.31640379043711e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0817652972206e-09</v>
+        <v>2.081765297220587e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.408515152594919e-09</v>
+        <v>1.408515152594925e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.694030809477031e-09</v>
+        <v>2.694030809477232e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.527640843394191e-09</v>
+        <v>1.527640843394213e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.430517458618938e-09</v>
+        <v>2.430517458618933e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.467075826973538e-09</v>
+        <v>2.467075826973532e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.690788397997651e-09</v>
+        <v>2.690788397997663e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.783273716322136e-09</v>
+        <v>1.783273716322125e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.48385589719695e-09</v>
+        <v>1.483855897196943e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.893454221233073e-09</v>
+        <v>4.893454221233065e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.947519034731369e-10</v>
+        <v>8.947519034731387e-10</v>
       </c>
       <c r="C6" t="n">
         <v>5.206937797959315e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.011397972119263e-10</v>
+        <v>9.011397972119296e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.648127129207329e-10</v>
+        <v>8.648127129207342e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.332091115573499e-10</v>
+        <v>5.332091115573492e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.930788532496532e-10</v>
+        <v>5.930788532496539e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.21396822394858e-10</v>
+        <v>5.213968223948571e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.526191137078322e-10</v>
+        <v>5.526191137078328e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.020274503207106e-10</v>
+        <v>9.020274503207098e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.737598956659326e-10</v>
+        <v>8.737598956659316e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.396350560099971e-10</v>
+        <v>9.396350560099965e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.340015001907614e-10</v>
+        <v>6.340015001907598e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.316294400634626e-09</v>
+        <v>5.24299321634364e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.6008539619322e-10</v>
+        <v>8.600853961932171e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.9611536611055e-10</v>
+        <v>8.961153661105487e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.6522616468933e-10</v>
+        <v>8.652261646893305e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.219102773165401e-10</v>
+        <v>5.219102773165408e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>8.98994694738232e-10</v>
+        <v>8.989946947382332e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.277565497987794e-10</v>
+        <v>5.277565497987775e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.069212462047706e-10</v>
+        <v>6.069212462047771e-10</v>
       </c>
       <c r="V6" t="n">
         <v>8.70554989856279e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.114671590422456e-10</v>
+        <v>9.114671590422434e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.865697254300654e-10</v>
+        <v>5.86569725430066e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.108148840106939e-10</v>
+        <v>6.108148840106925e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.837901783450724e-10</v>
+        <v>8.837901783450714e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.601896797195838e-10</v>
+        <v>8.601896797195864e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.037982417985961e-10</v>
+        <v>7.03798241798594e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3609,61 +3609,61 @@
         <v>1.251692617319674e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.203523365196122e-09</v>
+        <v>1.203523365196121e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.258080511058466e-09</v>
+        <v>1.258080511058469e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.22175342676727e-09</v>
+        <v>1.221753426767271e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.216038696957538e-09</v>
+        <v>1.216038696957539e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.275908438649844e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.204226407795046e-09</v>
+        <v>1.204226407795048e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.235448699108021e-09</v>
+        <v>1.23544869910802e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.258968164167247e-09</v>
+        <v>1.258968164167248e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.230700609512468e-09</v>
+        <v>1.230700609512469e-09</v>
       </c>
       <c r="L7" t="n">
         <v>1.296575769856536e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.316831085590949e-09</v>
+        <v>1.316831085590951e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.316294400634626e-09</v>
+        <v>1.206984564765722e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.219187176743519e-09</v>
+        <v>1.219187176743522e-09</v>
       </c>
       <c r="P7" t="n">
         <v>1.255205501582858e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.222166878535867e-09</v>
+        <v>1.222166878535868e-09</v>
       </c>
       <c r="R7" t="n">
         <v>1.204739862716729e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25593540858477e-09</v>
+        <v>1.255935408584772e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.210586135198967e-09</v>
+        <v>1.21058613519897e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.289756550083394e-09</v>
+        <v>1.289756550083409e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.227495703702819e-09</v>
@@ -3675,10 +3675,10 @@
         <v>1.269399310830255e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28551477882331e-09</v>
+        <v>1.285514778823311e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.240730892191608e-09</v>
+        <v>1.240730892191607e-09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.217130393566126e-09</v>
@@ -3694,82 +3694,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.213807019283716e-09</v>
+        <v>1.213807019283717e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.696804045293285e-09</v>
+        <v>1.696804045293288e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.751361191155631e-09</v>
+        <v>1.751361191155637e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.43220373216988e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.260902597191735e-09</v>
+        <v>1.260902597191738e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.879329906749454e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.697507087892211e-09</v>
+        <v>1.697507087892214e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.728729379205185e-09</v>
+        <v>1.728729379205189e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.75224884426441e-09</v>
+        <v>1.752248844264412e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.723981289609634e-09</v>
+        <v>1.723981289609637e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.789856449953699e-09</v>
+        <v>1.789856449953701e-09</v>
       </c>
       <c r="M8" t="n">
         <v>1.810111765688086e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.316294400634626e-09</v>
+        <v>1.288522517145288e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4139056797134e-09</v>
+        <v>1.413905679713405e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.422188088607002e-09</v>
+        <v>1.422188088607001e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.079894983550216e-09</v>
+        <v>1.079894983550219e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.698020542813894e-09</v>
+        <v>1.698020542813896e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.749216088681933e-09</v>
+        <v>1.749216088681936e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.703866815296135e-09</v>
+        <v>1.703866815296136e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.523804078978927e-09</v>
+        <v>1.523804078978926e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.575631225426535e-09</v>
+        <v>1.575631225426543e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.763988893107966e-09</v>
+        <v>1.763988893107968e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.175809860721491e-09</v>
+        <v>1.175809860721492e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.306969451141911e-09</v>
+        <v>2.306969451141914e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.192978607832666e-09</v>
+        <v>1.192978607832667e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.710411073663291e-09</v>
+        <v>1.710411073663293e-09</v>
       </c>
       <c r="AB8" t="n">
         <v>2.433858697557773e-09</v>
@@ -3782,25 +3782,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.98546368872052e-10</v>
+        <v>9.985463688720495e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.122037502003191e-09</v>
+        <v>1.122037502003194e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.176594647865542e-09</v>
+        <v>1.176594647865539e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.100649201553173e-09</v>
+        <v>1.100649201553172e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.388285326662234e-10</v>
+        <v>7.38828532666223e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.194422776581233e-09</v>
+        <v>1.19442277658123e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.122740544602124e-09</v>
+        <v>1.122740544602119e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.153962835915094e-09</v>
@@ -3809,16 +3809,16 @@
         <v>1.17748230097432e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.149214746319543e-09</v>
+        <v>1.14921474631954e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.215089906663608e-09</v>
+        <v>1.215089906663607e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.235345222398025e-09</v>
+        <v>1.23534522239802e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.316294400634626e-09</v>
+        <v>1.125498701572799e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.194619682105362e-09</v>
@@ -3827,40 +3827,40 @@
         <v>1.243010191257719e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.140681216467253e-09</v>
+        <v>1.140681216467252e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.123253999523802e-09</v>
+        <v>1.123253999523801e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.174449545391844e-09</v>
+        <v>1.174449545391842e-09</v>
       </c>
       <c r="T9" t="n">
         <v>1.129100272006042e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.208264968412034e-09</v>
+        <v>1.208264968412048e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34410228798706e-09</v>
+        <v>1.344102287987059e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.189117960354861e-09</v>
+        <v>1.189117960354862e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.187913447637326e-09</v>
+        <v>1.187913447637327e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.204028915630386e-09</v>
+        <v>1.204028915630385e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.055749161191398e-09</v>
+        <v>1.055749161191397e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.135644530373195e-09</v>
+        <v>1.135644530373197e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.304244561291832e-09</v>
+        <v>1.304244561291826e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2857703993488e-10</v>
+        <v>5.285770399348776e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.396787614265281e-10</v>
+        <v>5.396787614265292e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.287307160766484e-10</v>
+        <v>5.287307160766478e-10</v>
       </c>
       <c r="E2" t="n">
         <v>5.260062463059889e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.265299175588467e-10</v>
+        <v>5.265299175588464e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.307064922646786e-10</v>
+        <v>5.307064922646766e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.252254961170971e-10</v>
+        <v>5.252254961170972e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.273339522302119e-10</v>
+        <v>5.273339522302103e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.295609146395659e-10</v>
+        <v>5.295609146395643e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.272549121617078e-10</v>
+        <v>5.272549121617083e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.319436523653594e-10</v>
+        <v>5.31943652365358e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.321780068662938e-10</v>
+        <v>5.32178006866292e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.246188175131118e-10</v>
+        <v>5.246188175131105e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.350107186854332e-10</v>
+        <v>7.350107186854325e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.290715083187994e-10</v>
+        <v>5.290715083187995e-10</v>
       </c>
       <c r="Q2" t="n">
         <v>5.264385106475814e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.260133113906978e-10</v>
+        <v>5.260133113906954e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.294454737921844e-10</v>
+        <v>5.29445473792184e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.261324300729318e-10</v>
+        <v>5.261324300729315e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.366363486699353e-10</v>
+        <v>7.366363486699341e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.285837916632269e-10</v>
+        <v>5.285837916632261e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.605552945380481e-10</v>
+        <v>7.605552945380504e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.316918030583243e-10</v>
+        <v>5.316918030583241e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.365428473806929e-10</v>
+        <v>5.365428473806925e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.809264061952091e-10</v>
+        <v>7.809264061952071e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.264048671231796e-10</v>
+        <v>5.264048671231791e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.400167504004617e-10</v>
+        <v>5.40016750400462e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.721057474657227e-10</v>
+        <v>4.721057474657218e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.693410877215122e-10</v>
+        <v>4.693410877215123e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.734784321005167e-10</v>
+        <v>4.734784321005118e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.532357963249064e-10</v>
+        <v>4.532357963249034e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.578148377179953e-10</v>
+        <v>4.578148377179933e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.872254803093553e-10</v>
+        <v>4.872254803093526e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.48545756907144e-10</v>
+        <v>4.485457569071408e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.635651028462158e-10</v>
+        <v>4.635651028462124e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.792165501984892e-10</v>
+        <v>4.792165501984862e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.628737168370746e-10</v>
+        <v>4.628737168370719e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.961963299930887e-10</v>
+        <v>4.961963299930883e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.072788906357305e-10</v>
+        <v>5.072788906357352e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.440877733394862e-10</v>
+        <v>4.440877733394834e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.989438615284742e-10</v>
+        <v>7.989438615284722e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.755909068003773e-10</v>
+        <v>4.755909068003742e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.570590957454277e-10</v>
+        <v>4.570590957454256e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.541525069475903e-10</v>
+        <v>4.541525069475888e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.783267034375883e-10</v>
+        <v>4.783267034375878e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.549633045810529e-10</v>
+        <v>4.549633045810534e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.404408578826558e-10</v>
+        <v>8.404408578826543e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.720192564934819e-10</v>
+        <v>4.720192564934827e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.681877871954358e-10</v>
+        <v>8.681877871954352e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.945826965863377e-10</v>
+        <v>4.945826965863367e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.292527247712391e-10</v>
+        <v>5.292527247712331e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.86549494659822e-10</v>
+        <v>8.865494946598194e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.568212916834032e-10</v>
+        <v>4.568212916833999e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.545201522481596e-10</v>
+        <v>5.545201522481587e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4202,82 +4202,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.699611008464813e-10</v>
+        <v>4.699611008464831e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.263156167664166e-10</v>
+        <v>4.263156167664158e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.716969435622675e-10</v>
+        <v>4.716969435622676e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.409228041846569e-10</v>
+        <v>4.409228041846583e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.468379118863676e-10</v>
+        <v>4.468379118863684e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.940142445080242e-10</v>
+        <v>4.940142445080244e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.321038716382912e-10</v>
+        <v>4.321038716382905e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.55919853373655e-10</v>
+        <v>4.55919853373653e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.810311332328809e-10</v>
+        <v>4.810311332328783e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.550270594396754e-10</v>
+        <v>4.550270594396772e-10</v>
       </c>
       <c r="L4" t="n">
         <v>5.07988536966977e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.273814373610646e-10</v>
+        <v>5.273814373610627e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.176722493707848e-09</v>
+        <v>4.252511577203292e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.411173251146555e-10</v>
+        <v>4.411173251146562e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.75546348709542e-10</v>
+        <v>4.75546348709541e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.458054287743677e-10</v>
+        <v>4.458054287743672e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.410026075665414e-10</v>
+        <v>4.410026075665421e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.797704607640409e-10</v>
+        <v>4.797704607640391e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.42348107879676e-10</v>
+        <v>4.423481078796758e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.199305370061201e-10</v>
+        <v>5.199305370061196e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.699689957237989e-10</v>
+        <v>4.69968995723795e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.965994097397378e-10</v>
+        <v>4.965994097397367e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.05143783187611e-10</v>
+        <v>5.051437831876104e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.59527836236444e-10</v>
+        <v>5.595278362364493e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.657972096660348e-10</v>
+        <v>4.657972096660345e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.454254096894584e-10</v>
+        <v>4.454254096894577e-10</v>
       </c>
       <c r="AB4" t="n">
         <v>5.989481455193677e-10</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.847234146397726e-09</v>
+        <v>1.847234146397729e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.214000179508522e-09</v>
+        <v>1.21400017950852e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.020908576929547e-09</v>
+        <v>2.020908576929501e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.063094990107764e-09</v>
+        <v>1.063094990107765e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.603837615198971e-09</v>
+        <v>1.603837615198959e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23208985791055e-09</v>
+        <v>2.232089857910564e-09</v>
       </c>
       <c r="H5" t="n">
         <v>1.364302475526152e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.77059712536252e-09</v>
+        <v>1.770597125362518e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.089787255482625e-09</v>
+        <v>2.089787255482627e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.688850530197446e-09</v>
+        <v>1.688850530197437e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.552409358493213e-09</v>
+        <v>2.552409358493208e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.056911917772113e-09</v>
+        <v>3.056911917772085e-09</v>
       </c>
       <c r="N5" t="n">
         <v>1.176722493707848e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.384434894725478e-09</v>
+        <v>1.384434894725455e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.923275574106132e-09</v>
+        <v>1.923275574106158e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.532009485262258e-09</v>
+        <v>1.532009485262256e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.513437622252147e-09</v>
+        <v>1.513437622252145e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.032596332327923e-09</v>
+        <v>2.032596332327931e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.516838552501655e-09</v>
+        <v>1.51683855250165e-09</v>
       </c>
       <c r="U5" t="n">
         <v>2.716980701963347e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.77872096542264e-09</v>
+        <v>1.778720965422645e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.432828550086143e-09</v>
+        <v>2.432828550086144e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.597359219821312e-09</v>
+        <v>2.597359219821269e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.591309437059962e-09</v>
+        <v>3.591309437059973e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.730774271997542e-09</v>
+        <v>1.730774271997537e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.526486070489993e-09</v>
+        <v>1.526486070489992e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.591589344060355e-09</v>
+        <v>4.59158934406038e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.618972303415881e-10</v>
+        <v>5.618972303415843e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.18251746261523e-10</v>
+        <v>5.182517462615219e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.884027348364258e-10</v>
+        <v>8.884027348364286e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.576285954588169e-10</v>
+        <v>8.57628595458816e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.387740413814735e-10</v>
+        <v>5.387740413814723e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.859503740031315e-10</v>
+        <v>5.859503740031251e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.488096629124469e-10</v>
+        <v>8.488096629124521e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.478559828687603e-10</v>
+        <v>5.478559828687586e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.977369245070397e-10</v>
+        <v>8.9773692450703e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.717328507138347e-10</v>
+        <v>8.717328507138302e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.999246664620843e-10</v>
+        <v>5.99924666462083e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1931756685617e-10</v>
+        <v>6.193175668561706e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.176722493707848e-09</v>
+        <v>5.174159578654648e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.332623219026582e-10</v>
+        <v>5.332623219026576e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.901440840601359e-10</v>
+        <v>8.901440840601302e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.625112200485244e-10</v>
+        <v>8.625112200485228e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.577083988407e-10</v>
+        <v>8.577083988406988e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.717065902591469e-10</v>
+        <v>5.717065902591484e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.590538991538369e-10</v>
+        <v>8.590538991538358e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.370470524432341e-10</v>
+        <v>9.370470524432337e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.619051252189062e-10</v>
+        <v>5.619051252189032e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.98224425331704e-10</v>
+        <v>5.982244253317039e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.970799126827167e-10</v>
+        <v>5.97079912682714e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.601607419820142e-10</v>
+        <v>6.601607419820157e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.577333391611412e-10</v>
+        <v>5.577333391611405e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.621312009636162e-10</v>
+        <v>8.621312009636174e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.917434100914024e-10</v>
+        <v>6.91743410091403e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.238746609112041e-09</v>
+        <v>1.238746609112045e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.195101125031975e-09</v>
+        <v>1.195101125031973e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.240482451827827e-09</v>
+        <v>1.240482451827825e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.209708312450215e-09</v>
+        <v>1.209708312450212e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.215623420151927e-09</v>
+        <v>1.215623420151925e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.262799752773584e-09</v>
+        <v>1.262799752773568e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.20088937990385e-09</v>
+        <v>1.200889379903849e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.224705361639213e-09</v>
+        <v>1.224705361639216e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.24981664149844e-09</v>
+        <v>1.249816641498442e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.223812567705235e-09</v>
+        <v>1.223812567705232e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.276774045232537e-09</v>
+        <v>1.276774045232534e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.296166945626623e-09</v>
+        <v>1.296166945626617e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.176722493707848e-09</v>
+        <v>1.194036665985886e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.209872783107173e-09</v>
+        <v>1.20987278310717e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.244301806702059e-09</v>
+        <v>1.244301806702057e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.214590937039927e-09</v>
+        <v>1.214590937039922e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.209788115832102e-09</v>
+        <v>1.209788115832099e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.248555969029601e-09</v>
+        <v>1.248555969029598e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.211133616145234e-09</v>
+        <v>1.211133616145235e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.289229904511284e-09</v>
+        <v>1.289229904511286e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.238754503989357e-09</v>
+        <v>1.238754503989346e-09</v>
       </c>
       <c r="W7" t="n">
         <v>1.265384918005297e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.273929291453168e-09</v>
+        <v>1.273929291453165e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.328724068664961e-09</v>
+        <v>1.328724068664957e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.234582717931592e-09</v>
+        <v>1.23458271793159e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.214210917955018e-09</v>
+        <v>1.214210917955017e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.367733653784927e-09</v>
+        <v>1.36773365378494e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.194911011085566e-09</v>
+        <v>1.194911011085562e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.674926733202486e-09</v>
+        <v>1.674926733202487e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.720308059998338e-09</v>
+        <v>1.720308059998335e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.410699775347114e-09</v>
+        <v>1.41069977534711e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.253368117901201e-09</v>
+        <v>1.253368117901199e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.851209923389297e-09</v>
+        <v>1.851209923389295e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.68071498807436e-09</v>
+        <v>1.680714988074357e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.704530969809722e-09</v>
+        <v>1.704530969809721e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.72964224966895e-09</v>
+        <v>1.729642249668944e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.703638175875745e-09</v>
+        <v>1.703638175875744e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.756599653403046e-09</v>
+        <v>1.756599653403044e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.775992553797113e-09</v>
+        <v>1.775992553797112e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.176722493707848e-09</v>
+        <v>1.267937232759584e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.395355126152573e-09</v>
+        <v>1.395355126152571e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.402440126233876e-09</v>
+        <v>1.40244012623388e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.067843959995118e-09</v>
+        <v>1.067843959995115e-09</v>
       </c>
       <c r="R8" t="n">
         <v>1.68961372400261e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.728381577200111e-09</v>
+        <v>1.728381577200109e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.690959224315746e-09</v>
+        <v>1.690959224315742e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.513463547504285e-09</v>
+        <v>1.51346354750428e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.575569452229528e-09</v>
+        <v>1.57556945222953e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.745313440673594e-09</v>
+        <v>1.745313440673592e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.175176904527302e-09</v>
+        <v>1.1751769045273e-09</v>
       </c>
       <c r="Y8" t="n">
         <v>2.329390666354036e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.181019844146805e-09</v>
+        <v>1.181019844146801e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.694036526125529e-09</v>
+        <v>1.694036526125524e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.394567179726707e-09</v>
+        <v>2.394567179726698e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4642,49 +4642,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.681026392518848e-10</v>
+        <v>9.681026392518817e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.089657350821833e-09</v>
+        <v>1.089657350821834e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.135038677617684e-09</v>
+        <v>1.135038677617687e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.066137161138806e-09</v>
+        <v>1.066137161138804e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.293478458670956e-10</v>
+        <v>7.293478458670962e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.157356179050435e-09</v>
+        <v>1.157356179050434e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.095445605693706e-09</v>
+        <v>1.09544560569371e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.119261587429071e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.144372867288297e-09</v>
+        <v>1.144372867288294e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.118368793495093e-09</v>
+        <v>1.118368793495089e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.171330271022393e-09</v>
+        <v>1.17133027102239e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.190723171416482e-09</v>
+        <v>1.19072317141648e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.176722493707848e-09</v>
+        <v>1.088592891775747e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.159206454625496e-09</v>
+        <v>1.159206454625489e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.205542053822299e-09</v>
+        <v>1.205542053822292e-09</v>
       </c>
       <c r="Q9" t="n">
         <v>1.109147363316782e-09</v>
@@ -4693,10 +4693,10 @@
         <v>1.104344341621956e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.143112194819457e-09</v>
+        <v>1.143112194819461e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.105689841935092e-09</v>
+        <v>1.105689841935087e-09</v>
       </c>
       <c r="U9" t="n">
         <v>1.183682995224491e-09</v>
@@ -4705,22 +4705,22 @@
         <v>1.323948265195137e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.159941143795154e-09</v>
+        <v>1.159941143795153e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.168485517243027e-09</v>
+        <v>1.168485517243022e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.223280294454816e-09</v>
+        <v>1.223280294454824e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.029537995530246e-09</v>
+        <v>1.029537995530245e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.108767143744874e-09</v>
+        <v>1.108767143744871e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.262289879574784e-09</v>
+        <v>1.26228987957479e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>4.655149329677643e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>4.463579408137483e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.200952118299599e-10</v>
@@ -5274,7 +5274,7 @@
         <v>9.053506976212327e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>5.481136779949639e-10</v>
       </c>
       <c r="O6" t="n">
         <v>8.582145732464039e-10</v>
@@ -5362,7 +5362,7 @@
         <v>1.265414039853894e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>1.246257047699878e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.219962381823743e-09</v>
@@ -5450,7 +5450,7 @@
         <v>1.736718120093193e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>1.305320013362866e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.392344722130601e-09</v>
@@ -5538,7 +5538,7 @@
         <v>1.187547262598627e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>1.168390270444611e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.200972299633094e-09</v>
@@ -5806,7 +5806,7 @@
         <v>6.701909674101591e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.013620943461928e-10</v>
+        <v>5.013620943461927e-10</v>
       </c>
       <c r="W2" t="n">
         <v>6.957775636077873e-10</v>
@@ -5815,7 +5815,7 @@
         <v>5.041900543053837e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.026984144298089e-10</v>
+        <v>5.026984144298088e-10</v>
       </c>
       <c r="Z2" t="n">
         <v>7.397921763552683e-10</v>
@@ -5876,7 +5876,7 @@
         <v>7.211867035465177e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.26362332414237e-10</v>
+        <v>4.263623324142369e-10</v>
       </c>
       <c r="Q3" t="n">
         <v>4.308287989954856e-10</v>
@@ -5931,7 +5931,7 @@
         <v>4.3297567329816e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.065772067395494e-10</v>
+        <v>4.065772067395493e-10</v>
       </c>
       <c r="F4" t="n">
         <v>4.23759725936498e-10</v>
@@ -5958,7 +5958,7 @@
         <v>4.220112960504977e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.384556298573703e-09</v>
+        <v>4.166799599050532e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.108961285439616e-10</v>
@@ -5988,7 +5988,7 @@
         <v>4.528572460058631e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.49430794767745e-10</v>
+        <v>4.494307947677449e-10</v>
       </c>
       <c r="Y4" t="n">
         <v>4.322202736037577e-10</v>
@@ -6037,7 +6037,7 @@
         <v>1.404377970115716e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.500593685487828e-09</v>
+        <v>1.500593685487827e-09</v>
       </c>
       <c r="L5" t="n">
         <v>1.479700390316298e-09</v>
@@ -6134,7 +6134,7 @@
         <v>8.309803243311325e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.384556298573703e-09</v>
+        <v>5.126980370763956e-10</v>
       </c>
       <c r="O6" t="n">
         <v>8.183332802738364e-10</v>
@@ -6146,7 +6146,7 @@
         <v>8.228792062924004e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.221760869549969e-10</v>
+        <v>5.221760869549968e-10</v>
       </c>
       <c r="S6" t="n">
         <v>8.313979312469374e-10</v>
@@ -6222,7 +6222,7 @@
         <v>1.157069612037921e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.384556298573703e-09</v>
+        <v>1.151738275892475e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.145924870847546e-09</v>
@@ -6280,7 +6280,7 @@
         <v>1.554649115685468e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.577727588231765e-09</v>
+        <v>1.577727588231766e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.296137750627747e-09</v>
@@ -6310,7 +6310,7 @@
         <v>1.5667632109841e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.384556298573703e-09</v>
+        <v>1.189925839397326e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.286235092338288e-09</v>
@@ -6392,13 +6392,13 @@
         <v>1.052139698817278e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.05555876262417e-09</v>
+        <v>1.055558762624169e-09</v>
       </c>
       <c r="M9" t="n">
         <v>1.051303693381738e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.384556298573703e-09</v>
+        <v>1.045972357236293e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.091742934699874e-09</v>
@@ -6410,13 +6410,13 @@
         <v>1.043202781843733e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.055551022815488e-09</v>
+        <v>1.055551022815489e-09</v>
       </c>
       <c r="S9" t="n">
         <v>1.051721300297543e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.04333166070021e-09</v>
+        <v>1.043331660700211e-09</v>
       </c>
       <c r="U9" t="n">
         <v>1.04356278302523e-09</v>
@@ -6818,7 +6818,7 @@
         <v>4.191636589593262e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.383109448861235e-09</v>
+        <v>4.170229751622913e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.120820462449256e-10</v>
@@ -6994,7 +6994,7 @@
         <v>8.305114170550966e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.383109448861235e-09</v>
+        <v>5.138738864748978e-10</v>
       </c>
       <c r="O6" t="n">
         <v>5.089092114804107e-10</v>
@@ -7082,7 +7082,7 @@
         <v>1.152546661389805e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.383109448861235e-09</v>
+        <v>1.15040597759277e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.145435525502924e-09</v>
@@ -7170,7 +7170,7 @@
         <v>1.555469260292045e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.383109448861235e-09</v>
+        <v>1.184306076489764e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.280775734770642e-09</v>
@@ -7258,7 +7258,7 @@
         <v>1.028651661112651e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.383109448861235e-09</v>
+        <v>1.026510977315616e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.071716968677217e-09</v>
@@ -7678,7 +7678,7 @@
         <v>5.516368322846793e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>2.102631491862216e-09</v>
+        <v>4.673364679902732e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.421692987392203e-10</v>
@@ -7854,7 +7854,7 @@
         <v>6.514526910026106e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>2.102631491862216e-09</v>
+        <v>5.673142857868345e-10</v>
       </c>
       <c r="O6" t="n">
         <v>8.847794617450705e-10</v>
@@ -7942,7 +7942,7 @@
         <v>1.365235355574887e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.102631491862216e-09</v>
+        <v>1.28093499128048e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.255735778929448e-09</v>
@@ -8030,7 +8030,7 @@
         <v>1.86640830787913e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.102631491862216e-09</v>
+        <v>1.355463656452872e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.447542041834794e-09</v>
@@ -8118,7 +8118,7 @@
         <v>1.305591037403841e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.102631491862216e-09</v>
+        <v>1.221290673109434e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.257565601605949e-09</v>
@@ -8538,7 +8538,7 @@
         <v>4.446839478850853e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.317427773214493e-09</v>
+        <v>4.205365800912249e-10</v>
       </c>
       <c r="O4" t="n">
         <v>4.157048217527939e-10</v>
@@ -8714,7 +8714,7 @@
         <v>5.378138901312386e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.317427773214493e-09</v>
+        <v>5.137578095029329e-10</v>
       </c>
       <c r="O6" t="n">
         <v>8.261290633093135e-10</v>
@@ -8802,7 +8802,7 @@
         <v>1.195669985548427e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.317427773214493e-09</v>
+        <v>1.171522617754568e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.166661072805811e-09</v>
@@ -8890,7 +8890,7 @@
         <v>1.641404421931747e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.317427773214493e-09</v>
+        <v>1.228641084604484e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.330604369022817e-09</v>
@@ -8978,7 +8978,7 @@
         <v>1.103512165692359e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.317427773214493e-09</v>
+        <v>1.079364797898498e-09</v>
       </c>
       <c r="O9" t="n">
         <v>1.128555649661378e-09</v>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.463350399950662e-10</v>
+        <v>5.463350399950688e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.566409182810974e-10</v>
+        <v>5.566409182810968e-10</v>
       </c>
       <c r="D2" t="n">
         <v>5.437747928212817e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.413850846182864e-10</v>
+        <v>5.413850846182849e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.419965723545119e-10</v>
+        <v>5.419965723545135e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.469774847293357e-10</v>
+        <v>5.469774847293355e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.417742460407256e-10</v>
+        <v>5.417742460407257e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.442570036359376e-10</v>
+        <v>5.442570036359364e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.454049694833294e-10</v>
+        <v>5.454049694833311e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.47875269366498e-10</v>
+        <v>5.47875269366499e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.495618211097335e-10</v>
+        <v>5.495618211097298e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.508167853264101e-10</v>
+        <v>5.508167853264086e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.446978530106121e-10</v>
+        <v>5.446978530106119e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.794812284623043e-10</v>
+        <v>7.79481228462303e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.440006820984992e-10</v>
+        <v>5.440006820984984e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.414039406885866e-10</v>
+        <v>5.41403940688584e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.414918486672363e-10</v>
+        <v>5.414918486672356e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.446232639314269e-10</v>
+        <v>5.44623263931427e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.430159990910536e-10</v>
+        <v>5.430159990910559e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.833122721035108e-10</v>
+        <v>7.833122721035118e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.425933292949138e-10</v>
+        <v>5.425933292949132e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>8.05901524709959e-10</v>
+        <v>8.059015247099546e-10</v>
       </c>
       <c r="X2" t="n">
         <v>5.433583777265464e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.441964549356359e-10</v>
+        <v>5.44196454935635e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.084158133055745e-10</v>
+        <v>8.084158133055733e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.41878994853187e-10</v>
+        <v>5.418789948531869e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.578555737762103e-10</v>
+        <v>5.578555737762095e-10</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.039254990513439e-10</v>
+        <v>5.067528487288616e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.85996076865679e-10</v>
+        <v>4.87232890034794e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.860577024389669e-10</v>
+        <v>4.882693865725161e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.681387067931344e-10</v>
+        <v>4.696147137461067e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.73395094261016e-10</v>
+        <v>4.751607995121436e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.085753031214825e-10</v>
+        <v>5.115646000101219e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.718474892095622e-10</v>
+        <v>4.735585101813037e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.895488937338291e-10</v>
+        <v>4.918862379821099e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.974574519610227e-10</v>
+        <v>5.00060010127191e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.153725553452698e-10</v>
+        <v>5.1862178951462e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.271796557493943e-10</v>
+        <v>5.308327996317888e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.456463229842169e-10</v>
+        <v>5.500348567154257e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.925678703795427e-10</v>
+        <v>4.950062793527099e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.71924039275439e-10</v>
+        <v>8.739789929180864e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.873443566215607e-10</v>
+        <v>4.895848555699861e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.690468960942268e-10</v>
+        <v>4.706540117330964e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.697698395169668e-10</v>
+        <v>4.714057872263424e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.918366515723401e-10</v>
+        <v>4.942415110138896e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.806370041668763e-10</v>
+        <v>4.826568893298429e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.240486037601669e-10</v>
+        <v>9.281868424946573e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.772296199229701e-10</v>
+        <v>4.791187393172305e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.24711702221403e-10</v>
+        <v>9.27192028905829e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.830461821189937e-10</v>
+        <v>4.851506919645164e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.889387831829121e-10</v>
+        <v>4.912474953407337e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.233379269836608e-10</v>
+        <v>9.255599992689334e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.723913764442237e-10</v>
+        <v>4.741142072096202e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.869615553295345e-10</v>
+        <v>5.92737085882571e-10</v>
       </c>
     </row>
     <row r="4">
@@ -762,82 +762,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.278539630987049e-10</v>
+        <v>5.278539630987047e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.556029312365732e-10</v>
+        <v>4.556029312365717e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.989347934989025e-10</v>
+        <v>4.98934793498893e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.719419400259566e-10</v>
+        <v>4.719419400259562e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.788489753049216e-10</v>
+        <v>4.788489753049195e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.351106719114338e-10</v>
+        <v>5.351106719114321e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.763376973155262e-10</v>
+        <v>4.763376973155256e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>5.043815864783575e-10</v>
+        <v>5.043815864783565e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>5.173000419988158e-10</v>
+        <v>5.173000419988136e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.452515623895238e-10</v>
+        <v>5.452515623895236e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.643019401814586e-10</v>
+        <v>5.643019401814582e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.951278492036231e-10</v>
+        <v>5.951278492036172e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>5.093611829660402e-10</v>
+        <v>5.0936118296604e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.930299884108517e-10</v>
+        <v>4.930299884108391e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>5.014863167992645e-10</v>
+        <v>5.014863167992544e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.721549280142036e-10</v>
+        <v>4.721549280142033e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.731478890727428e-10</v>
+        <v>4.731478890727425e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>5.085186650039876e-10</v>
+        <v>5.085186650039829e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.903638692536289e-10</v>
+        <v>4.903638692536275e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.849051698081356e-10</v>
+        <v>5.849051698081295e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.854865348122859e-10</v>
+        <v>4.854865348122849e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.115111492096298e-10</v>
+        <v>5.115111492096281e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.942311934434479e-10</v>
+        <v>4.942311934434485e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.023658279055335e-10</v>
+        <v>5.023658279055292e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.004292380824816e-10</v>
+        <v>5.004292380824813e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.775208833391105e-10</v>
+        <v>4.775208833391098e-10</v>
       </c>
       <c r="AB4" t="n">
         <v>6.574072979529895e-10</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.69129623603007e-09</v>
+        <v>2.691296236030003e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.421779736162714e-09</v>
+        <v>1.421779736162709e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.349528101263999e-09</v>
+        <v>2.349528101263808e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.292711840886585e-09</v>
+        <v>1.292711840886583e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.962065067111062e-09</v>
+        <v>1.962065067111035e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.875851870210899e-09</v>
+        <v>2.875851870210878e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.934761487268682e-09</v>
+        <v>1.934761487268679e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.488711582602199e-09</v>
+        <v>2.488711582602202e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.58067567571185e-09</v>
+        <v>2.580675675711815e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>3.311696676376759e-09</v>
+        <v>3.311696676376753e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.558687250907498e-09</v>
+        <v>3.558687250907495e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.454857823689363e-09</v>
+        <v>4.45485782368924e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.513277329215015e-09</v>
+        <v>2.513277329215007e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>2.02720925174244e-09</v>
+        <v>2.027209251742198e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.207432314895757e-09</v>
+        <v>2.207432314895638e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.756797377524902e-09</v>
+        <v>1.7567973775249e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.833577527877228e-09</v>
+        <v>1.833577527877225e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.378110820512817e-09</v>
+        <v>2.378110820512805e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>2.173867464006194e-09</v>
+        <v>2.173867464006193e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>3.941546644881726e-09</v>
+        <v>3.941546644881579e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.845367915879351e-09</v>
+        <v>1.845367915879354e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.517990060444773e-09</v>
+        <v>2.51799006044477e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.23130413640702e-09</v>
+        <v>2.231304136406954e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.369161511032239e-09</v>
+        <v>2.369161511032113e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.210767804694137e-09</v>
+        <v>2.210767804694132e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.837513173851547e-09</v>
+        <v>1.837513173851546e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.9698153636282e-09</v>
+        <v>5.969815363628201e-09</v>
       </c>
     </row>
     <row r="6">
@@ -941,79 +941,79 @@
         <v>6.286053064078741e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>9.348824884006454e-10</v>
+        <v>9.348824884006456e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.782143506629735e-10</v>
+        <v>9.782143506629685e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>9.512214971900305e-10</v>
+        <v>9.512214971900307e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.796003186140914e-10</v>
+        <v>5.796003186140887e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.014390229075508e-09</v>
+        <v>1.014390229075507e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>9.556172544796012e-10</v>
+        <v>9.556172544796001e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>6.051329297875246e-10</v>
+        <v>6.051329297875242e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>6.180513853079852e-10</v>
+        <v>6.180513853079824e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.024531119553598e-09</v>
+        <v>1.024531119553599e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.043581497345531e-09</v>
+        <v>1.043581497345533e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.074407406367704e-09</v>
+        <v>1.074407406367691e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.103558620165358e-10</v>
+        <v>6.103558620165349e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.940246048475644e-10</v>
+        <v>5.940246048475578e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.780336611064409e-10</v>
+        <v>9.780336611064357e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.514344851782772e-10</v>
+        <v>9.514344851782774e-10</v>
       </c>
       <c r="R6" t="n">
         <v>9.524274462368165e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>6.092700083131551e-10</v>
+        <v>6.09270008313151e-10</v>
       </c>
       <c r="T6" t="n">
         <v>5.911152125627971e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.869883462664456e-10</v>
+        <v>6.869883462664424e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>9.647660919763598e-10</v>
+        <v>9.647660919763577e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.880585587546732e-10</v>
+        <v>9.880585587546719e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>9.735107506075219e-10</v>
+        <v>9.735107506075213e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.140147808017167e-10</v>
+        <v>6.140147808017129e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.011805813916512e-10</v>
+        <v>6.011805813916506e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.568004405031842e-10</v>
+        <v>9.568004405031832e-10</v>
       </c>
       <c r="AB6" t="n">
         <v>7.593388326474463e-10</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.437131800305525e-09</v>
+        <v>1.437131800305522e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.36488076844339e-09</v>
+        <v>1.364880768443389e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.408212630705725e-09</v>
+        <v>1.408212630705708e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.381219777232775e-09</v>
+        <v>1.381219777232772e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38812681251174e-09</v>
+        <v>1.388126812511737e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.444388509118252e-09</v>
+        <v>1.444388509118247e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.385615534522345e-09</v>
+        <v>1.385615534522342e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.413659423685175e-09</v>
+        <v>1.413659423685172e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.426577879205633e-09</v>
+        <v>1.42657787920563e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.454529399596343e-09</v>
+        <v>1.454529399596341e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.473579777388279e-09</v>
+        <v>1.473579777388275e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.504405686410443e-09</v>
+        <v>1.504405686410434e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.418639020172861e-09</v>
+        <v>1.418639020172858e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.402273097932817e-09</v>
+        <v>1.402273097932798e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.410729426321227e-09</v>
+        <v>1.410729426321214e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.381432765221022e-09</v>
+        <v>1.381432765221021e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.382425726279564e-09</v>
+        <v>1.382425726279558e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.417796502210806e-09</v>
+        <v>1.417796502210799e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.399641706460448e-09</v>
+        <v>1.399641706460445e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.495464165135048e-09</v>
+        <v>1.495464165135045e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.394764372019103e-09</v>
+        <v>1.394764372019101e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.420788986416448e-09</v>
+        <v>1.420788986416445e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.40350903065027e-09</v>
+        <v>1.403509030650266e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.412975498261499e-09</v>
+        <v>1.412975498261489e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.409707075289303e-09</v>
+        <v>1.409707075289299e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.386798720545928e-09</v>
+        <v>1.386798720545926e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.566685135159808e-09</v>
+        <v>1.566685135159805e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.415411597736131e-09</v>
+        <v>1.415411597736128e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.984176771714035e-09</v>
+        <v>1.984176771714034e-09</v>
       </c>
       <c r="D8" t="n">
         <v>2.02750863397636e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.659193559670535e-09</v>
+        <v>1.659193559670533e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.466269443108632e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.196603398508552e-09</v>
+        <v>2.196603398508551e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>2.004911537792989e-09</v>
+        <v>2.004911537792994e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.032955426955823e-09</v>
+        <v>2.032955426955826e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.045873882476282e-09</v>
+        <v>2.04587388247628e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.073825402866986e-09</v>
+        <v>2.07382540286699e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.092875780658924e-09</v>
+        <v>2.092875780658921e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.123701689681094e-09</v>
+        <v>2.123701689681081e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.541040224266172e-09</v>
+        <v>1.541040224266174e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.661260035038454e-09</v>
+        <v>1.661260035038432e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.636244412480984e-09</v>
+        <v>1.636244412480974e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.233738247699306e-09</v>
+        <v>1.233738247699305e-09</v>
       </c>
       <c r="R8" t="n">
         <v>2.00172172955021e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>2.037092505481452e-09</v>
+        <v>2.037092505481448e-09</v>
       </c>
       <c r="T8" t="n">
         <v>2.018937709731091e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.801927030166309e-09</v>
+        <v>1.801927030166308e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.838847349538308e-09</v>
+        <v>1.838847349538314e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>2.040210967830786e-09</v>
+        <v>2.040210967830783e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.314564922168587e-09</v>
+        <v>1.314564922168585e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.669598182239766e-09</v>
+        <v>2.66959818223977e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.376079667590832e-09</v>
+        <v>1.376079667590831e-09</v>
       </c>
       <c r="AA8" t="n">
         <v>2.006094723816577e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.855576166418481e-09</v>
+        <v>2.855576166418482e-09</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.209899623825658e-09</v>
+        <v>1.20989962382566e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.359817565357394e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.40314942761972e-09</v>
+        <v>1.403149427619714e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.324881058804325e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>8.709031888745905e-10</v>
+        <v>8.709031888745869e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.439325536798189e-09</v>
+        <v>1.439325536798187e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.38055233143635e-09</v>
+        <v>1.380552331436349e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.408596220599181e-09</v>
+        <v>1.408596220599179e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.421514676119642e-09</v>
+        <v>1.421514676119637e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.449466196510347e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.468516574302284e-09</v>
+        <v>1.46851657430228e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.499342483324443e-09</v>
+        <v>1.499342483324437e-09</v>
       </c>
       <c r="N9" t="n">
         <v>1.413575817086863e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.470871436650505e-09</v>
+        <v>1.470871436650495e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.495340283698702e-09</v>
+        <v>1.495340283698692e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.376369792900963e-09</v>
+        <v>1.37636979290096e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.377362523193568e-09</v>
+        <v>1.377362523193565e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.412733299124816e-09</v>
+        <v>1.412733299124806e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.394578503374453e-09</v>
+        <v>1.394578503374451e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.490451637078102e-09</v>
+        <v>1.490451637078095e-09</v>
       </c>
       <c r="V9" t="n">
         <v>1.646079437391094e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.415725783330456e-09</v>
+        <v>1.415725783330451e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.398445827564275e-09</v>
+        <v>1.39844582756427e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.407912295175505e-09</v>
+        <v>1.407912295175495e-09</v>
       </c>
       <c r="Z9" t="n">
         <v>1.270695828917359e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.381735517459935e-09</v>
+        <v>1.381735517459931e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.561621932073816e-09</v>
+        <v>1.561621932073811e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.091314136844836e-10</v>
+        <v>5.091314136844868e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.225784815283206e-10</v>
+        <v>5.225784815283205e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.100515504461368e-10</v>
+        <v>5.100515504461373e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.085593698658594e-10</v>
+        <v>5.085593698658623e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.095928088777841e-10</v>
+        <v>5.095928088777837e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.099286458878716e-10</v>
+        <v>5.099286458878743e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.094138956386602e-10</v>
+        <v>5.094138956386612e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.101445541055579e-10</v>
+        <v>5.101445541055586e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.09934703410606e-10</v>
+        <v>5.09934703410605e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.101534284832617e-10</v>
+        <v>5.101534284832576e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.098490894829952e-10</v>
+        <v>5.098490894829959e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.081717217625309e-10</v>
+        <v>5.081717217625305e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.088833085173329e-10</v>
+        <v>5.088833085173341e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.973392357873451e-10</v>
+        <v>6.973392357873446e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.085702209408072e-10</v>
+        <v>5.085702209408068e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.092887926116366e-10</v>
+        <v>5.092887926116361e-10</v>
       </c>
       <c r="R2" t="n">
         <v>5.107014094023465e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.095910268834568e-10</v>
+        <v>5.095910268834584e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.089854427135086e-10</v>
+        <v>5.089854427135109e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.935223347738282e-10</v>
+        <v>6.935223347738318e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.097782667292361e-10</v>
+        <v>5.097782667292354e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.236919018682414e-10</v>
+        <v>7.23691901868241e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.127698571970541e-10</v>
+        <v>5.127698571970603e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.132226518931026e-10</v>
+        <v>5.13222651893103e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.533538920223219e-10</v>
+        <v>7.533538920223243e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.1012149784431e-10</v>
+        <v>5.101214978443104e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.108386095086277e-10</v>
+        <v>5.1083860950863e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.381430842107281e-10</v>
+        <v>4.394915941357445e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.580921150632367e-10</v>
+        <v>4.593489186144328e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.448702123318799e-10</v>
+        <v>4.464644609393824e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.334607980500482e-10</v>
+        <v>4.34551498038086e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.416340130050556e-10</v>
+        <v>4.431161956663964e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.438063779753066e-10</v>
+        <v>4.453547612925084e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.404318748263574e-10</v>
+        <v>4.418700285399803e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.455809442524184e-10</v>
+        <v>4.472007632803964e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.439185341604759e-10</v>
+        <v>4.454729081748126e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.455316317522803e-10</v>
+        <v>4.471502767664883e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.432990876924551e-10</v>
+        <v>4.448330445369327e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.408166320414989e-10</v>
+        <v>4.423226213929346e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.365086991983586e-10</v>
+        <v>4.378032502598392e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.443935797005104e-10</v>
+        <v>7.455384015681014e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.341455260230435e-10</v>
+        <v>4.353524756439916e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.393660439905271e-10</v>
+        <v>4.407644944775372e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.496125916825716e-10</v>
+        <v>4.513765458050043e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.414132163495868e-10</v>
+        <v>4.428793890905565e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.372852020934303e-10</v>
+        <v>4.386092009010383e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.479991410324358e-10</v>
+        <v>7.495813434202384e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.426315121848939e-10</v>
+        <v>4.441389906303954e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.312787538394468e-10</v>
+        <v>8.344191002386079e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.642052333172201e-10</v>
+        <v>4.664881176864854e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.67488313414939e-10</v>
+        <v>4.698770213390321e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.447352235636884e-10</v>
+        <v>8.462452245520326e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.453248096256128e-10</v>
+        <v>4.469298618320545e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.514212695330936e-10</v>
+        <v>4.532476061648272e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.227097106614178e-10</v>
+        <v>4.227097106614192e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.181280627933661e-10</v>
+        <v>4.181280627933672e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.331030786681071e-10</v>
+        <v>4.331030786681091e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.162482125768976e-10</v>
+        <v>4.162482125768978e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.279213816220001e-10</v>
+        <v>4.279213816220011e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.317148151436151e-10</v>
+        <v>4.317148151436155e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.259004742819681e-10</v>
+        <v>4.25900474281969e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.341535977850651e-10</v>
+        <v>4.341535977850659e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.317403693042728e-10</v>
+        <v>4.317403693042715e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.342538379635831e-10</v>
+        <v>4.342538379635849e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.308161889527786e-10</v>
+        <v>4.308161889527808e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.29020310484379e-10</v>
+        <v>4.290203104843804e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.199072486644411e-10</v>
+        <v>4.199072486644424e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.135357866215628e-10</v>
+        <v>4.135357866215641e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.163707804601695e-10</v>
+        <v>4.163707804601701e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.244873780414783e-10</v>
+        <v>4.244873780414795e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.404435345283799e-10</v>
+        <v>4.404435345283813e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.279012531763187e-10</v>
+        <v>4.279012531763195e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.210609013942677e-10</v>
+        <v>4.210609013942691e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.326658362420881e-10</v>
+        <v>4.326658362420878e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.299510920719e-10</v>
+        <v>4.299510920719015e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.027406542560451e-10</v>
+        <v>5.027406542560484e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.638076039026314e-10</v>
+        <v>4.638076039026324e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.68560839150519e-10</v>
+        <v>4.685608391505193e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.29958545271572e-10</v>
+        <v>4.299585452715742e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.338931667078746e-10</v>
+        <v>4.338931667078762e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.434150824724813e-10</v>
+        <v>4.43415082472483e-10</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.312696829544578e-09</v>
+        <v>1.312696829544576e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.311021795760219e-09</v>
+        <v>1.311021795760222e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.579470939089917e-09</v>
+        <v>1.579470939089921e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>8.8769694981767e-10</v>
+        <v>8.876969498176722e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.507445159057147e-09</v>
+        <v>1.507445159057149e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.458186220073036e-09</v>
+        <v>1.45818622007306e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.510452083722514e-09</v>
+        <v>1.510452083722513e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.622387020502036e-09</v>
+        <v>1.622387020502041e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.49507129410519e-09</v>
+        <v>1.495071294105202e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.565782246780789e-09</v>
+        <v>1.565782246780792e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.473649139594923e-09</v>
+        <v>1.473649139594927e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.530320505814614e-09</v>
+        <v>1.530320505814615e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>1.333792638285738e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.168545675609558e-09</v>
+        <v>1.16854567560956e-09</v>
       </c>
       <c r="P5" t="n">
         <v>1.204573962888344e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.395824778683682e-09</v>
+        <v>1.395824778683681e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.763351704646206e-09</v>
+        <v>1.763351704646205e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.399257754568171e-09</v>
+        <v>1.399257754568172e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.378846789043674e-09</v>
+        <v>1.378846789043675e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.499177676399711e-09</v>
+        <v>1.499177676399713e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37542573897606e-09</v>
+        <v>1.375425738976061e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.775919261305543e-09</v>
+        <v>2.775919261305531e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.08849941878168e-09</v>
+        <v>2.088499418781667e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.205626986232897e-09</v>
+        <v>2.205626986232916e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.408446054897895e-09</v>
+        <v>1.408446054897896e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.570321363563355e-09</v>
+        <v>1.570321363563358e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.845434896241143e-09</v>
+        <v>1.845434896241148e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.169330384226747e-10</v>
+        <v>5.169330384226773e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.279948646097649e-10</v>
+        <v>8.279948646097676e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.273264064293659e-10</v>
+        <v>5.273264064293674e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.26115014393296e-10</v>
+        <v>8.261150143932978e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.377881834384002e-10</v>
+        <v>8.37788183438401e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.259381429048739e-10</v>
+        <v>5.259381429048738e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.201238020432257e-10</v>
+        <v>5.201238020432292e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.283769255463227e-10</v>
+        <v>5.283769255463224e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.416071711206725e-10</v>
+        <v>8.41607171120674e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.28477165724841e-10</v>
+        <v>5.284771657248428e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.406829907691789e-10</v>
+        <v>8.406829907691832e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>5.232436382456378e-10</v>
+        <v>5.232436382456407e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.14246091772904e-10</v>
+        <v>5.142460917729051e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.223396620189937e-10</v>
+        <v>8.223396620189945e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.002660523056427e-10</v>
+        <v>5.002660523056433e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.187107058027372e-10</v>
+        <v>5.187107058027375e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.346668622896392e-10</v>
+        <v>5.346668622896411e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>8.37768054992719e-10</v>
+        <v>8.377680549927198e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.152842291555273e-10</v>
+        <v>5.152842291555285e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>8.428939271982974e-10</v>
+        <v>8.42893927198299e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.241744198331598e-10</v>
+        <v>5.241744198331594e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.066158058872262e-10</v>
+        <v>6.066158058872246e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>8.736744057190303e-10</v>
+        <v>8.736744057190311e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.711518424178121e-10</v>
+        <v>5.711518424178115e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.241818730328308e-10</v>
+        <v>5.241818730328319e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.437599685242747e-10</v>
+        <v>8.437599685242761e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.377733187785074e-10</v>
+        <v>5.377733187785097e-10</v>
       </c>
     </row>
     <row r="7">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.170174219501497e-09</v>
+        <v>1.1701742195015e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.165592571633446e-09</v>
+        <v>1.165592571633448e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.180567587508188e-09</v>
@@ -1898,73 +1898,73 @@
         <v>1.16371272141698e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.175385890462081e-09</v>
+        <v>1.175385890462082e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.179179323983693e-09</v>
+        <v>1.179179323983697e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.173364983122045e-09</v>
+        <v>1.173364983122051e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.181618106625143e-09</v>
+        <v>1.181618106625145e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.179204878144352e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.181718346803666e-09</v>
+        <v>1.181718346803665e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.178280697792858e-09</v>
+        <v>1.178280697792861e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.17648481932446e-09</v>
+        <v>1.176484819324462e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.167371757504515e-09</v>
+        <v>1.167371757504522e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.160970564021574e-09</v>
+        <v>1.160970564021577e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.163805557860182e-09</v>
+        <v>1.163805557860185e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.171951886881559e-09</v>
+        <v>1.171951886881562e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18790804336846e-09</v>
+        <v>1.187908043368462e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.175365762016399e-09</v>
+        <v>1.175365762016402e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.168525410234347e-09</v>
+        <v>1.16852541023435e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.180581336831955e-09</v>
+        <v>1.180581336831957e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.177415600911982e-09</v>
+        <v>1.177415600911983e-09</v>
       </c>
       <c r="W7" t="n">
         <v>1.250205163096127e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.211272112742711e-09</v>
+        <v>1.211272112742714e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.216386637130404e-09</v>
+        <v>1.216386637130409e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.177423054111652e-09</v>
+        <v>1.177423054111655e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.181357675547955e-09</v>
+        <v>1.181357675547958e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.190879591312561e-09</v>
+        <v>1.190879591312563e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.109164248626489e-09</v>
+        <v>1.109164248626494e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.599703530640594e-09</v>
+        <v>1.599703530640595e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.614678546515336e-09</v>
+        <v>1.614678546515338e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.334186390403853e-09</v>
+        <v>1.33418639040386e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.191509973869554e-09</v>
+        <v>1.191509973869555e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.715956833219123e-09</v>
+        <v>1.715956833219116e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.607475942129197e-09</v>
+        <v>1.607475942129196e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.615729065632287e-09</v>
+        <v>1.615729065632295e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.613315837151496e-09</v>
+        <v>1.613315837151504e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.615829305810814e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.612391656800012e-09</v>
+        <v>1.612391656800011e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.610595778331579e-09</v>
+        <v>1.61059577833158e-09</v>
       </c>
       <c r="N8" t="n">
         <v>1.217681163941588e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.316781701069695e-09</v>
+        <v>1.316781701069694e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.293762959347283e-09</v>
+        <v>1.293762959347285e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.013639352685646e-09</v>
+        <v>1.013639352685648e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.622019002375603e-09</v>
+        <v>1.622019002375612e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.609476721023543e-09</v>
+        <v>1.60947672102355e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.60263636924149e-09</v>
+        <v>1.602636369241497e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.373033234151551e-09</v>
+        <v>1.373033234151554e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.476304633566983e-09</v>
+        <v>1.476304633566987e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.684413427613152e-09</v>
+        <v>1.684413427613163e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.098338395627527e-09</v>
+        <v>1.09833839562753e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.142943407644375e-09</v>
+        <v>2.142943407644387e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.107215957763989e-09</v>
+        <v>1.107215957763991e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.615468634555097e-09</v>
+        <v>1.615468634555105e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.142185762975544e-09</v>
+        <v>2.142185762975552e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.928976274997083e-10</v>
+        <v>8.928976274997102e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.044009285480794e-09</v>
+        <v>1.044009285480795e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.058984301355529e-09</v>
+        <v>1.058984301355532e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.006196215461901e-09</v>
+        <v>1.006196215461902e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>6.948867698722101e-10</v>
+        <v>6.948867698722104e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.057596246002218e-09</v>
+        <v>1.057596246002216e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.051781696969393e-09</v>
+        <v>1.051781696969395e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.060034820472487e-09</v>
+        <v>1.060034820472491e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.057621591991702e-09</v>
+        <v>1.057621591991698e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.060135060651007e-09</v>
+        <v>1.060135060651008e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.056697411640204e-09</v>
+        <v>1.056697411640208e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.054901533171803e-09</v>
+        <v>1.054901533171805e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.04578847135187e-09</v>
+        <v>1.045788471351867e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.091013844163316e-09</v>
+        <v>1.091013844163317e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.105070219056443e-09</v>
+        <v>1.105070219056442e-09</v>
       </c>
       <c r="Q9" t="n">
         <v>1.050368808900082e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.066324757215804e-09</v>
+        <v>1.066324757215806e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.053782475863743e-09</v>
+        <v>1.053782475863745e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.046942124081692e-09</v>
+        <v>1.046942124081695e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.058908348069322e-09</v>
+        <v>1.05890834806932e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.235499141471615e-09</v>
+        <v>1.235499141471617e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.128621876943472e-09</v>
+        <v>1.128621876943471e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.089688826590056e-09</v>
+        <v>1.089688826590059e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.094803350977751e-09</v>
+        <v>1.094803350977753e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.619706319833966e-10</v>
+        <v>9.619706319834017e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.059774389395301e-09</v>
+        <v>1.059774389395302e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.069296305159906e-09</v>
+        <v>1.069296305159908e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.369498967361081e-10</v>
+        <v>5.369498967361065e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.475404596684078e-10</v>
+        <v>5.475404596684082e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.352574855747016e-10</v>
+        <v>5.352574855746939e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.32901257238037e-10</v>
+        <v>5.329012572380297e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.322908501725607e-10</v>
+        <v>5.32290850172555e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.385371418553571e-10</v>
+        <v>5.385371418553514e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.321341066993048e-10</v>
+        <v>5.321341066992974e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.337775485270309e-10</v>
+        <v>5.337775485270228e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.368432290971372e-10</v>
+        <v>5.368432290971306e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.381882853276554e-10</v>
+        <v>5.381882853276575e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.409383968497138e-10</v>
+        <v>5.409383968497154e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.413921284836647e-10</v>
+        <v>5.413921284836645e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.334068969138743e-10</v>
+        <v>5.33406896913866e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.566427590917513e-10</v>
+        <v>7.566427590917526e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.364226786100682e-10</v>
+        <v>5.364226786100641e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.325637047816076e-10</v>
+        <v>5.325637047816081e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.323791225831114e-10</v>
+        <v>5.323791225831069e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.364585967668531e-10</v>
+        <v>5.3645859676685e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.328165221844254e-10</v>
+        <v>5.328165221844188e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.59331055894997e-10</v>
+        <v>7.593310558949972e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.331906659147608e-10</v>
+        <v>5.331906659147576e-10</v>
       </c>
       <c r="W2" t="n">
         <v>7.829774981658756e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.357745662691407e-10</v>
+        <v>5.357745662691345e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.356425647987616e-10</v>
+        <v>5.356425647987533e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.929765354200614e-10</v>
+        <v>7.929765354200606e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.329176224736212e-10</v>
+        <v>5.32917622473615e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.490490588085911e-10</v>
+        <v>5.490490588085954e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.893500357089301e-10</v>
+        <v>4.918418053605029e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.784627349307483e-10</v>
+        <v>4.796647308476934e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.776525696214732e-10</v>
+        <v>4.797446696022204e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.599754115032902e-10</v>
+        <v>4.613409360375863e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5645408459109e-10</v>
+        <v>4.577966273581884e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.007047970342079e-10</v>
+        <v>5.035947150466285e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.553792972537976e-10</v>
+        <v>4.566832329720444e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.670864965355184e-10</v>
+        <v>4.688049369526283e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.887441237575542e-10</v>
+        <v>4.912178686546033e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.984228505079783e-10</v>
+        <v>5.012559855880491e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.180232012286045e-10</v>
+        <v>5.215306495857884e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.306924548949995e-10</v>
+        <v>5.347289580124206e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.643440558968436e-10</v>
+        <v>4.659617812238852e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.349384993506578e-10</v>
+        <v>8.366481331002894e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.856286943824886e-10</v>
+        <v>4.879851076992247e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.583311171203277e-10</v>
+        <v>4.597370170353094e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.570933573695537e-10</v>
+        <v>4.584576696260483e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.859322604469126e-10</v>
+        <v>4.883067695173637e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.601843283281719e-10</v>
+        <v>4.616571494235257e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.820767887132148e-10</v>
+        <v>8.857271581152921e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.625221322114942e-10</v>
+        <v>4.64070676669993e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.984722261421285e-10</v>
+        <v>9.011062907511001e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.813098479123926e-10</v>
+        <v>4.835316579474825e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.802607797543661e-10</v>
+        <v>4.824410524413685e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.005606397608311e-10</v>
+        <v>9.025292277346343e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.608159522933141e-10</v>
+        <v>4.623076222868547e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.764618116125067e-10</v>
+        <v>5.820434482780057e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.997046019078404e-10</v>
+        <v>4.997046019078403e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.410277686009478e-10</v>
+        <v>4.410277686009463e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.805880392921566e-10</v>
+        <v>4.8058803929218e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.539733563109406e-10</v>
+        <v>4.539733563109389e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.470785277052627e-10</v>
+        <v>4.470785277052608e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.176332656985839e-10</v>
+        <v>5.176332656985823e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.453080380692683e-10</v>
+        <v>4.45308038069267e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.638714695340341e-10</v>
+        <v>4.638714695340332e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.984420524719977e-10</v>
+        <v>4.984420524719959e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>5.136927707362653e-10</v>
+        <v>5.136927707362638e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.447565454916974e-10</v>
+        <v>5.447565454917011e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.664916766869213e-10</v>
+        <v>5.664916766869246e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.596847890552572e-10</v>
+        <v>4.596847890552569e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.644263542304369e-10</v>
+        <v>4.644263542304241e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.937494306418962e-10</v>
+        <v>4.937494306418873e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.501605460337663e-10</v>
+        <v>4.501605460337678e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.480756051897577e-10</v>
+        <v>4.48075605189756e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.94155142745947e-10</v>
+        <v>4.941551427459368e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.530162349003424e-10</v>
+        <v>4.530162349003408e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.499214422739959e-10</v>
+        <v>5.499214422739897e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.570763047884662e-10</v>
+        <v>4.570763047884657e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.053926835260188e-10</v>
+        <v>5.053926835260182e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.864287036047153e-10</v>
+        <v>4.864287036047174e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.835482647942534e-10</v>
+        <v>4.835482647942503e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.759986191149284e-10</v>
+        <v>4.759986191149267e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.541582091752452e-10</v>
+        <v>4.54158209175245e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.35756571874659e-10</v>
+        <v>6.357565718746584e-10</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.309804799539831e-09</v>
+        <v>2.30980479954002e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.365298508109441e-09</v>
+        <v>1.365298508109443e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.160443069630955e-09</v>
+        <v>2.160443069631167e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.178568858160216e-09</v>
+        <v>1.178568858160229e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.512688636471565e-09</v>
+        <v>1.512688636471583e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.663543961950732e-09</v>
+        <v>2.663543961950687e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.503626717944205e-09</v>
+        <v>1.503626717944206e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.84231634234115e-09</v>
+        <v>1.84231634234116e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.37338083816723e-09</v>
+        <v>2.373380838167199e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.704639212691327e-09</v>
+        <v>2.704639212691325e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.276789173226854e-09</v>
+        <v>3.276789173226835e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.913769430243907e-09</v>
+        <v>3.913769430243782e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>1.709162838388551e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.687440289448535e-09</v>
+        <v>1.687440289448363e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.220252340756994e-09</v>
+        <v>2.220252340756936e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.531840938318311e-09</v>
+        <v>1.531840938318327e-09</v>
       </c>
       <c r="R5" t="n">
         <v>1.536695803627269e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.254183007465324e-09</v>
+        <v>2.254183007465275e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.612998951882021e-09</v>
+        <v>1.61299895188201e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>3.349074760539093e-09</v>
+        <v>3.349074760539154e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.507831371303322e-09</v>
+        <v>1.507831371303305e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.554062985841157e-09</v>
+        <v>2.554062985841167e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.252440009253706e-09</v>
+        <v>2.252440009253682e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.164758011631567e-09</v>
+        <v>2.164758011631745e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.920582997082591e-09</v>
+        <v>1.920582997082653e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.58457438540471e-09</v>
+        <v>1.584574385404717e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.490054187496271e-09</v>
+        <v>5.490054187496209e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.956412252894589e-10</v>
+        <v>5.956412252894635e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.882301318722722e-10</v>
+        <v>8.882301318722717e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.765246626737768e-10</v>
+        <v>5.765246626737905e-10</v>
       </c>
       <c r="E6" t="n">
         <v>9.011757195822643e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.430151510868834e-10</v>
+        <v>5.430151510868848e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.648356289699084e-10</v>
+        <v>9.648356289699098e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.925104013405928e-10</v>
+        <v>8.925104013405946e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>9.110738328053609e-10</v>
+        <v>9.110738328053584e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.456444157433206e-10</v>
+        <v>9.456444157433175e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>6.096293941178849e-10</v>
+        <v>6.096293941178841e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.91958908763022e-10</v>
+        <v>9.91958908763018e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.013694039958247e-09</v>
+        <v>1.013694039958246e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.558106342595712e-10</v>
+        <v>5.5581063425957e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.605249100152386e-10</v>
+        <v>5.605249100152591e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.384386538499475e-10</v>
+        <v>9.384386538499518e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.460971694153858e-10</v>
+        <v>5.460971694153872e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.952779684610844e-10</v>
+        <v>8.95277968461082e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.900917661275679e-10</v>
+        <v>5.900917661275697e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.489528582819637e-10</v>
+        <v>5.48952858281965e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.472474871344611e-10</v>
+        <v>6.472474871344792e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.530129281700862e-10</v>
+        <v>5.530129281700878e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.117330574885778e-10</v>
+        <v>6.117330574885764e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>9.336310668760424e-10</v>
+        <v>9.336310668760389e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.896333217922434e-10</v>
+        <v>5.896333217922412e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.71935242496549e-10</v>
+        <v>5.719352424965493e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.013605724465713e-10</v>
+        <v>9.013605724465691e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.327702943158122e-10</v>
+        <v>7.327702943158113e-10</v>
       </c>
     </row>
     <row r="7">
@@ -2749,82 +2749,82 @@
         <v>1.337919411957618e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.279242578650726e-09</v>
+        <v>1.279242578650725e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.318802849341938e-09</v>
+        <v>1.318802849341937e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.292188166360719e-09</v>
+        <v>1.29218816636072e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.28529333775504e-09</v>
+        <v>1.285293337755042e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.355848075748363e-09</v>
+        <v>1.35584807574836e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.283522848119048e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.302086279583814e-09</v>
+        <v>1.302086279583811e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.336656862521777e-09</v>
+        <v>1.336656862521774e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.351907580786045e-09</v>
+        <v>1.351907580786043e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.382971355541473e-09</v>
+        <v>1.382971355541471e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.404706486736699e-09</v>
+        <v>1.404706486736697e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.297899599105037e-09</v>
+        <v>1.297899599105036e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.302608831564928e-09</v>
+        <v>1.30260883156492e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.331931907976385e-09</v>
+        <v>1.331931907976405e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.288375356083546e-09</v>
+        <v>1.288375356083548e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.286290415239536e-09</v>
+        <v>1.286290415239535e-09</v>
       </c>
       <c r="S7" t="n">
         <v>1.332369952795727e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.291231044950123e-09</v>
+        <v>1.291231044950121e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.389461013526718e-09</v>
+        <v>1.389461013526726e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.295291114838244e-09</v>
+        <v>1.295291114838248e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.343607493575797e-09</v>
+        <v>1.343607493575796e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.324643513654494e-09</v>
+        <v>1.324643513654504e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.323152496322878e-09</v>
+        <v>1.32315249632287e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.314213429164707e-09</v>
+        <v>1.314213429164704e-09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.292373019225024e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.473971381924437e-09</v>
+        <v>1.47397138192444e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.30729795209697e-09</v>
+        <v>1.307297952096971e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.831360652261892e-09</v>
+        <v>1.831360652261886e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.870920922953101e-09</v>
+        <v>1.870920922953083e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.53401462812304e-09</v>
+        <v>1.534014628123039e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.345455886598257e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.028800987825819e-09</v>
+        <v>2.028800987825816e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.835640921730211e-09</v>
+        <v>1.835640921730209e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.854204353194975e-09</v>
+        <v>1.854204353194966e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.888774936132931e-09</v>
+        <v>1.888774936132941e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.904025654397207e-09</v>
+        <v>1.904025654397206e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.935089429152638e-09</v>
+        <v>1.935089429152645e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.956824560347839e-09</v>
+        <v>1.956824560347848e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.398297044096357e-09</v>
+        <v>1.398297044096352e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.527175360283274e-09</v>
+        <v>1.527175360283275e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.526069519452759e-09</v>
+        <v>1.526069519452746e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.143232277493983e-09</v>
+        <v>1.143232277493978e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.838408488850704e-09</v>
+        <v>1.838408488850696e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.884488026406885e-09</v>
+        <v>1.884488026406887e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.843349118561284e-09</v>
+        <v>1.843349118561279e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6571913058461e-09</v>
+        <v>1.657191305846109e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.688110054552134e-09</v>
+        <v>1.688110054552137e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.895840092283664e-09</v>
+        <v>1.895840092283659e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.2329096712782e-09</v>
+        <v>1.232909671278202e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.454632365570599e-09</v>
+        <v>2.454632365570592e-09</v>
       </c>
       <c r="Z8" t="n">
         <v>1.272767283284427e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.844491092836184e-09</v>
+        <v>1.844491092836183e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.634809626208707e-09</v>
+        <v>2.634809626208703e-09</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.090266345425976e-09</v>
+        <v>1.09026634542598e-09</v>
       </c>
       <c r="C9" t="n">
         <v>1.225207559148575e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.264767829839781e-09</v>
+        <v>1.264767829839776e-09</v>
       </c>
       <c r="E9" t="n">
         <v>1.193467056931219e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.849155955074694e-10</v>
+        <v>7.849155955074723e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.30181327149912e-09</v>
+        <v>1.301813271499112e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.229487828616893e-09</v>
+        <v>1.229487828616898e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.24805126008166e-09</v>
+        <v>1.248051260081662e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.282621843019625e-09</v>
+        <v>1.282621843019618e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.297872561283891e-09</v>
+        <v>1.297872561283889e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.328936336039323e-09</v>
+        <v>1.328936336039324e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.350671467234546e-09</v>
+        <v>1.350671467234537e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.243864579602885e-09</v>
+        <v>1.243864579602878e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.312771198629964e-09</v>
+        <v>1.312771198629967e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.356049026553432e-09</v>
+        <v>1.356049026553414e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.234340551834303e-09</v>
+        <v>1.234340551834301e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.232255395737385e-09</v>
+        <v>1.232255395737388e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.278334933293573e-09</v>
+        <v>1.278334933293568e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.237196025447965e-09</v>
+        <v>1.23719602544797e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.335490654300465e-09</v>
+        <v>1.335490654300455e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.464687206884831e-09</v>
+        <v>1.464687206884838e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.289572474073646e-09</v>
+        <v>1.289572474073645e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.270608494152342e-09</v>
+        <v>1.27060849415235e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.269117476820725e-09</v>
+        <v>1.269117476820739e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.143444029966845e-09</v>
+        <v>1.14344402996685e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.238337999722869e-09</v>
+        <v>1.238337999722875e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.419936362422285e-09</v>
+        <v>1.419936362422281e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.317365516493969e-10</v>
+        <v>5.31736551649389e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.42791397249387e-10</v>
+        <v>5.427913972493875e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.323020791910758e-10</v>
+        <v>5.323020791910699e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.290860008535753e-10</v>
+        <v>5.290860008535726e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.285800692847647e-10</v>
+        <v>5.28580069284758e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.338804060193333e-10</v>
+        <v>5.3388040601933e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.275343138096685e-10</v>
+        <v>5.275343138096619e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.302984589839388e-10</v>
+        <v>5.302984589839315e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.323855239649696e-10</v>
+        <v>5.32385523964963e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.298781051793136e-10</v>
+        <v>5.298781051793059e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.357101084984797e-10</v>
+        <v>5.357101084984772e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.360274122716252e-10</v>
+        <v>5.360274122716251e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.27778496602148e-10</v>
+        <v>5.277784966021406e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.431658565311645e-10</v>
+        <v>7.431658565311648e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.320502137871734e-10</v>
+        <v>5.320502137871668e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.291226042117177e-10</v>
+        <v>5.291226042117106e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.275797705613781e-10</v>
+        <v>5.275797705613702e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.321121708146687e-10</v>
+        <v>5.321121708146605e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.280973477534951e-10</v>
+        <v>5.280973477534881e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.44067381874613e-10</v>
+        <v>7.44067381874605e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.296073925395379e-10</v>
+        <v>5.296073925395304e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.691073186771853e-10</v>
+        <v>7.691073186771837e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.333041454857651e-10</v>
+        <v>5.333041454857583e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.347308663063985e-10</v>
+        <v>5.347308663063913e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.854793428775745e-10</v>
+        <v>7.854793428775712e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.286767184346353e-10</v>
+        <v>5.286767184346299e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.436369455765964e-10</v>
+        <v>5.43636945576596e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.787425483830094e-10</v>
+        <v>4.81006189074924e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.736706502438217e-10</v>
+        <v>4.748767039634807e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.831075037189989e-10</v>
+        <v>4.855407808580389e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.592889984646131e-10</v>
+        <v>4.607767718728696e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.565073494059374e-10</v>
+        <v>4.579998254260411e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.939837925833455e-10</v>
+        <v>4.967846815709037e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.490744055235476e-10</v>
+        <v>4.503012083276437e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.688102871764961e-10</v>
+        <v>4.70737251577544e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.834681633225552e-10</v>
+        <v>4.859039878098717e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.656515040996269e-10</v>
+        <v>4.67467520049965e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.072346847418034e-10</v>
+        <v>5.105086007755947e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.189559467018114e-10</v>
+        <v>5.227220379287978e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.507021217962893e-10</v>
+        <v>4.519838054913472e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.120189960102913e-10</v>
+        <v>8.135627586488678e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.809464835026262e-10</v>
+        <v>4.832851092957999e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.602979957435993e-10</v>
+        <v>4.619212626520023e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.493606253517999e-10</v>
+        <v>4.505972359933464e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.814382145853519e-10</v>
+        <v>4.838012130883321e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.530328144020603e-10</v>
+        <v>4.543988356263279e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.482269874900482e-10</v>
+        <v>8.513463643933128e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.634581041080991e-10</v>
+        <v>4.651866172102785e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.799391041207103e-10</v>
+        <v>8.826379953107517e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.90229403782246e-10</v>
+        <v>4.929151321205689e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.002936619265423e-10</v>
+        <v>5.03329182050039e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.922249954269669e-10</v>
+        <v>8.942475749505925e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.570898432151221e-10</v>
+        <v>4.585963697451289e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.644790266603305e-10</v>
+        <v>5.697831105831752e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.782185600891182e-10</v>
+        <v>4.782185600891184e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.300493079655637e-10</v>
+        <v>4.30049307965563e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.846064538279112e-10</v>
+        <v>4.846064538279084e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.482793695367129e-10</v>
+        <v>4.482793695367126e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.425646397269817e-10</v>
+        <v>4.425646397269806e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>5.024343814192858e-10</v>
+        <v>5.024343814192856e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.307523505644901e-10</v>
+        <v>4.307523505644896e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.619746418774631e-10</v>
+        <v>4.619746418774634e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.854941069366899e-10</v>
+        <v>4.854941069366876e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.572265522819116e-10</v>
+        <v>4.572265522819107e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.231017126259787e-10</v>
+        <v>5.231017126259774e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.43357028360392e-10</v>
+        <v>5.433570283603927e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.335105075351658e-10</v>
+        <v>4.335105075351655e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.457431933876856e-10</v>
+        <v>4.457431933876847e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.817615182270228e-10</v>
+        <v>4.817615182270208e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.486928213053096e-10</v>
+        <v>4.486928213053089e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.312658054861715e-10</v>
+        <v>4.312658054861719e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.82461351354213e-10</v>
+        <v>4.824613513542128e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.371120779684114e-10</v>
+        <v>4.371120779684107e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.153161476503573e-10</v>
+        <v>5.153161476503536e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.540216464722598e-10</v>
+        <v>4.540216464722601e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.9712976631723e-10</v>
+        <v>4.971297663172292e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.959252535996978e-10</v>
+        <v>4.959252535996961e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.110800948687052e-10</v>
+        <v>5.110800948687044e-10</v>
       </c>
       <c r="Z4" t="n">
         <v>4.672568349610522e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.436563363355664e-10</v>
+        <v>4.436563363355663e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.122563672541986e-10</v>
+        <v>6.122563672541987e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.999027085160532e-09</v>
+        <v>1.999027085160534e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.269843475671805e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.282377557838554e-09</v>
+        <v>2.282377557838562e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.191508332876996e-09</v>
+        <v>1.191508332876999e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.520150871912374e-09</v>
+        <v>1.520150871912369e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.396462884532306e-09</v>
+        <v>2.396462884532273e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.327122445555183e-09</v>
+        <v>1.327122445555181e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.88350658313909e-09</v>
+        <v>1.883506583139094e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.177267418047513e-09</v>
+        <v>2.177267418047505e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.717288072741898e-09</v>
+        <v>1.7172880727419e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.861608960613632e-09</v>
+        <v>2.861608960613637e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.426545919439199e-09</v>
+        <v>3.426545919439208e-09</v>
       </c>
       <c r="N5" t="n">
         <v>1.316294400634628e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.449223177982691e-09</v>
+        <v>1.44922317798268e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.043714386043225e-09</v>
+        <v>2.043714386043222e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.586327188954172e-09</v>
+        <v>1.586327188954176e-09</v>
       </c>
       <c r="R5" t="n">
         <v>1.31640379043711e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.081765297220587e-09</v>
+        <v>2.08176529722059e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.408515152594925e-09</v>
+        <v>1.408515152594917e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.694030809477232e-09</v>
+        <v>2.694030809477034e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.527640843394213e-09</v>
+        <v>1.52764084339419e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.430517458618933e-09</v>
+        <v>2.430517458618936e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.467075826973532e-09</v>
+        <v>2.467075826973537e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.690788397997663e-09</v>
+        <v>2.690788397997652e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.783273716322125e-09</v>
+        <v>1.783273716322135e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.483855897196943e-09</v>
+        <v>1.483855897196941e-09</v>
       </c>
       <c r="AB5" t="n">
         <v>4.893454221233065e-09</v>
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.947519034731387e-10</v>
+        <v>8.94751903473137e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.206937797959315e-10</v>
+        <v>5.206937797959316e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.011397972119296e-10</v>
+        <v>9.011397972119276e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.648127129207342e-10</v>
+        <v>8.648127129207325e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.332091115573492e-10</v>
+        <v>5.332091115573497e-10</v>
       </c>
       <c r="G6" t="n">
         <v>5.930788532496539e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.213968223948571e-10</v>
+        <v>5.213968223948578e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.526191137078328e-10</v>
+        <v>5.526191137078317e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>9.020274503207098e-10</v>
+        <v>9.020274503207082e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.737598956659316e-10</v>
+        <v>8.737598956659302e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.396350560099965e-10</v>
+        <v>9.396350560099998e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.340015001907598e-10</v>
+        <v>6.340015001907613e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.24299321634364e-10</v>
+        <v>5.242993216343631e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.600853961932171e-10</v>
+        <v>8.600853961932183e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.961153661105487e-10</v>
+        <v>8.961153661105499e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.652261646893305e-10</v>
+        <v>8.652261646893295e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.219102773165408e-10</v>
+        <v>5.219102773165404e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>8.989946947382332e-10</v>
+        <v>8.989946947382325e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.277565497987775e-10</v>
+        <v>5.277565497987796e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.069212462047771e-10</v>
+        <v>6.069212462047712e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>8.70554989856279e-10</v>
+        <v>8.705549898562787e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.114671590422434e-10</v>
+        <v>9.114671590422445e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.86569725430066e-10</v>
+        <v>5.86569725430065e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.108148840106925e-10</v>
+        <v>6.108148840106933e-10</v>
       </c>
       <c r="Z6" t="n">
         <v>8.837901783450714e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.601896797195864e-10</v>
+        <v>8.601896797195861e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.03798241798594e-10</v>
+        <v>7.037982417985975e-10</v>
       </c>
     </row>
     <row r="7">
@@ -3606,22 +3606,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.251692617319674e-09</v>
+        <v>1.251692617319676e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.203523365196121e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.258080511058469e-09</v>
+        <v>1.258080511058465e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.221753426767271e-09</v>
+        <v>1.221753426767272e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.216038696957539e-09</v>
+        <v>1.21603869695754e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.275908438649844e-09</v>
+        <v>1.275908438649842e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.204226407795048e-09</v>
@@ -3630,7 +3630,7 @@
         <v>1.23544869910802e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.258968164167248e-09</v>
+        <v>1.258968164167249e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.230700609512469e-09</v>
@@ -3639,31 +3639,31 @@
         <v>1.296575769856536e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.316831085590951e-09</v>
+        <v>1.316831085590949e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.206984564765722e-09</v>
+        <v>1.206984564765724e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.219187176743522e-09</v>
+        <v>1.219187176743521e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.255205501582858e-09</v>
+        <v>1.255205501582857e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.222166878535868e-09</v>
+        <v>1.222166878535867e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.204739862716729e-09</v>
+        <v>1.20473986271673e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.255935408584772e-09</v>
+        <v>1.255935408584771e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.21058613519897e-09</v>
+        <v>1.210586135198966e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.289756550083409e-09</v>
+        <v>1.289756550083396e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.227495703702819e-09</v>
@@ -3672,16 +3672,16 @@
         <v>1.270603823547787e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.269399310830255e-09</v>
+        <v>1.269399310830254e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.285514778823311e-09</v>
+        <v>1.28551477882331e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.240730892191607e-09</v>
+        <v>1.240730892191608e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.217130393566126e-09</v>
+        <v>1.217130393566125e-09</v>
       </c>
       <c r="AB7" t="n">
         <v>1.385730424484757e-09</v>
@@ -3694,25 +3694,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.213807019283717e-09</v>
+        <v>1.213807019283716e-09</v>
       </c>
       <c r="C8" t="n">
         <v>1.696804045293288e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.751361191155637e-09</v>
+        <v>1.751361191155633e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.43220373216988e-09</v>
+        <v>1.432203732169878e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.260902597191738e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.879329906749454e-09</v>
+        <v>1.879329906749451e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.697507087892214e-09</v>
+        <v>1.697507087892213e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.728729379205189e-09</v>
@@ -3721,43 +3721,43 @@
         <v>1.752248844264412e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.723981289609637e-09</v>
+        <v>1.723981289609635e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.789856449953701e-09</v>
+        <v>1.789856449953703e-09</v>
       </c>
       <c r="M8" t="n">
         <v>1.810111765688086e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.288522517145288e-09</v>
+        <v>1.288522517145287e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.413905679713405e-09</v>
+        <v>1.413905679713403e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.422188088607001e-09</v>
+        <v>1.422188088607004e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.079894983550219e-09</v>
+        <v>1.079894983550218e-09</v>
       </c>
       <c r="R8" t="n">
         <v>1.698020542813896e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.749216088681936e-09</v>
+        <v>1.749216088681937e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.703866815296136e-09</v>
+        <v>1.703866815296135e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.523804078978926e-09</v>
+        <v>1.523804078978928e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.575631225426543e-09</v>
+        <v>1.575631225426539e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.763988893107968e-09</v>
+        <v>1.763988893107967e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.175809860721492e-09</v>
@@ -3769,7 +3769,7 @@
         <v>1.192978607832667e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.710411073663293e-09</v>
+        <v>1.71041107366329e-09</v>
       </c>
       <c r="AB8" t="n">
         <v>2.433858697557773e-09</v>
@@ -3782,19 +3782,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.985463688720495e-10</v>
+        <v>9.985463688720505e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.122037502003194e-09</v>
+        <v>1.122037502003192e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.176594647865539e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.100649201553172e-09</v>
+        <v>1.100649201553174e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.38828532666223e-10</v>
+        <v>7.388285326662243e-10</v>
       </c>
       <c r="G9" t="n">
         <v>1.19442277658123e-09</v>
@@ -3803,31 +3803,31 @@
         <v>1.122740544602119e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.153962835915094e-09</v>
+        <v>1.153962835915093e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.17748230097432e-09</v>
+        <v>1.177482300974318e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.14921474631954e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.215089906663607e-09</v>
+        <v>1.215089906663608e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.23534522239802e-09</v>
+        <v>1.235345222398022e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.125498701572799e-09</v>
+        <v>1.125498701572795e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.194619682105362e-09</v>
+        <v>1.194619682105361e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.243010191257719e-09</v>
+        <v>1.243010191257718e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.140681216467252e-09</v>
+        <v>1.140681216467255e-09</v>
       </c>
       <c r="R9" t="n">
         <v>1.123253999523801e-09</v>
@@ -3836,31 +3836,31 @@
         <v>1.174449545391842e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.129100272006042e-09</v>
+        <v>1.129100272006041e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.208264968412048e-09</v>
+        <v>1.208264968412032e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.344102287987059e-09</v>
+        <v>1.34410228798706e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.189117960354862e-09</v>
+        <v>1.189117960354859e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.187913447637327e-09</v>
+        <v>1.187913447637326e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.204028915630385e-09</v>
+        <v>1.204028915630383e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.055749161191397e-09</v>
+        <v>1.055749161191396e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.135644530373197e-09</v>
+        <v>1.135644530373196e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.304244561291826e-09</v>
+        <v>1.304244561291829e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.285770399348776e-10</v>
+        <v>5.285770399348793e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.396787614265292e-10</v>
+        <v>5.396787614265275e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.287307160766478e-10</v>
+        <v>5.28730716076647e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.260062463059889e-10</v>
+        <v>5.26006246305988e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.265299175588464e-10</v>
+        <v>5.265299175588458e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.307064922646766e-10</v>
+        <v>5.307064922646774e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.252254961170972e-10</v>
+        <v>5.252254961170958e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.273339522302103e-10</v>
+        <v>5.273339522302108e-10</v>
       </c>
       <c r="J2" t="n">
         <v>5.295609146395643e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.272549121617083e-10</v>
+        <v>5.272549121617068e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.31943652365358e-10</v>
+        <v>5.319436523653584e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.32178006866292e-10</v>
+        <v>5.321780068662924e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.246188175131105e-10</v>
+        <v>5.246188175131106e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.350107186854325e-10</v>
+        <v>7.350107186854308e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.290715083187995e-10</v>
+        <v>5.290715083187979e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.264385106475814e-10</v>
+        <v>5.264385106475802e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.260133113906954e-10</v>
+        <v>5.260133113906966e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.29445473792184e-10</v>
+        <v>5.294454737921833e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.261324300729315e-10</v>
+        <v>5.261324300729307e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.366363486699341e-10</v>
+        <v>7.366363486699326e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.285837916632261e-10</v>
+        <v>5.28583791663226e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.605552945380504e-10</v>
+        <v>7.605552945380467e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.316918030583241e-10</v>
+        <v>5.316918030583233e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.365428473806925e-10</v>
+        <v>5.365428473806917e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.809264061952071e-10</v>
+        <v>7.809264061952075e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.264048671231791e-10</v>
+        <v>5.264048671231785e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.40016750400462e-10</v>
+        <v>5.400167504004606e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.721057474657218e-10</v>
+        <v>4.742163872388844e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.693410877215123e-10</v>
+        <v>4.704932693560668e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.734784321005118e-10</v>
+        <v>4.756514694382065e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.532357963249034e-10</v>
+        <v>4.545897254898694e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.578148377179933e-10</v>
+        <v>4.59433904819296e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.872254803093526e-10</v>
+        <v>4.898696711218124e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.485457569071408e-10</v>
+        <v>4.498332258738185e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.635651028462124e-10</v>
+        <v>4.653857014725308e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.792165501984862e-10</v>
+        <v>4.815843014308023e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.628737168370719e-10</v>
+        <v>4.646703210833675e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.961963299930883e-10</v>
+        <v>4.991634630733785e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.072788906357352e-10</v>
+        <v>5.107144947527103e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.440877733394834e-10</v>
+        <v>4.452144856952184e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.989438615284722e-10</v>
+        <v>8.00415106205504e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.755909068003742e-10</v>
+        <v>4.778219837582436e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.570590957454256e-10</v>
+        <v>4.58647566357567e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.541525069475888e-10</v>
+        <v>4.556389190774973e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.783267034375878e-10</v>
+        <v>4.806597742123177e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.549633045810534e-10</v>
+        <v>4.56477107804511e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.404408578826543e-10</v>
+        <v>8.436805299304749e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.720192564934827e-10</v>
+        <v>4.741295954653279e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.681877871954352e-10</v>
+        <v>8.70904729463618e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.945826965863367e-10</v>
+        <v>4.97505444094481e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.292527247712331e-10</v>
+        <v>5.333885848035218e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.865494946598194e-10</v>
+        <v>8.885695232138575e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.568212916833999e-10</v>
+        <v>4.583972174684441e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.545201522481587e-10</v>
+        <v>5.595549674432832e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.699611008464831e-10</v>
+        <v>4.699611008464814e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.263156167664158e-10</v>
+        <v>4.26315616766416e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.716969435622676e-10</v>
+        <v>4.716969435622667e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.409228041846583e-10</v>
+        <v>4.409228041846569e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.468379118863684e-10</v>
+        <v>4.468379118863676e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.940142445080244e-10</v>
+        <v>4.940142445080215e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.321038716382905e-10</v>
+        <v>4.321038716382908e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.55919853373653e-10</v>
+        <v>4.55919853373654e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.810311332328783e-10</v>
+        <v>4.810311332328791e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.550270594396772e-10</v>
+        <v>4.550270594396752e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.07988536966977e-10</v>
+        <v>5.079885369669767e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.273814373610627e-10</v>
+        <v>5.273814373610638e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.252511577203292e-10</v>
+        <v>4.252511577203286e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.411173251146562e-10</v>
+        <v>4.411173251146544e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.75546348709541e-10</v>
+        <v>4.755463487095414e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.458054287743672e-10</v>
+        <v>4.458054287743673e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.410026075665421e-10</v>
+        <v>4.410026075665412e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.797704607640391e-10</v>
+        <v>4.797704607640401e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.423481078796758e-10</v>
+        <v>4.42348107879676e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.199305370061196e-10</v>
+        <v>5.199305370061194e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.69968995723795e-10</v>
+        <v>4.699689957237968e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.965994097397367e-10</v>
+        <v>4.965994097397373e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>5.051437831876104e-10</v>
+        <v>5.051437831876097e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.595278362364493e-10</v>
+        <v>5.595278362364427e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.657972096660345e-10</v>
+        <v>4.657972096660343e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.454254096894577e-10</v>
+        <v>4.454254096894576e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.989481455193677e-10</v>
+        <v>5.989481455193673e-10</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.847234146397729e-09</v>
+        <v>1.847234146397727e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.21400017950852e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.020908576929501e-09</v>
+        <v>2.020908576929527e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.063094990107765e-09</v>
+        <v>1.063094990107763e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.603837615198959e-09</v>
+        <v>1.603837615198968e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.232089857910564e-09</v>
+        <v>2.232089857910508e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.364302475526152e-09</v>
+        <v>1.36430247552615e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.770597125362518e-09</v>
+        <v>1.770597125362516e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.089787255482627e-09</v>
+        <v>2.089787255482609e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.688850530197437e-09</v>
+        <v>1.688850530197442e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.552409358493208e-09</v>
+        <v>2.55240935849321e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.056911917772085e-09</v>
+        <v>3.05691191777211e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.176722493707848e-09</v>
+        <v>1.176722493707843e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.384434894725455e-09</v>
+        <v>1.384434894725466e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.923275574106158e-09</v>
+        <v>1.923275574106125e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.532009485262256e-09</v>
+        <v>1.532009485262258e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.513437622252145e-09</v>
+        <v>1.513437622252142e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.032596332327931e-09</v>
+        <v>2.032596332327915e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.51683855250165e-09</v>
+        <v>1.516838552501651e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.716980701963347e-09</v>
+        <v>2.716980701963343e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.778720965422645e-09</v>
+        <v>1.778720965422634e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.432828550086144e-09</v>
+        <v>2.432828550086137e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.597359219821269e-09</v>
+        <v>2.597359219821298e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.591309437059973e-09</v>
+        <v>3.591309437059955e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.730774271997537e-09</v>
+        <v>1.730774271997539e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.526486070489992e-09</v>
+        <v>1.52648607048999e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.59158934406038e-09</v>
+        <v>4.591589344060356e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.618972303415843e-10</v>
+        <v>5.61897230341585e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.182517462615219e-10</v>
+        <v>5.182517462615211e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.884027348364286e-10</v>
+        <v>8.884027348364236e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.57628595458816e-10</v>
+        <v>8.576285954588148e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.387740413814723e-10</v>
+        <v>5.387740413814727e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.859503740031251e-10</v>
+        <v>5.859503740031262e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.488096629124521e-10</v>
+        <v>8.48809662912448e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.478559828687586e-10</v>
+        <v>5.478559828687589e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.9773692450703e-10</v>
+        <v>8.977369245070374e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.717328507138302e-10</v>
+        <v>8.717328507138324e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.99924666462083e-10</v>
+        <v>5.999246664620808e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>6.193175668561706e-10</v>
+        <v>6.193175668561679e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.174159578654648e-10</v>
+        <v>5.174159578654681e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.332623219026576e-10</v>
+        <v>5.332623219026551e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.901440840601302e-10</v>
+        <v>8.901440840601323e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.625112200485228e-10</v>
+        <v>8.625112200485245e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.577083988406988e-10</v>
+        <v>8.57708398840699e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.717065902591484e-10</v>
+        <v>5.717065902591441e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>8.590538991538358e-10</v>
+        <v>8.590538991538338e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.370470524432337e-10</v>
+        <v>9.370470524432327e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.619051252189032e-10</v>
+        <v>5.619051252189016e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.982244253317039e-10</v>
+        <v>5.982244253317009e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.97079912682714e-10</v>
+        <v>5.970799126827149e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.601607419820157e-10</v>
+        <v>6.601607419820124e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.577333391611405e-10</v>
+        <v>5.577333391611395e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.621312009636174e-10</v>
+        <v>8.621312009636151e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.91743410091403e-10</v>
+        <v>6.917434100914009e-10</v>
       </c>
     </row>
     <row r="7">
@@ -4466,43 +4466,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.238746609112045e-09</v>
+        <v>1.238746609112039e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.195101125031973e-09</v>
+        <v>1.195101125031972e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.240482451827825e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.209708312450212e-09</v>
+        <v>1.209708312450213e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.215623420151925e-09</v>
+        <v>1.215623420151926e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.262799752773568e-09</v>
+        <v>1.26279975277358e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.200889379903849e-09</v>
+        <v>1.200889379903847e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.224705361639216e-09</v>
+        <v>1.224705361639212e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.249816641498442e-09</v>
+        <v>1.249816641498438e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.223812567705232e-09</v>
+        <v>1.223812567705233e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.276774045232534e-09</v>
+        <v>1.276774045232535e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.296166945626617e-09</v>
+        <v>1.296166945626622e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.194036665985886e-09</v>
+        <v>1.194036665985887e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.20987278310717e-09</v>
@@ -4511,40 +4511,40 @@
         <v>1.244301806702057e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.214590937039922e-09</v>
+        <v>1.214590937039926e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.209788115832099e-09</v>
+        <v>1.2097881158321e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.248555969029598e-09</v>
+        <v>1.2485559690296e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.211133616145235e-09</v>
+        <v>1.211133616145232e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.289229904511286e-09</v>
+        <v>1.289229904511282e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.238754503989346e-09</v>
+        <v>1.238754503989354e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.265384918005297e-09</v>
+        <v>1.265384918005295e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.273929291453165e-09</v>
+        <v>1.273929291453166e-09</v>
       </c>
       <c r="Y7" t="n">
         <v>1.328724068664957e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.23458271793159e-09</v>
+        <v>1.234582717931591e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.214210917955017e-09</v>
+        <v>1.214210917955016e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36773365378494e-09</v>
+        <v>1.367733653784925e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.194911011085562e-09</v>
+        <v>1.194911011085563e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.674926733202487e-09</v>
+        <v>1.674926733202482e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.720308059998335e-09</v>
+        <v>1.720308059998332e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.41069977534711e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.253368117901199e-09</v>
+        <v>1.253368117901198e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.851209923389295e-09</v>
+        <v>1.851209923389289e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.680714988074357e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.704530969809721e-09</v>
+        <v>1.704530969809718e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.729642249668944e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.703638175875744e-09</v>
+        <v>1.70363817587574e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.756599653403044e-09</v>
+        <v>1.756599653403041e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.775992553797112e-09</v>
+        <v>1.775992553797108e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.267937232759584e-09</v>
+        <v>1.267937232759583e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.395355126152571e-09</v>
+        <v>1.395355126152569e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.40244012623388e-09</v>
+        <v>1.402440126233873e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.067843959995115e-09</v>
+        <v>1.067843959995116e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68961372400261e-09</v>
+        <v>1.689613724002605e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.728381577200109e-09</v>
+        <v>1.728381577200106e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.690959224315742e-09</v>
+        <v>1.690959224315743e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.51346354750428e-09</v>
+        <v>1.513463547504281e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57556945222953e-09</v>
+        <v>1.575569452229526e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.745313440673592e-09</v>
+        <v>1.745313440673589e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.1751769045273e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.329390666354036e-09</v>
+        <v>2.329390666354026e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.181019844146801e-09</v>
+        <v>1.181019844146802e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.694036526125524e-09</v>
+        <v>1.694036526125523e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.394567179726698e-09</v>
+        <v>2.394567179726699e-09</v>
       </c>
     </row>
     <row r="9">
@@ -4642,31 +4642,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.681026392518817e-10</v>
+        <v>9.681026392518831e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.089657350821834e-09</v>
+        <v>1.089657350821832e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.135038677617687e-09</v>
+        <v>1.135038677617679e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.066137161138804e-09</v>
+        <v>1.066137161138801e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.293478458670962e-10</v>
+        <v>7.293478458670931e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.157356179050434e-09</v>
+        <v>1.157356179050433e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09544560569371e-09</v>
+        <v>1.095445605693704e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.119261587429071e-09</v>
+        <v>1.11926158742907e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.144372867288294e-09</v>
+        <v>1.144372867288293e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.118368793495089e-09</v>
@@ -4678,49 +4678,49 @@
         <v>1.19072317141648e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.088592891775747e-09</v>
+        <v>1.088592891775743e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.159206454625489e-09</v>
+        <v>1.159206454625492e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.205542053822292e-09</v>
+        <v>1.205542053822295e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.109147363316782e-09</v>
+        <v>1.109147363316777e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.104344341621956e-09</v>
+        <v>1.104344341621955e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.143112194819461e-09</v>
+        <v>1.143112194819453e-09</v>
       </c>
       <c r="T9" t="n">
         <v>1.105689841935087e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.183682995224491e-09</v>
+        <v>1.183682995224488e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.323948265195137e-09</v>
+        <v>1.323948265195134e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.159941143795153e-09</v>
+        <v>1.159941143795154e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.168485517243022e-09</v>
+        <v>1.168485517243023e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.223280294454824e-09</v>
+        <v>1.223280294454812e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.029537995530245e-09</v>
+        <v>1.029537995530243e-09</v>
       </c>
       <c r="AA9" t="n">
         <v>1.108767143744871e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.26228987957479e-09</v>
+        <v>1.262289879574781e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.082245678808425e-10</v>
+        <v>5.08224567880842e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.202596186647489e-10</v>
+        <v>5.20259618664748e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.105529350728374e-10</v>
+        <v>5.10552935072837e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.07564064682123e-10</v>
+        <v>5.075640646821226e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.077682449145429e-10</v>
+        <v>5.077682449145422e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.09101517375588e-10</v>
+        <v>5.091015173755875e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.088018511655712e-10</v>
+        <v>5.088018511655704e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.083358894048176e-10</v>
+        <v>5.083358894048175e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.090860968424337e-10</v>
+        <v>5.090860968424333e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.112864691623178e-10</v>
+        <v>5.112864691623173e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.10723178810469e-10</v>
+        <v>5.107231788104689e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.099854702422246e-10</v>
+        <v>5.099854702422244e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.097837449526011e-10</v>
+        <v>5.097837449526006e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.972834177389271e-10</v>
+        <v>6.97283417738927e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.086084571367426e-10</v>
+        <v>5.086084571367424e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.086027722340039e-10</v>
+        <v>5.086027722340028e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.081663591065022e-10</v>
+        <v>5.081663591065018e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.089894606504568e-10</v>
+        <v>5.089894606504565e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.078772677411654e-10</v>
+        <v>5.078772677411648e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.937504185330649e-10</v>
+        <v>6.937504185330645e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.078083832871585e-10</v>
+        <v>5.078083832871579e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.178134961137834e-10</v>
+        <v>7.178134961137832e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.087934505417027e-10</v>
+        <v>5.087934505417017e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.080112046583278e-10</v>
+        <v>5.080112046583274e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.523274771051633e-10</v>
+        <v>7.523274771051627e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.078737304416587e-10</v>
+        <v>5.078737304416583e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.118502620959505e-10</v>
+        <v>5.118502620959499e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.38766060399385e-10</v>
+        <v>4.401189671325014e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.503187832460018e-10</v>
+        <v>4.512997209909465e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.556088043709136e-10</v>
+        <v>4.575660980934766e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.334562223385503e-10</v>
+        <v>4.345292903248731e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.357196639000367e-10</v>
+        <v>4.369734331631811e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.449804281564093e-10</v>
+        <v>4.465531879662618e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.431937791448984e-10</v>
+        <v>4.447132038574963e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.39776966316363e-10</v>
+        <v>4.411729173728921e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.449213446730189e-10</v>
+        <v>4.464932203168098e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.606949118990076e-10</v>
+        <v>4.628361745646328e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.565341285133832e-10</v>
+        <v>4.585209974112358e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.606459996203105e-10</v>
+        <v>4.628450378089116e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.500089621616024e-10</v>
+        <v>4.517656739794232e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.466719551148116e-10</v>
+        <v>7.47832661249247e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.414932722692932e-10</v>
+        <v>4.429403163337453e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.415829781363157e-10</v>
+        <v>4.430426298364249e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.385934152473929e-10</v>
+        <v>4.399479789567653e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.441380705207158e-10</v>
+        <v>4.456854112736919e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.364703212915359e-10</v>
+        <v>4.377486464635682e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.592705868553377e-10</v>
+        <v>7.612592268141467e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.357072431320557e-10</v>
+        <v>4.369525508814295e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.005502955385599e-10</v>
+        <v>8.026313710784136e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.43000687169238e-10</v>
+        <v>4.44510216598234e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.373631962120485e-10</v>
+        <v>4.38670315644775e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.448347402851076e-10</v>
+        <v>8.46333153481524e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.363774440136105e-10</v>
+        <v>4.37649259013221e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.655940349279107e-10</v>
+        <v>4.679057085181768e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.287463185313426e-10</v>
+        <v>4.287463185313423e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.116408283507083e-10</v>
+        <v>4.116408283507081e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.55046297066756e-10</v>
+        <v>4.550462970667561e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.212856310553274e-10</v>
+        <v>4.212856310553271e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.235919407080585e-10</v>
+        <v>4.235919407080584e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.386518664911944e-10</v>
+        <v>4.386518664911946e-10</v>
       </c>
       <c r="H4" t="n">
         <v>4.352669987957853e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.300037463550771e-10</v>
+        <v>4.300037463550774e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.384273477203973e-10</v>
+        <v>4.384273477203982e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.633319020497891e-10</v>
+        <v>4.633319020497888e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.569692783992908e-10</v>
+        <v>4.569692783992904e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.655149329677643e-10</v>
+        <v>4.655149329677635e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.463579408137483e-10</v>
+        <v>4.46357940813748e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.200952118299599e-10</v>
+        <v>4.200952118299596e-10</v>
       </c>
       <c r="P4" t="n">
         <v>4.330825242745187e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.330183106828999e-10</v>
+        <v>4.330183106828993e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.280888236478093e-10</v>
+        <v>4.280888236478095e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.373861342322003e-10</v>
+        <v>4.373861342322002e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.248234036877395e-10</v>
+        <v>4.248234036877399e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.565022817846471e-10</v>
+        <v>4.56502281784647e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.23929480816483e-10</v>
+        <v>4.23929480816487e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.610812858067664e-10</v>
+        <v>4.610812858067657e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.351721098847093e-10</v>
+        <v>4.351721098847086e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.25723740097161e-10</v>
+        <v>4.257237400971612e-10</v>
       </c>
       <c r="Z4" t="n">
         <v>4.352704767884867e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.247834482625717e-10</v>
+        <v>4.247834482625716e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.707924062354256e-10</v>
+        <v>4.707924062354253e-10</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.438085052499762e-09</v>
+        <v>1.438085052499764e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.206587134593051e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.060536416899748e-09</v>
+        <v>2.060536416899743e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>9.656670203366542e-10</v>
+        <v>9.656670203366526e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.457642815503923e-09</v>
+        <v>1.457642815503921e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.600649173039673e-09</v>
+        <v>1.600649173039695e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.732460542847616e-09</v>
+        <v>1.732460542847614e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.582210974625228e-09</v>
+        <v>1.582210974625226e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.625654518735431e-09</v>
+        <v>1.625654518735434e-09</v>
       </c>
       <c r="K5" t="n">
         <v>2.134243153372094e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.935770926448053e-09</v>
+        <v>1.935770926448052e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>2.212226956765585e-09</v>
+        <v>2.212226956765584e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>1.835028794134852e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.292095454803784e-09</v>
+        <v>1.292095454803782e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.513052257233892e-09</v>
+        <v>1.513052257233893e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.584293239540233e-09</v>
+        <v>1.584293239540232e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.560683505212572e-09</v>
+        <v>1.560683505212577e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55302296152551e-09</v>
+        <v>1.553022961525509e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.465664181383474e-09</v>
+        <v>1.465664181383476e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.982898592319242e-09</v>
+        <v>1.982898592319239e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.299870936743166e-09</v>
+        <v>1.299870936743162e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.112752042520303e-09</v>
+        <v>2.112752042520305e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.656622336934374e-09</v>
+        <v>1.656622336934375e-09</v>
       </c>
       <c r="Y5" t="n">
         <v>1.459209975862863e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.541011927112612e-09</v>
+        <v>1.541011927112611e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.427295355396741e-09</v>
+        <v>1.42729535539674e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.432078646352091e-09</v>
+        <v>2.432078646352092e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.303887826265955e-10</v>
+        <v>5.303887826265941e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.132832924459611e-10</v>
+        <v>5.132832924459598e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.948820617202289e-10</v>
+        <v>8.948820617202274e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.611213957087996e-10</v>
+        <v>8.611213957087994e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.252344048033116e-10</v>
+        <v>5.252344048033111e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.402943305864459e-10</v>
+        <v>5.402943305864465e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.751027634492554e-10</v>
+        <v>8.751027634492558e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.698395110085487e-10</v>
+        <v>8.698395110085497e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.400698118156494e-10</v>
+        <v>5.400698118156498e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>9.031676667032631e-10</v>
+        <v>9.031676667032604e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.586117424945436e-10</v>
+        <v>5.586117424945428e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>9.053506976212327e-10</v>
+        <v>9.053506976212363e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.481136779949639e-10</v>
+        <v>5.481136779949644e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.582145732464039e-10</v>
+        <v>8.582145732464053e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.712095485221208e-10</v>
+        <v>8.712095485221211e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.728540753363696e-10</v>
+        <v>8.728540753363716e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.679245883012816e-10</v>
+        <v>8.679245883012807e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.39028598327452e-10</v>
+        <v>5.390285983274522e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.264658677829921e-10</v>
+        <v>5.26465867782992e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>5.587572885638524e-10</v>
+        <v>5.587572885638521e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>8.637652454699521e-10</v>
+        <v>8.637652454699586e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>8.991943368546196e-10</v>
+        <v>8.991943368546183e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.368145739799625e-10</v>
+        <v>5.36814573979961e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.364593623070212e-10</v>
+        <v>5.364593623070208e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.369129408837399e-10</v>
+        <v>5.369129408837392e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.646192129160416e-10</v>
+        <v>8.646192129160431e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.727209798874635e-10</v>
+        <v>5.727209798874632e-10</v>
       </c>
     </row>
     <row r="7">
@@ -5326,28 +5326,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.228645425417472e-09</v>
+        <v>1.22864542541747e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.211539935236839e-09</v>
+        <v>1.211539935236837e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.254945403952886e-09</v>
+        <v>1.254945403952883e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.221184737941457e-09</v>
+        <v>1.221184737941455e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.223491047594188e-09</v>
+        <v>1.223491047594185e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.238550973377323e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.235166105681916e-09</v>
+        <v>1.235166105681915e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.229902853241206e-09</v>
+        <v>1.229902853241204e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.238326454606527e-09</v>
@@ -5356,55 +5356,55 @@
         <v>1.263231008935919e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25686838528542e-09</v>
+        <v>1.256868385285419e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.265414039853894e-09</v>
+        <v>1.265414039853892e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.246257047699878e-09</v>
+        <v>1.246257047699877e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.219962381823743e-09</v>
+        <v>1.219962381823741e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.232949694268301e-09</v>
+        <v>1.2329496942683e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.232917417569028e-09</v>
+        <v>1.232917417569027e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.227987930533939e-09</v>
+        <v>1.227987930533938e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.237285241118329e-09</v>
+        <v>1.237285241118328e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.224722510573869e-09</v>
+        <v>1.224722510573868e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.257082100872315e-09</v>
+        <v>1.257082100872314e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.223828587702617e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.260980392692896e-09</v>
+        <v>1.260980392692895e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.235071216770838e-09</v>
+        <v>1.235071216770836e-09</v>
       </c>
       <c r="Y7" t="n">
         <v>1.226235389667242e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.235169583674615e-09</v>
+        <v>1.235169583674614e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.224682555148702e-09</v>
+        <v>1.224682555148701e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.270691513121554e-09</v>
+        <v>1.270691513121553e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5414,70 +5414,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.168140286495284e-09</v>
+        <v>1.168140286495285e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.682844015476172e-09</v>
+        <v>1.682844015476173e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.726249484192218e-09</v>
+        <v>1.726249484192222e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.409316096354327e-09</v>
+        <v>1.409316096354329e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.245835569640141e-09</v>
+        <v>1.245835569640142e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.820129159629699e-09</v>
+        <v>1.820129159629701e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.706470185921248e-09</v>
+        <v>1.706470185921251e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.701206933480542e-09</v>
+        <v>1.701206933480541e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.709630534845859e-09</v>
+        <v>1.709630534845863e-09</v>
       </c>
       <c r="K8" t="n">
         <v>1.734535089175255e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.728172465524753e-09</v>
+        <v>1.728172465524755e-09</v>
       </c>
       <c r="M8" t="n">
         <v>1.736718120093193e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.305320013362866e-09</v>
+        <v>1.305320013362869e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.392344722130601e-09</v>
+        <v>1.392344722130602e-09</v>
       </c>
       <c r="P8" t="n">
         <v>1.377562546170076e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.067899629110831e-09</v>
+        <v>1.067899629110832e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.699292010773273e-09</v>
+        <v>1.699292010773272e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.708589321357663e-09</v>
+        <v>1.708589321357664e-09</v>
       </c>
       <c r="T8" t="n">
         <v>1.696026590813204e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.468826609751068e-09</v>
+        <v>1.46882660975107e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.549866758154314e-09</v>
+        <v>1.549866758154318e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.732388988751082e-09</v>
+        <v>1.732388988751083e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.11879480001205e-09</v>
@@ -5489,7 +5489,7 @@
         <v>1.164785815469847e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.695986635388034e-09</v>
+        <v>1.695986635388035e-09</v>
       </c>
       <c r="AB8" t="n">
         <v>2.297514792002181e-09</v>
@@ -5502,31 +5502,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.732146788502752e-10</v>
+        <v>9.73214678850276e-10</v>
       </c>
       <c r="C9" t="n">
         <v>1.13367315798157e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.177078626697618e-09</v>
+        <v>1.177078626697617e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.102337089102023e-09</v>
+        <v>1.102337089102021e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.362905737423837e-10</v>
+        <v>7.362905737423827e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.160684414871255e-09</v>
+        <v>1.160684414871254e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.157299328426647e-09</v>
+        <v>1.157299328426646e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.152036075985939e-09</v>
+        <v>1.152036075985938e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.16045967735126e-09</v>
+        <v>1.160459677351259e-09</v>
       </c>
       <c r="K9" t="n">
         <v>1.185364231680651e-09</v>
@@ -5535,52 +5535,52 @@
         <v>1.179001608030152e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.187547262598627e-09</v>
+        <v>1.187547262598625e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.168390270444611e-09</v>
+        <v>1.16839027044461e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.200972299633094e-09</v>
+        <v>1.200972299633093e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.226757289799865e-09</v>
+        <v>1.226757289799862e-09</v>
       </c>
       <c r="Q9" t="n">
         <v>1.155050859062959e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.150121153278673e-09</v>
+        <v>1.150121153278672e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.159418463863062e-09</v>
+        <v>1.159418463863061e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.146855733318603e-09</v>
+        <v>1.146855733318601e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.179147154099464e-09</v>
+        <v>1.179147154099462e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.350866902107753e-09</v>
+        <v>1.350866902107754e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.183113615437629e-09</v>
+        <v>1.183113615437627e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.157204439515572e-09</v>
+        <v>1.15720443951557e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.148368612411976e-09</v>
+        <v>1.148368612411974e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.050247609391377e-09</v>
+        <v>1.050247609391375e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.146815777893434e-09</v>
+        <v>1.146815777893432e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.192824735866288e-09</v>
+        <v>1.192824735866286e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.019390661626653e-10</v>
+        <v>5.019390661626655e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.135422879289229e-10</v>
+        <v>5.135422879289235e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.02733263573844e-10</v>
+        <v>5.027332635738437e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.003961771244654e-10</v>
+        <v>5.003961771244661e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.019173652090922e-10</v>
+        <v>5.019173652090923e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.011788845593362e-10</v>
+        <v>5.011788845593361e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.016453889346728e-10</v>
+        <v>5.01645388934673e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.021632290407651e-10</v>
+        <v>5.021632290407639e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.015877410043734e-10</v>
+        <v>5.015877410043721e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.018365872285037e-10</v>
+        <v>5.018365872285035e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.021392808593969e-10</v>
+        <v>5.02139280859396e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.002518095507316e-10</v>
+        <v>5.002518095507322e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.012905854217089e-10</v>
+        <v>5.012905854217078e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.778634635705039e-10</v>
+        <v>6.778634635705033e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.004262747022972e-10</v>
+        <v>5.004262747022961e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.010453734615309e-10</v>
+        <v>5.010453734615306e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.021385956452789e-10</v>
+        <v>5.021385956452778e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.017995459288228e-10</v>
+        <v>5.017995459288227e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.010568015359023e-10</v>
+        <v>5.010568015359022e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.701909674101591e-10</v>
+        <v>6.701909674101583e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.013620943461927e-10</v>
+        <v>5.013620943461932e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>6.957775636077873e-10</v>
+        <v>6.957775636077877e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.041900543053837e-10</v>
+        <v>5.041900543053831e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.026984144298088e-10</v>
+        <v>5.026984144298071e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.397921763552683e-10</v>
+        <v>7.397921763552673e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.017186655000765e-10</v>
+        <v>5.017186655000769e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.019006849652416e-10</v>
+        <v>5.019006849652411e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.371271121306945e-10</v>
+        <v>4.386028302455599e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.4942542661527e-10</v>
+        <v>4.505983328453245e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.429537341507296e-10</v>
+        <v>4.446462431172659e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.255304828660898e-10</v>
+        <v>4.265053934457499e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.371748720066015e-10</v>
+        <v>4.386649830677807e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.317194280850631e-10</v>
+        <v>4.330055154644601e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.353256445423672e-10</v>
+        <v>4.367480738512644e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.389425242284398e-10</v>
+        <v>4.404922261349112e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.346566881385608e-10</v>
+        <v>4.360480336002167e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.36522355902757e-10</v>
+        <v>4.379858152651802e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.385256880918808e-10</v>
+        <v>4.400578811600854e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.345173155684981e-10</v>
+        <v>4.359668954335283e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.326120876154897e-10</v>
+        <v>4.339348079009785e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.211867035465177e-10</v>
+        <v>7.223715201103505e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.263623324142369e-10</v>
+        <v>4.274586519248227e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.308287989954856e-10</v>
+        <v>4.320907615914973e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.38803142766206e-10</v>
+        <v>4.403487260117563e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.360829023282525e-10</v>
+        <v>4.37526620245246e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.310123835475931e-10</v>
+        <v>4.322796564888401e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.106544779474654e-10</v>
+        <v>7.119187090215878e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.329061777667314e-10</v>
+        <v>4.342343316910545e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.711344995758327e-10</v>
+        <v>7.732616993624739e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.532913101165586e-10</v>
+        <v>4.553522566186809e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.426791841396908e-10</v>
+        <v>4.443558842814668e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.28975051292592e-10</v>
+        <v>8.304180316790867e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.356775735885651e-10</v>
+        <v>4.371062210114398e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.379549466350429e-10</v>
+        <v>4.394716640395052e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.240048481900377e-10</v>
+        <v>4.240048481900369e-10</v>
       </c>
       <c r="C4" t="n">
         <v>4.098972007518633e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3297567329816e-10</v>
+        <v>4.329756732981592e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.065772067395493e-10</v>
+        <v>4.065772067395495e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.23759725936498e-10</v>
+        <v>4.237597259364982e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.154182472796173e-10</v>
+        <v>4.154182472796177e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.206876288016599e-10</v>
+        <v>4.206876288016591e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.265368710181908e-10</v>
+        <v>4.265368710181901e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.199885519702203e-10</v>
+        <v>4.199885519702202e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.228473014860378e-10</v>
+        <v>4.228473014860373e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.262663652929295e-10</v>
+        <v>4.262663652929298e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.220112960504977e-10</v>
+        <v>4.220112960504981e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.166799599050532e-10</v>
+        <v>4.166799599050521e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.108961285439616e-10</v>
+        <v>4.10896128543962e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.069171727267222e-10</v>
+        <v>4.069171727267219e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.139101780117659e-10</v>
+        <v>4.139101780117667e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.262586254842487e-10</v>
+        <v>4.262586254842482e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.224289029663032e-10</v>
+        <v>4.224289029663023e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.140392633689706e-10</v>
+        <v>4.140392633689702e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.139086231128668e-10</v>
+        <v>4.139086231128669e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.173887882718268e-10</v>
+        <v>4.173887882718258e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.528572460058631e-10</v>
+        <v>4.528572460058633e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.494307947677449e-10</v>
+        <v>4.494307947677406e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.322202736037577e-10</v>
+        <v>4.32220273603754e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.224790316183022e-10</v>
+        <v>4.22479031618302e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.215153213167811e-10</v>
+        <v>4.215153213167813e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.251472277017476e-10</v>
+        <v>4.251472277017478e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6010,46 +6010,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.455438300020762e-09</v>
+        <v>1.455438300020763e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.294120675951215e-09</v>
+        <v>1.294120675951218e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.696186604215834e-09</v>
+        <v>1.696186604215833e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>8.440644764422597e-10</v>
+        <v>8.440644764422605e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.556116301001384e-09</v>
+        <v>1.556116301001386e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.312778922528341e-09</v>
+        <v>1.312778922528355e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.549396073580122e-09</v>
+        <v>1.549396073580126e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.611924870539604e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.404377970115716e-09</v>
+        <v>1.404377970115723e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.500593685487827e-09</v>
+        <v>1.500593685487826e-09</v>
       </c>
       <c r="L5" t="n">
         <v>1.479700390316298e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.503404311694081e-09</v>
+        <v>1.503404311694078e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.384556298573703e-09</v>
+        <v>1.384556298573706e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23978865289183e-09</v>
+        <v>1.239788652891831e-09</v>
       </c>
       <c r="P5" t="n">
         <v>1.169843538335472e-09</v>
@@ -6061,34 +6061,34 @@
         <v>1.625881688023994e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.402458709305868e-09</v>
+        <v>1.402458709305875e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.373517092964938e-09</v>
+        <v>1.373517092964937e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.313787347704532e-09</v>
+        <v>1.313787347704527e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.286665571796007e-09</v>
+        <v>1.286665571796004e-09</v>
       </c>
       <c r="W5" t="n">
         <v>1.97995980138703e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.956330114499688e-09</v>
+        <v>1.956330114499777e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.675838773729443e-09</v>
+        <v>1.675838773729407e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.412359798211867e-09</v>
+        <v>1.412359798211866e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.475393133269039e-09</v>
+        <v>1.475393133269042e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.602887024797316e-09</v>
+        <v>1.602887024797317e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.329738764706722e-10</v>
+        <v>8.32973876470672e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.058146622226118e-10</v>
+        <v>5.058146622226104e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.288931347689082e-10</v>
+        <v>5.288931347689077e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.02494668210298e-10</v>
+        <v>5.024946682102978e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.327287542171311e-10</v>
+        <v>8.32728754217131e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.243872755602509e-10</v>
+        <v>8.243872755602516e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.296566570822933e-10</v>
+        <v>8.296566570822927e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.355058992988251e-10</v>
+        <v>8.355058992988235e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.289575802508545e-10</v>
+        <v>8.289575802508527e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>8.318163297666711e-10</v>
+        <v>8.318163297666725e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>5.221838267636788e-10</v>
+        <v>5.221838267636779e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>8.309803243311325e-10</v>
+        <v>8.309803243311329e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.126980370763956e-10</v>
+        <v>5.126980370763944e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.183332802738364e-10</v>
+        <v>8.183332802738345e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>4.92604402048081e-10</v>
+        <v>4.926044020480805e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.228792062924004e-10</v>
+        <v>8.228792062923994e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.221760869549968e-10</v>
+        <v>5.221760869549956e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>8.313979312469374e-10</v>
+        <v>8.313979312469369e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.099567248397194e-10</v>
+        <v>5.099567248397187e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>5.101878471647392e-10</v>
+        <v>5.10187847164739e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.133062497425755e-10</v>
+        <v>5.133062497425729e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.580875100181961e-10</v>
+        <v>5.580875100181936e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>8.583998230483794e-10</v>
+        <v>8.583998230483745e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.36385170591052e-10</v>
+        <v>5.363851705910534e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.18396493089051e-10</v>
+        <v>5.183964930890498e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.304843495974149e-10</v>
+        <v>8.304843495974134e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.211491675410147e-10</v>
+        <v>5.211491675410136e-10</v>
       </c>
     </row>
     <row r="7">
@@ -6186,49 +6186,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.15906316417746e-09</v>
+        <v>1.159063164177459e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.144955516739285e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.168033989285582e-09</v>
+        <v>1.168033989285583e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.141635522726972e-09</v>
+        <v>1.14163552272697e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.158818041923921e-09</v>
+        <v>1.158818041923922e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.150476563267039e-09</v>
+        <v>1.150476563267038e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.155745944789083e-09</v>
+        <v>1.155745944789081e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.161595187005613e-09</v>
+        <v>1.161595187005612e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.155046867957641e-09</v>
+        <v>1.155046867957644e-09</v>
       </c>
       <c r="K7" t="n">
         <v>1.15790561747346e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.161324681280353e-09</v>
+        <v>1.161324681280352e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.157069612037921e-09</v>
+        <v>1.157069612037922e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.151738275892475e-09</v>
+        <v>1.151738275892477e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.145924870847546e-09</v>
+        <v>1.145924870847548e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.141945915030309e-09</v>
+        <v>1.14194591503031e-09</v>
       </c>
       <c r="Q7" t="n">
         <v>1.148968493999189e-09</v>
@@ -6237,34 +6237,34 @@
         <v>1.16131694147167e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.157487218953724e-09</v>
+        <v>1.157487218953726e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.149097579356393e-09</v>
+        <v>1.149097579356394e-09</v>
       </c>
       <c r="U7" t="n">
         <v>1.149416391873169e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15244710425925e-09</v>
+        <v>1.152447104259252e-09</v>
       </c>
       <c r="W7" t="n">
         <v>1.187915561993286e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.184489110755166e-09</v>
+        <v>1.184489110755175e-09</v>
       </c>
       <c r="Y7" t="n">
         <v>1.167640352172304e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.157537347605725e-09</v>
+        <v>1.157537347605726e-09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.156573637304203e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.160205543689171e-09</v>
+        <v>1.160205543689172e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6274,22 +6274,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.089497592615782e-09</v>
+        <v>1.089497592615783e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.554649115685468e-09</v>
+        <v>1.554649115685471e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.577727588231766e-09</v>
+        <v>1.577727588231767e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.296137750627747e-09</v>
+        <v>1.296137750627746e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.163915447914102e-09</v>
+        <v>1.163915447914104e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.659547673305256e-09</v>
+        <v>1.659547673305258e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.565439543735266e-09</v>
@@ -6301,58 +6301,58 @@
         <v>1.564740466903825e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.567599216419642e-09</v>
+        <v>1.567599216419643e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.571018280226536e-09</v>
+        <v>1.57101828022653e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5667632109841e-09</v>
+        <v>1.566763210984104e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.189925839397326e-09</v>
+        <v>1.189925839397328e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.286235092338288e-09</v>
+        <v>1.286235092338287e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.257230654640611e-09</v>
+        <v>1.25723065464061e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.852175568615236e-10</v>
+        <v>9.852175568615261e-10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.571010540417854e-09</v>
+        <v>1.571010540417853e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.567180817899909e-09</v>
+        <v>1.567180817899908e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.558791178302576e-09</v>
+        <v>1.558791178302573e-09</v>
       </c>
       <c r="U8" t="n">
         <v>1.325193172762153e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.431252179843297e-09</v>
+        <v>1.431252179843293e-09</v>
       </c>
       <c r="W8" t="n">
         <v>1.597703349155769e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.064663228931729e-09</v>
+        <v>1.064663228931726e-09</v>
       </c>
       <c r="Y8" t="n">
         <v>2.054005899190391e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.079069290895488e-09</v>
+        <v>1.079069290895486e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.566267236250385e-09</v>
+        <v>1.566267236250388e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.070525421282867e-09</v>
+        <v>2.070525421282865e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6362,61 +6362,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.97731954075397e-10</v>
+        <v>8.977319540753977e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.039189598083104e-09</v>
+        <v>1.039189598083095e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.062268070629399e-09</v>
+        <v>1.062268070629397e-09</v>
       </c>
       <c r="E9" t="n">
         <v>9.999659281855604e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>6.944313991488635e-10</v>
+        <v>6.944313991488646e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.044710851111583e-09</v>
+        <v>1.044710851111587e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.049980026132898e-09</v>
+        <v>1.049980026132899e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.055829268349431e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.049280949301461e-09</v>
+        <v>1.049280949301456e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.052139698817278e-09</v>
+        <v>1.052139698817277e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.055558762624169e-09</v>
+        <v>1.055558762624172e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.051303693381738e-09</v>
+        <v>1.05130369338174e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.045972357236293e-09</v>
+        <v>1.045972357236294e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.091742934699874e-09</v>
+        <v>1.091742934699878e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.098976133366906e-09</v>
+        <v>1.098976133366907e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.043202781843733e-09</v>
+        <v>1.043202781843738e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.055551022815489e-09</v>
+        <v>1.055551022815484e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.051721300297543e-09</v>
+        <v>1.051721300297542e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.043331660700211e-09</v>
+        <v>1.043331660700221e-09</v>
       </c>
       <c r="U9" t="n">
         <v>1.04356278302523e-09</v>
@@ -6425,22 +6425,22 @@
         <v>1.226200287953045e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.082149643337102e-09</v>
+        <v>1.082149643337104e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.078723192098984e-09</v>
+        <v>1.078723192098965e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.061874433516123e-09</v>
+        <v>1.06187443351612e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.579794736123018e-10</v>
+        <v>9.579794736123035e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.050807718648021e-09</v>
+        <v>1.05080771864802e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.054439625032988e-09</v>
+        <v>1.054439625032987e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.028879457577148e-10</v>
+        <v>5.028879457577149e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.139136802640658e-10</v>
+        <v>5.139136802640661e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.030203952033543e-10</v>
+        <v>5.030203952033592e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.013298685780076e-10</v>
+        <v>5.013298685780085e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.017128660629707e-10</v>
+        <v>5.017128660629718e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.023872339637914e-10</v>
+        <v>5.023872339637923e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.016113829805166e-10</v>
+        <v>5.016113829805167e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.022820265769751e-10</v>
+        <v>5.022820265769781e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.022103184730329e-10</v>
+        <v>5.022103184730353e-10</v>
       </c>
       <c r="K2" t="n">
         <v>5.017599183815809e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.019722223071671e-10</v>
+        <v>5.019722223071668e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.000730891284597e-10</v>
+        <v>5.000730891284602e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.013921894683169e-10</v>
+        <v>5.013921894683176e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.758101016733721e-10</v>
+        <v>6.75810101673373e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.007970554816545e-10</v>
+        <v>5.007970554816561e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.011230336581564e-10</v>
+        <v>5.011230336581571e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.028016789339373e-10</v>
+        <v>5.028016789339416e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.017835737484256e-10</v>
+        <v>5.017835737484286e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.012868869636105e-10</v>
+        <v>5.012868869636136e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.691220579275565e-10</v>
+        <v>6.691220579275591e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.018538805558936e-10</v>
+        <v>5.018538805558946e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.001244654242324e-10</v>
+        <v>7.001244654242347e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.050144769772769e-10</v>
+        <v>5.050144769772806e-10</v>
       </c>
       <c r="Y2" t="n">
         <v>5.034172945212042e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.386097896120483e-10</v>
+        <v>7.386097896120542e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.020029907138563e-10</v>
+        <v>5.020029907138564e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.027667631107156e-10</v>
+        <v>5.027667631107161e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.430189080491231e-10</v>
+        <v>4.447028647368983e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.51518443572085e-10</v>
+        <v>4.527693275723606e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.441750730996488e-10</v>
+        <v>4.459108926270803e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.31331334295778e-10</v>
+        <v>4.325120359998962e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3488958104296e-10</v>
+        <v>4.362977141261098e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.394519631824568e-10</v>
+        <v>4.410113104069819e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.342254808660397e-10</v>
+        <v>4.356093500075078e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.389514972191235e-10</v>
+        <v>4.405017471273311e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.382638621144654e-10</v>
+        <v>4.397835385901378e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.351531451419697e-10</v>
+        <v>4.365676144483646e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.365401878958831e-10</v>
+        <v>4.380011004557068e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.324295751573078e-10</v>
+        <v>4.338032999436163e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.325072778893091e-10</v>
+        <v>4.338262505239272e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.179149790066066e-10</v>
+        <v>7.191148437788579e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2815044127654e-10</v>
+        <v>4.293103513266311e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.305716309569293e-10</v>
+        <v>4.318237596751093e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.427093808392091e-10</v>
+        <v>4.443942562319345e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.351710776013832e-10</v>
+        <v>4.365816647553772e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.318167463289753e-10</v>
+        <v>4.33112856119852e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.104998196527773e-10</v>
+        <v>7.118478269136536e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.355618323355422e-10</v>
+        <v>4.369841894875273e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.08923043588671e-10</v>
+        <v>8.124685977331333e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.58289020259852e-10</v>
+        <v>4.605295522531998e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.469784609016921e-10</v>
+        <v>4.488072569846036e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.260846814679009e-10</v>
+        <v>8.274947242734856e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.368621036250412e-10</v>
+        <v>4.383331238255586e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.433201498216547e-10</v>
+        <v>4.450259867722773e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.339182305329199e-10</v>
+        <v>4.3391823053292e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.138814223765054e-10</v>
+        <v>4.138814223765066e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.35414307951239e-10</v>
+        <v>4.354143079512402e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.163190320372373e-10</v>
+        <v>4.16319032037238e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.20645164817439e-10</v>
+        <v>4.206451648174399e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.282624604817625e-10</v>
+        <v>4.28262460481763e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.194988667165867e-10</v>
+        <v>4.194988667165869e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.270740946499081e-10</v>
+        <v>4.270740946499084e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.262140528547635e-10</v>
+        <v>4.262140528547649e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.21176642401272e-10</v>
+        <v>4.211766424012721e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.235747129053971e-10</v>
+        <v>4.235747129053974e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.191636589593262e-10</v>
+        <v>4.191636589593269e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.170229751622913e-10</v>
+        <v>4.170229751622917e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.120820462449256e-10</v>
+        <v>4.120820462449258e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.103006630078024e-10</v>
+        <v>4.103006630078034e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.139827364687441e-10</v>
+        <v>4.139827364687458e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.329438070737095e-10</v>
+        <v>4.329438070737106e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.214438406518196e-10</v>
+        <v>4.214438406518201e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.158335349301269e-10</v>
+        <v>4.158335349301281e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.181708811769067e-10</v>
+        <v>4.181708811769068e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.221247947256514e-10</v>
+        <v>4.221247947256518e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>5.169349069961905e-10</v>
+        <v>5.169349069961912e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.579383789106074e-10</v>
+        <v>4.579383789106085e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.395252373035525e-10</v>
+        <v>4.395252373035528e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.21498908970929e-10</v>
+        <v>4.214989089709286e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.239222562131201e-10</v>
+        <v>4.239222562131211e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.340697703974212e-10</v>
+        <v>4.340697703974214e-10</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.597118800558287e-09</v>
+        <v>1.597118800558289e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.347450657616321e-09</v>
+        <v>1.34745065761632e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.73285575414754e-09</v>
+        <v>1.732855754147542e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>9.917558188691559e-10</v>
+        <v>9.917558188691573e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.495689169188638e-09</v>
+        <v>1.495689169188639e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.500538637871712e-09</v>
+        <v>1.500538637871716e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.506606753412571e-09</v>
+        <v>1.506606753412572e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.609286167310093e-09</v>
+        <v>1.609286167310096e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.50378011897696e-09</v>
+        <v>1.503780118976962e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.467647160260038e-09</v>
+        <v>1.467647160260039e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.443634464409098e-09</v>
+        <v>1.443634464409099e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.461558947752398e-09</v>
+        <v>1.461558947752401e-09</v>
       </c>
       <c r="N5" t="n">
         <v>1.383109448861235e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.243321356409309e-09</v>
+        <v>1.24332135640931e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.207553817448001e-09</v>
+        <v>1.207553817448031e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.321736233473096e-09</v>
+        <v>1.321736233473097e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.738545949287254e-09</v>
+        <v>1.738545949287257e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.394174415157858e-09</v>
+        <v>1.394174415157859e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.393693095551528e-09</v>
+        <v>1.393693095551532e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.368151422443294e-09</v>
+        <v>1.368151422443298e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.350569351788495e-09</v>
+        <v>1.350569351788494e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>3.06891018681328e-09</v>
+        <v>3.068910186813287e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.070125239862777e-09</v>
+        <v>2.07012523986278e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.79696260832744e-09</v>
+        <v>1.796962608327438e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.375368444906254e-09</v>
+        <v>1.375368444906257e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.502806130113561e-09</v>
+        <v>1.502806130113577e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.776041946441215e-09</v>
+        <v>1.776041946441216e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.452659886286909e-10</v>
+        <v>8.452659886286935e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.25229180472276e-10</v>
+        <v>8.252291804722781e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.467620660470082e-10</v>
+        <v>8.46762066047008e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.131083757191407e-10</v>
+        <v>5.131083757191413e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>8.319929229132102e-10</v>
+        <v>8.319929229132103e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.396102185775321e-10</v>
+        <v>8.396102185775348e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>8.308466248123576e-10</v>
+        <v>8.308466248123586e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.384218527456776e-10</v>
+        <v>8.384218527456798e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.23003396536666e-10</v>
+        <v>5.230033965366663e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.179659860831756e-10</v>
+        <v>5.179659860831753e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.349224710011684e-10</v>
+        <v>8.349224710011695e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>8.305114170550966e-10</v>
+        <v>8.305114170550982e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.138738864748978e-10</v>
+        <v>5.138738864748982e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>5.089092114804107e-10</v>
+        <v>5.089092114804111e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>8.190413581490152e-10</v>
+        <v>8.190413581490196e-10</v>
       </c>
       <c r="Q6" t="n">
         <v>8.253304945645154e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.442915651694797e-10</v>
+        <v>8.442915651694816e-10</v>
       </c>
       <c r="S6" t="n">
         <v>8.327915987475915e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.126228786120305e-10</v>
+        <v>5.126228786120317e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>8.298908702981302e-10</v>
+        <v>8.298908702981317e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.189141384075552e-10</v>
+        <v>5.189141384075558e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>9.256642972945688e-10</v>
+        <v>9.256642972945708e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>5.547277225925111e-10</v>
+        <v>5.54727722592511e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.44569701641248e-10</v>
+        <v>5.445697016412477e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.182882526528321e-10</v>
+        <v>5.182882526528322e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.352700143088905e-10</v>
+        <v>8.352700143088918e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.309309160266124e-10</v>
+        <v>5.309309160266131e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.167301232963398e-09</v>
+        <v>1.1673012329634e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.147264424806986e-09</v>
@@ -7061,7 +7061,7 @@
         <v>1.154028167247916e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.161645462912242e-09</v>
+        <v>1.16164546291224e-09</v>
       </c>
       <c r="H7" t="n">
         <v>1.152881869147065e-09</v>
@@ -7073,58 +7073,58 @@
         <v>1.159597055285242e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.154559644831752e-09</v>
+        <v>1.154559644831754e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.156957715335877e-09</v>
+        <v>1.156957715335879e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.152546661389805e-09</v>
+        <v>1.152546661389806e-09</v>
       </c>
       <c r="N7" t="n">
         <v>1.15040597759277e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.145435525502924e-09</v>
+        <v>1.145435525502923e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.143654142265802e-09</v>
+        <v>1.143654142265801e-09</v>
       </c>
       <c r="Q7" t="n">
         <v>1.147365738899223e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.166326809504188e-09</v>
+        <v>1.166326809504186e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.154826843082298e-09</v>
+        <v>1.154826843082297e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.149216537360606e-09</v>
+        <v>1.149216537360607e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.152025566551727e-09</v>
+        <v>1.152025566551728e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.155507797156131e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.250317909426669e-09</v>
+        <v>1.25031790942667e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.191321381341088e-09</v>
+        <v>1.191321381341087e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.173280470759485e-09</v>
+        <v>1.173280470759487e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.154881911401408e-09</v>
+        <v>1.154881911401407e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.157305258643599e-09</v>
+        <v>1.1573052586436e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.167452772827899e-09</v>
+        <v>1.1674527728279e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7137,40 +7137,40 @@
         <v>1.094168531604426e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.550187023709203e-09</v>
+        <v>1.550187023709208e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.571719909283936e-09</v>
+        <v>1.571719909283941e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.299139228723323e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.155059317900423e-09</v>
+        <v>1.155059317900424e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.663281229539298e-09</v>
+        <v>1.6632812295393e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.555804468049284e-09</v>
+        <v>1.555804468049289e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.563379695982606e-09</v>
+        <v>1.563379695982608e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.562519654187462e-09</v>
+        <v>1.562519654187467e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.55748224373397e-09</v>
+        <v>1.557482243733969e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.559880314238095e-09</v>
+        <v>1.559880314238098e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.555469260292045e-09</v>
+        <v>1.55546926029205e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.184306076489764e-09</v>
+        <v>1.184306076489766e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.280775734770642e-09</v>
@@ -7179,40 +7179,40 @@
         <v>1.254136166184853e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.806773055934511e-10</v>
+        <v>9.806773055934519e-10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.569249408406408e-09</v>
+        <v>1.569249408406411e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.557749441984519e-09</v>
+        <v>1.55774944198452e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.552139136262825e-09</v>
+        <v>1.552139136262826e-09</v>
       </c>
       <c r="U8" t="n">
         <v>1.322592427878117e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.428427549198417e-09</v>
+        <v>1.428427549198418e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.65333406688945e-09</v>
+        <v>1.653334066889454e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.068264362273124e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.049705008703568e-09</v>
+        <v>2.049705008703572e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.072906238428894e-09</v>
+        <v>1.072906238428895e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.560227857545818e-09</v>
+        <v>1.560227857545821e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.067654939998463e-09</v>
+        <v>2.067654939998462e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.920880574706688e-10</v>
+        <v>8.920880574706696e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.023369424529829e-09</v>
+        <v>1.023369424529835e-09</v>
       </c>
       <c r="D9" t="n">
         <v>1.044902310104567e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>9.908835755300318e-10</v>
+        <v>9.90883575530037e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>6.813032047029968e-10</v>
+        <v>6.813032047029992e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.037750669294964e-09</v>
+        <v>1.037750669294967e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.028986868869912e-09</v>
+        <v>1.028986868869915e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.036562096803235e-09</v>
+        <v>1.036562096803237e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.035702055008089e-09</v>
+        <v>1.035702055008094e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.030664644554596e-09</v>
+        <v>1.030664644554601e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.033062715058721e-09</v>
+        <v>1.033062715058725e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.028651661112651e-09</v>
+        <v>1.028651661112654e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.026510977315616e-09</v>
+        <v>1.02651097731562e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.071716968677217e-09</v>
+        <v>1.071716968677218e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.080841635279497e-09</v>
+        <v>1.0808416352795e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.023470945281947e-09</v>
+        <v>1.02347094528195e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.042431809227033e-09</v>
+        <v>1.042431809227038e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.030931842805146e-09</v>
+        <v>1.030931842805145e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.025321537083453e-09</v>
+        <v>1.025321537083457e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.028031114355686e-09</v>
+        <v>1.028031114355687e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.206230825004987e-09</v>
+        <v>1.206230825004991e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.126422909149514e-09</v>
+        <v>1.126422909149517e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.067426381063932e-09</v>
+        <v>1.067426381063936e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04938547048233e-09</v>
+        <v>1.049385470482333e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.397555892687708e-10</v>
+        <v>9.39755589268773e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.033410258366444e-09</v>
+        <v>1.033410258366448e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.043557772550746e-09</v>
+        <v>1.043557772550749e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.211429091878042e-10</v>
+        <v>5.21142909187804e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.320136828626488e-10</v>
+        <v>5.320136828626491e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.208791530115093e-10</v>
+        <v>5.208791530115084e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.189383283473377e-10</v>
+        <v>5.18938328347336e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.191115304556846e-10</v>
+        <v>5.191115304556839e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.246206259422871e-10</v>
+        <v>5.246206259422853e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.187427683175164e-10</v>
+        <v>5.187427683175142e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.208208885469471e-10</v>
+        <v>5.208208885469455e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.227601902120965e-10</v>
+        <v>5.22760190212093e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.235552800901195e-10</v>
+        <v>5.235552800901189e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.264843851243377e-10</v>
+        <v>5.264843851243341e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.277530587205759e-10</v>
+        <v>5.277530587205763e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.217386553043704e-10</v>
+        <v>5.21738655304369e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.211198686476675e-10</v>
+        <v>7.211198686476663e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.218054815194457e-10</v>
+        <v>5.218054815194449e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.194196174515024e-10</v>
+        <v>5.194196174515008e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.192362686607538e-10</v>
+        <v>5.192362686607526e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.211524088856292e-10</v>
+        <v>5.211524088856282e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.197848440355634e-10</v>
+        <v>5.197848440355624e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.205735511573736e-10</v>
+        <v>7.205735511573702e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.191911881517469e-10</v>
+        <v>5.191911881517456e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.415265978089067e-10</v>
+        <v>7.415265978089041e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.229933887126964e-10</v>
+        <v>5.229933887126929e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.215887986659921e-10</v>
+        <v>5.215887986659907e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.693519331667838e-10</v>
+        <v>7.693519331667821e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.190060293642773e-10</v>
+        <v>5.190060293642766e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.329835731448866e-10</v>
+        <v>5.329835731448868e-10</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.620098733410936e-10</v>
+        <v>4.638952510009249e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.625801707152445e-10</v>
+        <v>4.636785778058911e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.604272018047126e-10</v>
+        <v>4.622667334907403e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.457410075392912e-10</v>
+        <v>4.469609754559748e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.478017297653254e-10</v>
+        <v>4.491965974289239e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.867040293571238e-10</v>
+        <v>4.894601682650702e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.452206858652837e-10</v>
+        <v>4.465229017341251e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.600281216286131e-10</v>
+        <v>4.618552770571832e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.73576252251521e-10</v>
+        <v>4.758736456064475e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.793337705341704e-10</v>
+        <v>4.81850068143997e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.001625458662414e-10</v>
+        <v>5.034003993745264e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.182621350518366e-10</v>
+        <v>5.22228145397855e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.664944841330009e-10</v>
+        <v>4.685458626096344e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.83199811051776e-10</v>
+        <v>7.846760337728879e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.667412437782032e-10</v>
+        <v>4.687892889985669e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.499155086489872e-10</v>
+        <v>4.513820228127456e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.487161874391359e-10</v>
+        <v>4.501420406101307e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.620567256227708e-10</v>
+        <v>4.639486688408429e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.525980923176206e-10</v>
+        <v>4.541603905903784e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.175506846948152e-10</v>
+        <v>8.206264009387182e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.480393839359026e-10</v>
+        <v>4.494334600699147e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.298815211502567e-10</v>
+        <v>8.31957282918772e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.755099850881151e-10</v>
+        <v>4.778846271555679e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.653675362524934e-10</v>
+        <v>4.673784717719217e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.701598872492122e-10</v>
+        <v>8.719743163826935e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.469395843687013e-10</v>
+        <v>4.482978869145263e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.472824862891624e-10</v>
+        <v>5.521911243524316e-10</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.606072415469129e-10</v>
+        <v>4.606072415469051e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.246908608711783e-10</v>
+        <v>4.246908608711789e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.57627994201822e-10</v>
+        <v>4.576279942018232e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.357054867965467e-10</v>
+        <v>4.357054867965465e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.376618842872362e-10</v>
+        <v>4.376618842872382e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.998896521175376e-10</v>
+        <v>4.998896521175391e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.334965462976617e-10</v>
+        <v>4.334965462976599e-10</v>
       </c>
       <c r="I4" t="n">
-        <v>4.569698702716135e-10</v>
+        <v>4.56969870271614e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.788101341413564e-10</v>
+        <v>4.788101341413549e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.878560806340066e-10</v>
+        <v>4.87856080634006e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>5.209416694503923e-10</v>
+        <v>5.20941669450377e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>5.516368322846793e-10</v>
+        <v>5.516368322846816e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.673364679902732e-10</v>
+        <v>4.673364679902747e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.421692987392203e-10</v>
+        <v>4.421692987392212e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.680913008311304e-10</v>
+        <v>4.680913008311293e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.411418686320158e-10</v>
+        <v>4.411418686320153e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.390708596958944e-10</v>
+        <v>4.390708596958967e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.607145450039242e-10</v>
+        <v>4.607145450039229e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.452672709115144e-10</v>
+        <v>4.452672709115146e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>5.125088908352192e-10</v>
+        <v>5.125088908352183e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.383462531196453e-10</v>
+        <v>4.383462531196456e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.686560340235182e-10</v>
+        <v>4.686560340235196e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.815092590432091e-10</v>
+        <v>4.81509259043204e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.643760614780729e-10</v>
+        <v>4.643760614780726e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.573378368206167e-10</v>
+        <v>4.57337836820615e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.364702009268911e-10</v>
+        <v>4.364702009268915e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.941018386533677e-10</v>
+        <v>5.941018386533688e-10</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.845956456891273e-09</v>
+        <v>1.845956456891202e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.296113068757332e-09</v>
+        <v>1.296113068757333e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.956342583108897e-09</v>
+        <v>1.956342583108912e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.077762735662101e-09</v>
+        <v>1.077762735662082e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.573340655106414e-09</v>
+        <v>1.573340655106418e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.518361369247773e-09</v>
+        <v>2.518361369247779e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.522851985250025e-09</v>
+        <v>1.522851985250026e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.953217843762318e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>2.204515940202846e-09</v>
+        <v>2.204515940202842e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.420508453200257e-09</v>
+        <v>2.420508453200259e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>3.003601290837697e-09</v>
+        <v>3.003601290837406e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>3.669417676325327e-09</v>
+        <v>3.669417676325304e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.102631491862216e-09</v>
+        <v>2.102631491862217e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.523433459416669e-09</v>
+        <v>1.523433459416678e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.988887348389293e-09</v>
+        <v>1.988887348389306e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.591837246744682e-09</v>
+        <v>1.591837246744656e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.613437467801049e-09</v>
+        <v>1.613437467801055e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.836335321494346e-09</v>
+        <v>1.836335321494326e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.712076013603085e-09</v>
+        <v>1.712076013603079e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.880734941796555e-09</v>
+        <v>2.880734941796554e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.406125724859248e-09</v>
+        <v>1.406125724859251e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.097476755774135e-09</v>
+        <v>2.097476755774116e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.404204242965934e-09</v>
+        <v>2.404204242965926e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.03869539540374e-09</v>
+        <v>2.038695395403749e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.797251224145742e-09</v>
+        <v>1.797251224145684e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.4900883578664e-09</v>
+        <v>1.490088357866387e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.871518920263423e-09</v>
+        <v>4.871518920263386e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.604231002648443e-10</v>
+        <v>5.604231002648396e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.245067195891086e-10</v>
+        <v>5.245067195891098e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>5.574438529197549e-10</v>
+        <v>5.574438529197565e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.80037684763709e-10</v>
+        <v>8.800376847637079e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.374777430051672e-10</v>
+        <v>5.374777430051687e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>9.442218500846994e-10</v>
+        <v>9.442218500846988e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.333124050155903e-10</v>
+        <v>5.333124050155909e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>5.567857289895449e-10</v>
+        <v>5.567857289895454e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.786259928592866e-10</v>
+        <v>5.786259928592854e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>9.321882786011659e-10</v>
+        <v>9.321882786011661e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>9.652738674175537e-10</v>
+        <v>9.65273867417527e-10</v>
       </c>
       <c r="M6" t="n">
         <v>6.514526910026106e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.673142857868345e-10</v>
+        <v>5.673142857868334e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.847794617450705e-10</v>
+        <v>8.847794617450692e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>9.107097399394832e-10</v>
+        <v>9.107097399394807e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.409577273499464e-10</v>
+        <v>5.409577273499457e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.834030576630556e-10</v>
+        <v>8.834030576630569e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.605304037218553e-10</v>
+        <v>5.605304037218542e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.450831296294448e-10</v>
+        <v>5.450831296294459e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.581087956466429e-10</v>
+        <v>9.581087956466445e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.381621118375767e-10</v>
+        <v>5.381621118375772e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.78576664217296e-10</v>
+        <v>5.785766642172944e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>9.258414570103691e-10</v>
+        <v>9.258414570103646e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.74023975541476e-10</v>
+        <v>5.740239755414766e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.016700347877778e-10</v>
+        <v>9.01670034787776e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.808023988940512e-10</v>
+        <v>8.808023988940528e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.948563241079735e-10</v>
+        <v>6.948563241079737e-10</v>
       </c>
     </row>
     <row r="7">
@@ -7906,19 +7906,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.27420576483712e-09</v>
+        <v>1.274205764837115e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.238289384161386e-09</v>
+        <v>1.238289384161388e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.27122651749203e-09</v>
+        <v>1.271226517492034e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.249304010086753e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.251260407577444e-09</v>
+        <v>1.251260407577445e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.313488175407746e-09</v>
@@ -7927,61 +7927,61 @@
         <v>1.247095069587868e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.270568393561821e-09</v>
+        <v>1.270568393561823e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.292408657431564e-09</v>
+        <v>1.292408657431561e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.301454603924215e-09</v>
+        <v>1.301454603924213e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.334540192740598e-09</v>
+        <v>1.334540192740574e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.365235355574887e-09</v>
+        <v>1.36523535557489e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28093499128048e-09</v>
+        <v>1.280934991280482e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.255735778929448e-09</v>
+        <v>1.255735778929451e-09</v>
       </c>
       <c r="P7" t="n">
         <v>1.281657781021362e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.254740391922225e-09</v>
+        <v>1.254740391922222e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.252669382986104e-09</v>
+        <v>1.252669382986106e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.274313068294132e-09</v>
+        <v>1.27431306829413e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.258865794201722e-09</v>
+        <v>1.258865794201721e-09</v>
       </c>
       <c r="U7" t="n">
         <v>1.327350684328372e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.251944776409855e-09</v>
+        <v>1.251944776409853e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.282254557313724e-09</v>
+        <v>1.282254557313726e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.295107782333419e-09</v>
+        <v>1.295107782333413e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.279242291612543e-09</v>
+        <v>1.279242291612545e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.270936360110824e-09</v>
+        <v>1.270936360110823e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.250068724217099e-09</v>
+        <v>1.2500687242171e-09</v>
       </c>
       <c r="AB7" t="n">
         <v>1.407700361943577e-09</v>
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.224988770149327e-09</v>
+        <v>1.224988770149324e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.739462336465647e-09</v>
+        <v>1.739462336465649e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.772399469796289e-09</v>
+        <v>1.772399469796295e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.457410551090992e-09</v>
+        <v>1.457410551090993e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.287787734096774e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92878806868328e-09</v>
+        <v>1.928788068683285e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.748268021892125e-09</v>
+        <v>1.748268021892126e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.77174134586608e-09</v>
+        <v>1.771741345866083e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.793581609735821e-09</v>
+        <v>1.793581609735825e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.802627556228473e-09</v>
+        <v>1.802627556228476e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.835713145044858e-09</v>
+        <v>1.835713145044849e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.86640830787913e-09</v>
+        <v>1.866408307879131e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.355463656452872e-09</v>
+        <v>1.355463656452873e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.447542041834794e-09</v>
+        <v>1.447542041834796e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.444724325432203e-09</v>
+        <v>1.444724325432206e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.097359210593939e-09</v>
+        <v>1.097359210593942e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.753842335290364e-09</v>
+        <v>1.753842335290366e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.775486020598393e-09</v>
+        <v>1.775486020598395e-09</v>
       </c>
       <c r="T8" t="n">
         <v>1.760038746505982e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.559915980982414e-09</v>
+        <v>1.559915980982417e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.602694359181426e-09</v>
+        <v>1.602694359181428e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.783535677087071e-09</v>
+        <v>1.783535677087077e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.188170933333668e-09</v>
+        <v>1.188170933333666e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.32766552486522e-09</v>
+        <v>2.327665524865227e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.211495589581182e-09</v>
+        <v>1.211495589581179e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.751241676521357e-09</v>
+        <v>1.75124167652136e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.483801636807898e-09</v>
+        <v>2.483801636807896e-09</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.029159932892054e-09</v>
+        <v>1.029159932892048e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.178645065990341e-09</v>
+        <v>1.17864506599034e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.211582199320984e-09</v>
+        <v>1.21158219932099e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.146869939876161e-09</v>
+        <v>1.14686993987616e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.64214725909706e-10</v>
+        <v>7.64214725909705e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.253844066674595e-09</v>
+        <v>1.253844066674597e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.187450751416821e-09</v>
+        <v>1.187450751416823e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.210924075390775e-09</v>
+        <v>1.210924075390776e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.232764339260515e-09</v>
+        <v>1.232764339260517e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.241810285753167e-09</v>
+        <v>1.241810285753169e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.274895874569554e-09</v>
+        <v>1.27489587456953e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.305591037403841e-09</v>
+        <v>1.305591037403843e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.221290673109434e-09</v>
+        <v>1.221290673109435e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.257565601605949e-09</v>
+        <v>1.257565601605948e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.296850160239899e-09</v>
+        <v>1.296850160239897e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.195096283189071e-09</v>
+        <v>1.19509628318907e-09</v>
       </c>
       <c r="R9" t="n">
         <v>1.193025064815058e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.214668750123084e-09</v>
+        <v>1.214668750123085e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.199221476030677e-09</v>
+        <v>1.199221476030678e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.267730802798643e-09</v>
+        <v>1.267730802798645e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.406249870433562e-09</v>
+        <v>1.406249870433567e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.222610239142681e-09</v>
+        <v>1.222610239142682e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.23546346416237e-09</v>
+        <v>1.235463464162365e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.219597973441498e-09</v>
+        <v>1.219597973441501e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.099511498845397e-09</v>
+        <v>1.099511498845394e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.190424406046051e-09</v>
+        <v>1.190424406046052e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.348056043772533e-09</v>
+        <v>1.34805604377253e-09</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.127503827787366e-10</v>
+        <v>5.127503827787391e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.265761733446636e-10</v>
+        <v>5.26576173344664e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.137960316170158e-10</v>
+        <v>5.137960316170182e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.123532329703418e-10</v>
+        <v>5.123532329703412e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.130610209903345e-10</v>
+        <v>5.130610209903355e-10</v>
       </c>
       <c r="G2" t="n">
         <v>5.169265927470364e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.123958950695998e-10</v>
+        <v>5.123958950696028e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.135937283982902e-10</v>
+        <v>5.135937283982906e-10</v>
       </c>
       <c r="J2" t="n">
         <v>5.145909192109333e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.144200259980354e-10</v>
+        <v>5.144200259980381e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.157466127059592e-10</v>
+        <v>5.157466127059583e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.130191548950537e-10</v>
+        <v>5.130191548950545e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.123969090754414e-10</v>
+        <v>5.123969090754422e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.053292669866863e-10</v>
+        <v>7.053292669866881e-10</v>
       </c>
       <c r="P2" t="n">
         <v>5.139970249864388e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.136790865175958e-10</v>
+        <v>5.136790865175934e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.135183150322425e-10</v>
+        <v>5.135183150322465e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.135062304422192e-10</v>
+        <v>5.13506230442221e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.126462290014405e-10</v>
+        <v>5.126462290014437e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.004850784175676e-10</v>
+        <v>7.00485078417573e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.128334444737785e-10</v>
+        <v>5.128334444737801e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.26877084579236e-10</v>
+        <v>7.268770845792405e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.161098560615512e-10</v>
+        <v>5.161098560615537e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.181798130310448e-10</v>
+        <v>5.181798130310453e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.579224360786756e-10</v>
+        <v>7.579224360786776e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.129758225706339e-10</v>
+        <v>5.129758225706359e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.219306153759235e-10</v>
+        <v>5.219306153759242e-10</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.409756702661674e-10</v>
+        <v>4.423161148311894e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.623455084008989e-10</v>
+        <v>4.636313553597048e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>4.486118492774137e-10</v>
+        <v>4.502299794072325e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.375307054255642e-10</v>
+        <v>4.386571809577838e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.43382963384238e-10</v>
+        <v>4.448187081917144e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.705660280700841e-10</v>
+        <v>4.729516539683056e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.38698001029407e-10</v>
+        <v>4.399653474029561e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.472084199842949e-10</v>
+        <v>4.487770589229752e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.540790658375605e-10</v>
+        <v>4.558842187422559e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>4.529619200335645e-10</v>
+        <v>4.547367923995195e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>4.62300016694184e-10</v>
+        <v>4.64399235868613e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>4.523499838647698e-10</v>
+        <v>4.541604226764383e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.385787514553233e-10</v>
+        <v>4.398386468841451e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.546045898200059e-10</v>
+        <v>7.557490693581391e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.498167123176375e-10</v>
+        <v>4.514667021568693e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.476560266674695e-10</v>
+        <v>4.492418435695519e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>4.466998333885826e-10</v>
+        <v>4.482513352136432e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>4.463286528931102e-10</v>
+        <v>4.478610709988873e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.404087947581199e-10</v>
+        <v>4.417354315475773e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.560056908951535e-10</v>
+        <v>7.575634456991882e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.414554089229671e-10</v>
+        <v>4.428134737503703e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.109805555943211e-10</v>
+        <v>8.130828596291462e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>4.650919133036387e-10</v>
+        <v>4.672960289511569e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.798160228115407e-10</v>
+        <v>4.825345164288703e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.477763664582019e-10</v>
+        <v>8.492152149518378e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.426863307756955e-10</v>
+        <v>4.440904923255987e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.071861242456295e-10</v>
+        <v>5.108775546650807e-10</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.245292281758823e-10</v>
+        <v>4.245292281758827e-10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.215970627477849e-10</v>
+        <v>4.215970627477856e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.363403128264829e-10</v>
+        <v>4.363403128264834e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>4.200432383921294e-10</v>
+        <v>4.200432383921298e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2803802967652e-10</v>
+        <v>4.280380296765202e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>4.717014409193329e-10</v>
+        <v>4.717014409193325e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>4.205251264287844e-10</v>
+        <v>4.20525126428785e-10</v>
       </c>
       <c r="I4" t="n">
         <v>4.340552049068986e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.452603219420333e-10</v>
+        <v>4.452603219420334e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>4.43388616411693e-10</v>
+        <v>4.433886164116938e-10</v>
       </c>
       <c r="L4" t="n">
-        <v>4.583730235377284e-10</v>
+        <v>4.583730235377294e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>4.446839478850853e-10</v>
+        <v>4.446839478850859e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>4.205365800912249e-10</v>
+        <v>4.205365800912253e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.157048217527939e-10</v>
+        <v>4.157048217527943e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.386106253956327e-10</v>
+        <v>4.386106253956333e-10</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.350193641311242e-10</v>
+        <v>4.350193641311246e-10</v>
       </c>
       <c r="R4" t="n">
-        <v>4.332033762455234e-10</v>
+        <v>4.332033762455237e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>4.330668752420272e-10</v>
+        <v>4.330668752420275e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>4.233527633482237e-10</v>
+        <v>4.233527633482246e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>4.33249522945062e-10</v>
+        <v>4.332495229450624e-10</v>
       </c>
       <c r="V4" t="n">
-        <v>4.25295481186511e-10</v>
+        <v>4.252954811865118e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>4.583963773664244e-10</v>
+        <v>4.583963773664245e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>4.624760243393419e-10</v>
+        <v>4.624760243393426e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.849973465678e-10</v>
+        <v>4.849973465678001e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.289308953623912e-10</v>
+        <v>4.289308953623914e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.270756743327922e-10</v>
+        <v>4.270756743327925e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.285323073989097e-10</v>
+        <v>5.285323073989104e-10</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.322830622550626e-09</v>
+        <v>1.322830622550627e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.347193596308197e-09</v>
+        <v>1.347193596308199e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.621553610751429e-09</v>
+        <v>1.621553610751431e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>9.271191346765219e-10</v>
+        <v>9.271191346765225e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>1.483483219526255e-09</v>
+        <v>1.483483219526256e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.045491873100593e-09</v>
+        <v>2.045491873100562e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.382773665713848e-09</v>
+        <v>1.382773665713849e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.602083759316055e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.673575701573037e-09</v>
+        <v>1.673575701573025e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.692625783992241e-09</v>
+        <v>1.692625783992243e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.890374440917035e-09</v>
+        <v>1.890374440917037e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.759665477576221e-09</v>
+        <v>1.759665477576222e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.317427773214493e-09</v>
+        <v>1.317427773214492e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.181451415810188e-09</v>
+        <v>1.18145141581019e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.542704452104307e-09</v>
+        <v>1.542704452104306e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.535392191338974e-09</v>
+        <v>1.535392191338976e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.602379164863251e-09</v>
+        <v>1.602379164863253e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.452306035255245e-09</v>
+        <v>1.452306035255246e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.39347670069056e-09</v>
+        <v>1.393476700690567e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.502813990854655e-09</v>
+        <v>1.502813990854659e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.280653439249472e-09</v>
+        <v>1.280653439249471e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.97354803866596e-09</v>
+        <v>1.973548038665961e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>2.066282311953683e-09</v>
+        <v>2.0662823119537e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.45427959671217e-09</v>
+        <v>2.454279596712173e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.380670511790999e-09</v>
+        <v>1.380670511791e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.420564647925587e-09</v>
+        <v>1.420564647925583e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.433464839360914e-09</v>
+        <v>3.433464839360921e-09</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.36561792077949e-10</v>
+        <v>8.365617920779518e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>8.336296266498517e-10</v>
+        <v>8.336296266498515e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.483728767285485e-10</v>
+        <v>8.483728767285496e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>5.131731806382826e-10</v>
+        <v>5.131731806382839e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.211679719226726e-10</v>
+        <v>5.211679719226739e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>5.648313831654863e-10</v>
+        <v>5.648313831654868e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.136550686749373e-10</v>
+        <v>5.136550686749386e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>8.460877688089661e-10</v>
+        <v>8.460877688089663e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.57292885844101e-10</v>
+        <v>8.57292885844102e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>5.365185586578461e-10</v>
+        <v>5.365185586578479e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>8.70405587439795e-10</v>
+        <v>8.704055874397962e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>5.378138901312386e-10</v>
+        <v>5.3781389013124e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>5.137578095029329e-10</v>
+        <v>5.137578095029341e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>8.261290633093135e-10</v>
+        <v>8.261290633093146e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.213986798694273e-10</v>
+        <v>5.213986798694292e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.281493063772768e-10</v>
+        <v>5.281493063772776e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>8.452359401475906e-10</v>
+        <v>8.452359401475926e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>5.261968174881794e-10</v>
+        <v>5.26196817488181e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>5.164827055943771e-10</v>
+        <v>5.164827055943781e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>8.461418808163513e-10</v>
+        <v>8.461418808163534e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>5.184254234326648e-10</v>
+        <v>5.184254234326661e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>5.60903774099624e-10</v>
+        <v>5.60903774099622e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>8.745085882414093e-10</v>
+        <v>8.745085882414118e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.868838012211394e-10</v>
+        <v>5.868838012211406e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.409634592644585e-10</v>
+        <v>8.409634592644603e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.202056165789452e-10</v>
+        <v>5.202056165789466e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.222500104723018e-10</v>
+        <v>6.222500104723032e-10</v>
       </c>
     </row>
     <row r="7">
@@ -8769,7 +8769,7 @@
         <v>1.175515265839223e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.172583100411125e-09</v>
+        <v>1.172583100411126e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.187326350489825e-09</v>
@@ -8781,28 +8781,28 @@
         <v>1.17902406733986e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.222687478582675e-09</v>
+        <v>1.222687478582674e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.171511164092127e-09</v>
+        <v>1.171511164092128e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.18504124257024e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.196246359605374e-09</v>
+        <v>1.196246359605373e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.194374654075034e-09</v>
+        <v>1.194374654075035e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.20935906120107e-09</v>
+        <v>1.209359061201072e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.195669985548427e-09</v>
+        <v>1.19566998554843e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.171522617754568e-09</v>
+        <v>1.171522617754567e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.166661072805811e-09</v>
@@ -8814,37 +8814,37 @@
         <v>1.186005401794464e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.184189413908865e-09</v>
+        <v>1.184189413908866e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.184052912905368e-09</v>
+        <v>1.184052912905369e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.174338801011565e-09</v>
+        <v>1.174338801011566e-09</v>
       </c>
       <c r="U7" t="n">
         <v>1.185126365266435e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.176281518849853e-09</v>
+        <v>1.176281518849854e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.209382415029766e-09</v>
+        <v>1.209382415029767e-09</v>
       </c>
       <c r="X7" t="n">
         <v>1.213462062002685e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.236843178200364e-09</v>
+        <v>1.236843178200366e-09</v>
       </c>
       <c r="Z7" t="n">
         <v>1.179916933025734e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.178061711996133e-09</v>
+        <v>1.178061711996135e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.27951834506225e-09</v>
+        <v>1.279518345062251e-09</v>
       </c>
     </row>
     <row r="8">
@@ -8854,52 +8854,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.119917962123513e-09</v>
+        <v>1.119917962123515e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.618317536794478e-09</v>
+        <v>1.618317536794477e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.633060786873175e-09</v>
+        <v>1.633060786873176e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.349819349184964e-09</v>
+        <v>1.349819349184965e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.20152838955143e-09</v>
+        <v>1.201528389551431e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.772376317152675e-09</v>
+        <v>1.772376317152673e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.617245600475479e-09</v>
+        <v>1.617245600475478e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.630775678953591e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.641980795988725e-09</v>
+        <v>1.641980795988727e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.640109090458384e-09</v>
+        <v>1.640109090458386e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.655093497584421e-09</v>
+        <v>1.655093497584422e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.641404421931747e-09</v>
+        <v>1.641404421931748e-09</v>
       </c>
       <c r="N8" t="n">
         <v>1.228641084604484e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.330604369022817e-09</v>
+        <v>1.330604369022818e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.327332127152412e-09</v>
+        <v>1.327332127152413e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.031884968794682e-09</v>
+        <v>1.031884968794683e-09</v>
       </c>
       <c r="R8" t="n">
         <v>1.629923850292217e-09</v>
@@ -8908,31 +8908,31 @@
         <v>1.62978734928872e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.620073237394916e-09</v>
+        <v>1.620073237394915e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.386183576270342e-09</v>
+        <v>1.386183576270343e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.485046399559645e-09</v>
+        <v>1.485046399559647e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.655215377527783e-09</v>
+        <v>1.655215377527784e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.105289679182685e-09</v>
+        <v>1.105289679182688e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.181120955209192e-09</v>
+        <v>2.181120955209193e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.115007134848697e-09</v>
+        <v>1.115007134848698e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.623796148379484e-09</v>
+        <v>1.623796148379485e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.248935704715019e-09</v>
+        <v>2.248935704715023e-09</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.203443318034351e-10</v>
+        <v>9.203443318034413e-10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.080425280555058e-09</v>
+        <v>1.080425280555063e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.095168530633756e-09</v>
+        <v>1.095168530633763e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>1.04124885469385e-09</v>
+        <v>1.041248854693857e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>7.110762567355264e-10</v>
+        <v>7.110762567355295e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>1.130529867161193e-09</v>
+        <v>1.130529867161197e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.079353344236057e-09</v>
+        <v>1.079353344236063e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.092883422714172e-09</v>
+        <v>1.092883422714179e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.104088539749305e-09</v>
+        <v>1.104088539749313e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.102216834218966e-09</v>
+        <v>1.102216834218973e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.117201241345001e-09</v>
+        <v>1.117201241345012e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.103512165692359e-09</v>
+        <v>1.103512165692368e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.079364797898498e-09</v>
+        <v>1.079364797898506e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.128555649661378e-09</v>
+        <v>1.12855564966139e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.163210398798374e-09</v>
+        <v>1.163210398798385e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.093847790372982e-09</v>
+        <v>1.09384779037299e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.092031594052796e-09</v>
+        <v>1.092031594052803e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0918950930493e-09</v>
+        <v>1.091895093049306e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.082180981155496e-09</v>
+        <v>1.082180981155503e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.092937534721558e-09</v>
+        <v>1.092937534721565e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.272237419795731e-09</v>
+        <v>1.27223741979574e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.117224595173697e-09</v>
+        <v>1.117224595173703e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.121304242146615e-09</v>
+        <v>1.121304242146622e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.144685358344295e-09</v>
+        <v>1.144685358344303e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.894767837780706e-10</v>
+        <v>9.894767837780785e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.085903892140065e-09</v>
+        <v>1.085903892140072e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.187360525206182e-09</v>
+        <v>1.18736052520619e-09</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.463350399950689e-10</v>
+        <v>5.463350399950691e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.566409182810958e-10</v>
+        <v>5.566409182810954e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.437747928212818e-10</v>
+        <v>5.437747928212815e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.413850846182848e-10</v>
+        <v>5.413850846182845e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.419965723545135e-10</v>
+        <v>5.419965723545142e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.469774847293361e-10</v>
+        <v>5.469774847293364e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.417742460407252e-10</v>
+        <v>5.417742460407256e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.442570036359365e-10</v>
+        <v>5.442570036359366e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.454049694833309e-10</v>
+        <v>5.454049694833308e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.478752693664986e-10</v>
+        <v>5.478752693664981e-10</v>
       </c>
       <c r="L2" t="n">
         <v>5.4956182110973e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.508167853264088e-10</v>
+        <v>5.508167853264083e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.446978530106119e-10</v>
+        <v>5.446978530106109e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.794812284623027e-10</v>
+        <v>7.794812284623024e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.440006820984983e-10</v>
+        <v>5.440006820984984e-10</v>
       </c>
       <c r="Q2" t="n">
         <v>5.414039406885836e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.414918486672355e-10</v>
+        <v>5.414918486672368e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.446232639314272e-10</v>
+        <v>5.44623263931426e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.430159990910558e-10</v>
+        <v>5.430159990910553e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.833122721035112e-10</v>
+        <v>7.833122721035106e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.425933292949133e-10</v>
+        <v>5.425933292949141e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>8.059015247099544e-10</v>
+        <v>8.059015247099538e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.433583777265465e-10</v>
+        <v>5.433583777265464e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.44196454935635e-10</v>
+        <v>5.441964549356357e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.084158133055729e-10</v>
+        <v>8.084158133055715e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.418789948531872e-10</v>
+        <v>5.418789948531879e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.578555737762094e-10</v>
+        <v>5.578555737762089e-10</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.30806144605045e-10</v>
+        <v>5.888081175225896e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>6.009735728121325e-10</v>
+        <v>5.567837053648285e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.738977785735433e-10</v>
+        <v>5.714732933406356e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.490355630497906e-10</v>
+        <v>5.863072105016675e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>6.328371867263731e-10</v>
+        <v>5.574779159917584e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>7.457730967061564e-10</v>
+        <v>5.944378526729394e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>6.278141259688601e-10</v>
+        <v>5.560011580324297e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.85419434094218e-10</v>
+        <v>5.757138148840759e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>7.100763488517418e-10</v>
+        <v>5.826833973484867e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.693354237440019e-10</v>
+        <v>6.046421011983814e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>8.067446287217927e-10</v>
+        <v>6.163392308131679e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>8.723492458549042e-10</v>
+        <v>6.402946435818291e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>6.948154584769306e-10</v>
+        <v>5.782508460904279e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.959166051097691e-10</v>
+        <v>8.008725837750544e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>6.76848370816206e-10</v>
+        <v>5.707515547192048e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.183295818564123e-10</v>
+        <v>5.51820661293888e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>6.209300676889378e-10</v>
+        <v>5.532629080079819e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>6.918568533958316e-10</v>
+        <v>5.761140304472131e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>6.562549976065206e-10</v>
+        <v>5.65366378399946e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.083190582501616e-09</v>
+        <v>8.629115854136637e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>6.443661360349888e-10</v>
+        <v>5.589676249421098e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.597557522347083e-10</v>
+        <v>8.402811988953301e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>6.640450690834168e-10</v>
+        <v>5.678387516713268e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.829036272618546e-10</v>
+        <v>5.738508864088048e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.3958811332296e-10</v>
+        <v>8.348362249499219e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.290212503428799e-10</v>
+        <v>5.552615414483114e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.002007358250543e-09</v>
+        <v>6.892462735497228e-10</v>
       </c>
     </row>
     <row r="4">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.691296236030066e-09</v>
+        <v>2.69129623603006e-09</v>
       </c>
       <c r="C4" t="n">
         <v>1.421779736162708e-09</v>
@@ -771,76 +771,76 @@
         <v>2.349528101263808e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.292711840886583e-09</v>
+        <v>1.292711840886587e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.962065067111036e-09</v>
+        <v>1.962065067111033e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.875851870210875e-09</v>
+        <v>2.875851870210878e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.934761487268674e-09</v>
+        <v>1.934761487268672e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.488711582602199e-09</v>
+        <v>2.4887115826022e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.580675675711813e-09</v>
+        <v>2.580675675711816e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>3.311696676376761e-09</v>
+        <v>3.311696676376754e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>3.558687250907507e-09</v>
+        <v>3.558687250907482e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>4.45485782368924e-09</v>
+        <v>4.454857823689249e-09</v>
       </c>
       <c r="N4" t="n">
         <v>2.513277329215014e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>2.027209251742173e-09</v>
+        <v>2.027209251742188e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>2.207432314895627e-09</v>
+        <v>2.207432314895629e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.756797377524901e-09</v>
+        <v>1.7567973775249e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.833577527877226e-09</v>
+        <v>1.833577527877227e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>2.378110820512817e-09</v>
+        <v>2.378110820512802e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>2.173867464006194e-09</v>
+        <v>2.173867464006186e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>3.941546644881565e-09</v>
+        <v>3.941546644881571e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.845367915879351e-09</v>
+        <v>1.84536791587935e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.517990060444769e-09</v>
+        <v>2.517990060444771e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.231304136406957e-09</v>
+        <v>2.231304136406942e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.369161511032099e-09</v>
+        <v>2.369161511032103e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.210767804694129e-09</v>
+        <v>2.21076780469413e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.837513173851543e-09</v>
+        <v>1.837513173851542e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.969815363628182e-09</v>
+        <v>5.969815363628192e-09</v>
       </c>
     </row>
     <row r="5">
@@ -850,82 +850,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.415411597736126e-09</v>
+        <v>1.415411597736122e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.984176771714034e-09</v>
+        <v>1.984176771714032e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>2.027508633976355e-09</v>
+        <v>2.027508633976354e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.659193559670531e-09</v>
+        <v>1.659193559670528e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.466269443108629e-09</v>
+        <v>1.466269443108626e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.196603398508547e-09</v>
+        <v>2.196603398508545e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>2.004911537792988e-09</v>
+        <v>2.004911537792986e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.03295542695582e-09</v>
+        <v>2.032955426955817e-09</v>
       </c>
       <c r="J5" t="n">
         <v>2.045873882476276e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.073825402866986e-09</v>
+        <v>2.073825402866988e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>2.092875780658921e-09</v>
+        <v>2.09287578065892e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>2.123701689681077e-09</v>
+        <v>2.123701689681078e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.513277329215014e-09</v>
+        <v>1.541040224266169e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.661260035038435e-09</v>
+        <v>1.661260035038428e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.636244412480971e-09</v>
+        <v>1.636244412480967e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.233738247699303e-09</v>
+        <v>1.233738247699302e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>2.001721729550205e-09</v>
+        <v>2.001721729550204e-09</v>
       </c>
       <c r="S5" t="n">
         <v>2.037092505481444e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>2.018937709731091e-09</v>
+        <v>2.018937709731092e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.801927030166305e-09</v>
+        <v>1.801927030166302e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.838847349538308e-09</v>
+        <v>1.838847349538309e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>2.040210967830781e-09</v>
+        <v>2.040210967830776e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.314564922168583e-09</v>
+        <v>1.31456492216858e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.669598182239765e-09</v>
+        <v>2.669598182239766e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.376079667590829e-09</v>
+        <v>1.376079667590827e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.006094723816572e-09</v>
+        <v>2.006094723816575e-09</v>
       </c>
       <c r="AB5" t="n">
         <v>2.855576166418479e-09</v>
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.209899623825659e-09</v>
+        <v>1.209899623825658e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.359817565357393e-09</v>
+        <v>1.359817565357391e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.403149427619715e-09</v>
+        <v>1.403149427619711e-09</v>
       </c>
       <c r="E6" t="n">
         <v>1.324881058804324e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>8.70903188874587e-10</v>
+        <v>8.709031888745853e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.439325536798187e-09</v>
+        <v>1.439325536798184e-09</v>
       </c>
       <c r="H6" t="n">
         <v>1.380552331436347e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.408596220599177e-09</v>
+        <v>1.408596220599179e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.421514676119636e-09</v>
+        <v>1.421514676119632e-09</v>
       </c>
       <c r="K6" t="n">
         <v>1.449466196510345e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46851657430228e-09</v>
+        <v>1.468516574302277e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.499342483324438e-09</v>
+        <v>1.499342483324437e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.513277329215014e-09</v>
+        <v>1.41357581708686e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.470871436650494e-09</v>
+        <v>1.470871436650493e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.49534028369869e-09</v>
+        <v>1.495340283698688e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37636979290096e-09</v>
+        <v>1.376369792900954e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.377362523193565e-09</v>
+        <v>1.377362523193562e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.412733299124805e-09</v>
+        <v>1.412733299124804e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.394578503374449e-09</v>
+        <v>1.394578503374447e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.490451637078092e-09</v>
+        <v>1.490451637078096e-09</v>
       </c>
       <c r="V6" t="n">
         <v>1.646079437391092e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.415725783330449e-09</v>
+        <v>1.41572578333045e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.398445827564269e-09</v>
+        <v>1.398445827564266e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.407912295175492e-09</v>
+        <v>1.40791229517549e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.270695828917359e-09</v>
+        <v>1.270695828917354e-09</v>
       </c>
       <c r="AA6" t="n">
         <v>1.38173551745993e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56162193207381e-09</v>
+        <v>1.561621932073809e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.091314136844805e-10</v>
+        <v>5.091314136844815e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.225784815283189e-10</v>
+        <v>5.225784815283185e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.100515504461334e-10</v>
+        <v>5.100515504461346e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.085593698658563e-10</v>
+        <v>5.08559369865857e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.09592808877779e-10</v>
+        <v>5.095928088777798e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.099286458878685e-10</v>
+        <v>5.099286458878699e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.094138956386582e-10</v>
+        <v>5.094138956386599e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.101445541055545e-10</v>
+        <v>5.101445541055575e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.099347034106083e-10</v>
+        <v>5.099347034106026e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.101534284832529e-10</v>
+        <v>5.101534284832556e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.098490894829922e-10</v>
+        <v>5.098490894829933e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.081717217625286e-10</v>
+        <v>5.081717217625288e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.088833085173368e-10</v>
+        <v>5.088833085173318e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.973392357873399e-10</v>
+        <v>6.973392357873401e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.085702209408137e-10</v>
+        <v>5.085702209408055e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.092887926116325e-10</v>
+        <v>5.092887926116339e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.107014094023428e-10</v>
+        <v>5.107014094023442e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.095910268834525e-10</v>
+        <v>5.095910268834549e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.08985442713504e-10</v>
+        <v>5.089854427135051e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.935223347738335e-10</v>
+        <v>6.93522334773827e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.097782667292321e-10</v>
+        <v>5.097782667292332e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.236919018682413e-10</v>
+        <v>7.236919018682374e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.127698571970533e-10</v>
+        <v>5.127698571970558e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.132226518930994e-10</v>
+        <v>5.132226518931011e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.533538920223235e-10</v>
+        <v>7.533538920223212e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.10121497844307e-10</v>
+        <v>5.101214978443083e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.108386095086282e-10</v>
+        <v>5.108386095086287e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.630479639058311e-10</v>
+        <v>5.087248198008664e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.683808190369192e-10</v>
+        <v>5.20519351039144e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.855145235096946e-10</v>
+        <v>5.173244996313397e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.902679845128598e-10</v>
+        <v>5.484182632499609e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.751607868422931e-10</v>
+        <v>5.139511926146356e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.814378983898808e-10</v>
+        <v>5.148943567900786e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.71160249632344e-10</v>
+        <v>5.130928755591069e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.878672472741071e-10</v>
+        <v>5.184297083057443e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.819589347802688e-10</v>
+        <v>5.154756437398386e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.877223123269747e-10</v>
+        <v>5.176358719458706e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.800458866854041e-10</v>
+        <v>5.147287618302132e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.75854579841555e-10</v>
+        <v>5.13260174036155e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.580284492071413e-10</v>
+        <v>5.077949174428181e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.333364225476624e-10</v>
+        <v>6.915193701372793e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.500314763658531e-10</v>
+        <v>5.042965125453168e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.675151806563808e-10</v>
+        <v>5.107602051078435e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>6.011042554973944e-10</v>
+        <v>5.233253564081763e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.738250276798389e-10</v>
+        <v>5.123249812568667e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.607035779288377e-10</v>
+        <v>5.089802312269817e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.679610583712997e-10</v>
+        <v>6.995696697869169e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.776448488967011e-10</v>
+        <v>5.129121678245226e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.353704822866125e-10</v>
+        <v>7.735608100890094e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>6.487410997246288e-10</v>
+        <v>5.385626135787759e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.587150693759563e-10</v>
+        <v>5.425623697464716e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.214327268638512e-10</v>
+        <v>7.569582495164119e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.866156832494991e-10</v>
+        <v>5.175325809342065e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.068600931600476e-10</v>
+        <v>5.257313357520919e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1358,43 +1358,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.312696829544573e-09</v>
+        <v>1.312696829544571e-09</v>
       </c>
       <c r="C4" t="n">
         <v>1.311021795760218e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.579470939089917e-09</v>
+        <v>1.579470939089916e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.876969498176692e-10</v>
+        <v>8.876969498176675e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.507445159057146e-09</v>
+        <v>1.507445159057147e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.458186220073033e-09</v>
+        <v>1.458186220073031e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.510452083722511e-09</v>
+        <v>1.510452083722514e-09</v>
       </c>
       <c r="I4" t="n">
         <v>1.622387020502036e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.49507129410519e-09</v>
+        <v>1.495071294105189e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.565782246780789e-09</v>
+        <v>1.565782246780788e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.473649139594923e-09</v>
+        <v>1.473649139594922e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.530320505814612e-09</v>
+        <v>1.530320505814611e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>1.333792638285734e-09</v>
       </c>
       <c r="O4" t="n">
         <v>1.168545675609556e-09</v>
@@ -1403,40 +1403,40 @@
         <v>1.204573962888341e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.39582477868368e-09</v>
+        <v>1.395824778683677e-09</v>
       </c>
       <c r="R4" t="n">
         <v>1.763351704646202e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.399257754568167e-09</v>
+        <v>1.399257754568165e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.378846789043674e-09</v>
+        <v>1.378846789043673e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.499177676399708e-09</v>
+        <v>1.499177676399705e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.375425738976058e-09</v>
+        <v>1.375425738976049e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.775919261305529e-09</v>
+        <v>2.775919261305528e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.088499418781671e-09</v>
+        <v>2.088499418781682e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2056269862329e-09</v>
+        <v>2.205626986232905e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.408446054897892e-09</v>
+        <v>1.408446054897893e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.570321363563351e-09</v>
+        <v>1.570321363563348e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.84543489624114e-09</v>
+        <v>1.845434896241143e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1446,82 +1446,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.109164248626487e-09</v>
+        <v>1.109164248626488e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.599703530640586e-09</v>
+        <v>1.599703530640588e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.614678546515327e-09</v>
+        <v>1.614678546515332e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.334186390403852e-09</v>
+        <v>1.334186390403851e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.191509973869549e-09</v>
+        <v>1.191509973869552e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.715956833219107e-09</v>
+        <v>1.715956833219108e-09</v>
       </c>
       <c r="H5" t="n">
         <v>1.60747594212919e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.615729065632287e-09</v>
+        <v>1.615729065632284e-09</v>
       </c>
       <c r="J5" t="n">
         <v>1.613315837151493e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.615829305810805e-09</v>
+        <v>1.615829305810801e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6123916568e-09</v>
+        <v>1.612391656799998e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.610595778331571e-09</v>
+        <v>1.610595778331572e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>1.21768116394158e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.316781701069688e-09</v>
+        <v>1.316781701069687e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.29376295934728e-09</v>
+        <v>1.293762959347277e-09</v>
       </c>
       <c r="Q5" t="n">
         <v>1.013639352685642e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.622019002375602e-09</v>
+        <v>1.622019002375599e-09</v>
       </c>
       <c r="S5" t="n">
         <v>1.60947672102354e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.602636369241489e-09</v>
+        <v>1.602636369241492e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.373033234151547e-09</v>
+        <v>1.373033234151552e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.476304633566978e-09</v>
+        <v>1.476304633566974e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.684413427613155e-09</v>
+        <v>1.684413427613156e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.098338395627522e-09</v>
+        <v>1.098338395627526e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.142943407644376e-09</v>
+        <v>2.142943407644378e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.107215957763987e-09</v>
+        <v>1.107215957763986e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.615468634555096e-09</v>
+        <v>1.615468634555095e-09</v>
       </c>
       <c r="AB5" t="n">
         <v>2.142185762975543e-09</v>
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.928976274997076e-10</v>
+        <v>8.928976274997065e-10</v>
       </c>
       <c r="C6" t="n">
         <v>1.044009285480789e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.05898430135553e-09</v>
+        <v>1.058984301355526e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.006196215461897e-09</v>
+        <v>1.006196215461899e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>6.948867698722094e-10</v>
+        <v>6.948867698722079e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.057596246002216e-09</v>
+        <v>1.057596246002215e-09</v>
       </c>
       <c r="H6" t="n">
         <v>1.05178169696939e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.060034820472485e-09</v>
+        <v>1.060034820472486e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.057621591991693e-09</v>
+        <v>1.057621591991692e-09</v>
       </c>
       <c r="K6" t="n">
         <v>1.060135060651006e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.056697411640203e-09</v>
+        <v>1.056697411640202e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.054901533171802e-09</v>
+        <v>1.0549015331718e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.333792638285733e-09</v>
+        <v>1.045788471351865e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.091013844163315e-09</v>
+        <v>1.091013844163313e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.105070219056437e-09</v>
+        <v>1.105070219056438e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.05036880890008e-09</v>
+        <v>1.050368808900079e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.066324757215803e-09</v>
+        <v>1.0663247572158e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.053782475863739e-09</v>
+        <v>1.05378247586374e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.046942124081691e-09</v>
+        <v>1.046942124081692e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.058908348069319e-09</v>
+        <v>1.058908348069318e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.235499141471613e-09</v>
+        <v>1.235499141471611e-09</v>
       </c>
       <c r="W6" t="n">
         <v>1.128621876943469e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.089688826590052e-09</v>
+        <v>1.089688826590054e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.094803350977749e-09</v>
+        <v>1.09480335097775e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.619706319833978e-10</v>
+        <v>9.619706319833937e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.059774389395298e-09</v>
+        <v>1.059774389395297e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.069296305159905e-09</v>
+        <v>1.069296305159904e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.369498967361077e-10</v>
+        <v>5.3694989673611e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.475404596684087e-10</v>
+        <v>5.475404596684111e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.352574855747016e-10</v>
+        <v>5.352574855747033e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.329012572380371e-10</v>
+        <v>5.329012572380391e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.322908501725607e-10</v>
+        <v>5.322908501725622e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.385371418553571e-10</v>
+        <v>5.385371418553576e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.321341066993037e-10</v>
+        <v>5.321341066993075e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.337775485270306e-10</v>
+        <v>5.337775485270318e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.368432290971388e-10</v>
+        <v>5.368432290971389e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.38188285327656e-10</v>
+        <v>5.381882853276562e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.409383968497131e-10</v>
+        <v>5.409383968497174e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.413921284836645e-10</v>
+        <v>5.413921284836661e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.334068969138734e-10</v>
+        <v>5.334068969138749e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.5664275909175e-10</v>
+        <v>7.566427590917525e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.36422678610068e-10</v>
+        <v>5.3642267861007e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.325637047816075e-10</v>
+        <v>5.325637047816094e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.323791225831124e-10</v>
+        <v>5.323791225831128e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.364585967668526e-10</v>
+        <v>5.364585967668548e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.328165221844253e-10</v>
+        <v>5.328165221844247e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.593310558949956e-10</v>
+        <v>7.593310558949972e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.331906659147605e-10</v>
+        <v>5.331906659147619e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.829774981658775e-10</v>
+        <v>7.829774981658792e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.357745662691408e-10</v>
+        <v>5.357745662691428e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.356425647987608e-10</v>
+        <v>5.35642564798762e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.929765354200602e-10</v>
+        <v>7.92976535420063e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.329176224736216e-10</v>
+        <v>5.329176224736228e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.490490588085958e-10</v>
+        <v>5.490490588085975e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.952275100346102e-10</v>
+        <v>5.70246984351866e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.921865083803689e-10</v>
+        <v>5.467924971586561e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.582329703899124e-10</v>
+        <v>5.596674684982337e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.366492934197869e-10</v>
+        <v>5.772449750425964e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.892720630949134e-10</v>
+        <v>5.357512813504933e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>7.319351093754468e-10</v>
+        <v>5.831367158689346e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.857432707193826e-10</v>
+        <v>5.348343997602429e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.238586063208633e-10</v>
+        <v>5.478058037747897e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.935274276498669e-10</v>
+        <v>5.705935183285836e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>7.262258796284941e-10</v>
+        <v>5.819823472574599e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.886689272103174e-10</v>
+        <v>6.037320565684943e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>8.353100918961631e-10</v>
+        <v>6.208161315453575e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>6.146554691194337e-10</v>
+        <v>5.440902070706591e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.460375123525444e-10</v>
+        <v>7.687128199263345e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>6.828680606316112e-10</v>
+        <v>5.663439933506865e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.951522529611444e-10</v>
+        <v>5.37387634953444e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.912952551077428e-10</v>
+        <v>5.365269973609079e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>6.843796610924654e-10</v>
+        <v>5.67005628589628e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>6.012882824316958e-10</v>
+        <v>5.397866315646679e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.019614395635551e-09</v>
+        <v>8.254701347804829e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>6.083314078085545e-10</v>
+        <v>5.402122321236699e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.537502865672569e-10</v>
+        <v>8.216967481587387e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>6.701497761256764e-10</v>
+        <v>5.635477733256723e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.66404042756759e-10</v>
+        <v>5.61663300225775e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.051857704847473e-10</v>
+        <v>8.124110986178764e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.03080183056218e-10</v>
+        <v>5.398983931555798e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.795102010382946e-10</v>
+        <v>6.750256740682533e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.309804799539829e-09</v>
+        <v>2.30980479953994e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.365298508109441e-09</v>
+        <v>1.365298508109443e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.160443069630958e-09</v>
+        <v>2.160443069630943e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.17856885816022e-09</v>
+        <v>1.17856885816038e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.512688636471562e-09</v>
+        <v>1.51268863647156e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.663543961950717e-09</v>
+        <v>2.663543961950731e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.503626717944206e-09</v>
+        <v>1.503626717944212e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.842316342341147e-09</v>
+        <v>1.84231634234116e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.373380838167244e-09</v>
+        <v>2.373380838167248e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>2.704639212691327e-09</v>
+        <v>2.704639212691359e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>3.276789173226628e-09</v>
+        <v>3.276789173228341e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>3.913769430243897e-09</v>
+        <v>3.913769430243962e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>1.709162838388557e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.687440289448537e-09</v>
+        <v>1.687440289448548e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22025234075699e-09</v>
+        <v>2.220252340757083e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.531840938318312e-09</v>
+        <v>1.531840938318362e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.536695803627269e-09</v>
+        <v>1.536695803627276e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>2.254183007465324e-09</v>
+        <v>2.254183007465357e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.612998951882018e-09</v>
+        <v>1.612998951882044e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>3.349074760539092e-09</v>
+        <v>3.349074760539099e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.507831371303325e-09</v>
+        <v>1.507831371303322e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.554062985841159e-09</v>
+        <v>2.554062985841156e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.252440009253704e-09</v>
+        <v>2.252440009253798e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.164758011631562e-09</v>
+        <v>2.164758011631599e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.920582997082592e-09</v>
+        <v>1.920582997082814e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.584574385404711e-09</v>
+        <v>1.584574385404783e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.490054187496246e-09</v>
+        <v>5.490054187496319e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2042,61 +2042,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.30729795209697e-09</v>
+        <v>1.307297952096981e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.83136065226189e-09</v>
+        <v>1.831360652261891e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.870920922953097e-09</v>
+        <v>1.870920922953098e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.534014628123036e-09</v>
+        <v>1.534014628123047e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.345455886598256e-09</v>
+        <v>1.345455886598257e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.028800987825816e-09</v>
+        <v>2.028800987825818e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.835640921730209e-09</v>
+        <v>1.835640921730211e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.854204353194974e-09</v>
+        <v>1.854204353194973e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.888774936132939e-09</v>
+        <v>1.88877493613294e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.904025654397207e-09</v>
+        <v>1.904025654397209e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.93508942915264e-09</v>
+        <v>1.935089429152694e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.956824560347838e-09</v>
+        <v>1.956824560347839e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>1.39829704409636e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.527175360283279e-09</v>
+        <v>1.527175360283276e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.526069519452754e-09</v>
+        <v>1.526069519452761e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.143232277493982e-09</v>
+        <v>1.143232277493986e-09</v>
       </c>
       <c r="R5" t="n">
         <v>1.838408488850698e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.884488026406887e-09</v>
+        <v>1.884488026406892e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.843349118561281e-09</v>
+        <v>1.843349118561286e-09</v>
       </c>
       <c r="U5" t="n">
         <v>1.6571913058461e-09</v>
@@ -2105,22 +2105,22 @@
         <v>1.688110054552135e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.895840092283663e-09</v>
+        <v>1.895840092283665e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.232909671278197e-09</v>
+        <v>1.2329096712782e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.454632365570596e-09</v>
+        <v>2.454632365570595e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.272767283284429e-09</v>
+        <v>1.272767283284436e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.844491092836186e-09</v>
+        <v>1.844491092836189e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.634809626208707e-09</v>
+        <v>2.634809626208713e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.090266345425977e-09</v>
+        <v>1.090266345425996e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.225207559148573e-09</v>
+        <v>1.225207559148577e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.264767829839783e-09</v>
+        <v>1.264767829839785e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.193467056931219e-09</v>
+        <v>1.193467056931231e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>7.849155955074692e-10</v>
+        <v>7.849155955074703e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.301813271499118e-09</v>
+        <v>1.301813271499122e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.229487828616895e-09</v>
+        <v>1.229487828616897e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.24805126008166e-09</v>
+        <v>1.248051260081666e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.282621843019624e-09</v>
+        <v>1.282621843019625e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.297872561283891e-09</v>
+        <v>1.297872561283897e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.328936336039325e-09</v>
+        <v>1.328936336039315e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.350671467234547e-09</v>
+        <v>1.35067146723455e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.709162838388546e-09</v>
+        <v>1.243864579602889e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.312771198629966e-09</v>
+        <v>1.312771198629967e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.356049026553432e-09</v>
+        <v>1.356049026553436e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.234340551834301e-09</v>
+        <v>1.234340551834303e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.232255395737385e-09</v>
+        <v>1.232255395737387e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.278334933293572e-09</v>
+        <v>1.278334933293574e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.237196025447968e-09</v>
+        <v>1.237196025447975e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.335490654300468e-09</v>
+        <v>1.335490654300471e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46468720688483e-09</v>
+        <v>1.464687206884834e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.289572474073645e-09</v>
+        <v>1.289572474073649e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.270608494152341e-09</v>
+        <v>1.270608494152368e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.269117476820725e-09</v>
+        <v>1.269117476820729e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.143444029966849e-09</v>
+        <v>1.143444029966854e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.23833799972287e-09</v>
+        <v>1.238337999722874e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.419936362422284e-09</v>
+        <v>1.419936362422296e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.317365516493955e-10</v>
+        <v>5.317365516493975e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.42791397249387e-10</v>
+        <v>5.427913972493862e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.323020791910744e-10</v>
+        <v>5.323020791910761e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.290860008535743e-10</v>
+        <v>5.290860008535761e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.285800692847646e-10</v>
+        <v>5.285800692847663e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.33880406019332e-10</v>
+        <v>5.338804060193347e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.275343138096683e-10</v>
+        <v>5.275343138096694e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.302984589839374e-10</v>
+        <v>5.302984589839403e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.323855239649697e-10</v>
+        <v>5.323855239649698e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.298781051793117e-10</v>
+        <v>5.298781051793151e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.35710108498479e-10</v>
+        <v>5.357101084984809e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.360274122716245e-10</v>
+        <v>5.360274122716242e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.27778496602147e-10</v>
+        <v>5.277784966021475e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.431658565311637e-10</v>
+        <v>7.431658565311668e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.320502137871729e-10</v>
+        <v>5.320502137871759e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.291226042117166e-10</v>
+        <v>5.291226042117197e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.275797705613764e-10</v>
+        <v>5.275797705613772e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.321121708146666e-10</v>
+        <v>5.321121708146692e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.280973477534941e-10</v>
+        <v>5.280973477534969e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.440673818746082e-10</v>
+        <v>7.440673818746123e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.296073925395365e-10</v>
+        <v>5.296073925395386e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.691073186771836e-10</v>
+        <v>7.691073186771871e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.333041454857643e-10</v>
+        <v>5.333041454857654e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.347308663063977e-10</v>
+        <v>5.34730866306398e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.85479342877574e-10</v>
+        <v>7.854793428775767e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.286767184346342e-10</v>
+        <v>5.28676718434634e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.436369455765957e-10</v>
+        <v>5.43636945576593e-10</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.66158761508445e-10</v>
+        <v>5.573576906546025e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.84009292880159e-10</v>
+        <v>5.404158749358035e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.81496062070936e-10</v>
+        <v>5.644300439228927e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.412546384300784e-10</v>
+        <v>5.765386997860444e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.949448904058675e-10</v>
+        <v>5.343927959461424e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>7.156070456378968e-10</v>
+        <v>5.740391874524746e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.705741886915265e-10</v>
+        <v>5.262623427556874e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.349357215562005e-10</v>
+        <v>5.484292452688259e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.819061108959504e-10</v>
+        <v>5.632760917870006e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>6.246783255055841e-10</v>
+        <v>5.438498046509165e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.590649255102017e-10</v>
+        <v>5.901532663777982e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>8.023850454969787e-10</v>
+        <v>6.061207841226199e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.756574422957914e-10</v>
+        <v>5.273265881614171e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.141596189630292e-10</v>
+        <v>7.490443358638583e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>6.731148233972332e-10</v>
+        <v>5.595944599922363e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.07031338154337e-10</v>
+        <v>5.380997256246173e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.714751529077919e-10</v>
+        <v>5.263316959403015e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>6.752127213932255e-10</v>
+        <v>5.604815652079442e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.833851980194839e-10</v>
+        <v>5.303020240907488e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.537648424366442e-10</v>
+        <v>7.935903429315899e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>6.167924772489675e-10</v>
+        <v>5.39661462669075e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.418006462494638e-10</v>
+        <v>8.07889272143972e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>7.046998995217414e-10</v>
+        <v>5.722135691312022e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.369880776308254e-10</v>
+        <v>5.827024753557249e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.985680467379555e-10</v>
+        <v>8.03995389924486e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.963595212890267e-10</v>
+        <v>5.343307219342608e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.458898152520275e-10</v>
+        <v>6.600561138518894e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.999027085160532e-09</v>
+        <v>1.999027085160536e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.269843475671804e-09</v>
+        <v>1.269843475671805e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.282377557838556e-09</v>
+        <v>2.282377557838558e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.191508332876998e-09</v>
+        <v>1.191508332877001e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.520150871912368e-09</v>
+        <v>1.520150871912374e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.396462884532306e-09</v>
+        <v>2.396462884532296e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.327122445555182e-09</v>
+        <v>1.327122445555178e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.883506583139094e-09</v>
+        <v>1.88350658313909e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.177267418047508e-09</v>
+        <v>2.177267418047516e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.717288072741902e-09</v>
+        <v>1.71728807274192e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.861608960613643e-09</v>
+        <v>2.861608960613639e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>3.426545919439215e-09</v>
+        <v>3.426545919439207e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.316294400634627e-09</v>
+        <v>1.316294400634621e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.449223177982679e-09</v>
+        <v>1.449223177982678e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>2.043714386043222e-09</v>
+        <v>2.043714386043213e-09</v>
       </c>
       <c r="Q4" t="n">
         <v>1.586327188954174e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.316403790437111e-09</v>
+        <v>1.31640379043711e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>2.081765297220588e-09</v>
+        <v>2.081765297220585e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.408515152594916e-09</v>
+        <v>1.408515152594919e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>2.69403080947703e-09</v>
+        <v>2.694030809477028e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.527640843394186e-09</v>
+        <v>1.52764084339419e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.430517458618933e-09</v>
+        <v>2.430517458618937e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.467075826973534e-09</v>
+        <v>2.467075826973545e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.690788397997647e-09</v>
+        <v>2.690788397997659e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.783273716322134e-09</v>
+        <v>1.783273716322133e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.483855897196949e-09</v>
+        <v>1.483855897196953e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.893454221233075e-09</v>
+        <v>4.893454221233085e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.213807019283714e-09</v>
+        <v>1.213807019283717e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.696804045293285e-09</v>
+        <v>1.69680404529329e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.751361191155629e-09</v>
+        <v>1.751361191155632e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.432203732169876e-09</v>
+        <v>1.432203732169877e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.260902597191735e-09</v>
+        <v>1.260902597191737e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87932990674945e-09</v>
+        <v>1.879329906749447e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.697507087892213e-09</v>
+        <v>1.69750708789221e-09</v>
       </c>
       <c r="I5" t="n">
         <v>1.728729379205186e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.752248844264411e-09</v>
+        <v>1.75224884426441e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.723981289609634e-09</v>
+        <v>1.723981289609636e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.789856449953699e-09</v>
+        <v>1.789856449953698e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.810111765688082e-09</v>
+        <v>1.810111765688084e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.316294400634627e-09</v>
+        <v>1.28852251714528e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4139056797134e-09</v>
+        <v>1.413905679713398e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.422188088606999e-09</v>
+        <v>1.422188088606998e-09</v>
       </c>
       <c r="Q5" t="n">
         <v>1.079894983550217e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.698020542813892e-09</v>
+        <v>1.698020542813896e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.749216088681933e-09</v>
+        <v>1.749216088681931e-09</v>
       </c>
       <c r="T5" t="n">
         <v>1.703866815296134e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.523804078978926e-09</v>
+        <v>1.523804078978927e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.575631225426534e-09</v>
+        <v>1.575631225426536e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.763988893107963e-09</v>
+        <v>1.763988893107961e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.17580986072149e-09</v>
+        <v>1.175809860721494e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.306969451141907e-09</v>
+        <v>2.306969451141908e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.192978607832666e-09</v>
+        <v>1.192978607832667e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.710411073663288e-09</v>
+        <v>1.710411073663286e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.433858697557769e-09</v>
+        <v>2.43385869755777e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.985463688720497e-10</v>
+        <v>9.985463688720571e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.122037502003192e-09</v>
+        <v>1.122037502003191e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.176594647865537e-09</v>
+        <v>1.176594647865545e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.100649201553174e-09</v>
+        <v>1.100649201553178e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>7.388285326662243e-10</v>
+        <v>7.388285326662212e-10</v>
       </c>
       <c r="G6" t="n">
         <v>1.19442277658123e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.122740544602119e-09</v>
+        <v>1.122740544602117e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.153962835915094e-09</v>
+        <v>1.153962835915092e-09</v>
       </c>
       <c r="J6" t="n">
         <v>1.177482300974318e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.14921474631954e-09</v>
+        <v>1.149214746319535e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.215089906663607e-09</v>
+        <v>1.215089906663608e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.235345222398021e-09</v>
+        <v>1.23534522239803e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.316294400634627e-09</v>
+        <v>1.125498701572795e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.194619682105361e-09</v>
+        <v>1.194619682105378e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.243010191257717e-09</v>
+        <v>1.243010191257721e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.140681216467253e-09</v>
+        <v>1.14068121646726e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.123253999523801e-09</v>
+        <v>1.123253999523803e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.174449545391841e-09</v>
+        <v>1.174449545391843e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.129100272006041e-09</v>
+        <v>1.129100272006046e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.208264968412033e-09</v>
+        <v>1.208264968412038e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.344102287987054e-09</v>
+        <v>1.344102287987064e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.189117960354858e-09</v>
+        <v>1.189117960354862e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.187913447637325e-09</v>
+        <v>1.187913447637326e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.204028915630382e-09</v>
+        <v>1.204028915630383e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.055749161191396e-09</v>
+        <v>1.055749161191404e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.135644530373196e-09</v>
+        <v>1.135644530373197e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.304244561291828e-09</v>
+        <v>1.304244561291822e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.285770399348807e-10</v>
+        <v>5.285770399348798e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.396787614265284e-10</v>
+        <v>5.396787614265278e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.287307160766484e-10</v>
+        <v>5.287307160766478e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.260062463059896e-10</v>
+        <v>5.260062463059884e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.265299175588478e-10</v>
+        <v>5.265299175588465e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.307064922646789e-10</v>
+        <v>5.307064922646777e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.252254961170976e-10</v>
+        <v>5.252254961170961e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.27333952230212e-10</v>
+        <v>5.273339522302109e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.295609146395664e-10</v>
+        <v>5.295609146395653e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.272549121617084e-10</v>
+        <v>5.27254912161707e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.319436523653601e-10</v>
+        <v>5.31943652365359e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.321780068662932e-10</v>
+        <v>5.321780068662927e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.246188175131125e-10</v>
+        <v>5.24618817513111e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.350107186854338e-10</v>
+        <v>7.350107186854322e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.290715083188e-10</v>
+        <v>5.290715083187986e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.264385106475815e-10</v>
+        <v>5.264385106475806e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.26013311390698e-10</v>
+        <v>5.26013311390697e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.294454737921849e-10</v>
+        <v>5.29445473792184e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.261324300729322e-10</v>
+        <v>5.261324300729312e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.366363486699358e-10</v>
+        <v>7.366363486699343e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.285837916632279e-10</v>
+        <v>5.285837916632268e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.605552945380485e-10</v>
+        <v>7.605552945380473e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.316918030583245e-10</v>
+        <v>5.316918030583238e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.365428473806932e-10</v>
+        <v>5.365428473806921e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.809264061952093e-10</v>
+        <v>7.809264061952083e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.264048671231797e-10</v>
+        <v>5.264048671231791e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.400167504004618e-10</v>
+        <v>5.400167504004614e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.475971781166711e-10</v>
+        <v>5.488778048180355e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.742873997717508e-10</v>
+        <v>5.350162309722011e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.53089484183831e-10</v>
+        <v>5.522485582653236e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.251351553444587e-10</v>
+        <v>5.69448503720198e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>6.021391617454796e-10</v>
+        <v>5.349864609857751e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.966879882261481e-10</v>
+        <v>5.653012047289357e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.717280600830606e-10</v>
+        <v>5.248628544349729e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.207213304050009e-10</v>
+        <v>5.415034224618179e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.711432694040101e-10</v>
+        <v>5.574363030301807e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>6.184764864905318e-10</v>
+        <v>5.398940771088866e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.263000466471335e-10</v>
+        <v>5.762872074833775e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>7.674440943263893e-10</v>
+        <v>5.909655155890765e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.569810074202706e-10</v>
+        <v>5.190227345152897e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.97743343251989e-10</v>
+        <v>7.381522696236779e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>6.587293030973981e-10</v>
+        <v>5.524898015352898e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.993880834848862e-10</v>
+        <v>5.334551402198507e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.900109786557054e-10</v>
+        <v>5.310407407901627e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>6.680099673057934e-10</v>
+        <v>5.560014653028816e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.925506755410272e-10</v>
+        <v>5.316887120081473e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.54943631861047e-10</v>
+        <v>7.878314612500523e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>6.474830923996947e-10</v>
+        <v>5.4790115209446e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.329671517487281e-10</v>
+        <v>7.990568186588588e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>7.219753902428918e-10</v>
+        <v>5.757061139779012e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.338694332673015e-10</v>
+        <v>6.148417817530925e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.918430464491184e-10</v>
+        <v>7.980217947966213e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.98326272183037e-10</v>
+        <v>5.331973843579748e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.165771854906837e-10</v>
+        <v>6.470877854419308e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3146,85 +3146,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.847234146397727e-09</v>
+        <v>1.847234146397728e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.214000179508519e-09</v>
+        <v>1.21400017950852e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.020908576929539e-09</v>
+        <v>2.020908576929552e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.063094990107763e-09</v>
+        <v>1.063094990107764e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.60383761519897e-09</v>
+        <v>1.603837615198966e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.232089857910595e-09</v>
+        <v>2.232089857910506e-09</v>
       </c>
       <c r="H4" t="n">
         <v>1.364302475526153e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.770597125362515e-09</v>
+        <v>1.770597125362519e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.089787255482618e-09</v>
+        <v>2.089787255482614e-09</v>
       </c>
       <c r="K4" t="n">
         <v>1.688850530197448e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.552409358493214e-09</v>
+        <v>2.552409358493213e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>3.056911917772113e-09</v>
+        <v>3.056911917772108e-09</v>
       </c>
       <c r="N4" t="n">
         <v>1.176722493707847e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.384434894725477e-09</v>
+        <v>1.384434894725476e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.923275574106131e-09</v>
+        <v>1.923275574106135e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.532009485262257e-09</v>
+        <v>1.532009485262256e-09</v>
       </c>
       <c r="R4" t="n">
         <v>1.513437622252146e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>2.032596332327923e-09</v>
+        <v>2.032596332327926e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.516838552501652e-09</v>
+        <v>1.516838552501654e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>2.716980701963352e-09</v>
+        <v>2.716980701963342e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.778720965422641e-09</v>
+        <v>1.778720965422652e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.432828550086143e-09</v>
+        <v>2.432828550086142e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.597359219821312e-09</v>
+        <v>2.597359219821311e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.591309437059968e-09</v>
+        <v>3.591309437059961e-09</v>
       </c>
       <c r="Z4" t="n">
         <v>1.730774271997541e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.52648607048999e-09</v>
+        <v>1.526486070489993e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.591589344060353e-09</v>
+        <v>4.591589344060361e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3234,22 +3234,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.194911011085564e-09</v>
+        <v>1.194911011085566e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.674926733202487e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.720308059998337e-09</v>
+        <v>1.720308059998338e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.410699775347114e-09</v>
+        <v>1.410699775347115e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2533681179012e-09</v>
+        <v>1.253368117901201e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.851209923389295e-09</v>
+        <v>1.851209923389294e-09</v>
       </c>
       <c r="H5" t="n">
         <v>1.680714988074361e-09</v>
@@ -3261,58 +3261,58 @@
         <v>1.72964224966895e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.703638175875746e-09</v>
+        <v>1.703638175875745e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.756599653403046e-09</v>
+        <v>1.756599653403047e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.775992553797113e-09</v>
+        <v>1.775992553797111e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.176722493707847e-09</v>
+        <v>1.267937232759586e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.395355126152575e-09</v>
+        <v>1.395355126152573e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.402440126233878e-09</v>
+        <v>1.402440126233876e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.067843959995119e-09</v>
+        <v>1.067843959995118e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.68961372400261e-09</v>
+        <v>1.689613724002611e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.728381577200111e-09</v>
+        <v>1.728381577200112e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.690959224315746e-09</v>
+        <v>1.690959224315747e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.513463547504282e-09</v>
+        <v>1.513463547504284e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57556945222953e-09</v>
+        <v>1.575569452229529e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.745313440673595e-09</v>
+        <v>1.745313440673593e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.175176904527301e-09</v>
+        <v>1.175176904527303e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.329390666354035e-09</v>
+        <v>2.329390666354036e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.181019844146806e-09</v>
+        <v>1.181019844146805e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.694036526125526e-09</v>
+        <v>1.694036526125528e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.394567179726706e-09</v>
+        <v>2.394567179726705e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.681026392518854e-10</v>
+        <v>9.68102639251886e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.089657350821833e-09</v>
+        <v>1.089657350821832e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.135038677617684e-09</v>
+        <v>1.135038677617682e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.066137161138804e-09</v>
+        <v>1.066137161138805e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>7.293478458670962e-10</v>
+        <v>7.293478458670949e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.157356179050432e-09</v>
+        <v>1.157356179050435e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.095445605693705e-09</v>
+        <v>1.095445605693708e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.11926158742907e-09</v>
+        <v>1.119261587429072e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.144372867288296e-09</v>
+        <v>1.144372867288295e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.11836879349509e-09</v>
+        <v>1.118368793495094e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.171330271022391e-09</v>
+        <v>1.171330271022393e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.190723171416479e-09</v>
+        <v>1.190723171416482e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.176722493707847e-09</v>
+        <v>1.088592891775746e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.159206454625499e-09</v>
+        <v>1.159206454625494e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.205542053822299e-09</v>
+        <v>1.205542053822298e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.10914736331678e-09</v>
+        <v>1.109147363316782e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.104344341621956e-09</v>
+        <v>1.104344341621957e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.143112194819454e-09</v>
+        <v>1.143112194819457e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.105689841935091e-09</v>
+        <v>1.105689841935093e-09</v>
       </c>
       <c r="U6" t="n">
         <v>1.183682995224491e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.323948265195137e-09</v>
+        <v>1.323948265195136e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.159941143795153e-09</v>
+        <v>1.159941143795155e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.168485517243026e-09</v>
+        <v>1.168485517243027e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.223280294454815e-09</v>
+        <v>1.223280294454817e-09</v>
       </c>
       <c r="Z6" t="n">
         <v>1.029537995530246e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.108767143744871e-09</v>
+        <v>1.108767143744874e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.262289879574785e-09</v>
+        <v>1.262289879574786e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3566,70 +3566,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.082245678808425e-10</v>
+        <v>5.082245678808418e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.202596186647484e-10</v>
+        <v>5.202596186647477e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.105529350728374e-10</v>
+        <v>5.10552935072837e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.07564064682123e-10</v>
+        <v>5.075640646821226e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.077682449145426e-10</v>
+        <v>5.077682449145428e-10</v>
       </c>
       <c r="G2" t="n">
         <v>5.091015173755879e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.088018511655708e-10</v>
+        <v>5.088018511655709e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.083358894048173e-10</v>
+        <v>5.083358894048179e-10</v>
       </c>
       <c r="J2" t="n">
         <v>5.090860968424338e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.112864691623172e-10</v>
+        <v>5.112864691623178e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.107231788104693e-10</v>
+        <v>5.107231788104688e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.099854702422248e-10</v>
+        <v>5.099854702422244e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.097837449526008e-10</v>
+        <v>5.097837449526005e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.972834177389275e-10</v>
+        <v>6.972834177389256e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.086084571367427e-10</v>
+        <v>5.086084571367418e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.086027722340039e-10</v>
+        <v>5.086027722340033e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.081663591065019e-10</v>
+        <v>5.081663591065016e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.089894606504572e-10</v>
+        <v>5.089894606504567e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.078772677411655e-10</v>
+        <v>5.078772677411652e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.937504185330635e-10</v>
+        <v>6.937504185330641e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.078083832871586e-10</v>
+        <v>5.078083832871583e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.178134961137838e-10</v>
+        <v>7.178134961137822e-10</v>
       </c>
       <c r="X2" t="n">
         <v>5.087934505417019e-10</v>
@@ -3638,13 +3638,13 @@
         <v>5.080112046583282e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.523274771051629e-10</v>
+        <v>7.523274771051637e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.078737304416586e-10</v>
+        <v>5.078737304416585e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.118502620959504e-10</v>
+        <v>5.1185026209595e-10</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.678037482612987e-10</v>
+        <v>5.093632395652031e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.470730450544261e-10</v>
+        <v>5.120812580400758e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.232566097523189e-10</v>
+        <v>5.297238840296715e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.93185732106231e-10</v>
+        <v>5.4856998932383e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.585386711447693e-10</v>
+        <v>5.073450094520546e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.880169218750413e-10</v>
+        <v>5.160336103924358e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.829680056262318e-10</v>
+        <v>5.1635874298016e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.71648359731792e-10</v>
+        <v>5.11927820746609e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.879197946733859e-10</v>
+        <v>5.163039321883465e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>6.400570428988068e-10</v>
+        <v>5.344492720474925e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.25984612456252e-10</v>
+        <v>5.288537632224084e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>6.437430416553949e-10</v>
+        <v>5.350180357056509e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>6.048375226532878e-10</v>
+        <v>5.227235071277953e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.399547024574835e-10</v>
+        <v>6.93307005362935e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.765120643695099e-10</v>
+        <v>5.123320966571172e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.774907020416062e-10</v>
+        <v>5.133026728264056e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.678363850157802e-10</v>
+        <v>5.107758648654386e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.855724141249554e-10</v>
+        <v>5.148171071863553e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.608358350724025e-10</v>
+        <v>5.08002700587914e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.092745295536977e-10</v>
+        <v>7.125775483919303e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.578730370214447e-10</v>
+        <v>5.053563945231749e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.415039878075249e-10</v>
+        <v>7.398557397098124e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.82097022499127e-10</v>
+        <v>5.15263613774653e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.635327587400396e-10</v>
+        <v>5.085848087800462e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.246837825160501e-10</v>
+        <v>7.572261723399335e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.602939061786698e-10</v>
+        <v>5.074496017915032e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.558337602928015e-10</v>
+        <v>5.417901240510756e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.43808505249976e-09</v>
+        <v>1.438085052499762e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.206587134593045e-09</v>
+        <v>1.206587134593051e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.060536416899728e-09</v>
+        <v>2.060536416899745e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.656670203366538e-10</v>
+        <v>9.656670203366511e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.457642815503921e-09</v>
+        <v>1.457642815503922e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.600649173039669e-09</v>
+        <v>1.600649173039671e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.732460542847616e-09</v>
+        <v>1.732460542847615e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.582210974625224e-09</v>
+        <v>1.582210974625225e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.625654518735428e-09</v>
+        <v>1.625654518735429e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>2.134243153372079e-09</v>
+        <v>2.134243153372091e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.935770926448043e-09</v>
+        <v>1.935770926448051e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>2.21222695676557e-09</v>
+        <v>2.212226956765578e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>1.835028794134847e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.292095454803779e-09</v>
+        <v>1.292095454803781e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.513052257233875e-09</v>
+        <v>1.513052257233896e-09</v>
       </c>
       <c r="Q4" t="n">
         <v>1.584293239540231e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.560683505212569e-09</v>
+        <v>1.560683505212573e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.553022961525491e-09</v>
+        <v>1.553022961525511e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.465664181383477e-09</v>
+        <v>1.465664181383475e-09</v>
       </c>
       <c r="U4" t="n">
         <v>1.982898592319245e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.299870936743166e-09</v>
+        <v>1.299870936743154e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.112752042520297e-09</v>
+        <v>2.112752042520303e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.656622336934336e-09</v>
+        <v>1.656622336934375e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.459209975862856e-09</v>
+        <v>1.459209975862865e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.541011927112606e-09</v>
+        <v>1.541011927112609e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.427295355396743e-09</v>
+        <v>1.427295355396741e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.432078646352096e-09</v>
+        <v>2.43207864635209e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3830,73 +3830,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.168140286495283e-09</v>
+        <v>1.168140286495284e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.682844015476171e-09</v>
+        <v>1.682844015476169e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.726249484192225e-09</v>
+        <v>1.726249484192218e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.40931609635433e-09</v>
+        <v>1.409316096354328e-09</v>
       </c>
       <c r="F5" t="n">
         <v>1.245835569640141e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.820129159629699e-09</v>
+        <v>1.820129159629697e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.706470185921254e-09</v>
+        <v>1.706470185921245e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.701206933480543e-09</v>
+        <v>1.701206933480538e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.709630534845862e-09</v>
+        <v>1.709630534845861e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.734535089175251e-09</v>
+        <v>1.734535089175256e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.728172465524758e-09</v>
+        <v>1.728172465524751e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.736718120093196e-09</v>
+        <v>1.736718120093188e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>1.305320013362866e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.392344722130599e-09</v>
+        <v>1.392344722130601e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.377562546170071e-09</v>
+        <v>1.377562546170076e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.067899629110829e-09</v>
+        <v>1.06789962911083e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.699292010773269e-09</v>
+        <v>1.699292010773272e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.708589321357664e-09</v>
+        <v>1.708589321357659e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6960265908132e-09</v>
+        <v>1.696026590813203e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.468826609751075e-09</v>
+        <v>1.468826609751065e-09</v>
       </c>
       <c r="V5" t="n">
         <v>1.549866758154316e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.732388988751077e-09</v>
+        <v>1.732388988751078e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.118794800012047e-09</v>
+        <v>1.118794800012049e-09</v>
       </c>
       <c r="Y5" t="n">
         <v>2.226437988602587e-09</v>
@@ -3905,10 +3905,10 @@
         <v>1.164785815469846e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.695986635388046e-09</v>
+        <v>1.695986635388033e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.297514792002187e-09</v>
+        <v>2.297514792002179e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3918,85 +3918,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.73214678850282e-10</v>
+        <v>9.73214678850276e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.133673157981563e-09</v>
+        <v>1.133673157981568e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.177078626697611e-09</v>
+        <v>1.177078626697617e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.10233708910202e-09</v>
+        <v>1.102337089102021e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>7.362905737423882e-10</v>
+        <v>7.362905737423824e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.160684414871249e-09</v>
+        <v>1.160684414871253e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.157299328426644e-09</v>
+        <v>1.157299328426646e-09</v>
       </c>
       <c r="I6" t="n">
         <v>1.152036075985937e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.160459677351257e-09</v>
+        <v>1.16045967735126e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.185364231680657e-09</v>
+        <v>1.185364231680651e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.179001608030147e-09</v>
+        <v>1.179001608030153e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.187547262598623e-09</v>
+        <v>1.187547262598626e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.835028794134849e-09</v>
+        <v>1.168390270444609e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.200972299633093e-09</v>
+        <v>1.200972299633094e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.226757289799856e-09</v>
+        <v>1.226757289799863e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.155050859062957e-09</v>
+        <v>1.155050859062961e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.150121153278671e-09</v>
+        <v>1.150121153278672e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.159418463863054e-09</v>
+        <v>1.159418463863062e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.146855733318598e-09</v>
+        <v>1.146855733318603e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.179147154099463e-09</v>
+        <v>1.179147154099462e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.350866902107755e-09</v>
+        <v>1.350866902107754e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.183113615437621e-09</v>
+        <v>1.183113615437627e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.157204439515563e-09</v>
+        <v>1.157204439515571e-09</v>
       </c>
       <c r="Y6" t="n">
         <v>1.148368612411975e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.050247609391369e-09</v>
+        <v>1.050247609391375e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.146815777893432e-09</v>
+        <v>1.146815777893433e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.192824735866282e-09</v>
+        <v>1.192824735866285e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.01939066162666e-10</v>
+        <v>5.019390661626643e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.135422879289234e-10</v>
+        <v>5.135422879289229e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.027332635738444e-10</v>
+        <v>5.027332635738432e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.003961771244664e-10</v>
+        <v>5.003961771244649e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.019173652090924e-10</v>
+        <v>5.019173652090923e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.011788845593369e-10</v>
+        <v>5.011788845593354e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.01645388934673e-10</v>
+        <v>5.016453889346718e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.021632290407652e-10</v>
+        <v>5.021632290407647e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.015877410043733e-10</v>
+        <v>5.015877410043735e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.018365872285042e-10</v>
+        <v>5.018365872285029e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.021392808593973e-10</v>
+        <v>5.02139280859396e-10</v>
       </c>
       <c r="M2" t="n">
         <v>5.002518095507319e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.012905854217085e-10</v>
+        <v>5.012905854217077e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.778634635705035e-10</v>
+        <v>6.778634635705022e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.004262747022976e-10</v>
+        <v>5.004262747022972e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.010453734615311e-10</v>
+        <v>5.010453734615305e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.02138595645279e-10</v>
+        <v>5.021385956452779e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.017995459288232e-10</v>
+        <v>5.01799545928822e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.010568015359026e-10</v>
+        <v>5.010568015359015e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.7019096741016e-10</v>
+        <v>6.70190967410158e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.013620943461934e-10</v>
+        <v>5.013620943461921e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>6.957775636077881e-10</v>
+        <v>6.957775636077858e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.041900543053845e-10</v>
+        <v>5.041900543053831e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.026984144298089e-10</v>
+        <v>5.026984144298081e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.397921763552686e-10</v>
+        <v>7.397921763552676e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.017186655000768e-10</v>
+        <v>5.017186655000752e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.019006849652426e-10</v>
+        <v>5.01900684965242e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.712873648805252e-10</v>
+        <v>5.051966685383972e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.561779114878383e-10</v>
+        <v>5.093803447662219e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.910263374491319e-10</v>
+        <v>5.127810832552163e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.78488637273138e-10</v>
+        <v>5.396078149991369e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.723733491096033e-10</v>
+        <v>5.066004151070255e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.538111273118709e-10</v>
+        <v>4.992574787428488e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.662176972912615e-10</v>
+        <v>5.051282298255554e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.779227684978304e-10</v>
+        <v>5.086609102826013e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.634674140783591e-10</v>
+        <v>5.026765924355035e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.699845341054078e-10</v>
+        <v>5.053648530535251e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.763204466540798e-10</v>
+        <v>5.065752371637171e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.671233013058169e-10</v>
+        <v>5.035289105705857e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.570892850867252e-10</v>
+        <v>5.008920727007489e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.215984371683786e-10</v>
+        <v>6.732438539972874e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.363642067387905e-10</v>
+        <v>4.933492737341204e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.514417645913695e-10</v>
+        <v>4.986799068196498e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.775337687577895e-10</v>
+        <v>5.087451675643273e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.682238838367538e-10</v>
+        <v>5.037165411126471e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.519784902878748e-10</v>
+        <v>4.99553443224657e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.208712231137824e-10</v>
+        <v>6.678783301542539e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.576537010211538e-10</v>
+        <v>4.997940062060288e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.223794983767189e-10</v>
+        <v>7.171248598406338e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>6.248432672884597e-10</v>
+        <v>5.239757198333111e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.897017655594221e-10</v>
+        <v>5.122943322884958e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.06202885644953e-10</v>
+        <v>7.41870002042223e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.668909361735745e-10</v>
+        <v>5.043898439268349e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.748186155607357e-10</v>
+        <v>5.077634283087732e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4338,82 +4338,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.455438300020763e-09</v>
+        <v>1.455438300020764e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.29412067595122e-09</v>
+        <v>1.294120675951218e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.696186604215836e-09</v>
+        <v>1.696186604215833e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.4406447644226e-10</v>
+        <v>8.440644764422594e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.556116301001388e-09</v>
+        <v>1.556116301001386e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.312778922528358e-09</v>
+        <v>1.312778922528356e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.549396073580125e-09</v>
+        <v>1.549396073580124e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.611924870539608e-09</v>
+        <v>1.611924870539601e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.40437797011572e-09</v>
+        <v>1.404377970115717e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.50059368548783e-09</v>
+        <v>1.500593685487828e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4797003903163e-09</v>
+        <v>1.479700390316299e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.503404311694082e-09</v>
+        <v>1.503404311694081e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.384556298573707e-09</v>
+        <v>1.384556298573706e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.239788652891833e-09</v>
+        <v>1.239788652891831e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.169843538335475e-09</v>
+        <v>1.169843538335473e-09</v>
       </c>
       <c r="Q4" t="n">
         <v>1.318363782884315e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.625881688023997e-09</v>
+        <v>1.625881688023995e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.402458709305871e-09</v>
+        <v>1.402458709305869e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.373517092964941e-09</v>
+        <v>1.37351709296494e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.313787347704534e-09</v>
+        <v>1.313787347704533e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.286665571796007e-09</v>
+        <v>1.286665571796002e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.979959801387031e-09</v>
+        <v>1.979959801387028e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.956330114499666e-09</v>
+        <v>1.956330114499678e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.675838773729445e-09</v>
+        <v>1.675838773729446e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.412359798211869e-09</v>
+        <v>1.412359798211865e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.475393133269039e-09</v>
+        <v>1.475393133269036e-09</v>
       </c>
       <c r="AB4" t="n">
         <v>1.60288702479732e-09</v>
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.089497592615787e-09</v>
+        <v>1.089497592615784e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.554649115685476e-09</v>
+        <v>1.554649115685471e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.577727588231773e-09</v>
+        <v>1.577727588231768e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.296137750627752e-09</v>
+        <v>1.296137750627747e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.163915447914106e-09</v>
+        <v>1.163915447914102e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.659547673305263e-09</v>
+        <v>1.659547673305257e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.565439543735271e-09</v>
+        <v>1.565439543735266e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.571288785951801e-09</v>
+        <v>1.571288785951797e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.564740466903831e-09</v>
+        <v>1.564740466903826e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.56759921641965e-09</v>
+        <v>1.567599216419644e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.571018280226543e-09</v>
+        <v>1.571018280226537e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.566763210984105e-09</v>
+        <v>1.5667632109841e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.384556298573707e-09</v>
+        <v>1.189925839397327e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.286235092338292e-09</v>
+        <v>1.286235092338289e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.257230654640616e-09</v>
+        <v>1.257230654640613e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.852175568615278e-10</v>
+        <v>9.852175568615249e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57101054041786e-09</v>
+        <v>1.571010540417854e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.567180817899915e-09</v>
+        <v>1.567180817899911e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.558791178302582e-09</v>
+        <v>1.558791178302577e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.325193172762159e-09</v>
+        <v>1.325193172762154e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.431252179843302e-09</v>
+        <v>1.431252179843298e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.597703349155776e-09</v>
+        <v>1.59770334915577e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.064663228931732e-09</v>
+        <v>1.06466322893173e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.0540058991904e-09</v>
+        <v>2.054005899190395e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.079069290895492e-09</v>
+        <v>1.079069290895487e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.566267236250393e-09</v>
+        <v>1.566267236250388e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.070525421282877e-09</v>
+        <v>2.070525421282868e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.977319540753985e-10</v>
+        <v>8.97731954075397e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.039189598083105e-09</v>
+        <v>1.039189598083103e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.062268070629403e-09</v>
+        <v>1.062268070629398e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.999659281855616e-10</v>
+        <v>9.999659281855587e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.944313991488639e-10</v>
+        <v>6.944313991488627e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.044710851111589e-09</v>
+        <v>1.044710851111584e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.049980026132901e-09</v>
+        <v>1.049980026132898e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.055829268349432e-09</v>
+        <v>1.05582926834943e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.049280949301462e-09</v>
+        <v>1.049280949301459e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.05213969881728e-09</v>
+        <v>1.052139698817277e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.055558762624173e-09</v>
+        <v>1.055558762624168e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.051303693381739e-09</v>
+        <v>1.051303693381737e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.384556298573707e-09</v>
+        <v>1.045972357236292e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.091742934699877e-09</v>
+        <v>1.091742934699874e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.098976133366909e-09</v>
+        <v>1.098976133366905e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.043202781843736e-09</v>
+        <v>1.043202781843733e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.05555102281549e-09</v>
+        <v>1.055551022815487e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.051721300297546e-09</v>
+        <v>1.051721300297543e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.043331660700212e-09</v>
+        <v>1.04333166070021e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.043562783025232e-09</v>
+        <v>1.04356278302523e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.226200287953047e-09</v>
+        <v>1.226200287953043e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.082149643337104e-09</v>
+        <v>1.082149643337101e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.078723192098986e-09</v>
+        <v>1.078723192098984e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.061874433516125e-09</v>
+        <v>1.061874433516122e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.579794736123039e-10</v>
+        <v>9.57979473612302e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.050807718648023e-09</v>
+        <v>1.050807718648021e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.054439625032989e-09</v>
+        <v>1.054439625032987e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.028879457577177e-10</v>
+        <v>5.028879457577147e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.139136802640665e-10</v>
+        <v>5.139136802640662e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.030203952033618e-10</v>
+        <v>5.030203952033595e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.013298685780122e-10</v>
+        <v>5.013298685780102e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.017128660629745e-10</v>
+        <v>5.017128660629722e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.023872339637935e-10</v>
+        <v>5.023872339637924e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.016113829805188e-10</v>
+        <v>5.016113829805177e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.022820265769799e-10</v>
+        <v>5.022820265769786e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.02210318473036e-10</v>
+        <v>5.022103184730346e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.017599183815837e-10</v>
+        <v>5.017599183815819e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.019722223071707e-10</v>
+        <v>5.019722223071685e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.000730891284601e-10</v>
+        <v>5.000730891284604e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.01392189468318e-10</v>
+        <v>5.013921894683175e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>6.758101016733746e-10</v>
+        <v>6.758101016733736e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.007970554816544e-10</v>
+        <v>5.007970554816568e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.011230336581597e-10</v>
+        <v>5.011230336581577e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.028016789339435e-10</v>
+        <v>5.028016789339418e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.017835737484313e-10</v>
+        <v>5.017835737484296e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.012868869636177e-10</v>
+        <v>5.012868869636146e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>6.691220579275589e-10</v>
+        <v>6.691220579275583e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.018538805558928e-10</v>
+        <v>5.018538805558951e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.001244654242338e-10</v>
+        <v>7.001244654242325e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.050144769772822e-10</v>
+        <v>5.050144769772803e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.034172945212078e-10</v>
+        <v>5.034172945212059e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.386097896120563e-10</v>
+        <v>7.386097896120545e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.020029907138594e-10</v>
+        <v>5.020029907138573e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.027667631107165e-10</v>
+        <v>5.027667631107158e-10</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.894804276892171e-10</v>
+        <v>5.111577609599531e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.623179970389971e-10</v>
+        <v>5.113383881313174e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.940534251500044e-10</v>
+        <v>5.138545626642073e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.967564980680899e-10</v>
+        <v>5.458960347749483e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.639037841026094e-10</v>
+        <v>5.037575111539619e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.779848613403565e-10</v>
+        <v>5.072077518704999e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.617019543827761e-10</v>
+        <v>5.034073914271269e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.770112171243479e-10</v>
+        <v>5.083043916560464e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.742995322939242e-10</v>
+        <v>5.063697915813384e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.645372715829741e-10</v>
+        <v>5.035737997074478e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.688398645404529e-10</v>
+        <v>5.042821886515214e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.592423968028094e-10</v>
+        <v>5.010814081248578e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.55790523822161e-10</v>
+        <v>5.004662606741089e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.197808480653284e-10</v>
+        <v>6.710389000686881e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.412451126589592e-10</v>
+        <v>4.948595940004563e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.496026029883508e-10</v>
+        <v>4.982039455511641e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.893678320045776e-10</v>
+        <v>5.128394838824181e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.642477645437223e-10</v>
+        <v>5.02596213567229e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.53665957386326e-10</v>
+        <v>5.000956427611724e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.260854083573026e-10</v>
+        <v>6.685138395260581e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.65354690924624e-10</v>
+        <v>5.023019135030934e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>9.504791722473592e-10</v>
+        <v>7.5987251857338e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>6.403334588464792e-10</v>
+        <v>5.289015393601331e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.027368527156065e-10</v>
+        <v>5.167932122834894e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.010203274658844e-10</v>
+        <v>7.391625468000674e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.698200652245242e-10</v>
+        <v>5.053125100123286e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.912852566217285e-10</v>
+        <v>5.13754150817941e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4940,25 +4940,25 @@
         <v>1.347450657616321e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.73285575414754e-09</v>
+        <v>1.732855754147542e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.917558188691571e-10</v>
+        <v>9.917558188691567e-10</v>
       </c>
       <c r="F4" t="n">
         <v>1.495689169188639e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.500538637871643e-09</v>
+        <v>1.500538637871706e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.506606753412571e-09</v>
+        <v>1.506606753412572e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.609286167310095e-09</v>
+        <v>1.609286167310097e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.503780118976968e-09</v>
+        <v>1.50378011897696e-09</v>
       </c>
       <c r="K4" t="n">
         <v>1.46764716026004e-09</v>
@@ -4967,25 +4967,25 @@
         <v>1.4436344644091e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.461558947752401e-09</v>
+        <v>1.4615589477524e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.383109448861234e-09</v>
+        <v>1.383109448861236e-09</v>
       </c>
       <c r="O4" t="n">
         <v>1.24332135640931e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.207553817448003e-09</v>
+        <v>1.207553817448002e-09</v>
       </c>
       <c r="Q4" t="n">
         <v>1.321736233473096e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.738545949287259e-09</v>
+        <v>1.738545949287256e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.394174415157859e-09</v>
+        <v>1.394174415157861e-09</v>
       </c>
       <c r="T4" t="n">
         <v>1.393693095551531e-09</v>
@@ -4997,19 +4997,19 @@
         <v>1.350569351788497e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.068910186813275e-09</v>
+        <v>3.068910186813284e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.070125239862784e-09</v>
+        <v>2.070125239862776e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.796962608327437e-09</v>
+        <v>1.796962608327441e-09</v>
       </c>
       <c r="Z4" t="n">
         <v>1.375368444906256e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.502806130113564e-09</v>
+        <v>1.502806130113563e-09</v>
       </c>
       <c r="AB4" t="n">
         <v>1.776041946441218e-09</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.094168531604427e-09</v>
+        <v>1.094168531604428e-09</v>
       </c>
       <c r="C5" t="n">
         <v>1.550187023709206e-09</v>
@@ -5031,76 +5031,76 @@
         <v>1.571719909283939e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.299139228723322e-09</v>
+        <v>1.299139228723324e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.155059317900425e-09</v>
+        <v>1.155059317900424e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6632812295393e-09</v>
+        <v>1.663281229539301e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.555804468049285e-09</v>
+        <v>1.555804468049287e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.563379695982611e-09</v>
+        <v>1.56337969598261e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.562519654187465e-09</v>
+        <v>1.562519654187463e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.557482243733971e-09</v>
+        <v>1.557482243733972e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.559880314238098e-09</v>
+        <v>1.559880314238099e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.555469260292048e-09</v>
+        <v>1.55546926029205e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.383109448861234e-09</v>
+        <v>1.184306076489766e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.280775734770641e-09</v>
+        <v>1.280775734770643e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.254136166184853e-09</v>
+        <v>1.254136166184854e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.806773055934529e-10</v>
+        <v>9.806773055934533e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.569249408406412e-09</v>
+        <v>1.56924940840641e-09</v>
       </c>
       <c r="S5" t="n">
         <v>1.55774944198452e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.552139136262824e-09</v>
+        <v>1.552139136262827e-09</v>
       </c>
       <c r="U5" t="n">
         <v>1.322592427878118e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.428427549198423e-09</v>
+        <v>1.428427549198421e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65333406688945e-09</v>
+        <v>1.653334066889453e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.068264362273124e-09</v>
+        <v>1.068264362273125e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.049705008703572e-09</v>
+        <v>2.049705008703571e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.072906238428897e-09</v>
+        <v>1.072906238428896e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.560227857545821e-09</v>
+        <v>1.56022785754582e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.067654939998466e-09</v>
+        <v>2.067654939998464e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5110,61 +5110,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.920880574706703e-10</v>
+        <v>8.920880574706701e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.023369424529835e-09</v>
+        <v>1.023369424529834e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.04490231010457e-09</v>
+        <v>1.044902310104569e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.908835755300372e-10</v>
+        <v>9.908835755300359e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.813032047029994e-10</v>
+        <v>6.813032047029997e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.037750669294961e-09</v>
+        <v>1.037750669294967e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02898686886992e-09</v>
+        <v>1.028986868869916e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.036562096803238e-09</v>
+        <v>1.036562096803237e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.035702055008093e-09</v>
+        <v>1.035702055008092e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.030664644554603e-09</v>
+        <v>1.030664644554601e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.033062715058724e-09</v>
+        <v>1.033062715058726e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.028651661112659e-09</v>
+        <v>1.028651661112655e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.383109448861234e-09</v>
+        <v>1.02651097731562e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.07171696867722e-09</v>
+        <v>1.071716968677219e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.080841635279501e-09</v>
+        <v>1.0808416352795e-09</v>
       </c>
       <c r="Q6" t="n">
         <v>1.023470945281949e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.04243180922704e-09</v>
+        <v>1.042431809227038e-09</v>
       </c>
       <c r="S6" t="n">
         <v>1.030931842805148e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.025321537083458e-09</v>
+        <v>1.025321537083455e-09</v>
       </c>
       <c r="U6" t="n">
         <v>1.028031114355688e-09</v>
@@ -5173,22 +5173,22 @@
         <v>1.206230825004989e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.126422909149519e-09</v>
+        <v>1.126422909149518e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.067426381063937e-09</v>
+        <v>1.067426381063934e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.049385470482333e-09</v>
+        <v>1.049385470482335e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.397555892687747e-10</v>
+        <v>9.397555892687726e-10</v>
       </c>
       <c r="AA6" t="n">
         <v>1.033410258366449e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.043557772550751e-09</v>
+        <v>1.04355777255075e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.211429091878073e-10</v>
+        <v>5.211429091878041e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.320136828626428e-10</v>
+        <v>5.320136828626491e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>5.208791530115078e-10</v>
+        <v>5.208791530115088e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.189383283473384e-10</v>
+        <v>5.189383283473372e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.191115304556831e-10</v>
+        <v>5.191115304556842e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.246206259422822e-10</v>
+        <v>5.246206259422863e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.187427683175149e-10</v>
+        <v>5.187427683175183e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.208208885469469e-10</v>
+        <v>5.208208885469488e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.22760190212098e-10</v>
+        <v>5.227601902120955e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.235552800901238e-10</v>
+        <v>5.235552800901205e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.264843851243354e-10</v>
+        <v>5.26484385124341e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>5.277530587205786e-10</v>
+        <v>5.27753058720576e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.217386553043628e-10</v>
+        <v>5.217386553043707e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.211198686476685e-10</v>
+        <v>7.211198686476698e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.218054815194448e-10</v>
+        <v>5.218054815194447e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.194196174514984e-10</v>
+        <v>5.194196174515038e-10</v>
       </c>
       <c r="R2" t="n">
         <v>5.192362686607563e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.211524088856324e-10</v>
+        <v>5.211524088856297e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.197848440355611e-10</v>
+        <v>5.197848440355657e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.205735511573717e-10</v>
+        <v>7.205735511573769e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.191911881517457e-10</v>
+        <v>5.191911881517466e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.415265978089083e-10</v>
+        <v>7.415265978089096e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.229933887126936e-10</v>
+        <v>5.229933887126973e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.21588798665996e-10</v>
+        <v>5.215887986659915e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.693519331667788e-10</v>
+        <v>7.693519331667825e-10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.190060293642783e-10</v>
+        <v>5.190060293642791e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.329835731448838e-10</v>
+        <v>5.329835731448866e-10</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.262696433831449e-10</v>
+        <v>5.364010601222959e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.678113893370829e-10</v>
+        <v>5.268247603060577e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>6.21892322050773e-10</v>
+        <v>5.36611731008302e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>6.139467234383909e-10</v>
+        <v>5.615298020146128e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.809443473216771e-10</v>
+        <v>5.224052161918774e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>7.064012461216857e-10</v>
+        <v>5.632323087099449e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.724626236872306e-10</v>
+        <v>5.198451115671497e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>6.207189029570365e-10</v>
+        <v>5.362773620862943e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.64110663296795e-10</v>
+        <v>5.49519870770763e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>6.83926702003944e-10</v>
+        <v>5.565385974736459e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>7.506208068674684e-10</v>
+        <v>5.793484663553513e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>8.153713242824191e-10</v>
+        <v>6.008666902944924e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>6.414262674390496e-10</v>
+        <v>5.429647810026148e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.902240749372247e-10</v>
+        <v>7.253210081966462e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>6.413374533723214e-10</v>
+        <v>5.417112091148624e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.875857561888311e-10</v>
+        <v>5.242101153707595e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.838299918519901e-10</v>
+        <v>5.235864036051657e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>6.267602358092508e-10</v>
+        <v>5.363237690143417e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.963931392375996e-10</v>
+        <v>5.277154591499703e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>9.30496830489594e-10</v>
+        <v>7.691697348195557e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.810020169373828e-10</v>
+        <v>5.204850091351091e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.633994747774279e-10</v>
+        <v>7.631489887683742e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>6.710784137366333e-10</v>
+        <v>5.53468610116086e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.377065425166266e-10</v>
+        <v>5.413244114694798e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.682182133200176e-10</v>
+        <v>7.827683710804787e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.776918715835639e-10</v>
+        <v>5.207130590395798e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.04411467963601e-10</v>
+        <v>6.378638079700173e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.845956456891014e-09</v>
+        <v>1.845956456891275e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.296113068757333e-09</v>
+        <v>1.296113068757335e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.956342583108885e-09</v>
+        <v>1.956342583108898e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.077762735661872e-09</v>
+        <v>1.077762735662101e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.573340655106414e-09</v>
+        <v>1.573340655106415e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.518361369247772e-09</v>
+        <v>2.51836136924778e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.522851985250022e-09</v>
+        <v>1.522851985250026e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.953217843762308e-09</v>
+        <v>1.95321784376232e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.20451594020279e-09</v>
+        <v>2.204515940202846e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>2.420508453200251e-09</v>
+        <v>2.420508453200261e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>3.003601290836502e-09</v>
+        <v>3.0036012908377e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>3.66941767632531e-09</v>
+        <v>3.669417676325314e-09</v>
       </c>
       <c r="N4" t="n">
         <v>2.102631491862222e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.523433459416658e-09</v>
+        <v>1.523433459416669e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.988887348389267e-09</v>
+        <v>1.988887348389289e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.591837246744732e-09</v>
+        <v>1.591837246744684e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.613437467801045e-09</v>
+        <v>1.61343746780105e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.836335321494279e-09</v>
+        <v>1.836335321494349e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.712076013603083e-09</v>
+        <v>1.712076013603087e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>2.880734941796551e-09</v>
+        <v>2.880734941796572e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.40612572485925e-09</v>
+        <v>1.406125724859238e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.097476755774137e-09</v>
+        <v>2.097476755774132e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.404204242966041e-09</v>
+        <v>2.404204242965936e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.038695395403722e-09</v>
+        <v>2.038695395403738e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.797251224145794e-09</v>
+        <v>1.797251224145741e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.490088357866312e-09</v>
+        <v>1.490088357866405e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.871518920263397e-09</v>
+        <v>4.871518920263392e-09</v>
       </c>
     </row>
     <row r="5">
@@ -5618,85 +5618,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.224988770149338e-09</v>
+        <v>1.22498877014933e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.739462336465647e-09</v>
+        <v>1.739462336465649e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.772399469796291e-09</v>
+        <v>1.772399469796294e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.457410551090988e-09</v>
+        <v>1.457410551090994e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.287787734096772e-09</v>
+        <v>1.287787734096775e-09</v>
       </c>
       <c r="G5" t="n">
         <v>1.928788068683282e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.748268021892125e-09</v>
+        <v>1.748268021892128e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.771741345866082e-09</v>
+        <v>1.771741345866083e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.793581609735823e-09</v>
+        <v>1.793581609735822e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.802627556228473e-09</v>
+        <v>1.802627556228476e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.835713145044863e-09</v>
+        <v>1.835713145044861e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.866408307879126e-09</v>
+        <v>1.866408307879127e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.102631491862222e-09</v>
+        <v>1.355463656452874e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.447542041834793e-09</v>
+        <v>1.447542041834794e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.444724325432203e-09</v>
+        <v>1.444724325432204e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.09735921059394e-09</v>
+        <v>1.097359210593941e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.753842335290364e-09</v>
+        <v>1.753842335290362e-09</v>
       </c>
       <c r="S5" t="n">
         <v>1.77548602059839e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76003874650598e-09</v>
+        <v>1.760038746505983e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.559915980982414e-09</v>
+        <v>1.559915980982416e-09</v>
       </c>
       <c r="V5" t="n">
         <v>1.602694359181425e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.783535677087075e-09</v>
+        <v>1.783535677087073e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.188170933333649e-09</v>
+        <v>1.188170933333668e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.327665524865222e-09</v>
+        <v>2.327665524865224e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.211495589581176e-09</v>
+        <v>1.211495589581183e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.751241676521358e-09</v>
+        <v>1.75124167652136e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.483801636807896e-09</v>
+        <v>2.483801636807895e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.029159932892048e-09</v>
+        <v>1.029159932892056e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.178645065990337e-09</v>
+        <v>1.178645065990341e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.211582199320983e-09</v>
+        <v>1.211582199320985e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.14686993987616e-09</v>
+        <v>1.146869939876161e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>7.64214725909705e-10</v>
+        <v>7.642147259097054e-10</v>
       </c>
       <c r="G6" t="n">
         <v>1.253844066674594e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.187450751416818e-09</v>
+        <v>1.187450751416823e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.210924075390774e-09</v>
+        <v>1.210924075390776e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.232764339260516e-09</v>
+        <v>1.232764339260518e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.241810285753167e-09</v>
+        <v>1.241810285753168e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.274895874569543e-09</v>
+        <v>1.274895874569556e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.305591037403839e-09</v>
+        <v>1.305591037403842e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.102631491862222e-09</v>
+        <v>1.221290673109437e-09</v>
       </c>
       <c r="O6" t="n">
         <v>1.257565601605948e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.296850160239896e-09</v>
+        <v>1.2968501602399e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.195096283189068e-09</v>
+        <v>1.195096283189072e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.193025064815056e-09</v>
+        <v>1.193025064815058e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.214668750123079e-09</v>
+        <v>1.214668750123087e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.199221476030676e-09</v>
+        <v>1.199221476030679e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.267730802798644e-09</v>
+        <v>1.267730802798645e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.406249870433561e-09</v>
+        <v>1.406249870433562e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.222610239142678e-09</v>
+        <v>1.222610239142681e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.23546346416238e-09</v>
+        <v>1.235463464162371e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.219597973441496e-09</v>
+        <v>1.2195979734415e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.099511498845386e-09</v>
+        <v>1.099511498845397e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.190424406046049e-09</v>
+        <v>1.190424406046054e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.348056043772529e-09</v>
+        <v>1.348056043772531e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5950,85 +5950,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.127503827787364e-10</v>
+        <v>5.127503827787366e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>5.265761733446636e-10</v>
+        <v>5.265761733446638e-10</v>
       </c>
       <c r="D2" t="n">
         <v>5.13796031617016e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>5.123532329703419e-10</v>
+        <v>5.123532329703421e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>5.130610209903348e-10</v>
+        <v>5.130610209903347e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>5.169265927470365e-10</v>
+        <v>5.169265927470363e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>5.123958950695998e-10</v>
+        <v>5.123958950696e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>5.135937283982902e-10</v>
+        <v>5.135937283982904e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>5.145909192109337e-10</v>
+        <v>5.145909192109333e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>5.144200259980352e-10</v>
+        <v>5.144200259980356e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>5.157466127059595e-10</v>
+        <v>5.157466127059598e-10</v>
       </c>
       <c r="M2" t="n">
         <v>5.130191548950533e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>5.123969090754407e-10</v>
+        <v>5.123969090754411e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>7.053292669866859e-10</v>
+        <v>7.053292669866863e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.139970249864393e-10</v>
+        <v>5.13997024986439e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.136790865175955e-10</v>
+        <v>5.13679086517596e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>5.135183150322428e-10</v>
+        <v>5.135183150322422e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>5.135062304422197e-10</v>
+        <v>5.135062304422192e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>5.126462290014408e-10</v>
+        <v>5.126462290014407e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>7.004850784175681e-10</v>
+        <v>7.004850784175674e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>5.128334444737785e-10</v>
+        <v>5.128334444737786e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>7.268770845792357e-10</v>
+        <v>7.268770845792362e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.161098560615519e-10</v>
+        <v>5.161098560615512e-10</v>
       </c>
       <c r="Y2" t="n">
         <v>5.181798130310452e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.579224360786752e-10</v>
+        <v>7.579224360786757e-10</v>
       </c>
       <c r="AA2" t="n">
         <v>5.129758225706342e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.219306153759231e-10</v>
+        <v>5.219306153759228e-10</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.669311942799838e-10</v>
+        <v>5.122831240389319e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.758986711481929e-10</v>
+        <v>5.254322136704415e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.923439171497851e-10</v>
+        <v>5.21987999105253e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.976141040427095e-10</v>
+        <v>5.52725421400386e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.755135363366099e-10</v>
+        <v>5.162450049170221e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>6.630605964327188e-10</v>
+        <v>5.44017613294259e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.600959739999534e-10</v>
+        <v>5.113995248756411e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.877967565654303e-10</v>
+        <v>5.206812502393405e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>6.096442137459037e-10</v>
+        <v>5.267512469940943e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>6.066761453815467e-10</v>
+        <v>5.261872499159204e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.366159039768943e-10</v>
+        <v>5.357875009500606e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>6.08369517625836e-10</v>
+        <v>5.262487312212253e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.59454988386272e-10</v>
+        <v>5.10430512387229e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.422655734486393e-10</v>
+        <v>6.996148740906904e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.954636156122774e-10</v>
+        <v>5.218134617450204e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.893122189133333e-10</v>
+        <v>5.201240253545419e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.862078578400971e-10</v>
+        <v>5.203073908978098e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.845229819130437e-10</v>
+        <v>5.180117279588232e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.655606799348358e-10</v>
+        <v>5.128163354970636e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.737568706724868e-10</v>
+        <v>7.061115628557931e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.685158424212248e-10</v>
+        <v>5.120793255040887e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.481309462651085e-10</v>
+        <v>7.481548487208101e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>6.461718171574701e-10</v>
+        <v>5.402340745255151e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.936199965849345e-10</v>
+        <v>5.56396444835442e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.207261436513046e-10</v>
+        <v>7.598868269256682e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.727431209081002e-10</v>
+        <v>5.14872209114852e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.830956675537324e-10</v>
+        <v>5.89912156449626e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6126,25 +6126,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.322830622550625e-09</v>
+        <v>1.322830622550626e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.347193596308196e-09</v>
+        <v>1.347193596308198e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.621553610751426e-09</v>
+        <v>1.621553610751427e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.271191346765198e-10</v>
+        <v>9.271191346765213e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>1.483483219526255e-09</v>
+        <v>1.483483219526254e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.045491873100565e-09</v>
+        <v>2.045491873100564e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.382773665713847e-09</v>
+        <v>1.382773665713848e-09</v>
       </c>
       <c r="I4" t="n">
         <v>1.602083759316053e-09</v>
@@ -6153,7 +6153,7 @@
         <v>1.673575701573027e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.692625783992242e-09</v>
+        <v>1.69262578399224e-09</v>
       </c>
       <c r="L4" t="n">
         <v>1.890374440917036e-09</v>
@@ -6162,10 +6162,10 @@
         <v>1.759665477576221e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.317427773214491e-09</v>
+        <v>1.317427773214492e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.181451415810187e-09</v>
+        <v>1.181451415810189e-09</v>
       </c>
       <c r="P4" t="n">
         <v>1.54270445210431e-09</v>
@@ -6174,28 +6174,28 @@
         <v>1.535392191338972e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.602379164863251e-09</v>
+        <v>1.602379164863252e-09</v>
       </c>
       <c r="S4" t="n">
         <v>1.452306035255245e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.393476700690564e-09</v>
+        <v>1.393476700690562e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.502813990854656e-09</v>
+        <v>1.502813990854655e-09</v>
       </c>
       <c r="V4" t="n">
         <v>1.280653439249471e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.973548038665955e-09</v>
+        <v>1.973548038665956e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>2.066282311953709e-09</v>
+        <v>2.066282311953708e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.454279596712179e-09</v>
+        <v>2.454279596712177e-09</v>
       </c>
       <c r="Z4" t="n">
         <v>1.380670511790998e-09</v>
@@ -6204,7 +6204,7 @@
         <v>1.420564647925582e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.433464839360912e-09</v>
+        <v>3.433464839360913e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.119917962123511e-09</v>
+        <v>1.119917962123513e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1.618317536794473e-09</v>
+        <v>1.618317536794476e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>1.63306078687317e-09</v>
+        <v>1.633060786873175e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>1.349819349184962e-09</v>
+        <v>1.349819349184964e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.201528389551427e-09</v>
+        <v>1.20152838955143e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.772376317152668e-09</v>
+        <v>1.77237631715267e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>1.617245600475473e-09</v>
+        <v>1.617245600475477e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>1.630775678953585e-09</v>
+        <v>1.63077567895359e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.64198079598872e-09</v>
+        <v>1.641980795988725e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>1.640109090458381e-09</v>
+        <v>1.640109090458384e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>1.655093497584417e-09</v>
+        <v>1.65509349758442e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.641404421931743e-09</v>
+        <v>1.641404421931747e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.317427773214491e-09</v>
+        <v>1.228641084604483e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.330604369022812e-09</v>
+        <v>1.330604369022816e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.327332127152411e-09</v>
+        <v>1.327332127152412e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.03188496879468e-09</v>
+        <v>1.031884968794682e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>1.629923850292212e-09</v>
+        <v>1.629923850292215e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.629787349288716e-09</v>
+        <v>1.629787349288719e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.620073237394912e-09</v>
+        <v>1.620073237394915e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.386183576270339e-09</v>
+        <v>1.386183576270342e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.485046399559641e-09</v>
+        <v>1.485046399559645e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.655215377527779e-09</v>
+        <v>1.655215377527781e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.105289679182684e-09</v>
+        <v>1.105289679182686e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.181120955209184e-09</v>
+        <v>2.181120955209191e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.115007134848695e-09</v>
+        <v>1.115007134848696e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.623796148379481e-09</v>
+        <v>1.623796148379483e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.248935704715014e-09</v>
+        <v>2.248935704715019e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6302,13 +6302,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.203443318034355e-10</v>
+        <v>9.203443318034346e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>1.080425280555057e-09</v>
+        <v>1.080425280555056e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.095168530633755e-09</v>
+        <v>1.095168530633754e-09</v>
       </c>
       <c r="E6" t="n">
         <v>1.041248854693849e-09</v>
@@ -6317,28 +6317,28 @@
         <v>7.110762567355258e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.13052986716119e-09</v>
+        <v>1.130529867161189e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.079353344236055e-09</v>
+        <v>1.079353344236056e-09</v>
       </c>
       <c r="I6" t="n">
         <v>1.092883422714169e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.104088539749304e-09</v>
+        <v>1.104088539749305e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.102216834218965e-09</v>
+        <v>1.102216834218964e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.117201241345001e-09</v>
+        <v>1.117201241345e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.103512165692355e-09</v>
+        <v>1.103512165692357e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.317427773214491e-09</v>
+        <v>1.079364797898497e-09</v>
       </c>
       <c r="O6" t="n">
         <v>1.128555649661379e-09</v>
@@ -6347,40 +6347,40 @@
         <v>1.163210398798374e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.09384779037298e-09</v>
+        <v>1.093847790372981e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.092031594052794e-09</v>
+        <v>1.092031594052795e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.091895093049298e-09</v>
+        <v>1.091895093049299e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.082180981155493e-09</v>
+        <v>1.082180981155495e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.092937534721558e-09</v>
+        <v>1.092937534721557e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27223741979573e-09</v>
+        <v>1.272237419795732e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.117224595173698e-09</v>
+        <v>1.117224595173696e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.121304242146616e-09</v>
+        <v>1.121304242146615e-09</v>
       </c>
       <c r="Y6" t="n">
         <v>1.144685358344294e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.894767837780698e-10</v>
+        <v>9.894767837780702e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.085903892140063e-09</v>
+        <v>1.085903892140064e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18736052520618e-09</v>
+        <v>1.187360525206181e-09</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity carcinogenic results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.888081175225896e-10</v>
+        <v>5.633249845992816e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.567837053648285e-10</v>
+        <v>5.446544115423232e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.714732933406356e-10</v>
+        <v>5.494795575939176e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.863072105016675e-10</v>
+        <v>5.757997294290724e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.574779159917584e-10</v>
+        <v>5.395817645839484e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.944378526729394e-10</v>
+        <v>5.669771956454272e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.560011580324297e-10</v>
+        <v>5.383815304355291e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.757138148840759e-10</v>
+        <v>5.522284314903273e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.826833973484867e-10</v>
+        <v>5.583163692784358e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>6.046421011983814e-10</v>
+        <v>5.724333062293756e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.163392308131679e-10</v>
+        <v>5.815880784529238e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>6.402946435818291e-10</v>
+        <v>5.958917692640188e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.782508460904279e-10</v>
+        <v>5.545470063021993e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>8.008725837750544e-10</v>
+        <v>7.824080087295454e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.707515547192048e-10</v>
+        <v>5.503711594982891e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.51820661293888e-10</v>
+        <v>5.361393240102095e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.532629080079819e-10</v>
+        <v>5.367362695285568e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.761140304472131e-10</v>
+        <v>5.539083888511628e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.65366378399946e-10</v>
+        <v>5.452362971246826e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.629115854136637e-10</v>
+        <v>8.241348217122571e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.589676249421098e-10</v>
+        <v>5.424471015188744e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.402811988953301e-10</v>
+        <v>8.165487750109317e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.678387516713268e-10</v>
+        <v>5.471111784647742e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.738508864088048e-10</v>
+        <v>5.516912903467644e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.348362249499219e-10</v>
+        <v>8.14406836707191e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.552615414483114e-10</v>
+        <v>5.387397809837291e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.892462735497228e-10</v>
+        <v>6.286407858488264e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.087248198008664e-10</v>
+        <v>4.961531412892346e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.20519351039144e-10</v>
+        <v>5.07910491017723e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.173244996313397e-10</v>
+        <v>5.014731896390289e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.484182632499609e-10</v>
+        <v>5.412005424656905e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.139511926146356e-10</v>
+        <v>4.989549544874914e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.148943567900786e-10</v>
+        <v>5.005767664816063e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.130928755591069e-10</v>
+        <v>4.980323212277668e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.184297083057443e-10</v>
+        <v>5.02042852565199e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.154756437398386e-10</v>
+        <v>5.00686545154232e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.176358719458706e-10</v>
+        <v>5.019743887414303e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.147287618302132e-10</v>
+        <v>5.002018740523971e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.13260174036155e-10</v>
+        <v>4.979853712038895e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.077949174428181e-10</v>
+        <v>4.949175314097251e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>6.915193701372793e-10</v>
+        <v>6.80674325107096e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.042965125453168e-10</v>
+        <v>4.930268577357064e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.107602051078435e-10</v>
+        <v>4.971478909251472e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.233253564081763e-10</v>
+        <v>5.052157365529132e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.123249812568667e-10</v>
+        <v>4.987124227367075e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.089802312269817e-10</v>
+        <v>4.955412684760477e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>6.995696697869169e-10</v>
+        <v>6.847445024433745e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.129121678245226e-10</v>
+        <v>4.996306908990512e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.735608100890094e-10</v>
+        <v>7.432952973167639e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.385626135787759e-10</v>
+        <v>5.165925667047988e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.425623697464716e-10</v>
+        <v>5.191594480782586e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.569582495164119e-10</v>
+        <v>7.432544708876181e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.175325809342065e-10</v>
+        <v>5.018084194685116e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.257313357520919e-10</v>
+        <v>5.066097169633325e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.70246984351866e-10</v>
+        <v>5.473654492190341e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.467924971586561e-10</v>
+        <v>5.344697521139829e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.596674684982337e-10</v>
+        <v>5.383384120833161e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.772449750425964e-10</v>
+        <v>5.673022918720351e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.357512813504933e-10</v>
+        <v>5.217438184207904e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.831367158689346e-10</v>
+        <v>5.562524322027089e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.348343997602429e-10</v>
+        <v>5.209138482178289e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.478058037747897e-10</v>
+        <v>5.300694553632404e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.705935183285836e-10</v>
+        <v>5.46939128968901e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.819823472574599e-10</v>
+        <v>5.545612526046727e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>6.037320565684943e-10</v>
+        <v>5.698613960281728e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>6.208161315453575e-10</v>
+        <v>5.79611955420609e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.440902070706591e-10</v>
+        <v>5.278910999473849e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.687128199263345e-10</v>
+        <v>7.528291561688782e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.663439933506865e-10</v>
+        <v>5.444589098516653e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.37387634953444e-10</v>
+        <v>5.231886196331888e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.365269973609079e-10</v>
+        <v>5.222452618784915e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.67005628589628e-10</v>
+        <v>5.447209388739302e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.397866315646679e-10</v>
+        <v>5.246542787917992e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>8.254701347804829e-10</v>
+        <v>7.90815979555325e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.402122321236699e-10</v>
+        <v>5.263818363161377e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.216967481587387e-10</v>
+        <v>7.959715373798007e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.635477733256723e-10</v>
+        <v>5.411917630005663e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.61663300225775e-10</v>
+        <v>5.403346574825873e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.124110986178764e-10</v>
+        <v>7.938863894839352e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.398983931555798e-10</v>
+        <v>5.251184636336798e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.750256740682533e-10</v>
+        <v>6.158583265493827e-10</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.573576906546025e-10</v>
+        <v>5.366193579625616e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.404158749358035e-10</v>
+        <v>5.283891019022863e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.644300439228927e-10</v>
+        <v>5.401487961608359e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.765386997860444e-10</v>
+        <v>5.657471922497525e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.343927959461424e-10</v>
+        <v>5.193241784439596e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.740391874524746e-10</v>
+        <v>5.485266116489678e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.262623427556874e-10</v>
+        <v>5.135118484665968e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.484292452688259e-10</v>
+        <v>5.289608621354111e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.632760917870006e-10</v>
+        <v>5.403507715271057e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.438498046509165e-10</v>
+        <v>5.264469568306497e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.901532663777982e-10</v>
+        <v>5.589549028063183e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>6.061207841226199e-10</v>
+        <v>5.679548337780108e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.273265881614171e-10</v>
+        <v>5.147498890456987e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.490443358638583e-10</v>
+        <v>7.349236880923718e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.595944599922363e-10</v>
+        <v>5.383298074178637e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.380997256246173e-10</v>
+        <v>5.222629702574738e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.263316959403015e-10</v>
+        <v>5.137248831986603e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.604815652079442e-10</v>
+        <v>5.387391163268995e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.303020240907488e-10</v>
+        <v>5.165917052819749e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.935903429315899e-10</v>
+        <v>7.644483401243191e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.39661462669075e-10</v>
+        <v>5.246435916217817e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>8.07889272143972e-10</v>
+        <v>7.818732122053314e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.722135691312022e-10</v>
+        <v>5.45714445087119e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.827024753557249e-10</v>
+        <v>5.535477618538945e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.03995389924486e-10</v>
+        <v>7.858767591556906e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.343307219342608e-10</v>
+        <v>5.197403560491681e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.600561138518894e-10</v>
+        <v>6.040067835876967e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.488778048180355e-10</v>
+        <v>5.29990591122064e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.350162309722011e-10</v>
+        <v>5.236710539255612e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.522485582653236e-10</v>
+        <v>5.311619000948535e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.69448503720198e-10</v>
+        <v>5.602205668305218e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.349864609857751e-10</v>
+        <v>5.189169916462045e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.653012047289357e-10</v>
+        <v>5.417985918702443e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.248628544349729e-10</v>
+        <v>5.116690486812876e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.415034224618179e-10</v>
+        <v>5.234169361071469e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.574363030301807e-10</v>
+        <v>5.355879496595645e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.398940771088866e-10</v>
+        <v>5.228418754288704e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.762872074833775e-10</v>
+        <v>5.488658159266905e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.909655155890765e-10</v>
+        <v>5.57338584180557e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.190227345152897e-10</v>
+        <v>5.081407983414564e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.381522696236779e-10</v>
+        <v>7.248162296686279e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.524898015352898e-10</v>
+        <v>5.327013099038451e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.334551402198507e-10</v>
+        <v>5.182912912893171e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.310407407901627e-10</v>
+        <v>5.160530259275892e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.560014653028816e-10</v>
+        <v>5.348685736700346e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.316887120081473e-10</v>
+        <v>5.166747040133936e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.878314612500523e-10</v>
+        <v>7.584628837514691e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4790115209446e-10</v>
+        <v>5.298904624154921e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.990568186588588e-10</v>
+        <v>7.730194189005237e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.757061139779012e-10</v>
+        <v>5.476733320204656e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.148417817530925e-10</v>
+        <v>5.747952903107761e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.980217947966213e-10</v>
+        <v>7.805710752753341e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.331973843579748e-10</v>
+        <v>5.180993299263284e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.470877854419308e-10</v>
+        <v>5.947446901667273e-10</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.093632395652031e-10</v>
+        <v>4.96169033657873e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.120812580400758e-10</v>
+        <v>5.014425379772185e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.297238840296715e-10</v>
+        <v>5.094237535153102e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4856998932383e-10</v>
+        <v>5.409179190471014e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.073450094520546e-10</v>
+        <v>4.938562431129926e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.160336103924358e-10</v>
+        <v>5.010197654922389e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1635874298016e-10</v>
+        <v>4.997334042654188e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.11927820746609e-10</v>
+        <v>4.970306702965003e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.163039321883465e-10</v>
+        <v>5.009893557642515e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.344492720474925e-10</v>
+        <v>5.13369343583998e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.288537632224084e-10</v>
+        <v>5.100637168082008e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.350180357056509e-10</v>
+        <v>5.130345874531614e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.227235071277953e-10</v>
+        <v>5.050077895624218e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>6.93307005362935e-10</v>
+        <v>6.817498282133865e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.123320966571172e-10</v>
+        <v>4.982959929271043e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.133026728264056e-10</v>
+        <v>4.984166350726616e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.107758648654386e-10</v>
+        <v>4.961124893952174e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.148171071863553e-10</v>
+        <v>5.003558636524296e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.08002700587914e-10</v>
+        <v>4.944330008832005e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.125775483919303e-10</v>
+        <v>6.932274908645949e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.053563945231749e-10</v>
+        <v>4.937522394368686e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.398557397098124e-10</v>
+        <v>7.190051514899761e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.15263613774653e-10</v>
+        <v>4.99541109998931e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.085848087800462e-10</v>
+        <v>4.951100740522613e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.572261723399335e-10</v>
+        <v>7.428828783811796e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.074496017915032e-10</v>
+        <v>4.943367693707399e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.417901240510756e-10</v>
+        <v>5.172490230950466e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.051966685383972e-10</v>
+        <v>4.908667983564194e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.093803447662219e-10</v>
+        <v>4.969335897930259e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.127810832552163e-10</v>
+        <v>4.954863073928647e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.396078149991369e-10</v>
+        <v>5.328757253097423e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.066004151070255e-10</v>
+        <v>4.909795327760799e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>4.992574787428488e-10</v>
+        <v>4.866426722436639e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.051282298255554e-10</v>
+        <v>4.895540145057964e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.086609102826013e-10</v>
+        <v>4.923616481011697e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.026765924355035e-10</v>
+        <v>4.88948511190269e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.053648530535251e-10</v>
+        <v>4.904425462111356e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.065752371637171e-10</v>
+        <v>4.919639348741529e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.035289105705857e-10</v>
+        <v>4.885599558877259e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.008920727007489e-10</v>
+        <v>4.873752273501073e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>6.732438539972874e-10</v>
+        <v>6.6150489449726e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.933492737341204e-10</v>
+        <v>4.824541556613462e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.986799068196498e-10</v>
+        <v>4.8597436731476e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.087451675643273e-10</v>
+        <v>4.922638099551172e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.037165411126471e-10</v>
+        <v>4.900442281752682e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>4.99553443224657e-10</v>
+        <v>4.861440318980383e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>6.678783301542539e-10</v>
+        <v>6.552359403588236e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>4.997940062060288e-10</v>
+        <v>4.875384498394675e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.171248598406338e-10</v>
+        <v>6.964543730185432e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.239757198333111e-10</v>
+        <v>5.035636735136112e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.122943322884958e-10</v>
+        <v>4.952548111709638e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.41870002042223e-10</v>
+        <v>7.280716752741242e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.043898439268349e-10</v>
+        <v>4.89772864699237e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.077634283087732e-10</v>
+        <v>4.915620022022972e-10</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.111577609599531e-10</v>
+        <v>4.951397619472675e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.113383881313174e-10</v>
+        <v>4.982578412454726e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.138545626642073e-10</v>
+        <v>4.961193496328636e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.458960347749483e-10</v>
+        <v>5.373967307898074e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.037575111539619e-10</v>
+        <v>4.888672140357831e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.072077518704999e-10</v>
+        <v>4.923528608926049e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.034073914271269e-10</v>
+        <v>4.883627727011159e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.083043916560464e-10</v>
+        <v>4.920431968316873e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.063697915813384e-10</v>
+        <v>4.914472321603625e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.035737997074478e-10</v>
+        <v>4.890490156356729e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.042821886515214e-10</v>
+        <v>4.900952520336816e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.010814081248578e-10</v>
+        <v>4.866087545269026e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.004662606741089e-10</v>
+        <v>4.869697521279787e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>6.710389000686881e-10</v>
+        <v>6.592673611905385e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.948595940004563e-10</v>
+        <v>4.835228072240099e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.982039455511641e-10</v>
+        <v>4.854536344985789e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.128394838824181e-10</v>
+        <v>4.949998789400379e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.02596213567229e-10</v>
+        <v>4.890147134494344e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.000956427611724e-10</v>
+        <v>4.864485324722441e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>6.685138395260581e-10</v>
+        <v>6.55228120227577e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.023019135030934e-10</v>
+        <v>4.892869216810821e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.5987251857338e-10</v>
+        <v>7.260892645322932e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.289015393601331e-10</v>
+        <v>5.071400918915304e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.167932122834894e-10</v>
+        <v>4.982952908598764e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.391625468000674e-10</v>
+        <v>7.25822317752337e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.053125100123286e-10</v>
+        <v>4.903730931478138e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.13754150817941e-10</v>
+        <v>4.954492991211154e-10</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.364010601222959e-10</v>
+        <v>5.186742107603544e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.268247603060577e-10</v>
+        <v>5.152237485335389e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.36611731008302e-10</v>
+        <v>5.175336044092604e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.615298020146128e-10</v>
+        <v>5.526627436387326e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.224052161918774e-10</v>
+        <v>5.076543548045797e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.632323087099449e-10</v>
+        <v>5.379588514370258e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.198451115671497e-10</v>
+        <v>5.056464087617105e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.362773620862943e-10</v>
+        <v>5.172286367158649e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.49519870770763e-10</v>
+        <v>5.277360849821208e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.565385974736459e-10</v>
+        <v>5.322880780094024e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.793484663553513e-10</v>
+        <v>5.485420449237319e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>6.008666902944924e-10</v>
+        <v>5.624898368694052e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.429647810026148e-10</v>
+        <v>5.222586614194604e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>7.253210081966462e-10</v>
+        <v>7.112187507149242e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.417112091148624e-10</v>
+        <v>5.223698789334615e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.242101153707595e-10</v>
+        <v>5.092802610601702e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.235864036051657e-10</v>
+        <v>5.083743961709372e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.363237690143417e-10</v>
+        <v>5.187128793812195e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.277154591499703e-10</v>
+        <v>5.114015724708751e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.691697348195557e-10</v>
+        <v>7.397424338139145e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.204850091351091e-10</v>
+        <v>5.077354510897515e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.631489887683742e-10</v>
+        <v>7.425200406954242e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.53468610116086e-10</v>
+        <v>5.293367793853834e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.413244114694798e-10</v>
+        <v>5.213602123034655e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.827683710804787e-10</v>
+        <v>7.65583101552146e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.207130590395798e-10</v>
+        <v>5.069403326516486e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.378638079700173e-10</v>
+        <v>5.856644794637054e-10</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.122831240389319e-10</v>
+        <v>4.995943356771656e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>5.254322136704415e-10</v>
+        <v>5.12394264926325e-10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.21987999105253e-10</v>
+        <v>5.056290235624298e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.52725421400386e-10</v>
+        <v>5.450412033970702e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.162450049170221e-10</v>
+        <v>5.015460275857553e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.44017613294259e-10</v>
+        <v>5.226879453564798e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>5.113995248756411e-10</v>
+        <v>4.978927223826696e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>5.206812502393405e-10</v>
+        <v>5.045421025411655e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.267512469940943e-10</v>
+        <v>5.098409081031602e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>5.261872499159204e-10</v>
+        <v>5.090092787762466e-10</v>
       </c>
       <c r="L3" t="n">
-        <v>5.357875009500606e-10</v>
+        <v>5.162716030863058e-10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.262487312212253e-10</v>
+        <v>5.082297558845865e-10</v>
       </c>
       <c r="N3" t="n">
-        <v>5.10430512387229e-10</v>
+        <v>4.977597633695676e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>6.996148740906904e-10</v>
+        <v>6.88621731405846e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>5.218134617450204e-10</v>
+        <v>5.064921693366653e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.201240253545419e-10</v>
+        <v>5.048503321029298e-10</v>
       </c>
       <c r="R3" t="n">
-        <v>5.203073908978098e-10</v>
+        <v>5.041535677392098e-10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.180117279588232e-10</v>
+        <v>5.037758994371341e-10</v>
       </c>
       <c r="T3" t="n">
-        <v>5.128163354970636e-10</v>
+        <v>4.992087906346128e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>7.061115628557931e-10</v>
+        <v>6.912429697367714e-10</v>
       </c>
       <c r="V3" t="n">
-        <v>5.120793255040887e-10</v>
+        <v>4.999398710929596e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>7.481548487208101e-10</v>
+        <v>7.275752900065945e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.402340745255151e-10</v>
+        <v>5.1852044270727e-10</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.56396444835442e-10</v>
+        <v>5.300186301398075e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.598868269256682e-10</v>
+        <v>7.465144549442124e-10</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.14872209114852e-10</v>
+        <v>5.00965777885296e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.89912156449626e-10</v>
+        <v>5.51554471861692e-10</v>
       </c>
     </row>
     <row r="4">
